--- a/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A496"/>
+  <dimension ref="A1:A802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,3465 +438,5607 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/we-arent-enemies-maharashtra-cm-devendra-fadnavis-thanks-opponents-uddhav-thackeray-sharad-pawar-heres-why/articleshow/122840085.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cm-devendra-fadnavis-to-inaugurate-dabbawallahs-museum-in-bandra-today/articleshow/123302681.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/sharad-pawars-birthday-praise-for-devendra-fadnavis-maharashtra-nayak-coffee-book-one-cannot-deny-101753198260918.html</t>
+          <t>https://www.msn.com/en-in/autos/photos/sharad-pawar-is-hallucinating-devendra-fadnavis-slams-ncp-sp-chief-over-financial-aid-claim/ar-AA1tnzDv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/we-are-ideological-opponents-not-enemies-d-fadnavis-on-uddhav-thackeray-sharad-pawar-8926863</t>
+          <t>https://www.ndtv.com/india-news/order-in-place-since-1988-devendra-fadnavis-on-row-over-independence-day-meat-ban-9078331</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/online-gaming-ban-maharashtra-cm-devendra-fadnavis-mulls-shutdown-of-online-gaming-due-to-rise-in-suicide-scams-and-crimes/ar-AA1J3nYD</t>
+          <t>https://www.ap7am.com/en/106826/ganeshotsav-mandals-should-create-awareness-about-operation-sindoor-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/devendra-fadnavis-55th-birthday-responds-to-praise-from-sharad-pawar-uddhav-thackeray-says-we-are-not-enemies-2025-07-22-1000099</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-devendra-fadnavis-says-birthday-wishes-from-opposition-leaders-shouldnt-be-politicised-23586123</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-23589010</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/matter-of-happiness-fadnavis-says-nothing-political-in-rajs-matoshree-visit-extends-birthday-wishes-to-uddhav/articleshow/122935685.cms</t>
+          <t>https://www.msn.com/en-in/money/topstories/business-as-usual-won-t-work-devendra-fadnavis-on-rising-property-prices-in-mumbai/ar-AA1KELqU?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/manhandling-will-not-be-tolerated-d-fadnavis-amid-language-row-in-maharashtra-8945568</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/fadnavis-turns-to-shah-nadda-to-discuss-errant-mahayuti-leaders-101753469853217.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/ports-shipping/devendra-fadnavis-and-singapores-yong-collaborate-on-indias-largest-container-port/123274805</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/amruta-fadnavis-leads-say-no-to-drugs-rally-by-ekata-manch/articleshow/122828462.cms</t>
+          <t>http://www.msn.com/en-in/weather/climate-change/gives-me-sleepless-nights-climate-change-a-major-economic-risk-for-maharashtra-says-cm-devendra-fadnavis/ar-AA1CxKxh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/sharad-pawars-ncp-urges-devendra-fadnavis-to-sack-minister-manikrao-kokate-over-rummy-video-row-8952741</t>
+          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/time-ripe-for-chief-minister-devendra-fadnavis-to-reshuffle-cabinet-team-uddhav-8922026</t>
+          <t>http://www.msn.com/en-in/news/India/devendra-fadnavis-infrastructure-work-shouldn-t-drag-on-for-years/ar-AA1JUyyJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/manikrao-kokate-devendra-fadnavis-decision-on-rummy-playing-minister-likely-on-monday-says-ajit-pawar-8943152</t>
+          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/devendra-fadnavis-the-relentless-rise-of-maharashtras-political-strategist-564268</t>
+          <t>https://www.msn.com/en-in/news/other/maharashtra-cm-devendra-fadnavis-asks-dhananjay-munde-to-resign-as-minister-report/ar-AA1AbOok?ocid=BingNewsVerp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-sends-a-message-of-progress-with-sustainability-in-once-naxal-dominated-gadchiroli-3643871</t>
+          <t>https://www.ndtv.com/video/devendra-fadnavis-rejects-election-rigging-claims-calls-opposition-allegations-fabricated-978678</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/sharad-pawar-praises-maharashtra-chief-minister-devendra-fadnavis-on-his-birthday-wonders-how-does-he-never-get-tired-2025-07-22-1000030</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/more-maharashtra-civic-bodies-order-closure-of-slaughterhouses-on-aug-15-chief-minister-fadnavis-says-govt-played-no-role/articleshow/123289673.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/a-file-war-between-devendra-fadnavis-eknath-shinde-101753312674378.html</t>
+          <t>https://www.msn.com/en-in/autos/photos/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra/ar-AA1KmsuB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-pushes-for-key-projects-global-funding-in-high-level-meetings-with-union-ministers-in-delhi-23586492</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya/ar-AA1Kz9Qg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sharad-pawar-uddhav-thackeray-heap-praises-on-fadnavis-on-latters-birthday-3642663</t>
+          <t>http://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cm-fadnavis-unhappy-with-shiv-sena-minister-shirsat-and-junior-minister-from-bjp-misal-engaging-in-war-of-letters/articleshow/122938484.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/did-you-use-vote-riggers-fadnavis-asks-sharad-pawar/articleshow/123224044.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/media-others-news/cm-fadnavis-birthday-firebrand-leader-with-a-vision-for-development-governance-trust-145598.html</t>
+          <t>http://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-vows-to-bring-elephant-home-mahadevi/ar-AA1JYQ3u?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/22-07-2025-governor-releases-coffee-table-book-on-cm-devendra-fadnavis/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/videoshow/123305295.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/delhi/jnu-to-teach-shivajis-war-tactics-marathi-fadnavis-hails-mother-tongue-on-campus/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-cm-fadnavis-urges-ganesh-mandals-to-promote-operation-sindoor-and-swadeshi-goods-23589371</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/muslim-bjp-leaders-celebrate-maharashtra-cm-devendra-fadnaviss-birthday-with-prayers-at-sufi-shrine-distribute-umbrellas-among-needy/articleshow/122896019.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/redeveloping-dharavi-is-like-building-a-new-city-maharashtra-cm-devendra-fadnavis-23589541</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/governors-comment-on-language-hatred-harming-maha-is-correct-says-cm-fadnavis/articleshow/122866081.cms</t>
+          <t>https://www.msn.com/en-in/news/India/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/kokate-refers-to-govt-as-beggar-triggers-new-row-inappropriate-says-cm-as-oppn-pushes-for-ouster/articleshow/122843986.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis/articleshow/123261137.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/birthday-visits-should-not-be-viewed-from-political-lens-devendra-fadnavis-on-thackeray-brothers-meetup-23586830</t>
+          <t>https://www.ndtv.com/video/maharashtra-cm-devendra-fadnavis-participates-in-flag-hoisting-ceremony-on-i-day-980963</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-asks-sena-bjp-ministers-to-refrain-from-turf-war-3650989</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-takes-major-leap-in-urban-infrastructure-as-cm-devendra-fadnavis-inaugurates-four-landmark-mmrda-projects-23589505</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-cm-devendra-fadnavis-accuses-opposition-of-spreading-misinformation-to-avoid-development-debate-23586890</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/what-happened-during-maharashtra-assembly-polls-fadnavis-on-raj-s-matoshree-visit-2025-07-27-1000809</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/we-are-ideological-opponents-not-enemies-fadnavis-on-thackeray-pawar-3642482</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmcs-pot-of-sins-broken-says-maharashtra-cm-devendra-fadnavis-23589784</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/pm-modi-extends-birthday-greetings-to-maha-cm-fadnavis-deputy-cm-ajit-pawar/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya-says-no-one-can-stop-indias-development-23589603</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/wrong-to-give-political-colour-to-birthday-wishes-of-pawar-thackeray-fadnavis-101753301232781.html</t>
+          <t>https://www.business-standard.com/politics/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-125081100764_1.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cm-fadnavis-brands-agri-minister-kokates-govt-is-beggar-comment-inappropriate/articleshow/122844592.cms</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/when-uddhav-met-fadnavis-closed-door-meet-that-set-tongues-wagging-101753040239099.html</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.en.etemaaddaily.com/world/national/maharashtra-cm-devendra-fadnavis-inaugurates-lays-foundation-stone-of-various-development-projects-in-gadchiroli:179088</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-to-inaugurate-dabbawallahs-museum-in-bandra-today/ar-AA1KvJtc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/fadnavis-cracks-whip-on-shinde-maharashtra-cm-tightens-grip-on-urban-development-amid-rift-buzz-2025-07-23-1000209</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-appeals-to-aviation-ministry-to-shift-radars-in-mumbai-to-allow-redevelopment/ar-AA1IrbnT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/fadnavis-inaugurates-marathi-centre-strategic-security-centre-at-jnu-101753384374494.html</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-prominent-in-indian-s-unstoppable-growth-story-cm-fadnavis-125081500462_1.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/language-is-a-subject-of-dialogue-not-dispute-fadnavis-on-marathi-hindi-row-in-maharashtra-2025-07-24-1000413</t>
+          <t>https://www.business-standard.com/india-news/mmr-region-can-become-1-5-trillion-growth-hub-says-maharashtra-cm-125081500149_1.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/marathi-language-row-language-should-not-divide-us-says-maharashtra-cm-fadnavis-at-jnu-event-23586325</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes-101755198744381.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/content/press-releases-ani/maharashtra-chief-minister-devendra-fadnavis-inaugurates-tsl-foundation-s-bright-bus-initiative-a-digital-literacy-initiative-supported-by-crocs-india-125072300553_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-broke-handi-of-corruption-mahayuti-sounds-poll-bugle-101755369969997.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/crypto-christians-misusing-caste-benefits-to-face-action-cm-fadnavis/ar-AA1IOr0N?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-opens-key-projects-on-independence-day-by-maharashtra-cm-devendra-fadnavis-to-cut-traffic-travel-time-and-give-scenic-commutes-heres-how-article-152469772</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/delhi-news/fadnavis-sets-stone-for-marathi-centre-at-jnu-in-delhi-101753381313526.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/civic-bodies-are-only-following-the-meat-ban-imposed-by-congress-in-1988-cm-101755112861436.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/cm-fadnavis-birthday-celebrated-with-statewide-social-initiatives-and-public-participation/articleshow/122844566.cms</t>
+          <t>https://www.news18.com/videos/india/rahul-gandhi-has-no-evidence-of-vote-chori-he-is-living-in-an-illusion-devendra-fadnavis-9503697.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/urban-naxals-using-foreign-funds-to-derail-development-in-gadchiroli-cm-fadnavis-3642104</t>
+          <t>https://www.hindustantimes.com/real-estate/third-and-fourth-mumbai-to-power-1-5-trillion-mmr-economy-city-can-surpass-dubai-in-10-years-devendra-fadnavis-101755244116021.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/insistence-on-marathi-natural-but-also-respect-indian-languages-fadnavis-101753371102034.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/11/most-financial-fraud-platforms-run-by-foreign-operators-cm-fadnavis-.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/train-blasts-verdict-shocking-will-move-sc-says-fadnavis/articleshow/122823571.cms</t>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://muslimmirror.com/fadnavis-pledges-to-challenge-acquittal-of-12-muslim-men-in-7-11-mumbai-blasts-case-in-apex-court/</t>
+          <t>https://www.ptinews.com/story/business/we-missed-the-bus-earlier,-no-compromise-on-mumbai's-development-now:-fadnavis/2823252</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/maharashtra-govt-is-beggar-minister-manikrao-kokate-adds-fuel-to-fire-after-rummy-video-row-fadnavis-reacts-11753185675908.html</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-prominent-player-in-india%E2%80%99s-unstoppable-growth-story:-fadnavis/2824090/0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/government-is-beggar-maharashtra-minister-manikrao-kokate-sparks-row-with-fresh-remark-cm-fadnavis-terms-it-inappropriate/articleshow/122837575.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sea-stroll-anytime-5-25-km-mumbai-coastal-road-promenade-opens-to-public-from-today-23589539</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/violence-in-language-row-unacceptable-says-fadnavis</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-at-mantralaya-in-mumbai-106920</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/verdict-shocking-will-appeal-says-cm-oppn-questions-govt/articleshow/122821224.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rahul-gandhi-acting-on-diktats-of-urban-naxals-cm-fadnavis/articleshow/122843156.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/activists-politicians-question-parvati-janata-vasahat-tdr-approval-101755033157676.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/fadnavis-meets-amit-shah-in-delhi-maharashtra-cabinet-reshuffle-likely-soon-2025-07-25-1000553</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/articleshow/123309898.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/shivajis-legacy-transcends-time-geography-cm-fadnavis-3642035</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/aap-ki-adalat-i-told-rekha-gupta-and-fadnavis-one-day-you-will-become-cms-says-smriti-irani-2025-07-26-1000710</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/fadnavis-dismisses-political-angle-to-raj-uddhav-meet/articleshow/122939414.cms</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-to-launch-state-run-apps-for-rickshaws-taxis-and-e-bikes-check-details-23586889</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-crime-news/article/mumbai-7-11-train-blasts-maharashtra-government-to-challenge-acquittal-of-accused-in-supreme-court-23585793</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-pushes-for-key-projects-global-funding-in-high-level-meetings-with-union-ministers-in-delhi-23586392</t>
+          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/2006-mumbai-train-blasts-case-cm-fadnavis-calls-bombay-high-court-verdict-acquitting-all-12-very-shocking-vows-to-challenge-in-supreme-court/articleshow/122818718.cms</t>
+          <t>https://www.ptinews.com/editor-detail/As-chawl-residents-move-into-modern-homes--Fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/minister-kokate-must-go-why-is-cm-fadnavis-backing-him-asks-congress-sapkal-3642406</t>
+          <t>https://www.aninews.in/news/business/ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra20250813190131</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/pm-modi-extends-birthday-wishes-to-ajit-pawar-devendra-fadnavis-23585888</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fadnavis-pushes-for-maharashtra-projects/30900020250725</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ganeshotsav-festival-2025-fadnavis-appeals-for-themes-on-operation-sindoor-3679230</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Insistence-on-Marathi-natural--but-also-respect-other-Indian-languages--Fadnavis/2757885</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbais-dharavi-redevelopment-project-use-dharavi-land-50-50-for-rehabilitation-units-and-for-sale-buildings-directs-maharashtra-chief-minister-fadnavis/articleshow/123222610.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://solarquarter.com/2025/07/28/maharashtra-explores-solar-integration-in-textile-sector-fadnavis-calls-for-joint-committee/</t>
+          <t>https://www.hindustantimes.com/india-news/eknath-shinde-won-political-lottery-maharashtra-bjp-mla-ganesh-naik-mahayuti-101755432617411.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/bihar-sir-maharashtra-cm-devendra-fadnavis-backs-electoral-roll-revision-dismisses-oppositions-false-narratives-23586929</t>
+          <t>https://www.ptinews.com/story/business/-third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation/2834267</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/in-delhi-fadnavis-pitches-10000-crore-fertiliser-plant-for-vidarbha/articleshow/122912516.cms</t>
+          <t>https://globalprimenews.com/2025/08/14/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-and-union-minister-gajendra-singh-shekhawat/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-issues-social-media-guidelines-for-officials-warns-of-disciplinary-action-if-violated-check-full-list-of-dos-and-donts-2025-07-28-1000963</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-maharashtra-cm-devendra-fadnavis-inaugurates-flats-under-worlis-bdd-chawl-redevelopment-hands-over-keys-23589461</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://www.news18.com/videos/india/devendra-fadnavis-at-cnn-news18-townhall-on-student-mental-health-tricolour-true-freedom-9503816.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/to-make-city-slum-free-all-slums-to-be-surveyed-by-yearend-101753470386286.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-coastal-road-to-remain-open-24-hours-from-aug-15-cm-fadnavis-warns-against-turning-the-stretch-into-a-racetrack/articleshow/123306484.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/will-challenge-it-sc-fadnavis-shocked-over-hc-decision-on-mumbai-blasts-125072101419_1.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/dahi-handi-festivities-kick-starts-maharasthra-local-body-poll-campaign-3683995</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/23/lmel-transforming-gadchiroli-into-a-steel-hub-cm-fadnavis/</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ours-is-a-battle-of-ideas-not-personal-enmity-says-bjp-mla-ram-kadam-on-uddhavs-praise-for-maharashtra-cm20250723110941</t>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/they-dont-have-courage-to-debate-maharashtra-cm-lashes-out-at-opposition-over-op-sindoor-discussion20250728201615</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/28/divya-deshmukh-crowned-world-champion-pm-modi-cm-fadnavis-gadkari-praise-win/</t>
+          <t>https://www.newsband.in/article_detail/cmfadnavisinaugurates-first-phase-of-worli-bdd-chawl-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-meets-union-ministers-in-delhi-seeks-support-for-key-infrastructure-projects20250725210814</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/nagpur-to-get-rs-25567-crore-comprehensive-mobility-plan-for-infrastructure-development-3651482</t>
+          <t>https://money.rediff.com/news/market/mumbai-development-fadnavis-inaugurates-projects/32017320250814</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/sports/Fadnavis-congratulates-Nagpur-teen-Divya-for-winning-top-chess-title;-kin-say-hard-work-paid-off=/2770195</t>
+          <t>https://www.ptinews.com/story/national/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/cm-fadnavis-directs-formation-of-committee-to-explore-use-of-solar-power-in-textiles-sector-991294</t>
+          <t>https://www.ptinews.com/editor-detail/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/mumbai-local-trains-to-soon-get-ac-coaches-no-changes-in-fare-says-cm-devendra-fadnavis-19640493.htm</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-cm-devendra-fadnavis-comments-on-the-kabutar-khana-issue-cnn-news18-townhall-n18s-9503954.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/2006-mumbai-bomb-blasts-maharashtra-govt-moves-sc-against-hc-verdict-acquitting-12-accused-fadnavis-called-order-shocking/articleshow/122828555.cms</t>
+          <t>https://www.ptinews.com/detail/national/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/amid-speculation-of-mundes-return-as-minister-jarange-slams-cm-fadnavis-ajit-pawar/2703339/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/from-160-sq-ft-to-sky-high-towers-fadnavis-delivers-bdd-chawl-homes-years-after-launching-project-3680811</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/sena-editorial-claims-uddhav-government-fell-after-fadnavis-honey-trapped-mlas-1503461114.html</t>
+          <t>https://www.news18.com/short-videos/trending/bmc-in-focus-ballots-on-the-horizon-hear-it-straight-from-cm-of-maharashtra-devendra-fadnavis-9503385.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fadnavis-chouhan-meet-boosting-agriculture-rural-development/30839020250725</t>
+          <t>https://www.aninews.in/news/business/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli20250814181439</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/gadkari-cm-fadnavis-applaud-launch-of-nagpurs-new-diagnostic-centre-equipped-with-indigenous-medical-technology/</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-chief-minster-devendra-fadnavis-attacks-rahul-gandhi-on-alleged-vote-chori-ruckus-9503712.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/2006-mumbai-train-blasts-case-bombay-high-court-acquits-all-12-accused-cm-fadnavis-says-will-move-supreme-court-watch-video-2025-07-21-999914</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/worlis-bdd-chawl-redevelopment-556-people-to-get-key-from-cm-fadnavis-on-august-14-says-mhada-23589353</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/will-challenge-in-supreme-court-fadnavis-on-bombay-hcs-acquittal-of-2006-mumbai-train-blasts-accused-101753111193018.html</t>
+          <t>https://www.news18.com/short-videos/trending/aaditya-thackeray-greets-maharashtra-cm-devendra-fadnavis-warmly-at-cnn-news18-townhall-n18s-9503626.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-most-helpless-CM-in-Maharashtra-s-history--Congress-leader-Sapkal/2753330</t>
+          <t>https://www.aninews.in/news/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/mira-bhayandar-news-cm-fadnavisbirthdaymarkedas-seva-diwas-inmira-bhayandar</t>
+          <t>https://www.msn.com/en-in/news/India/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year/ar-AA1KtMtq</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/news/west/politics-marathi-fadnavis/3525216.html</t>
+          <t>https://www.news18.com/short-videos/trending/like-munnabhai-mbbs-rahul-gandhi-is-living-in-an-illusion-maharashtra-cm-devendra-fadnavis-9504355.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-cm-fadnavis-slams-bombay-hc-verdict-on-2006-blasts-vows-supreme-court-appeal-2934940.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/promote-operation-sindoor-swadeshi-at-ganesh-pandals-maharashtra-cm-23589390</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/2006-mumbai-train-blasts-fadnavis-govt-approaches-supreme-court-over-acquittal-of-12-accused-matter-to-be-heard-on-july-24-485684-2025-07-22</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/nagpurs-mobility-plan-to-be-executed-in-phases-says-cm-fadnavis/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mahayuti-hands-over-keys-to-redeveloped-worli-bdd-chawl-flats-23589547</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/working-on-plan-to-make-maharashtras-health-care-system-best-in-country-in-4-years-cm-fadnavis-23586721</t>
+          <t>https://www.news18.com/short-videos/trending/marathi-is-compulsory-ye-maharashtra-ki-ghajini-hain-devendra-fadnavis-attacks-ubt-govt-on-nep-9503705.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/sir-of-electoral-rolls-will-protect-rights-of-genuine-voters-fadnavis/2705297/</t>
+          <t>https://www.ptinews.com/editor-detail/BJP-may-have--panna-pramukhs--but-we-have-workers-at-the-grassroots-level--Raj-Thackeray/2823246</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/07/22/remove-manikrao-kolkate-immediately-maharashtra-congress-president-attacks-agricultural-minister-s-actions-in-assembly.html</t>
+          <t>https://www.constructionweekonline.in/projects-tenders/bdd-chawl-development</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://uniindia.com/photoes/627411.html</t>
+          <t>https://www.news18.com/short-videos/trending/big-political-voices-devendra-fadnavis-aaditya-thackeray-more-all-under-one-roof-n18s-9503158.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.newsmobile.in/nation/maharashtra-cm-fadnavis-breaks-silence-on-7-11-blasts-acquittal-heres-what-he-said/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278471295/it-appears-that-a-crime-has-taken-place-cm-fadnavis-on-pune-rave-party</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-7-killed-after-pickup-van-falls-down-slope-cm-fadnavis-announces-financial-assistance-of-rs-4-lakh20250811192235</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/pm-modi-extends-birthday-wishes-to-ajit-pawar-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/news/India/savitribai-phule-pune-university-withdraws-voice-of-devendra-competition-notice-after-nsui-objection/ar-AA1Kqjjv</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/devendra-fadnavis-most-helpless-cm-congress-harshwardhan-sapkal-1790021</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/30-camps-2321-units-shatrughan-kates-call-for-blood-donation-on-cm-fadnavis-birthday-gets-massive-response/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom30-mh-rains-mumbai-ld-cm.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/business/maharashtra-to-hit-dollar-1-trillion-economy-by-2030-surpassing-singapore-cm-fadnavis-1790415</t>
+          <t>https://tennews.in/chawl-redevelopment-project-maha-cm-fadnavis-hands-over-556-flats-at-worli-in-phase-1/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/meritorious-students-felicitated-on-cm-devendra-fadnavis-birthday-by-sc-morcha-nagpur/07241843</t>
+          <t>https://tennews.in/viksit-maharashtra-making-special-contribution-in-realising-dream-of-viksit-bharat-says-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278465504/right-step-says-cm-devendra-fadnavis-after-sc-stays-bombay-hc-decision-in-2006-mumbai-train-blasts</t>
+          <t>https://www.bignewsnetwork.com/news/278510817/mmr-region-has-potential-to-become-15-trillion-dollars-says-maharashtra-cm</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/bombay-hc-verdict-very-shocking-will-challenge-it-in-supreme-court-cm-fadnavis-on-2006-mumbai-blasts-acquittal-1789528</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-meeting-with-amit-shah-fm-nirmala-sitharaman-union-minister-jp-nadda-manohar-lal-khattar-niti-aayog-in-delhi-2985489</t>
+          <t>https://www.bignewsnetwork.com/news/278515875/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-nda-vp-nomination</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/prime-minister-narendra-modi-congratulated-maharashtra-chief-minister-devendra-fadnavis-on-his-birthday/</t>
+          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-thanks-opponents-uddhav-thackeray-sharad-pawar-and-says-we-arent-enemies-know-why/articleshow/122841206.cms</t>
+          <t>https://www.latestly.com/india/news/devendra-fadnavis-led-maharashtra-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers-7055240.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-devendra-fadnavis-eknath-shinde-delhi-visit-jnu-marathi-shivaji-center-inauguration-9436491.html</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/fadnavis-meets-top-leaders-in-delhi-amid-speculation-on-uddhav-thackeray-hindi/</t>
+          <t>https://news.abplive.com/cities/maharashtra-meat-shop-ban-controversy-devendra-fadnavis-ajit-pawar-aaditya-thackeray-independence-day-2025-1794498</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/maharashtra-cm-devendra-fadnavis-in-jnu-called-marathi-language-is-oldest-language-of-country-hindi-news-dln25072407636</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-ncp-sharad-pawar-birthday-praise-for-devendra-fadnavis-what-did-cm-replied-201753206459847.html</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/on-birthday-devendra-fadnavis-launched-coffee-table-book-on-sharad-pawar-and-uddhav-thackeray-ideological-differences-2983872</t>
+          <t>https://www.latestly.com/socially/india/news/maharashtra-meat-ban-on-independence-day-2025-aaditya-thackeray-terms-august-15-meat-ban-wrong-cm-devendra-fadnavis-distances-govt-from-decision-watch-video-7058930.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-meets-amtis-shah-in-delhi-reason/articleshow/122910993.cms</t>
+          <t>https://www.latestly.com/quickly/agency-news/fadnavis-presents-shawl-to-cp-radhakrishnan-on-nda-s-vp-nomination-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-uddhav-thackeray-praised-devendra-fadnavis-called-him-unique-on-book-launch-9429650.html</t>
+          <t>https://news.abplive.com/education/jobs/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra-1794239</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-praises-maharashtra-cm-devendra-fadnavis-in-a-coffee-book-on-his-55th-birthday-for-his-tremendous-work-ann-2983736</t>
+          <t>https://www.newsx.com/india/in-operation-sindoor-under-the-leadership-of-pm-modi-maharashtra-cm-devendra-fadnavis-47149/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-will-fight-maharashtra-civic-poll-alone-only-in-mumbai-devendra-fadnavis-want-alliance-with-eknath-shinde-and-ajit-pawar/articleshow/122948175.cms</t>
+          <t>https://www.newsdrum.in/national/fadnavis-his-deputies-congratulate-governor-radhakrishnan-over-vp-nomination-9670364</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-birthday-sharad-pawar-ncp-sp-praised-maharashtra-cm-ann-2983631</t>
+          <t>https://www.devdiscourse.com/article/headlines/3542847-diwali-comes-early-new-gst-reforms-announced-on-independence-day</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-train-blasts-2006-cm-devendra-fadnavis-says-we-will-challenge-in-supreme-court-2983129</t>
+          <t>https://www.latestly.com/agency-news/business-news-maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli-7058938.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-urban-development-department-file-will-not-go-ahead-without-the-approval-of-devendra-fadnavis-setback-for-eknath-shinde-ann-2984046</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-on-maharashtra-local-body-election-and-bjp-mahayuti-alliance-ann-2986919</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-at-jnu-over-language-controversy-a-marathi-manush-cannot-be-narrow-minded-2985026</t>
+          <t>https://lawchakra.in/legal-updates/law-advocates-cm-fadnavis-high-court/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/devendra-fadnavis-warns-his-ministers-dont-involved-in-letter-war-if-you-have-a-problem-come-to-me-ntc-dskc-2297497-2025-07-27</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-is-eknath-shinde-uphappy-over-devendra-fadnavis-strong-buzz-all-is-not-well-in-mahayuti-govt-know-all/articleshow/122908257.cms</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/pune-rave-party-case-maharashtra-cm-devendra-fadnavis-reaction-2986422</t>
+          <t>https://www.jagran.com/politics/national-uddhav-thackeray-claims-and-big-attack-says-cm-devendra-fadnavis-shielding-corrupt-ministers-24009940.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-devendra-fadnavis-meeting-congress-leader-arif-naseem-khan-reaction-2984268</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-and-ajit-pawar-faction-assigned-flag-hoisting-duties-in-maharashtra-eknath-shinde-out/articleshow/123242552.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/supriya-sule-with-yugendra-pawar-wishes-happy-birthday-to-ajit-pawar-dcm-congratulate-cm-fadnavis-with-oath-ceremony-photo-know-all/articleshow/122838448.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%95-%E0%A4%87%E0%A4%A4%E0%A4%A8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%B9%E0%A5%88-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AC%E0%A4%A8-%E0%A4%AE-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9C%E0%A4%AE%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%B0/ar-AA1IVb2V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-to-meet-cm-devendra-fadnavis-manikrao-kokate-controversy-may-be-discussed-ann-2985664</t>
+          <t>https://www.abplive.com/states/maharashtra/krishna-janmashtami-2025-maharashtra-cm-devendra-fadnavis-target-congress-shiv-sena-uddhav-thackeray-sharad-pawar-bmc-2996712</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/opinion-analysis-/story/maharashtra-politics-bjp-fadnavis-thackeray-alliance-strategy-for-bmc-and-civic-polls-opnm1-dskc-2298001-2025-07-28</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/photo/fadnavis-made-big-announcement-for-dharavi-it-will-be-built-like-a-new-city-1550</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/grand-blood-donation-camp-on-chief-minister-devendra-fadnavis-birthday/</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/grand-blood-donation-camp-on-chief-minister-devendra-fadnavis-birthday-2/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/august-15-meat-ban-row-maharashtra-cm-devendra-fadnavis-said-govt-not-interested-in-regulating-people-food-choices-know-all/articleshow/123294081.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/cm-devendra-fadnavis-tightened-the-noose-on-eknath-shinde-banned-fund-allocation-now-permission-will-have-to-be-taken-sources-2025-07-23-1151265</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-has-world-s-best-technology-to-curb-cyber-crime-devendra-fadnavis-11078</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/maharashtra-cm-fadnavis-big-gift-to-gadchiroli-inaugurate-lloyds-metals-and-energy-ltd-plant-in-konsari-along-with-anti-naxal-operation/articleshow/122833648.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-handover-556-flats-in-worli-bdd-chawl-redevelopment-project-ann-2995711</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-says-matter-of-happiness-nothing-political-in-raj-matoshree-visit-extends-birthday-wishes-to-uddhav/articleshow/122937087.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cabinet-reshuffle-buzz-cm-fadnavis-likely-to-not-happy-with-few-ministers-chandrashekhar-bawankule-hints-amit-shah-delhi-visit-know-all/articleshow/122933934.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%AE%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%96-%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%9C-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%A1%E0%A4%BC/ar-AA1G9764?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-says-uddhav-sharad-not-enemies-just-political-opponents-9430659.html</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-police-recruitment-2025-devendra-fadnavis-cabinet-approves-recruitment-of-15000-post-2994374</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-civic-polls-cm-fadnavis-said-bjp-wants-to-contest-under-mahayuti-alliance-in-friendly-fight-should-not-work-against-each-other/articleshow/122959386.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/sharad-pawar-wishes-devendra-fadnavis-on-his-birthday-praised-in-book-why-does-he-never-get-tired-1344937.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-calls-uddhav-thackeray-politics-ghajini-but-why-ws-l-9506496.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/we-are-ideological-opponents-not-enemies-says-devendra-fadnavis-on-udhhav-thackeray-sharad-pawar-lclnt-dskc-2293760-2025-07-22</t>
+          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-and-aaditya-thackeray-will-on-one-stage-with-devendra-fadnavis-201755068550172.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-news-mahayuti-alliance-bjp-and-eknath-sindhe-minister-letter-war-devendra-fadnavis-meet-in-delhi-9442103.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ganeshotsav-2025-cm-devendra-fadnavis-appeals-to-ganpati-mandals-operation-sindoor-show-indigenous-tableaux/articleshow/123286430.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/devendar-fadnavis-birthday-special/07221008</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97%E0%A4%A2%E0%A4%BC%E0%A4%9A-%E0%A4%B0-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%82%E0%A4%9F-%E0%A4%B9-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%94%E0%A4%B0-%E0%A4%9F-%E0%A4%89%E0%A4%A8%E0%A4%B6-%E0%A4%AA-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A5%87%E0%A4%A1-%E0%A4%95-%E0%A4%B0-%E0%A4%A1-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%96-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B5-%E0%A4%95-%E0%A4%A8-%E0%A4%82%E0%A4%B5/ar-AA1J3wnZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/cm-devendra-fadnavis-inaugurate-kusumagaraj-marathi-language-centre-at-jnu-in-delhi-2025-07-24-1151517</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/how-was-chief-minister-devendra-fadnavis-delhi-visit-know-here-8950048</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis-2025-08-13</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/ahead-of-polls-oppn-starts-creating-false-narratives-as-it-cannot-debate-on-development-fadnavis-2025-07-28</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-in-a-protest-organised-against-mahayuti-government-accused-devendra-fadnavis-of-protecting-the-corrupt-ministers/articleshow/123248772.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/2006-mumbai-train-blast-bombay-high-court-acquitted-all-12-accused-cm-devendra-fadnavis-said-will-go-to-supreme-court-2025-07-21-1150818</t>
+          <t>https://hindi.news18.com/news/maharashtra/nagpur-why-no-action-was-taken-against-those-who-guaranteed-160-seats-devendra-fadnavis-hits-back-at-sharad-pawar-9496304.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-raj-thackeray-wished-uddhav-thackeray-birthday-at-matoshree-2986357</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cm-devendra-fadnavis-reply-on-15th-august-meat-ban-controversy-9078739</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/sharad-pawar-uddhav-praised-cm-fadnavis-bjp-leader-said-this-is-a-part-of-the-state-s-culture-2025-07-23</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-meeting-on-ganeshotsav-2025-he-also-directs-on-eid-e-milad-festival-ann-2995187</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-maharashtra-cm-fadnavis-no-tolerance-for-violence-over-marathi-language-23993448.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-municipal-body-looted-devendra-fadnavis-target-uddhav-thackeray-bmc-elections-9516480.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/something-new-in-maharashtra-now-ncp-chief-sharad-pawar-praise-cm-fadnavis-so-much-2025-07-22-1151011</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/bdd-chawl-redevelopment-scheme-cm-devendra-fadnavis-give-mhada-houses/articleshow/123310540.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-cm-fadnavis-on-bombay-hc-acquitting-all-12-people-in-relation-to-2006-mumbai-train-bombings-2025-07-21</t>
+          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-maharashtra-government-fadnavis-faces-embarrassment-due-to-controversial-ministers-23995337.html</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-government-of-maharashtra-gave-permission-for-school-buses-pratap-sarnaik-ann-2994680</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-language-row-cm-fadnavis-warns-mns-request-to-speak-marathi-is-fine-but-manhandling-unacceptable-after-cp-radhakrishnan-remark/articleshow/122903693.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-fadnavis-calls-for-promotion-of-indigenous-sports-sports-minister-kokate-inaugurates-khelo-mahakumbh/articleshow/123286194.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-maharashtra-minister-rummy-video-row-sharad-pawar-ncp-urges-devendra-fadnavis-to-sack-manikrao-kikate-23994653.html</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://thewirehindi.com/306124/gadchiroli-shrinking-maoism-paves-way-for-mining/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-meat-ban-order-cm-devendra-fadnavis-backs-decision-ajit-pawar-says-this-wrong-2995176</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-cm-approval-mandatory-for-urban-development-files-eknath-shinde-setback-hindi/</t>
+          <t>https://www.agniban.com/good-news-for-the-youth-devendra-fadnavis-cabinet-approved-recruitment-for-15-thousand-posts/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-uddhav-thackeray-devendra-fadnavis-closed-door-meeting-created-political-stir-in-eknath-shinde-in-tension-maharashtra-politics-live-updates-9423943.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/uddhav-thackeray-targets-shindes-tainted-ministers-puts-moral-pressure-on-cm-fadnavis-amid-brewing-cold-war-ntc-rpti-2308276-2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-mumbai-local-trains-to-get-acs-metro-style-facelift-no-fare-hike-says-devendra-fadnavis-9424428.html</t>
+          <t>https://www.abplive.com/states/maharashtra/abu-asim-azmi-demands-cm-devendra-fadnavis-to-take-action-in-jamner-murder-case-2995099</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-cm-fadnavis-in-gadchiroli-integrated-steel-plant-ytvd-2294837-2025-07-24</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-protest-many-places-against-cm-fadnavis-corrupt-minister-uddhav-chief-minister-protecting-everyone-2025-08-11</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-cm-fadnavis-thanked-sharad-pawar-and-uddhav-thackeray-for-their-praise-23991634.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-vegetarians-are-impotent-nonsense-talk-cm-devendra-fadnavis-reaction-on-slaughterhouse-meat-shops-9506829.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-jnu-to-install-chhatrapati-shivaji-maharaj-statue-new-delhi-city-news-devendra-fadnavis-23993609.html</t>
+          <t>https://www.abplive.com/states/maharashtra/congress-leader-balasaheb-thorat-again-expressed-fear-of-rigging-in-maharashtra-assembly-election-2993690</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/07/21/419118/bharat/maharashtra/not-to-spend-money-for-hoardings-and-banners-on-devendra-fadnavis-birthday-donate-to-the-mukhyamantri-sahayata-nidhi/</t>
+          <t>http://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/cm-devendra-fadnavis-reached-jnu-said-our-dispute-is-not-between-marathi-and-hindi/articleshow/122895636.cms</t>
+          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16?src=top-subnav</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/pune-court-issues-notice-to-amruta-fadnavis-for-filing-reply-in-cyber-defamation-case-ntc-rptc-2294813-2025-07-24</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%A6%E0%A4%B0%E0%A4%B5-%E0%A4%9C-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-ac-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%AC-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1KyN36</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cm-fadnavis-advice-to-cabinet-ministers-do-not-start-letter-war-solve-problem-by-talking-among-themselves-2025-07-27</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-govt-approves-recruitment-of-15000-police-personnel-know-cabinet-meeting-decisions/articleshow/123260370.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/7/22/cm-fadnvis-celebrate-his-birthday-with-works.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-political-changes-cabinet-reshuffle-may-soon-cm-devendra-fadnavis-in-new-delhi-ws-kl-9439811.html</t>
+          <t>https://ndtv.in/india/cm-fadnavis-told-how-dharavi-is-being-redeveloped-says-this-is-the-center-of-economic-development-9084680</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-cm-advocates-respect-for-all-indian-languages-at-jnu-event-201753376875370.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-leader-sanjay-raut-post-photo-and-demands-cbi-probe-in-maharashtra-honey-trap-case-after-cm-fadnavis-rejected-claim-know-all/articleshow/122809107.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/sclr-extension-mumbai-opening-eastern-western-expressway-highway-link-mumbai/articleshow/123308994.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bombay-high-court-decision-in-2006-mumbai-train-blast-case-is-shocking-cm-devendra-fadnavis-challenge-in-supreme-court-9426405.html</t>
+          <t>https://www.jagran.com/news/national-cm-fadnavis-advised-mumbaikars-not-to-sell-their-houses-24013649.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-local-blasts-case-maharashtra-govt-to-appeal-acquittal-of-12-accused-in-supreme-court-says-devendra-fadnavis/articleshow/122818333.cms</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/will-he-play-in-maharashtra-ukrainian-tech-cm-and-shopkeeper-are-now-friends-2294706-2025-07-23</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-slams-sharad-pawar-over-august-15-meat-sale-ban-says-its-pawar-governments-decision/articleshow/123286747.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-praises-devendra-fadnavis-stir-in-maharashtra-politics-know-inside-story-9430023.html</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/whom-did-chief-minister-devendra-fadnavis-target-regarding-bmc-125081600082_1.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/amid-rummy-video-row-minister-manikrao-kokate-calls-govt-beggar-fadnavis-says-comments-inappropriate-2025-07-22-1151073</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%95%E0%A4%88-%E0%A4%9C%E0%A4%97%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%95-%E0%A4%AC%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1Kiekp</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-local-body-election-cm-devendra-fadnavis-gave-indication-about-bjp-mahayuti-participatio-1349465.html</t>
+          <t>https://www.jagran.com/news/national-maharashtra-cyber-crime-control-cm-fadnavis-lauds-garud-drishti-initiative-24009491.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/chief-minister-devendra-fadnavis-reached-gadchiroli-on-the-occasion-of-his-birthday-inaugurated-various-works-including-the-steel-plant-located-at-konsari-1753174105310</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1JArmJ</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-fadnaviss-control-over-shindes-department-is-everything-fine-in-the-maha-yuti-ytvd-2294823-2025-07-24</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bdd-chawl-redevelopment-flats-ready-in-worli-cm-fadnavis-inaugurates-them-11129</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bjp-shiv-sena-ubt-reunion-buzz-in-maharashtra-politics-after-uddhav-and-aditya-thackeray-meeting-with-devendra-fadnavis-know-inside-story-9421137.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/nagpur-what-is-garuda-vision-of-maharashtra-police-done-patent-communal-violence-cyber-fraud-check-social-media-post-10-crore-recovery-ws-kl-9498865.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-gears-up-for-maharashtra-civic-polls-cm-fadnavis-says-mahayuti-fight-together-warns-workers-19816657</t>
+          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-saamana-claimed-about-devendra-fadnavis-government-cabinet-will-reshuffle-8-ministers-ann-2985131</t>
+          <t>https://www.msn.com/hi-in/news/India/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-556-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%82%E0%A4%AA-bdd-%E0%A4%9A-%E0%A4%B2-%E0%A4%95-%E0%A4%9A-%E0%A4%AC-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B0-%E0%A4%B0-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%88-%E0%A4%A6%E0%A5%82%E0%A4%B0/ar-AA1KxhQD</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-political-bjp-minister-stir-shiv-sena-ubt-mp-in-touch-with-bjp-9424103.html</t>
+          <t>https://www.pratahkal.com/Encyc/2025/8/16/cm-fadnavis-praised-the-army-on-independence-day.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/maharashtra-sarpmitra-insurance-identity-recognition-devendra-fadnavis-government-announcement-9437242.html</t>
+          <t>https://hindi.theprint.in/india/bjp-leader-targets-maratha-reservation-activist-jarange-for-his-remarks-against-fadnavis/854383/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/hindi/special-news/%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%A0%E0%A4%BE%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%80-13-%E0%A4%B8%E0%A4%BE%E0%A4%B2-%E0%A4%AC%E0%A4%BE%E0%A4%A6-%E0%A4%AE%E0%A4%BE%E0%A4%A4%E0%A5%8B%E0%A4%B6</t>
+          <t>https://ndtv.in/maharashtra-news/cm-fadnavis-inaugurated-mumbai-dabbawala-international-experience-center-dabbawalas-will-get-their-own-house-9088159</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/aap-ki-adalat-smriti-irani-says-yes-i-told-rekha-gupta-devendra-fadnavis-one-day-you-will-become-chief-ministers-2025-07-26-1151961</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-chhagan-bhujbal-skips-gondia-flag-hoisting-amid-guardian-minister-row-bjp-mangal-prabhat-deputed-know-all/articleshow/123305574.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-bombay-high-court-acquits-12-accused-in-2006-mumbai-train-blast-government-to-challenge-in-supreme-court-201753131021759.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/aimim-leader-imtiaz-jaleel-organised-a-biryani-party-at-his-home-to-protest-against-civic-bodys-meat-ban-also-targeted-cm-devendra-fadnavis/articleshow/123329000.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/supreme-courts-decision-on-mumbai-train-blast-why-was-devendra-fadnavis-happy-4256104.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/independence-day-meat-ban-row-sanjay-raut-slams-cm-fadnavis-said-shivaji-maharaj-was-not-eat-only-rice-and-ghee-know-all/articleshow/123274873.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/hamara-kisi-se-koi-bair-nahin/</t>
+          <t>https://bhasha.ptinews.com/detail/2830925</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/rumours-of-reshuffle-in-mahayuti-government-intensify-sudhir-mungantiwar-said-there-will-be-no-change-in-view-of-the-upcoming-elections/articleshow/122916746.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-mahayuti-eknath-shinde-missing-devendra-fadnavis-govt-cabinet-meeting-sa-9502234.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/101-units-of-blood-collected-on-cm-fadnavis-birthday/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/dispute-over-guardian-minister-post-deepens-in-mahayuti-government-eknath-shinde-distances-himself-from-cabinet-meeting/articleshow/123270600.cms</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/mumbai-train-blast-devendra-fadnavis-govt-challenges-high-court-verdict-in-supreme-court-ws-l-9428322.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/public-security-act-is-a-direct-attack-on-fundamental-rights-opposition-parties-in-the-field-11142</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/news/india/jamaat-e-islami-hind-vice-president-malik-moatasim-khan-on-maharashtra-government-over-bombay-high-court-order-ann-2983727</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/uddhav-thackeray-roared-with-jan-akrosh-andolan-in-dadar-lashed-out-at-shinde-fadnavis-government-1541</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-will-get-2-billion-dollar-cm-fadnavis-met-finance-minister-sitharaman-10832</t>
+          <t>https://mandalnews.com/amravati/cm-fadnavis-handed-over-the-keys-of-new-houses-to-bdd-chawl-residents/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/rahul-gandhi-is-surrounded-by-people-with-extreme-leftist-ideology-congress-leaders-are-now-protesting-on-his-orders-chief-minister-fadnavis-1753181338143</t>
+          <t>https://www.msn.com/hi-in/news/other/ganeshotsav-2025-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%88%E0%A4%A6-%E0%A4%8F-%E0%A4%AE-%E0%A4%B2-%E0%A4%A6-%E0%A4%95-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1KskuP</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-fadnavis-government-action-ban-online-gaming-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/work-is-on-to-make-maharashtras-healthcare-system-the-best-in-the-country-in-four-years-fadnavis/847961/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-inaugurates-bombay-high-court-new-circuit-bench-at-kolhapur-cm-fadnavis-and-dcm-eknath-shinde-also-present-know-all/articleshow/123346652.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-raj-thackeray-meets-uddhav-matoshri-cm-devendra-fadnavis-first-reaction-maharashtra-politics-9446972.html</t>
+          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-not-reached-devendra-fadnavis-govt-cabinet-meeting-201754983032466.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/maharashtra-cm-devendra-fadnavis-approved-budget-for-7-flyovers-in-vasai-virar/articleshow/122925149.cms</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-police-bharti-2025-mega-recruitment-drive-hire-15000-personnel-various-posts-announced-check-details-go-to-this-link-and-see-b507/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/delhi-ncr/video-jnu-students-union-protest-on-arrival-of-maharashtra-cm-devendra-fadnavis-2025-07-24</t>
+          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%B5-%E0%A4%A6-%E0%A4%9C-%E0%A4%8F-%E0%A4%AF-%E0%A4%A6%E0%A5%82%E0%A4%B8%E0%A4%B0%E0%A5%87/ar-AA1KrMtV</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-ex-cm-bjp-leader-ashok-chavan-gives-offer-to-uddav-thackeray-to-join-mahayuti-govt-after-cm-fadnavis-know-all/articleshow/122826647.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-agriculture-minister-manikrao-kokate-beggar-remark-controversy-fadnavis-slams-minister-201753247176643.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-unhappy-eknath-shinde-skips-cabinet-meeting-know-what-is-going-in-mahayuti-amid-guardian-minister-row/articleshow/123283685.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/mumbai-train-blast-bombay-high-court-verdict-acquits-all-accused-shivsena-mp-priyanka-chaturvedi-targets-devendra-fadnavis/4056334/</t>
+          <t>https://hindi.theprint.in/india/economy/committee-formed-to-give-suggestions-to-help-sectors-affected-by-us-tariffs-fadnavis/854538/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/mumbai-local-train-fadnavis-government-will-challenge-hc-decision-of-acquitting-train-blast-accused-1344619.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/kc-tyagi-jdu-claims-sharad-pawar-and-uddhav-thackeray-factions-in-touch-with-bjp-in-maharashtra-2984165</t>
+          <t>https://ndtv.in/maharashtra-news/aimim-and-ncp-sp-leaders-held-a-chicken-mutton-party-in-protest-against-meat-ban-in-maharashtra-9092115</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/8-ministers-in-the-state-will-go-home/</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-faction-minister-bharat-gogawale-angry-he-will-stay-away-from-cabinet-meeting-2994340</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-sena-leader-anil-parabs-open-challenge-to-yogesh-kadam-said-file-a-defamation-case-against-me-in-maharashtra/articleshow/122852255.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-leader-parinay-fuke-hits-out-at-maratha-quota-activist-manoj-jarange-for-remarks-against-devendra-fadnavis-2994554</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/minister-manikrao-kokate-accused-of-playing-rummy-in-maharashtra-assembly-warned-and-gave-this-logic-1344811.html</t>
+          <t>https://www.jagran.com/politics/national-maharashtra-meat-ban-protest-opposition-condemns-independence-day-shop-closure-24014311.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/national-hindi-news/aaj-ke-taaja-samachar-latest-breaking-news-today-in-hindi-27-july-2025-live-update-125072700004_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/signs-of-a-big-upheaval-in-maharashtra-politics-thackeray-fadnavis-meeting-in-the-news/</t>
+          <t>https://www.newsonair.gov.in/hi/garuda-drishti-device-is-playing-an-important-role-in-monitoring-social-media-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/raj-thackeray-reached-matoshree-after-13-years-said-happy-birthday-to-uddhav-thackeray-minister-rane-said-this-is-called-downfall-8960625</t>
+          <t>https://www.abplive.com/news/india/cji-br-gavai-praise-devendra-fadnavis-govt-said-maharashtra-government-always-leader-judiciary-infrastructure-2997155</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/why-bjp-planning-to-contest-solo-local-body-elections-tension-for-ajit-pawar-eknath-shinde-maharashtra-politics/4066658/</t>
+          <t>https://hindi.theprint.in/india/a-middle-path-should-be-found-in-the-matter-of-feeding-pigeons-fadnavis/854960/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/amp/india/maharashtra/story/maharashtra-government-employees-new-order-regarding-social-media-criticize-government-then-action-will-be-taken-ntc-rptc-2298395-2025-07-29</t>
+          <t>https://hindi.theprint.in/india/maharashtra-cm-fadnavis-is-protecting-corrupt-ministers-uddhav/853904/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-supreme-court-stay-in-mumbai-bomb-blast-case-is-a-right-step-devendra-fadnavis-news-hindi-1-739150-KKN.html</t>
+          <t>https://hindi.theprint.in/india/jarange-has-lost-credibility-his-remote-control-is-in-sharad-pawars-hands-bjp-leader/854582/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/there-is-no-law-to-ban-online-games-chief-minister-fadnavis-will-write-a-letter-to-the-center/</t>
+          <t>https://hindi.theprint.in/india/pune-university-withdraws-voice-of-devendra-contest-notification-after-nsui-objects/854442/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://lalluram.com/maharashtra-agriculture-ministers-harsh-words-called-his-own-government-beggar-cm-fadnavis-reacted/</t>
+          <t>https://www.agniban.com/protests-at-many-places-against-cm-fadnavis-corrupt-ministers-uddhav-said-chief-minister-is-protecting-everyone/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/editorial-rum-rummy-and-ramani-honey-trap-corporation/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%A7-%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%87-%E0%A4%B9%E0%A5%88-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0/ar-AA1KvM5B</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%8B%E0%A4%B2%E0%A5%87-%E0%A4%AB%E0%A4%A1%E0%A4%A3/</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-meat-ban-cm-devendra-fadnavis-says-govt-wont-decide-who-eats-what-201755168216321.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/kokates-ministerial-post-in-danger-he-was-playing-rummy-in-the-assembly-during-the-monsoon-session-now-cm-fadnavis-expressed-displeasure/</t>
+          <t>https://www.agniban.com/fadnavis-clarification-on-meat-ban-in-maharashtra-government-will-not-decide-who-should-eat-what/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-and-amit-shah-congratulated-maharashtra-chief-minister-devendra-fadnavis-on-his-birthday-539262</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/maharashtra-politics-uddhav-thackeray-attacks-devendra-fadnavis-for-not-acting-against-corrupt-ministers-frvd-2308298-2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.theprintlines.com/tpspecial/meri-baat/devendra-fadnavis-turns-55-a-visionary-leader-who-shaped-the-future-of-maharashtra-428416</t>
+          <t>https://www.livehindustan.com/maharashtra/i-pity-devendra-fadnavis-why-did-uddhav-thackeray-say-this-after-taking-the-names-of-these-3-ministers-201754912659397.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/devendra-fadnavis-who-made-maharashtra-number-1-538771</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/on-janmashtami-enthusiasm-for-dahi-handi-in-mumbai-a-unique-display-in-the-presence-of-cm-fadnavis-ytvd-2311680-2025-08-16</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://jaihindjanab.com/mumbai-news-9/</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-politics-saamna-editorial-devendra-fadnavis-eknath-shinde-ajit-pawar-uddhav-thackeray-sanjay-raut-201755148013599.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-mahesh-landge-donated-5-lakhs-to-the-chief-ministers-relief-fund-blood-donation-campaign-at-8-places-in-bhosari/</t>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/fadnavis-meets-chouhan-discussion-on-agriculture-and-rural-issues-3179780.html</t>
+          <t>https://www.hindisaamana.com/fadnavis-reprimands-shindes-osd/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/delhi-shivajis-strategy-and-marathi-will-be-taught-in-jnu-fadnavis-4169138</t>
+          <t>https://www.hindisaamana.com/home-minister-fadnavis-is-not-worried-the-protectors-of-law-are-committing-suicide-in-4-days-3-policemen-committed-their-lives/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/maharashtra-government-started-an-important-scheme-kisan-samridhi-yojana-for-farmers-agriculture</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/maharashtra-agriculture-minister-manikrao-kokate-may-lose-his-portfolio-1250834-2025-07-26?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://hindi.newsdanka.com/news-update/devendra-fadnavis-hoists-tricolour-maharashtra-engine-of-indias-progress/111395/amp</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://hindi.newsroompost.com/india/maharashtra-minister-girish-mahajan-claims-that-mp-s-of-uddhav-thackeray-will-join-bjp/1039860.html</t>
+          <t>https://hindi.latestly.com/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.ucanews.com/news/indias-maharashtra-state-threatens-action-against-crypto-christians/109711</t>
+          <t>https://bharatexpress.com/india/c-p-radhakrishnan-becomes-ndas-vice-presidential-candidate-maharashtra-chief-minister-devendra-fadnavis-congratulates-him-552637</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-agriculture-minister-manikrao-kokate-on-junglee-rummy-row-will-sue-who-defamed-me-8922314</t>
+          <t>https://samacharnama.com/states/maharashtra-news/paul-tixs-ghajini-devendra-fadnavis-lashes-out-at-uddhav/cid17238362.htm</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://energy.economictimes.indiatimes.com/news/renewable/maharashtra-cm-fadnavis-forms-committee-to-boost-solar-power-in-textiles-sector/122932353</t>
+          <t>https://www.rokthoklekhani.com/article/43041/flats-of-worli-bdd-chawl-redevelopment-project-inaugurated-by-cm</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/sena-bjp-turf-war-escalates-mos-misal-minister-shirsat-clash-over-authority-fadnavis-steps-in/articleshow/122936060.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/maharashtra-7-killed-as-pickup-van-falls-off-slope-cm-fadnavis-announces-rs-4-lakh-aid-4206354</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gift-to-children-on-cm-fadnavis-birthday-uniforms-distributed/articleshow/122843477.cms</t>
+          <t>https://www.newsnationtv.com/fadnavis-ka-vipaksh-par-tanz-mahanagar-palika-mein-toot-chuki-hai-paap-ki-haandi--20250816171044/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-cm-fadnavis-inaugurates-marathi-centre-lays-foundation-for-shivaji-strategic-studies-at-jnu-106558</t>
+          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/sports/fadnavis-congratulates-nagpur-teen-divya-for-winning-top-chess-title-kin-say-hard-work-paid-off/2770195</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rummy-video-row-maharashtra-minister-manikrao-kokate-must-go-why-is-cm-fadnavis-backing-him-asks-congress-harshwardhan-sapkal-23585959</t>
+          <t>https://bharatexpress.com/india/maharashtra-cm-devendra-fadnavis-independence-day-wishes-three-languages-reply-to-opposition-551631</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://theprint.in/ani-press-releases/maharashtra-chief-minister-devendra-fadnavis-inaugurates-tsl-foundations-bright-bus-initiative-a-digital-literacy-initiative-supported-by-crocs-india/2699242/</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/amid-rummy-video-row-maharashtra-minister-manikrao-kokate-calls-govt-beggar-sparks-row-devendra-fadnavis-19641416.htm</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/cm-fadnavis-arrived-at-dahi-handi-on-operation-sindoor-theme/article-101120</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/627417.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/mmr-region-has-15-trillion-potential-maharashtra-cm-4213325</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-to-get-usd-2-billion-aid-for-key-infra-projects-cm-fadnavis-meets-finance-minister-nirmala-sitharaman-in-delhi-23586460</t>
+          <t>https://bharat24live.com/news/maharashtra-cabinet-approves-recruitment-for-15000-police-posts-in-2025</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/cm-to-launch-1-crore-plantation-drive-steel-plant-construction-in-gadchiroli-today/amp_articleshow/122822027.cms</t>
+          <t>https://www.rokthoklekhani.com/tag/29359/mumbai%3A-rapid-redeevelopment-is-necessary-for-a-slum--free-mumbai---chief-minister-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/right-step-says-cm-devendra-fadnavis-after-sc-stays-bombay-hc-decision-in-2006-mumbai-train-blasts/</t>
+          <t>https://hindi.latestly.com/quickly/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/it-appears-that-a-crime-has-taken-place-cm-fadnavis-on-pune-rave-party/</t>
+          <t>https://www.rokthoklekhani.com/tag/29261/other-places-should</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/student-federation-of-india-protest-against-devendra-fadnavis-in-jnu/articleshow/122883002.cms</t>
+          <t>https://indiagroundreport.com/mumbai-dabbawalas-in-mumbai-will-get-500-square-feet-house-for-rs-25-50-lakh-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/raj-thackeray-to-meet-chief-minister-devendra-fadnavis-in-two-days-for-nashik-issues-1445481.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/farmers-compensation-pending-sharad-pawar-to-discuss-with-chief-minister-4216652</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-chief-minister-devendra-fadnavis-meets-amit-shah-in-delhi-signs-of-political-reshuffle-in-maharashtra-85197</t>
+          <t>https://joindia.co.in/news/fadnaviss-retort-on-sharad-pawars-160-seat-offer-statement-said-this-story-is-like-salim-javeds-script/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-has-expressed-displeasure-with-eknath-shinde-and-ajit-pawar-regarding-the-behavior-of-the-ministers-manikrao-kokate-sanjay-gaikwad-sanjay-shirsat-maharashtra-politics-1372333</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/devendra-fadnavis-birthday-uddhav-thackeray-praise-for-maharashtra-cm-bjp-leader-girish-mahajan-coffee-table-book-marathi-news-1371658</t>
+          <t>https://www.msn.com/en-in/news/India/guaranteed-victory-claim-row-erupts-in-maharashtra-did-you-use-vote-riggers-devendra-fadnavis-asks-sharad-pawar/ar-AA1Khn2c</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli-news-devendra-fadnavis-appeals-to-maoists-in-inauguration-and-foundation-of-various-projects-of-lloyds-metals-and-energy-limited-program-in-gadchiroli-1371643</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832775</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/sunil-tatkare-meets-cm-devendra-fadnavis-in-delhi-maharashtra-political-happenings/photoshow/122887919.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sppu-withdraws-voice-of-devendra-contest-notice-after-protest-101755032437944.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-and-sunil-tatkare-on-manikrao-kokate-the-issue-of-manikrao-kokate-resignation-was-discussed-in-the-meeting-between-devendra-fadnavis-and-sunil-tatkare-maharashtra-politics-1372302</t>
+          <t>https://www.msn.com/en-in/news/India/credai-mchi-appoints-sukhraj-nahar-as-18th-president-in-presence-of-cm-devendra-fadnavis/ar-AA1KxDEc</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-devendra-fadanvis-ajit-pawar-devendra-fadanvis-birthday-bjp-mahayuti-marathi-news-abp-majha-1371773</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-to-inaugurate-slew-of-projects-today-metro-3-may-launch-by-aug-end-101754936573343.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-cabinet-chances-of-major-reshuffle-mahajan-likely-to-be-dropped-rahul-narvekar-may-get-inducted/articleshow/122878832.cms</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-speech-in-wardha-says-we-will-contest-local-bodies-election-as-mahayuti-but-show-bjp-power-1373161</t>
+          <t>https://www.newsband.in/article_detail/new-psa-terminal-at-jnpa-to-be-opened-soon-fadnavis-</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-first-reaction-on-raj-thackeray-meets-uddhav-thackeray/articleshow/122935374.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-uddhav-thackeray-manikrao-kokate-kalyan-crime-mahadev-munde-ajit-pawar-mumbai-rain-flood-eknath-khadase-son-in-law-thalak-batmya-sund-1455864.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos--106878</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/23/chief-minister-devendra-fadnavis-nitesh-rane-cheque.html</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/r-madhavan-met-cm-devendra-fadnavis-thanks-for-collab-between-ftii-mfscdc/articleshow/122830379.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-14-news-updates-live-updates-weather-update-mumbai-monsoon-18331384</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sfi-agiation-jnu-against-devendra-fadnavis-marathi-language-study-centre-inaugurated-in-jnu-students-protest-raise-slogans-against-mahayuti-government-1372229</t>
+          <t>https://zeenews.india.com/india/maharashtra-7-dead-as-pickup-van-falls-cm-fadnavis-announces-4-lakh-aid-2944690.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-praised-by-uddhav-thackeray-sharad-pawar-maharashtra-nayak-coffee-table-book-launch-on-birthday/articleshow/122834006.cms</t>
+          <t>https://www.ptinews.com/editor-detail/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-full-devendra-fadanvis-ajit-pawar-manikrao-kokate-sanjay-shirsat-marathi-news-abp-majha-1372560</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-ubt-protests-in-nagpur-seeking-sacking-of-corrupt-maharashtra-ministers/2812465</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-give-birthday-wishes-to-eknath-shinde-and-ajit-pawar-on-birthday-1371526</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-deputy-cm-ajit-pawar-led-ncp-questions-meat-ban-on-august-15-bjp-cites-1988-order-23589362</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-devendra-fadnavis-visits-delhi-meets-amit-shah-nirmala-sitharaman-jp-nadda-shivraj-singh-chouhan-in-new-delhi-1372464</t>
+          <t>http://www.uniindia.com/photoes/631755.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/marathi-celebrities-troll-for-share-devendra-fadnavis-birthday-video/articleshow/122850047.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278509383/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-warns-dcm-eknath-shinde-and-ajit-pawar-about-controversial-ministers-and-mlas/articleshow/122906555.cms</t>
+          <t>https://www.apnnews.com/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-takes-big-decision-fadnavis-has-direct-control-over-eknath-shinde-portfolio-1441467.html</t>
+          <t>https://www.socialnews.xyz/?p=6622494</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-reaction-on-minister-manikrao-kokate-video/articleshow/122817759.cms</t>
+          <t>https://www.punekarnews.in/congresss-ramesh-chennithala-questions-cm-fadnaviss-remarks-on-rahul-gandhis-allegations-against-election-commission/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-reaction-on-honey-trap-case/articleshow/122818265.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/bhiwandi-will-be-developed-as-an-urban-city-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-praises-cm-devendra-fadnavis-work-style-and-speed-give-birthday-wishes-1371651</t>
+          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-speech-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A4%B0%E0%A4%95%E0%A5%81%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A4%E0%A4%B0%E0%A4%A3-marathi-news/vi-AA1KFM8O?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-meets-amit-shah-amid-buzz-of-cabinet-reshuffle-ahead-of-local-body-polls/articleshow/122921793.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-statement-that-kolhapur-has-become-centralized-due-to-the-circuit-bench/912997/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/23/devendra-fadnavis-pandharpur-development-plan.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/underground-road-plan-to-ease-central-pune-traffic-cm-devendra-fadnavis-meeting-9101801</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-turns-to-amit-shah-discuss-controversial-mahayuti-ministers/articleshow/122922815.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-jnu-protest-students-oppose-devendra-fadnavis-s-program-over-hindi-imposition-and-anti-people-policies-at-chhatrapati-shivaji-maharaj-strategic-studies-center-inauguration-1372245</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-after-president-trump-who-is-the-clown-in-politics-it-is-devendra-fadnavis-raut-criticizes-the-chief-minister/912795/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/big-blow-to-eknath-shinde-as-cm-devendra-fadnavis-nod-must-for-urban-development-department-project/articleshow/122880620.cms</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/devendra-fadnavis-targets-thackeray-brothers-over-marathi-hindi-dispute-while-speaking-at-jnu/905090/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-national-international-ind-vs-eng-4th-test-entertainment-news-24-july-2025-926443</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-believes-that-maharashtra-will-lead-the-countrys-development-system-amy-95-5307598/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-comment-on-raj-thackeray-visit-matoshree-for-birthday-wish-to-uddhav-thackeray-1444613.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-once-again-slams-to-agriculture-minister-manikrao-kokate-over-his-bhikari-sarkar-statement-1451891.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-slam-agriculture-minister-manikrao-kokate-over-his-viral-video-playing-rummy-1440439.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/solapur-news-mla-vijay-kumar-deshmukh-expressed-regret-over-chief-minister-devendra-fadnavis-neglect-of-solapur-in-the-last-two-years-1377700</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-expresses-gratitude-to-sharad-pawar-and-uddhav-thackeray-for-birthday-wishes-1452201.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-likely-to-go-for-major-cabinet-shuffle-ahead-of-local-body-elections/articleshow/122877677.cms</t>
+          <t>https://www.saamana.com/after-donald-trump-devendra-fadnavis-is-biggest-joker-in-politics-sanjay-raut-criticized/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ncp-sharad-pawar-praises-cm-devendra-fadnavis-chhagan-bhujbal-first-reaction-in-indapur/articleshow/122880048.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/cm-devendra-fadnavis-criticizes-thackeray-group-saying-we-broke-the-pot-of-sin-in-municipal-corporation/912631/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/marathi-live-breaking-news-22-july-2025-maharashtra-weather-update-rain-politics-devendra-fadnavis-eknath-shinde-raj-thackeray-local-election/liveblog/122825123.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/only-then-will-the-dream-of-a-slum-free-mumbai-be-realized-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/special/sharad-pawar-praise-devendra-fadnavis-278747/amp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-challenges-uddhav-and-raj-thackeray-over-mumbai-municipal-corporation-bmc-elections-during-dahi-handi-festival/articleshow/123333235.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/file-war-between-cm-devendra-fadnavis-and-eknath-shinde-dcm-ask-shiv-sena-ministers-to-send-files-to-his-office/articleshow/122899449.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/pandharpur-money-demanded-from-the-contractor-for-darshan-queue-manoj-shrotri-action-cm-devendra-fadnavis-visit-by-mandir-samiti-1372010</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announced-it-park-to-be-set-up-in-solapur-for-employment-generation-1460220.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/governor-cp-radhakrishnan-asserted-that-chief-minister-devendra-fadnavis-has-taken-maharashtra-on-the-path-of-progress/904445/</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-showered-praise-on-devendra-fadnavis-while-wishing-him-on-his-birthday/904281/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devedra-fadnavis-challenges-opposition-over-upcoming-municipal-elections-at-dahi-handi-2025/articleshow/123340653.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/breaking-news/impact-of-chief-ministers-medical-assistance-cell-aid-extended-to-1048-patients-in-nashik-district/903980/</t>
+          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-strong-answer-to-uddhav-thackeray-said-he-stole-public-mandate-and-now-teaching-us-scj-81-5296450/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-ubt-sanjay-raut-attack-on-cm-devendra-fadnavis-over-sanjay-shirsat-manikrao-kokate-yogesh-kadam-sanjay-gaikwad/905602/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288/amp/1</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-reaction-on-rave-party/</t>
+          <t>https://www.mymahanagar.com/photo-gallery/dahi-handi-2025-tembhinaka-dahihandi-cm-devendrad-fadnavis-political-statement-on-bmc-election/912700/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/agriculture-minister-manikrao-kokate-has-announced-a-new-scheme-for-farmers-agriculture-news-1440653.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raj-thackeray-uddhav-thackeray-shiv-sena-ubt-mns-reunite-for-best-employees-credit-society-election-against-bjp-devendra-fadnavis-samruddhi-panel/articleshow/123328116.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-reshuffle-on-cards-following-fadnavis-shah-meeting-controversial-ministers-face-potential-dismissal-1454339.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/a-committee-should-be-formed-for-the-use-of-solar-energy-in-the-textile-sector-chief-minister-devendra-fadnavis-directs/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/eknath-shinde-call-meeting-of-all-shiv-sena-ministers-at-muktagiri-bungalow/articleshow/122837363.cms</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-mumbai-dahihandi-mahapalik-dahihandi-and-challage-to-uddhav-thackeray-bmc-election-1377445</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-assembly-speaker-rahul-narvekar-reaction-on-probability-of-changes-in-maharashtra-cabinet/articleshow/122903334.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/police-bharati-maharashtra-cabinet-decisions-today-under-cm-devendra-fadnavis-15000-police-bharti-know-details-in-marathi-1376621</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ncp-sharad-pawar-party-mla-rohit-pawar-makes-big-claim-about-phone-tapping-of-mahayuti-minister/articleshow/122906907.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-india-independence-day-cm-fadnavis-dy-cms-opposition-leaders-hoist-flag-across-maharashtra-delhi-rahul-gandhi-in-rain-1377336</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/dr-ulhas-patil-hospital-response-to-cm-devendra-fadnavis-appeal-120037/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-reshuffle-cm-devendra-fadnavis-targets-8-controversial-underperforming-ministers-article-152342658</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-stated-bandra-versova-sea-link-will-be-extended-up-to-vadhavan-port-local18-1459825.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/digital-governance-necessity-requirement-cm-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/07/amruta-fadnavis.html</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/cm-devendra-fadnavisbirthday-celebrated-social-event/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A6%E0%A4%B9-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%95-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F/ar-AA1KD8k2</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/manikrao-kokate-resignation-matter-reviewed-in-key-meeting-between-devendra-fadnavis-and-sunil-tatkare-amid-maharashtra-political-row-article-152343956</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9A-%E0%A4%AB-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KE0LG</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-to-meet-chief-minister-devendra-fadnavis-what-exactly-will-be-discussed-curiosity-is-at-its-peak/</t>
+          <t>http://www.msn.com/mr-in/news/other/harshvardhan-sapkal-on-devendra-fadanvis-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%9A%E0%A5%87-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%87/ar-AA1KbAUb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://buldanalive.com/main-news/tomorrow-is-a-great-blood-donation!-chief-minister-devendra/cid17120484.htm</t>
+          <t>https://deshdoot.com/fadnavis-targets-thackeray-camp-we-broke-the-pot-of-corruption-in-bmc-now-development-will-flow/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/cm-help-desk-support-for-aid-room-needy-patients/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/chess-player-divya-deshmukh-worthy-of-pride-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/maharashtra/900-blood-bags-collected-from-south-district-on-the-occasion-of-chief-minister-fadnavis-birthday/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%96%E0%A5%87%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%86%E0%A4%B2-%E0%A4%9A-%E0%A4%AC-%E0%A4%A1-%E0%A4%A1-%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1KcLlH</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/amphetamine-drugs-seized-in-kannada-ghat-chalisgaon-120198/</t>
+          <t>https://marathi.ndtv.com/cities/jain-muni-nileshchandra-appeal-to-cm-devendra-fadnavis-over-dadar-kabutar-khana-issue-9075708</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/sant-namdev-maharaj-temple-restored-cm-devendra-fadnavis/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-uddhav-thackeray-before-criticizing-devendra-fadnavis-look-in-the-mirror-public-not-forgotten-rs-100-crore-recovery-case-maharashtra-politics-marathi-news-1376412</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-cm-devendra-fadnavis-permission-will-have-to-fund-distribution-in-eknath-shindes-urban-development-department-84699</t>
+          <t>https://www.msn.com/mr-in/news/other/third-mumbai-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A6%E0%A5%81%E0%A4%AC%E0%A4%88%E0%A4%AA%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%86%E0%A4%A3-%E0%A4%86%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B7%E0%A4%95-%E0%A4%B9-%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KDOAo</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/devendra-fadnavis-mediates-in-sanjay-shirsat-vs-madhuri-misal-dispute-8960770</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/operation-sindoor-broke-the-yoke-of-pakistans-sins.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/devendra-fadnavis-says-proud-of-marathi-language-but-will-not-tolerate-attacks-on-language-chief-minister-reprimands-to-mns-1372265</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mumbai-within-59-minutes-metro-local-railway-bus-roadways-to-become-congestion-free/articleshow/123316080.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mahayuti-government-corporation-seats-distribution-finalized-bjp-gets-44-corporations-shinde-shivsena-group-gets-33-and-ajit-pawar-ncp-gets-23-corporations-maharashtra-politics-marathi-news-1371824</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/emotional-moment-as-bdd-residents-get-their-dream-home-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chief-minister-devendra-fadnavis-inquiry-into-eknath-shinde-urban-development-department/926448</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-22-july-bjp-leader-praful-lodha-honey-trap-case-monsoon-maharashtra-politics-national-international-live-update-in-marathi-925856</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-and-ajit-pawar-battle-over-additional-municipal-corporations-in-pune/articleshow/123235053.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/cm-devendra-fadnavis-reaction-on-raj-thackeray-uddhav-thackeray-meet-at-matoshree-and-pune-rave-party-case-maharashtra-news-mhs25072704047</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/11/gopinath-munde-taught-chief-minister-devendra-fadnavis-to-struggle-without-compromising-with-power-home-minist.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-july-21-breaking-news-in-marathi-925555</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B5%E0%A4%B2%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%8A%E0%A4%A8%E0%A4%B9-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%98%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%82%E0%A4%AE%E0%A4%A4-%E0%A4%95%E0%A4%B6-%E0%A4%95-%E0%A4%AF/ar-AA1KA4bi?cvid=709e293f49bb433db28c9ad0d1e1c64d</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-21-july-2025-marathi-news-live-maharashtra-weather-update-honey-trap-case-parliament-monsoon-session-sanjay-raut-thackeray-brothers/liveblog/122804783.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/worli-bdd-chawl-redevelopment-program-cm-devendra-fadnavis-speech-dharavi-project-9083348</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nashik/manikrao-kokate-video-agriculture-minister-press-conference-in-nashik-after-ajit-pawar-call-devendra-fadnavis-reaction-marathi-news-1371479</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-news-controversy-over-state-level-oratory-competition-on-the-occasion-of-chief-minister-devendra-fadnavis/articleshow/123257068.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-news-minister-chandrashekhar-bawankule-informed-sarpmitra-will-get-accident-insurance-of-rs-10-lakh-along-with-identity-card/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/congress-sangli-leader-prithviraj-patil-resigns-to-join-bjp-in-presence-of-devendra-fadnavis/articleshow/123269760.cms</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/eknath-shinde-devendra-fadnavis-funds-distributed-through-the-urban-development-department-now-require-the-approval-of-chief-minister-devendra-fadnavis/126911/</t>
+          <t>https://www.navarashtra.com/maharashtra/devendra-fadnavis-appeal-to-public-ganeshotsav-committees-958689.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/maharashtra-chief-minister-devendra-fadnavis-inaugurates-tsl-foundations-bright-bus-initiative-a-digital-literacy-initiative-supported-by-crocs-india/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-slams-cm-devendra-fadnavis-and-mahayuti-government-in-mumbai-speech-1376389</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cm-fadnavis-lays-foundation-stone-for-shivaji-study-centre-inaugurates-marathi-literature-centre-at-jawaharlal-nehru-university-in-delhi/articleshow/122887498.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%82%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF/ar-AA1KyPVX</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/court-denies-anticipatory-bail-to-two-in-cm-s-wife-derogatory-post-case-101753383594075.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/close-on-the-heels-of-rummy-row-ncp-minister-kokate-calls-govt-beggar-fadnavis-calls-remarks-inappropriate-3642199</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-calling-vegetarians-impotent-is-foolish-chief-minister-devendra-fadnavis/911740/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/construction/maharashtra-launches-first-integrated-steel-plant-in-gadchiroli/122853721</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-thackeray-group-morcha-kabutar-khana-thalak-batmya-monday-11-august-2025-1466781.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rummy-video-row-pressure-mounts-on-ncp-minister-kokate-to-step-down-3644542</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B2-%E0%A4%A8-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%87%E0%A4%B6%E0%A4%B5%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AD-%E0%A4%A4-%E0%A4%96-%E0%A4%8A%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A5%AC%E0%A5%AB-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%A8/ar-AA1KqsEZ</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-and-tatkare-rap-kokate-for-playing-rummy-in-legislative-council-101753125744672.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/manoj-jarange-patil-criticizes-on-chief-minister-devendra-fadnavis-on-maratha-reservation-nanded-1377172</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/we-will-challenge-it-in-the-supreme-court-maharashtra-cm-fadnavis-expresses-shock-over-bombay-hcs-decision-on-2006-mumbai-blasts</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-big-announcement-for-mumbai-dabewala-will-give-a-500-square-feet-house-for-25-lakhs-1458046.html</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-mns-raj-thackeray-over-mumbai-municipal-bmc-elections/articleshow/123306829.cms</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/i-dont-know-how-to-play-online-rummy-will-sue-oppn-leaders-who-defamed-me-minister-kokate-3641785</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ubt-leader-sanjay-raut-talk-on-cm-devendra-fadnavis-in-press-conference/articleshow/123271049.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/2006-mumbai-train-blasts-case-accused-acquitted-maharashtra-govt-will-study-hc-order-says-bawankule/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-ubt-mns-aim-to-prevent-mumbai-from-gujarati-people-says-sanjay-raut/articleshow/123340988.cms</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.digit.in/news/general/why-maharashtra-govt-wants-to-ban-online-gaming.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-vice-presidential-election-nda-nominates-cp-radhakrishnan-rajnath-singh-calls-kharge-for-unopposed-poll-india-alliance-to-meet-1377786</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/navi-mumbai-two-booked-as-woman-performs-aura-farming-on-merc-bonnet-23586340</t>
+          <t>https://www.saamana.com/sanjay-raut-media-briefing-in-nashik-slams-pm-modi-devendra-fadnavis-and-bjp-on-independence/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.udayavani.com/english-news/urban-naxals-using-foreign-funds-to-keep-gadchiroli-away-from-development-fadnavis</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/gadchirolis-steel-resolve-cm-fadnavis-lays-foundation-for-vidarbhas-first-integrated-steel-plant-564611</t>
+          <t>https://prahaar.in/2025/08/18/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/other-courts/anticipatory-derogatory-post-cms-wife/</t>
+          <t>https://news18marathi.com/maharashtra/pankaja-munde-emotional-speech-at-latur-gopinath-munde-statue-inauguration-latur-1455554.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/unique-poster-campaign-by-locals-to-oppose-pandharpur-corridor-8929403</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-devendra-fadnavis-in-delhi-for-high-profile-meetings-with-nirmala-sitharaman-amit-shah-j-p-nadda-and-shivraj-singh-chouhan-also-met-sunil-tatkare-1372340</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-breaking-news-22-july-2025-latest-marathi-news-manikrao-kokate-may-resign-rain-weather-updates-1371512</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/decision-today-on-bail-application-of-accused-who-spread-defamatory-content-about-amruta-fadnavis-pune-print-news-rbk-25-amy-95-5251419/</t>
+          <t>https://vishwanewsmarathi.com/we-broke-the-pot-of-sin-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/business/news-for-investors-today-gold-price-increases-by-rs-150-1373175</t>
+          <t>https://marathi.timesnownews.com/maharashtra/third-mumbai-can-be-bigger-and-more-attractive-than-dubai-says-cm-devendra-fadnavis-article-152473589</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-new-social-media-policy-bars-govt-employees-from-criticising-policies-of-government-in-state-2025-07-28</t>
+          <t>https://www.dainikprabhat.com/alandi-news-universal-thoughts-in-dnyaneshwari-are-the-root-of-indian-culture-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-breaking-news-25-july-2025-manikrao-kokate-ajit-pawar-sunil-tatkare-devendra-fadnavis-vijaykumar-ghadge-maharashtra-weather-mumbai-konkan-rains-maharashtra-politics-1372299</t>
+          <t>https://vishwanewsmarathi.com/devendra-fadnavis-is-not-the-chief-but-a-thief-minister-thackerays-attack/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-in-wardha-bjp-manthan-mela-announcements-everyone-get-house-who-applies-for-pradhan-mantri-awas-yojana-electricity-rates-will-be-reduced-by-26-percent-1373152</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-july-26-breaking-news-in-marathi-926965</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-july-24-breaking-news-in-marathi-926467</t>
+          <t>https://vishwanewsmarathi.com/rightful-houses-for-workers-of-solapur-houses-distributed-by-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/wardha-news-sudhir-mungantiwar-absence-in-bjp-vidarbha-level-meeting-today-in-sevagram-of-wardha-meeting-led-by-the-cm-devendra-fadnavis-1373108</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-july-27-breaking-news-in-marathi-927181</t>
+          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-big-announcement-for-solapur-residents-will-thousands-of-youth-get-employment/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-july-22-breaking-news-in-marathi-925859</t>
+          <t>https://www.dainikprabhat.com/houses-in-mumbai-are-worth-gold-keep-them-safe-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/announcement-of-new-survey-for-vasai-virar-ring-route-project-gives-relief-to-passengers/articleshow/122806631.cms</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/pune-news/mou-between-ftii-and-maharashtra-cultural-corporation-youth-in-film-and-media-sector-will-get-professional-training/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/it-park-will-be-set-up-in-solapur-says-cm-devendra-fadnavis-article-152478385</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/no-place-for-bangladeshi-infiltrators-in-haryana-nayab-singh-saini-101753552842600.html</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/ours-is-a-battle-of-ideas-not-personal-enmity-says-bjp-mla-ram-kadam-on-uddhavs-praise-for-maharashtra-cm/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-public-awareness-should-be-created-about-vermilion-and-swadeshi-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-committee-formed-for-those-industries-chief-minister-devendra-fadnavis-gave-information/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/birthday-visits-should-not-be-viewed-from-political-lens-maharashtra-cm-fadnavis-on-thackeray-brothers-meetup/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-dabbawalas-will-get-500-square-feet-house-in-25-lakh-50-thousand-cm-devendra-fadnavis-big-annoucement-for-dabbawala-article-152466274</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-on-delhi-tour/926363</t>
+          <t>https://www.dainikprabhat.com/devendra-fadanvis-cant-bear-it-cant-even-say-it-devendra-fadnaviss-attack-on-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/with-the-help-of-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/the-historic-sword-of-the-brave-maratha-sardar-raghuji-bhosale-is-in-the-possession-of-the-government-when-will-it-be-brought-to-mumbai/129289/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/while-being-proud-of-one-s-mother-tongue-one-should-respect-other-languages-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-orders-give-preference-to-locals-in-railway-bogie-factory/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/harshvardhan-sapkal-attacked-chief-minister-fadnavis-125072300060_1.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-government-s-cabinet-approves-recruitment-of-15000-police-officers-125081200048_1.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/213468/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/devendra-fadanvis-chief-minister-devendra-fadanvis-clear-opinion-on-tariff-said-the-industries-that-will-be-affected/128946/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/first-ai-technology-based-anganwadi-in-nagpur-inaugurated-by-cm-devendra-fadnavis-children-get-a-first-hand-experience-of-virtual-events-1373060</t>
+          <t>https://www.thodkyaat.com/manoj-jaranges-ultimatum-to-government-threatens-chalo-mumbai-on-august-29/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://policenama.com/devendra-fadnavis-birthday-blood-donation-camp-on-the-birthday-of-maharashtras-successful-chief-minister-devendra-fadnavis/</t>
+          <t>https://marathi.ndtv.com/cities/chief-minister-devendra-fadnavis-announces-that-mumbai-dabbawalas-will-get-houses-worth-rs-25-50-lakh-9087324</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/new-controversy-over-funds-in-mahayuti-fadnavis-restraint-on-the-allocation-of-funds-for-the-urban-development-department-97170/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/rajpaat-power-tussle-bjp-internal-conflicts-maharashtra-bengal-dhami-ucc-politics/4066260/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/cm-devendra-fadnavis-takes-big-decision-transfer-7-ias-officer-in-state-88422</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/who-is-62-year-old-praful-was-he-responsible-for-the-fall-of-maha-vikas-aghadi-government/4060937/</t>
+          <t>https://www.loksatta.com/photos/news/5301075/marathi-ekikaran-samiti-agitation-at-kabutar-khana-mumbai-what-did-they-say/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-12-political-news-in-marathi-931564</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/sanjay-nirupam-claims-uddhav-and-raj-thackeray-deviated-from-balasaheb-ideals-eknath-shinde-is-true-heir/articleshow/122819615.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-nagpur-high-speed-rail-project-parallel-lines-to-samruddhi-mahamarg-know-detail-by-cm-devendra-fadnavis-article-152450605</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leadership-message-to-maharashtra-bjp-about-shinde-led-shiv-sena-for-bmc-election/articleshow/122814810.cms</t>
+          <t>https://lokmanthan.com/give-priority-to-locals-for-employment-in-railway-bogie-factory-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/congress-alliance-government-led-by-vilasrao-deshmukh-that-time-home-minister-r-r-patil-had-banned-dance-bars-in-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/india/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/articleshow/123290009.cms</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/relief-for-uddhav-thackeray-shiv-sena-outgoing-stopped-in-mumbai-party-workers-hopeful-for-raj-thackerays-mns-alliance/articleshow/122953599.cms</t>
+          <t>http://www.msn.com/en-in/news/India/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav/ar-AA1KiaOZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/eknath-shinde-faces-trouble-due-to-shiv-sena-leader-sanjay-shirsat-sanjay-gaikwad-sanjay-raut/articleshow/122818010.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-savvy-maharashtra-cm-fadnavis-gives-ipads-to-ministers-to-ensure-cabinet-agenda-secrecy/articleshow/123242160.cms</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-criticized-eknath-shindes-shameless-support-for-dance-bars/</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/23/bom20-news-highlights-from-western-region-at-1700-hrs.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/actor-complains-about-redevelopment-project-fraud-cm-intervenes-101755026135161.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/kapil-patil-challenges-development-claims-by-sitting-bhiwandi-mp-demands-proof-of-work/articleshow/122949261.cms</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/mumbais-journey-to-become-slum-free-cm-fadnavis-emphasizes-rapid-redevelopment/123320003</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-seeks-centres-nod-funding-for-major-infra-projects-in-state/articleshow/122912244.cms</t>
+          <t>https://www.ptinews.com/editor-detail/We-missed-the-bus-earlier--no-compromise-on-Mumbai-s-development-now--Fadnavis/2823252</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/3-deputy-collector-rank-officials-to-interact-with-traders-residents-to-get-consent-for-pandharpur-temple-corridor-plan/articleshow/122801039.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/17/bom26-mh-vp-candidate-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/7/23/-window-on-vidarbha.html</t>
+          <t>https://www.ptinews.com/editor-detail/Quota-activist-Jarange-lost-credibility--his-remote-control-is-in-Sharad-Pawar-s-hands--BJP-MLC/2816227</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/25/nagpur-vidhan-bhavan-to-get-central-vista-style-makeover-under-maha-vista-plan/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MTk5ODg=/maharashtra-cm-meets-union-ministers-to-fast-track-funding-for-rural-and-industrial-projects</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/pune-university-withdraws-voice-of-devendra-competition-notice-after-objection-from-nsui/123300501</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Hyderabad/telangana-42432-people-live-in-166-ghmc-slums-minister-directs-lands-to-be-identified-for-g3-buildings-for-poor/article69843667.ece</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/first-batch-of-redeveloped-bdd-chawls-to-handed-over-by-august-15-101753642325945.html</t>
+          <t>https://english.newsnationtv.com/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/maharashtra-chief-minister-devendra-fadnavis-inaugurates-tsl-foundations-bright-bus-initiative-a-digital-literacy-initiative-supported-by-crocs-india20250723114407/</t>
+          <t>https://www.latestly.com/agency-news/india-news-newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis-7056055.html</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/itwari-umred-section-of-nagpur-nagbhid-broad-gauge-line-likely-to-open-before-diwali/articleshow/122844269.cms</t>
+          <t>http://www.msn.com/en-in/news/India/script-by-salim-javed-fadnavis-mocks-rahul-s-vote-chori-claims-says-congress-chief-is-speaking-fiction/ar-AA1Ka5DS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Visakhapatnam/some-trains-to-be-cancelled-to-facilitate-commissioning-of-3rd-line-between-vijayawada-and-gudur/article69843896.ece</t>
+          <t>https://www.deccanherald.com/opinion/election-commission-and-the-trust-it-must-rebuild-3678073</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-meets-union-ministers-leaders-in-delhi-to-seek-central-aid-for-mahas-development-projects</t>
+          <t>http://www.msn.com/en-in/news/India/uddhav-thackeray-s-last-row-seat-at-rahul-gandhi-dinner-meet-gets-bjp-taunt/ar-AA1Kc4YH?cvid=6e808800d5b0453f91562cfa362d3523&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/sewage-projects-in-16-merged-pune-villages-get-rs-533-cr-boost-under-amrut-2-0/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ex-mla-from-maharashtra-says-he-too-was-offered-voter-fraud-services/articleshow/123349170.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/24/green-municipal-bonds-are-a-good-and-new-option-for-investors.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-delhi-tour-maharashtra-projects-033379.html</t>
+          <t>https://timesofindia.indiatimes.com/city/indore/cm-leads-tiranga-rally-in-indore-criticises-rahul-gandhi/articleshow/123289456.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://theindianeye.com/2025/07/28/tesla-rolls-into-india-model-y-debuts-in-maharashtra-amid-ev-momentum/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statement-in-pune-court-apprehending-threat-to-rahuls-life-being-withdrawn-congress-spokespersons/articleshow/123289899.cms</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-ajit-pawar-voiced-our-concern-high-time-to-transform-basic-infrastructure-of-hinjewadi-says-fites-pavanjit-mane-3650623</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/my-bihar-yatra-is-to-save-democracy-says-rahul/articleshow/123308887.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ferguson-college-road-turns-unsafe-after-dark-mla-shirole-urges-pmc-pune-police-to-act/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/surrendered-maoist-commander-returns-home-to-celebrate-i-day/articleshow/123339065.cms</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://hindinews.careers360.com/uma-kanjilal-appointed-ignou-first-woman-vice-chancellor-with-over-36-years-of-service-in-odl</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/24/maharashtras-economy-will-become-1-trillion-in-the-next-five-years.html</t>
+          <t>https://www.news18.com/videos/india/fight-to-save-constitution-says-rahul-gandhi-as-police-detain-opposition-mps-amid-protest-9498093.html</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173433/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.eurasiareview.com/22072025-indias-maharashtra-state-threatens-action-against-crypto-christians/</t>
+          <t>https://m.economictimes.com/news/india/red-fort-2025-guest-list-vips-special-guests-and-leaders-joining-the-ceremony/historical-significance/slideshow/123258949.cms</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/mahayuti-meets-in-nashik-to-discuss-strategy-for-civic-polls/articleshow/122801413.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bailey-bridges-set-to-bring-year-round-connectivity-to-14-gadchiroli-villages/articleshow/123339082.cms</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-july-20-2025-weather-today-rain-alert-world-championship-of-legends-india-vs-pakistan-match-donald-trump-india-pakistan-ukraine-russia/liveblog/122792184.cms</t>
+          <t>https://www.business-standard.com/india-news/rahul-gandhi-kharge-extend-greetings-to-nation-on-79th-independence-day-125081500455_1.html</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-assam-government-launches-path-samanvay-aimed-at-better-coordination-in-execution-of-public-works-7013411.html</t>
+          <t>https://timesofindia.indiatimes.com/city/guwahati/himanta-calls-rahul-traitor-slams-priyankas-proposed-visit-to-dhubri/articleshow/123080085.cms</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/chhava-organization-gave-ultimatum-to-remove-agriculture-minister-said-if-he-is-not-removed-there-will-be-protest-against-ajit-pawar/articleshow/122916579.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/bjp-mla-wants-daily-screening-of-at-least-1-marathi-film-in-all-theatres-across-maharashtra-writes-to-cm-cultural-minister/articleshow/123311633.cms</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%85%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A5%80-9/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tricolour-rises-in-maoist-hq-foothills-kawandes-first-tryst-with-independence-day/articleshow/123310883.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/we-aren-t-enemies-maharashtra-cm-devendra-fadnavis-thanks-opponents-uddhav-thackeray-sharad-pawar-here-s-why/ar-AA1J4NmQ</t>
+          <t>https://arunachal24.in/rahul-gandhi-alleges-massive-voter-fraud-accuses-election-commission-of-collusion-with-bjp/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/pm-narendra-modi-traded-national-pride-for-business-uddhav-thackeray-101753040418717.html</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/cong-prepares-for-rahuls-yatra-evades-question-on-oppn-cm-face/articleshow/123285236.cms</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/pm-modi-extends-birthday-wishes-to-ajit-pawar-devendra-fadnavis20250722090121</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/bjp-set-honeytraps-to-bring-down-mva-government-alleges-sanjay-raut/article69839465.ece</t>
+          <t>https://m.economictimes.com/news/india/9-indian-monuments-and-places-that-tell-the-story-of-freedom/red-fort-delhi/slideshow/123275019.cms</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/28/bom8-mh-fadnavis-oppn.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/drugs-seized-after-raid-at-party-in-pune-husband-of-former-minister-eknath-khadses-daughter-rohini-khadse-detained-3650606</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bombay-hc-acquits-all-711-train-blasts-accused-maha-govt-will-study-order-says-bjps-chandrashekhar-bawankule-3640296</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cji-gavai-to-inaugurate-bombay-high-courts-circuit-bench-at-kolhapur-today/articleshow/123338656.cms</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/political-row-over-contractors-alleged-suicide-in-maharashtra-over-govt-dues-3645889</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/we-respect-verdict-but-maharashtra-govt-will-challenge-it-in-sc-bjps-ram-kadam-on-2006-mumbai-train-blast-verdict20250722104649/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/jagdeep-dhankhad-could-have-behaved-like-bhairon-singh-shekhawat-but-he-failed-279009/amp/</t>
+          <t>https://www.zoomnews.in/en/news-detail/evm-tampering-sir-vote-theft-is-rahuls-conflict-with-ec-increasing-1.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/devendra-fadnavis-accuses-thackeray-of-political-manoeuvring-over-maharashtra-language-policy-debate-1456352.html</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%B5%E0%A4%B9-%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%87%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4-%E0%A4%AE-%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%87%E0%A4%82%E0%A4%A1-%E0%A4%AF-%E0%A4%AC%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%AC%E0%A5%88%E0%A4%A0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4%E0%A4%82%E0%A4%9C/ar-AA1K9Ujk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-doubtful-voters-made-rahul-gandhi-win-raebareli-2025-08-13-1155872</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharastra-government-stand-on-issue-of-kunbi-certificates-for-relatives-zws-70-5242573/</t>
+          <t>http://www.msn.com/hi-in/news/other/160-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%9F%E0%A4%B2%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%AF-%E0%A4%A6/ar-AA1KcU3e?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/25/girish-mahajan-exposes-the-opposition-in-the-honeytrap-case.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-india-block-s-show-of-strength-will-march-to-the-election-commission-office-under-led-of-rahul-gandhi-2025-08-11-1155278</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-pune-nagpur-news-live-21-july-2025-mumbai-local-train-blast-case-result-heavy-rain-alert-pune-accident-breaking-news-css-98-5242944/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-march-on-vote-theft-could-rahul-gandhi-become-in-charge-2025-08-11-1155436</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/28/union-railway-minister-reviews-indias-leap-in-railway-equipment-exports.html</t>
+          <t>https://www.indiatv.in/video/kurukshetra/will-the-election-commission-take-rahul-gandhi-to-court-over-vote-theft-allegations-2025-08-12-1155626</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mangal-prabhat-lodha/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/no-conflict-between-marathi-and-hindi-maharashtra-cm-at-jnu/articleshow/122888438.cms</t>
+          <t>https://bharatexpress.com/india/independence-day-2025-rahul-gandhi-congratulated-on-79th-independence-day-said-it-is-the-duty-of-all-of-us-to-protect-the-pride-and-honor-of-the-precious-heritage-551556</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/the-many-controversies-of-maharashtra-minister-manikrao-kokate-who-played-rummy-in-assembly-8947460</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A%E0%A5%87-5-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%A6-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B3-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1K51qk</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/who-is-manikrao-kokate-maharashtra-minister-facing-heat-over-viral-rummy-video-and-8930220</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-first-side-every-claim-of-rahul-gandhi-is-unacceptable-shehzad-poonawala-amy-95-5297251/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/activist-damania-visits-dance-bar-demands-resignation-of-shiv-sena-minister-yogesh-kadam-101753298667619.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-criticizes-india-aghadi-and-uddhav-thackerays-protest/910941/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-devotees-hold-march-to-keep-elephant-in-nandani-village-of-dist/articleshow/122910608.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-should-have-experimented-with-them-both-hasan-mushrif-counterattack-also-criticizes-rahul-gandhi-1376392</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/states/maharashtra/rummy-video-controversy-maharashtra-minister-kokate-vows-legal-action-against-defamation-1789613</t>
+          <t>https://www.loksatta.com/desh-videsh/minta-devi-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%BE%E0%A4%9D%E0%A4%BE-%E0%A4%AB%E0%A5%8B%E0%A4%9F-5300887/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-ministers-of-the-mahayuti-government-are-causing-the-fadnavis-government-embarrassment-8953383</t>
+          <t>https://www.loksatta.com/desh-videsh/i-had-the-experience-of-having-tea-with-dead-people-rahul-gandhi-criticizes-election-commission-by-sharing-video-gkt-96-5302274/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/manikrao-kokate-refers-maharashtra-govt-beggar-triggers-new-row-after-rummy-playing-video/articleshow/122846731.cms</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5297490/india-alliance-parliament-protest-rahul-gandhi-election-commission-photos-viral-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/07/21/419098/bharat/maharashtra/mumbai-local-train-blasts-case-bombay-high-court-verdict-cm-devendra-fadnavis-says-we-will-challenge-it-in-the-supreme-court/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/karnataka-supporters-protest-after-rajannas-ouster-doubts-were-cast-on-rahul-gandhis-claim-of-vote-rigging.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/07/22/419349/bharat/maharashtra/mumbai-local-train-blast-case-maharashtra-government-challenges-bombay-hc-decision-in-supreme-court/</t>
+          <t>https://www.loksatta.com/politics/bjp-says-sonia-gandhis-name-added-to-voter-list-list-before-indian-citizenship-sdp-92-5301499/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mns-chief-raj-thackeray-visits-matoshree-after-years-on-cousin-uddhav-thackerays-birthday-calls-him-shiv-sena-chief/articleshow/122940360.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/not-uddhav-or-raj-eknath-shinde-is-true-torchbearer-of-bal-thackerays-legacy-sanjay-nirupam-3640736</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/rahul-gandhi-the-king-of-fake-news-keshav-upadhyays-criticism.html</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/27072025/uddhav-thackeray/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/rahul-gandhi-claims-life-threat-in-pune-court-over-voter-fraud-issue-vvg94</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-maharashtra-politics-shiv-sena-ubt-mp-in-touch-with-bjp-claims-girish-mahajan-23989915.html</t>
+          <t>https://www.loksatta.com/navimumbai/in-uran-maritime-conference-cm-fadnavis-on-jnpa-and-port-of-singapore-to-build-indias-largest-port-rds-00-5299525/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/07/support-is-necessary-in-the-fight-for-marathi-manus-said-uddhav-thackeray-on-his-friendship-with-mns-chief-raj-thackeray/</t>
+          <t>https://www.loksatta.com/desh-videsh/anurag-thakur-criticizes-bjp-over-vote-rigging-issue-amy-95-5302546/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nanded-bus-stop-public-toilet-operater-assaulted-by-mns-workers-apologise-to-raj-thackeray/articleshow/122870437.cms</t>
+          <t>https://www.loksatta.com/business/finance/nobel-laureate-abhijit-on-trump-50-per-cent-tariff-us-trade-does-russian-oil-import-worth-it-marathi-news-rak-94-5295923/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/uddhav-thackeray-is-now-seen-trying-to-persuade-devendra-fadnavis-as-he-is-not-able-to-form-an-alliance-with-raj-thackeray-in-marathi/904447/</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5295848/monsoon-tips-for-immunity-these-10-best-fruits-to-stay-healthy-and-energised-svk-05/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-government-issues-social-media-guidelines-for-officials-disciplinary-action-if-rules-violated-know-all/articleshow/122958889.cms</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5296622/how-to-beat-afternoon-sleepiness-and-boost-energy-with-simple-breathing-exercises-instead-of-coffee-svk-05/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-thackeray-praise-sharad-pawar-278805/amp/</t>
+          <t>https://www.loksatta.com/desh-videsh/bihar-list-of-voters-dispute-big-deabte-in-supreme-court-what-sc-said-and-what-kapil-sibbal-claims-scj-81-5298737/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-asks-bjp-mlas-about-impact-of-raj-and-uddhav-thackeray-coming-together/articleshow/122838925.cms</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5299053/liver-damage-symptoms-on-feet-liver-failure-signs-on-body-solution-expert-advice-dvr-99/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/thackeray-group-denounced-governor-cp-radhakrishnans-stance-on-marathi-hindi-dispute/904780/</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5297669/5-biggest-gold-mines-in-india-kolar-hutti-sonbhadra-ramagiri-gold-field-know-the-details-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/uddhav-thackeray-mlas-mps-bjp-contact-girish-mahajan-279161/amp/</t>
+          <t>https://www.loksatta.com/photos/picture-gallery-others/5298318/how-did-the-netherlands-end-the-problem-of-stray-dogs-what-measures-takern-for-stray-dogs-in-indian-cities-including-mumbai-aam-93/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-slams-manikrao-kokate-and-devendra-fadanvis/</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5298525/mumbai-ganpati-bappa-maha-aagman-sohala-sunday-10-august-2025-lalbaug-parel-photos-sdn-96/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-critized-cm-devendra-fadnavis-over-agriculture-minister-manikrao-kokate/</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5298218/surya-gochar-in-singh-rashi-leo-virgo-and-aquarius-will-get-new-job-and-success-in-business-sap-20/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/chandrashekhar-bawankule-slams-sanjay-raut-over-remarks-against-pm-modi-issues-strong-warning-article-152324507</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5302433/ncp-has-entrusted-suraj-chavan-with-a-big-responsibility-appointed-as-ncps-regional-general-secretary-gkt-96/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-opposed-by-sfi-organization-in-delhi-jnu-university-marathi-hindi-controversy-033327.html</t>
+          <t>https://www.loksatta.com/photos/news/5302284/dhananjay-munde-government-bungalow-row-karuna-munde-slams-says-he-have-many-flats-in-mumbai-kvg-85/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/uddhav-raj-bonhomie-inside-the-thackeray-cousins-political-reset-before-bmc-polls-desperate-photo-op-or-strategic-comeback/articleshow/122934141.cms</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5301397/mukesh-ambanis-wealth-on-twelth-of-indias-gdp-check-indias-top-10-wealthiest-families-kvg-85/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/not-right-to-cast-doubt-on-vp-dhankhars-resignation-bjp-leader-bawankule-3641964</t>
+          <t>https://www.loksatta.com/thane/jitendra-awhad-sharad-pawar-ncp-protest-against-election-commission-in-mumbra-css-98-5299492/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/22/bes19-mh-modi-fadnavis.html</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5302315/these-special-bollywood-movies-still-rule-the-hearts-of-the-people-today-how-many-of-these-have-you-seen-scj-81/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-claims-4-maharashtra-ministers-honey-trapped-bjp-asks-for-proof-3640638</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5302393/jui-gadkari-shares-his-bond-with-madhubhau-aka-narayan-jadhav-in-serial-and-real-life-ssm-00/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/maha-congress-leader-alleges-honey-trap-linked-praful-lodha-made-rs-200-crore-1503461560.html/amp</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5299829/maharashtrachi-hasyajatra-fame-nimish-kulkarni-also-part-of-chala-hawa-yeu-dya-2-with-gaurav-more-ssm-00/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/self-redevelopment-becoming-people-led-movement-in-maharashtra-bjp-leader-pravin-darekar</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nandurbar/padmakar-valvi-to-join-ajit-pawar-led-ncp-after-leaving-bjp-congress-in-nandurbar/articleshow/123273982.cms</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/article/comparing-devendra-fadnavis-with-sharad-pawar-is-not-his-real-praise-278952/amp/</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5293131/hsrp-number-plate-deadline-and-fine-only-a-few-days-left-to-install-hsrp-number-plates-otherwise-you-will-have-to-pay-a-heavy-fine-gkt-96/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/congress-leader-set-to-join-bjp-shocking-turn-of-events-in-state-politics-source-8950091</t>
+          <t>https://maharashtramirror.com/rahul-gandhi-clashes-in-delhi-over-ghost-in-voter-list-opposition-mps-including-rahul-gandhi-akhilesh-yadav-arrested/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/congress-leader-kailas-gorantyal-may-join-bjp-big-blow-in-marathwada-8947644</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis/ar-AA1KrS1p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/22/des3-up-cm-fadnavis.html</t>
+          <t>https://www.ndtv.com/india-news/mumbai-pigeons-kabootarkhanas-mumbais-pigeon-feeding-ban-how-a-public-health-move-clashed-with-faith-9077531</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://digitallearning.eletsonline.com/2025/07/maharashtra-government-collaborates-with-iit-bombay/</t>
+          <t>http://www.msn.com/en-in/news/India/karnataka-netas-unite-to-oppose-fadnavis-over-almatti-height/ar-AA1GbrxF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.onmanorama.com/news/kerala/2025/07/21/kerala-foreign-aid-dispute-maharshtra-who-is-lying-why.html</t>
+          <t>https://punemirror.com/city/pcmc/pune-news-illegal-construction-on-pavana-river-flood-line-sparks-controversy/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
+          <t>https://www.devdiscourse.com/article/law-order/3541769-meat-ban-controversy-on-independence-day-ignites-debate-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/7/29/divya-has-made-india-proud-cm-fadnavis-.html</t>
+          <t>https://www.newsbytesapp.com/news/politics/maharashtra-federation-demands-national-meat-sale-calendar-amid-non-veg-row/story</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-challenges-acquittal-of-2006-mumbai-train-blasts-accused-in-supreme-court-101753162247494.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE-%E0%A4%9F-%E0%A4%95-%E0%A4%A6%E0%A5%81%E0%A4%95-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%87%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%A8-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%9A-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Ksgnw</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+          <t>https://hindi.newsbytesapp.com/news/india/maharashtra-meat-ban-on-independence-day-whats-the-controversy/story</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-signs-mou-with-iit-bombay-for-cm-fellowship-2025-26-4690</t>
+          <t>https://hindi.news18.com/amp/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/working-on-plan-to-make-maharashtras-health-care-system-best-in-country-in-4-years-fadnavis/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/jain-muni-nileshchandra-threatens-for-hunger-strike-from-august-13-against-closure-of-the-kabutarkhana-in-mumbai-bombay-high-court-know-all/articleshow/123229693.cms</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.prameyanews.com/maharashtra-government-on-collision-course-with-judiciary-over-acquittal-of-2006-mumbai-blasts-suspects</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%97-%E0%A4%B2-%E0%A4%9F-%E0%A4%AA-%E0%A4%A6-%E0%A4%A2%E0%A4%BC-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%B9%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AC%E0%A4%AF-%E0%A4%A8/ar-AA1IpDnk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/25/maharashtra-government-to-provide-identity-cards-insurance-for-sarpamitras/</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/shiv-sena-tensions-flare-over-raigad-nashik-flag-hoisting-guardian-minister-dispute-ntcpmm-dskc-2308822-2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/25/bom19-mh-ncp-sp-kokate.html</t>
+          <t>https://www.hindisaamana.com/cold-war-on-guardian-minister-controversy-shinde-stays-away-from-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.indiatodaygaming.com/news/story/maharashtra-government-to-submit-proposal-to-centre-for-online-gaming-ban-10173</t>
+          <t>https://www.theindiadaily.com/india/there-is-uproar-in-maharashtra-over-meat-ban-opposition-opened-front-warned-of-protest-outside-kdmc-office-news-89830</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-targets-50-lakh-homes-in-10-years-under-new-housing-policy-2025-aims-for-slum-free-state</t>
+          <t>https://www.hindisaamana.com/political-temperature-rises-in-mahayuti-dissatisfaction-rising-in-shinde-faction/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/dahi-handi-2025-festival-maharashtra-government-announces-insurance-coverage-to-1-5-lakh-govindas-payout-of-inr-10-lakh-for-fatality-7017720.html</t>
+          <t>https://bharatexpress.com/legal/supreme-court-hearing-on-elephant-mahadevi-transfer-to-vantara-jamnagar-controversy-549836</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.sportstiger.com/news/no-need-to-panic-maharashtras-gaming-ban-is-for-real-money-games-not-skill-based-titles-like-bgmi</t>
+          <t>https://www.travelandleisureasia.com/in/news/nagpur-pune-vande-bharat-express-becomes-longest-in-india/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-government-to-launch-app-based-transport-service-to-compete-with-ola-uber/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pm-flags-off-nagpur-pune-vande-bharat-cm-attends-nagpur-launch-101754853627589.html</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-directs-to-form-a-committee-for-the-use-of-solar-energy-in-the-textile-sector-85522</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ngp-pune-vande-bharat-oversubscribed-waiting-list-crosses-150-for-sunday-journey/articleshow/123339056.cms</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-fellowship-maharashtra-fellows-will-receive-training-from-iit-mumbai-know-detail-marathi-news-1371491</t>
+          <t>https://www.newsonair.gov.in/pm-narendra-modi-flags-off-three-vande-bharat-trains-from-ksr-railway-station-in-bengaluru/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/cm-devendra-fadnavis-had-to-react-to-manikrao-kokate-controversial-statements-for-second-consecutive-day-what-will-happen-with-agriculture-minister-now-3192511-2025-07-22</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/jarange-slams-fadnavis-govt-over-dhananjay-mundes-possible-return-to-cabinet-amid-murder-case-probe-85365</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/14/palak-excels-as-nagpur-eves-get-better-of-thane.html</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-claims-urban-maoists-active-again-in-kolkata-bengaluru-and-other-places/articleshow/122847447.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/maharashtra-govt-singapore-partner-for-350-bedded-multi-speciality-hospital-in-city.html</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-23-july-2025-marathi-news-live-maharashtra-weather-update-honey-trap-case-kalyan-hospital-receptionist-case-updates-mumbai-rain/liveblog/122849150.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/rtmnu-to-shift-examination-deptt-to-maharajbag-campus.html</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-pierced-minister-manikrao-kokate-ears-over-that-statement/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/shriram-urban-cooperative-bank-posts-net-profit-of-rs-12995-lakh-.html</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/the-central-government-clarified-that-the-three-language-formula-will-remain-and-it-is-the-states-decision-which-language-to-teach/904157/</t>
+          <t>https://marathi.ndtv.com/maharashtra/nagpur-pune-vande-bharat-express-timings-route-stops-ticket-price-train-number-schedule-and-more-9062515</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/mumbai-local-serial-blast-maharashtra-govt-challenges-acquittal-in-supreme-court/</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-new-railway-route-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0-100-%E0%A4%95-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%9A-%E0%A4%B6-%E0%A4%AB-%E0%A4%B0%E0%A4%B8/ar-AA1KfxgY</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ajit-pawar-reaction-on-minister-manikrao-kokate-video-and-controversial-statement/articleshow/122881032.cms</t>
+          <t>https://www.loksatta.com/mumbai/mumbai-pune-nagpur-news-live-11-august-kabutar-khana-dadar-latest-news-pune-st-bus-metro-breaking-news-sud-02-5295305/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-will-not-stop-now-maharashtra-is-a-leader-in-all-important-economic-sectors-chief-minister-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-nagpur-high-speed-rail-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A4%E0%A5%87-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B5%E0%A4%98%E0%A5%8D%E0%A4%AF-2-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%A4-%E0%A4%96%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1KmwMT</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-we-will-create-the-best-healthcare-system-in-the-country-in-maharashtra-in-the-next-four-years-chief/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-live-updates-political-crime-sports-national-international-breaking-news-955926.html</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/kokate-directly-calling-the-government-a-beggar-chief-minister-devendra-fadnavis-angry/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/st-receives-record-income-of-rs-137-crore-in-four-days-from-beloved-sisters-information-from-transport-ministe.html</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-felicitate-world-chess-champion-divya-deshmukh-125072900019_1.html</t>
+          <t>https://trak.in/stories/3rd-mumbai-being-developed-by-govt-says-maharashtra-cm/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/through-e-governance-all-government-services-will-now-be-available-at-one-place-chief-minister-devendra-fadnavis/</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/photo/fadnavis-made-a-big-announcement-about-dharavi-it-will-be-built-like-a-new-city-1550</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-professor-recruitment-2025/</t>
+          <t>https://marathi.ndtv.com/cities/ajit-pawar-on-dharavi-redevelopment-project-in-bdd-mhada-home-distribution-9083170</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/ganpati-2025-court-allows-immersion-of-large-ganesh-idols-in-the-sea-for-public-ganesh-celebrations/127078/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/drps-big-scheme-for-businessmen-in-dharavi-drppl-nmdpl-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/parliament-monsoon-session-2025-live-updates-maharashtra-politics-mumbai-pune-rain-news-crime-accident-local-headline-8921099</t>
+          <t>https://www.msn.com/en-in/news/India/ensure-timely-completion-of-5-000-mw-solar-agri-feeder-scheme-by-sep-2025-fadnavis/ar-AA1JA6xO</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/parliament-monsoon-session-2025-operation-sindoor-ahmedabad-plane-crash-8-new-bils-govt-vs-opposition-8914450</t>
+          <t>https://m.economictimes.com/news/india/pm-modis-independence-day-speeches-highlights-a-look-back-from-2025-to-2014/2025-the-era-of-self-reliant-bharat-103-minutes/slideshow/123319643.cms</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-add-main-events-date-28-july-943158.html</t>
+          <t>https://economictimes.indiatimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/213322/</t>
+          <t>https://www.mypunepulse.com/pune-pmc-dismantles-traffic-circle-at-sm-ghule-chowk-in-mohamadwadi-after-residents-protest/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hinjewadi-or-ten-hot-spots-of-traffic-congestion-in-it-park-joint-inspection-by-police-commissioner-and-it-staff/</t>
+          <t>https://www.msn.com/en-in/news/India/fadnavis-says-maharashtra-has-access-to-top-global-tech-to-fight-cybercrime/ar-AA1KhsyI</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/disturbing-that-pms-i-day-speech-didnt-have-nehrus-mention-pawar/articleshow/123339182.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>https://newsarenaindia.com/states/sharad-pawar-slams-pm-modi-for-ignoring-nehru-in-i-day-speech/53504</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis-9652523</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/hi-in/news/other/devendra-fadnavis-on-sharad-pawar-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%A6%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1KdfSS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/list-of-spokespersons-of-ncp-sharad-pawar-group-announced-mumbai-print-news-css-98-5299884/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-thackeray-group-called-him-a-thief-minister-devendra-fadnavis-criticized-uddhav-thackeray-calling-him-a-mandate-thief/911143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/editorial/agralekha/the-revelation-made-by-sharad-pawar-is-likely-to-undermine-rahul-gandhis-efforts/911074/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-comment-on-manoj-jarange-patil-protest-for-maratha-reservation-in-mumbai-on-august-29-1470254.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-bhaskar-jadhav-comment-on-brahman-samaj-1376769</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-alleges-that-the-public-safety-act-is-meant-for-bunch-of-thought/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/can-you-get-reservation-by-criticizing-fadnavis-vikhe-patils-direct-question-97495/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/those-who-came-to-power-by-cutting-reds-teach-wisdom-rauts-target-97526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/politics/sharad-pawar-high-level-inquiry-by-election-commission-demand-by-bjp-mla-prashant-bamb-957164.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%88%E0%A4%B8-%E0%A4%91%E0%A4%AB-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%88-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/ar-AA1KkbZY</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/rohit-pawar-criticizes-on-savitribai-phule-pune-university-administration-on-the-issue-of-voice-of-devendra-1376510</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/parinay-fuke-criticized-on-manoj-jarange-patil-said-manoj-jarange-remote-is-in-sharad-pawar-hand-criticism-over-cm-devendra-fadnavis-maratha-reservation-1376608</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/pune/pune-news-maharashtra-will-have-to-face-a-maratha-vs-obc-conflict-warns-haake-a-a1008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/manoj-jaranges-remote-in-sharad-pawars-hands/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/sanjay-raut-slams-devendra-fadnavis-over-ban-on-meat-sales-on-august-15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>https://www.ainvest.com/news/ibm-maharashtra-collaborate-quantum-computing-initiatives-2508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/companies/news/ibm-mumbai-client-centre-maharashtra-quantum-initiative-support-125081301837_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>https://www.itvoice.in/ibm-unveils-new-india-client-experience-centre-in-mumbai-and-announces-plans-to-support-government-of-maharashtras-quantum-initiatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/independence-day-at-red-fort-where-to-book-and-what-to-carry/event-timings/slideshow/123258257.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/raipur/chhattisgarh-cm-sai-flags-off-sbi-cyber-security-awareness-van-in-raipur-launches-statewide-drive-against-online-fraud/articleshow/123334545.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/maharashtra-politics-uddhav-thackeray-shivsena-bmc-elections-mns-shivena-ubt-raj-thackeray-bmc-elections-news-bjp-shivsena-ubt/4096856/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-alleges-vote-theft-holds-candle-march-protest-in-nagpur/articleshow/123312003.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/politicians-must-not-hate-any-community-while-ensuring-welfare-of-their-own-fadnavis/articleshow/123244376.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis/2719488/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/political-buzz-on-janmashtami-festivities-in-mumbai-ahead-of-local-body-polls-3683780</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/india/eknath-shinde-slams-uddhav-thackeray-amid-fadnavis-meet-buzz-changed-colours-like-a-chameleon/ar-AA1IS5La?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/mumbai-bahujan-vikas-aaghadi-bva-leaders-cross-over-to-bjp-mahesh-patil-among-new-joinees/ar-AA1KqIKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/ratnagiri-news-ncp-sharad-pawar-group-leader-prashant-yadav-join-bjp-9083531</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%86%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%95/ar-AA1KEzpJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/sharad-pawar-gets-a-setback-in-konkan-big-leader-joins-bjp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary-says-cji-gavai-3684747</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>https://indiplomacy.com/2025/08/15/singapore-deepens-infrastructure-ties-in-maharashtra-with-major-investments/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/versova-bandra-sea-link-on-track-for-two-year-completion-maha-cm/123321974</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/submit-proposal-to-convert-circuit-bench-in-kolhapur-into-permanent-bench-cji-bhushan-gavai-to-hc/articleshow/123349240.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/autos/news/2025-maharashtra-ev-policy-gets-green-signal-subsidies-to-toll-waiver-everything-you-must-know/ar-AA1DTk4A?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/17/lokmat-global-economic-convention-to-be-held-on-august-18-in-london.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>https://propnewstime.com/getdetailsStories/MjAzNDk=/maharashtra-must-fix-tendering-to-speed-up-infrastructure-work-cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment/2812408</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/business/3538840-maharashtras-digital-leap-rapid-growth-in-data-and-infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/08/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/law-order/3544738-maharashtras-commitment-to-judiciary-kolhapur-gets-a-new-bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/will-the-political-power-of-farmers-survive-article-on-agrowon-rat16</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/video/meet-sanjay-india-s-robotic-war-dog-are-robodogs-the-future-of-warfare-978929</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bes21-mp-vote-theft-campaign-cong.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/wayanad-voters-refute-anurag-singh-thakurs-fraud-claims/articleshow/123311455.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/des117-hr-rahul-saini.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/119-voters-from-one-single-house-cong-alleges-vote-theft-in-chandrapur/articleshow/123312033.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/ec-acting-like-bjp-agent-hebbalkar/articleshow/123325268.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/119-voters-in-one-house-cong-alleges-vote-theft/articleshow/123310094.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-maharashtra-cm-prithviraj-chavan-backs-stir-over-alleged-bogus-voting-in-karad-south-during-2024-assembly-polls/articleshow/123311995.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>https://humenglish.com/world/vote-chori-protest-rahul-gandhi-arrested-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/sonia-gandhi-was-a-voter-before-becoming-an-indian-citizen-bjp-alleges-that-it-is-congresss-voter-scam.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/video/political-turmoil-in-maharashtra-uddhavs-public-outrage-questions-over-dhanakar-the-dove-seed-controversy-ytvd-2308283-2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/news/national-debate-erupts-over-closing-meat-shops-in-maharashtra-on-independence-day-24012549.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-slams-mahayuti-govt-signals-bmc-shakeup-4214626</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/vice-president-election-2025-pm-modi-gives-big-joy-to-rss-by-nominating-cp-radhakrishnan-ahead-of-100-years-celebration-know-all/articleshow/123377347.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes/ar-AA1Kyjju</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/idontknowhomeminister-goes-viral-g-parameshwara-tells-trolls-to-find-out-who-is-the-best/articleshow/123338015.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-maratha-royal-raghuji-bhonsle-returns-home-on-aug-18-after-200-years/articleshow/123244523.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/raipur/bastar-kids-visit-city-from-remote-areas-on-edu-expedition/articleshow/123289148.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-says-govt-will-take-steps-to-increase-number-of-loudspeaker-days-for-ganeshotsav/articleshow/123284079.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/we-missed-the-bus-earlier-no-compromise-on-mumbais-development-now-fadnavis/ar-AA1KxlQf</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/seat-sharing-formula-for-mumbai-civic-election-will-depend-on-party-strength-says-cm-fadnavis/articleshow/123288144.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-orders-partial-rollback-of-ban-on-feeding-pigeons/ar-AA1JYREe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year-101755112441600.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/museum-to-honour-dabbawalas-to-be-inaugurated-in-mumbai-3677005</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>https://www.businessworld.in/article/ibm-opens-new-mumbai-office-as-gateway-to-viksit-bharat-567381</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/Maharashtra-prominent-player-in-Indian%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/business/as-chawl-residents-move-into-modern-homes-fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/record-10-tier-human-pyramids-lend-thrill-to-mumbais-rainy-dahi-handi-in-poll-year/articleshow/123337445.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-gives-go-ahead-for-recruiment-of-over-15000-constables/articleshow/123261279.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/mumbai-gets-5-km-sea-facing-promenade-coastal-road-to-stay-open-24x7/ar-AA1Kxl74</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>https://www.businessworld.in/article/fadnavis-singapore-leaders-review-phase-2-of-bharat-mumbai-container-terminal-567159</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-13-news-updates-live-updates-weather-update-mumbai-monsoon-18331383</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cabinet-recruitment-police-10184591/lite/</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day20250815151854</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/16/mumbai-worli-parivartan-dahi-handi-gallery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>https://indiacsr.in/national-stem-challenge-grand-finale-set-for-august-18-19-in-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%95%E0%A4%AC%E0%A5%82%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%A8-%E0%A4%AF%E0%A4%AE-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JYvBC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/the-dream-of-mumbai-within-59-minutes-will-be-soon-filfilled-cm-devendra-fadnavis-9089297</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/entertainment/actor-kishor-kadam-appeals-to-cm-devendra-fadnavis-to-save-mumbai-residence-details-9065124</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-on-plan-of-slum-free-mumbai-89066</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-bdd-says-houses-in-mumbai-are-worth-as-much-as-gold-do-not-sell-houses-remember-you-want-to-pass-this-house-on-to-the-next-generation-1377083</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/web-stories/news/flag-hoisting-on-the-occasion-of-independence-at-high-cout-with-the-presence-of-cm-devendra-fadnavis-1377273</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-12-hour-electricity-for-farmers-in-the-state-and-steel-hub-in-gadchiroli-chief-minister-assures-on-independence-day-in-mumbai-1377256</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-announces-that-coastal-road-will-be-open-24-hours-from-august-15/912175/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sclr-to-weh-connector-chembur-to-mumbai-airport-cable-bridge-inaugurated-by-devendra-fadnavis/articleshow/123317604.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/politics/we-broke-the-pot-of-sin-in-mumbai-municipal-corporation-fadnavis-taunts-thackeray-961442.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/aaditya-thackeray-welcome-cm-devendra-fadnavis-in-mumbai-maharashtra-politics-news-1457232.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/worli-bdd-chawl-redevelopment-program-keys-distribution-cm-devendra-fadnavis-speech-today-1469211.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/editorial/editorial-on-pune-municipal-corporation-issue-cm-devendra-fadnavis-ajit-pawar/articleshow/123227690.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-big-statement-on-slaughter-houses-closed-on-independence-day/articleshow/123293008.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/the-flag-hoisting-will-be-done-by-fadnavis-in-mumbai-and-radhakrishnan-in-pune-15226401</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/india/mumbai-to-receive-several-projects-ahead-of-bmc-elections-metro-3-phase-3-likely-to-be-launched-by-end-of-august-ask-chatgpt-2726817.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis-4212867</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/newly-built-capitaland-data-centre-in-mumbai-will-put-india-ahead-in-digital-revolution-fadnavis-4210177</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/mumbai/cm-fadnavis-said-dream-of-mumbai-within-59-minutes-will-soon-be-fulfilled/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>https://joindia.co.in/news/mumbais-development-gets-new-momentum-many-big-projects-of-mmrda-inaugurated-coastal-road-will-be-open-24-hours-from-august-15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-rapid-redevelopment-is-needed-for-a-slum-free-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/flag-hoisting-flag-hoisting-ceremony-completed-in-mumbai-thane-and-beed-by-the-chief-minister-and-deputy-chief-minister/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-gets-emotional-after-seeing-the-encampment-on-dahihandi-tower/129236/</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/politics-in-the-dahi-handi-festival-in-mumbai-fadnavis-hints-at-change/129241/</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/cm-devendra-fadnavis-chief-minister-devendra-fadnavis-should-not-be-influenced-by-my-voice-manoj-jarange-patil/128997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/mumbai-dabbawalas-to-get-500-sq-ft-homes-at-%E2%82%B925-50-lakh-cm-devendra-fadnavis-announce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/cji-gavai-inaugurates-bombay-hcs-4th-bench-in-kolhapur/amp_articleshow/123345149.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/i-day-navroz-and-janmashtami-bring-cheer-to-festive-weekend/articleshow/123309219.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/delhi/new-delhi-weather-alert-rainfall-humidity-and-a-cooler-day-ahead-on-august-15-2025/articleshow/123314541.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/ranchi/school-celebrates-dahi-handi-event/articleshow/123350561.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/committee-seeks-deputation-of-physical-education-teachers-to-rural-schools-twice-a-week/articleshow/123325270.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/en/india-singapore-green-digital-maritime-corridor-takes-center-stage-at-mumbai-dialogue-ahead-of-india-maritime-week-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/kolkata-weather-forecast-patchy-rain-and-humidity-expected-on-august-15-2025/articleshow/123314563.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>https://hindi.newsdanka.com/business/india-maritime-week-2025-preparations-green-digital-corridors/111129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/maratha-leader-manoj-jarange-patil-aggressive-for-mumbai-march/articleshow/123323428.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/marathwada/latur/latur-news-chief-minister-knows-about-art-he-stopped-a-convoy-of-vehicles-and-met-a-young-child-artist-ar84</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://www.constructionweekonline.in/business/sukhraj-nahar-becomes-credai-mchi-president</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://indiacsr.in/welspun-living-cultivating-community-value-through-strategic-csr-initiatives/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nashik/970-nashik-district-women-voluntarily-opt-out-of-ladki-bahin-scheme/articleshow/123266291.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/pawar-defends-scrutiny-of-ladki-bahin-scheme-beneficiaries/articleshow/123308892.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/state/maharashtra-governor-governor-c-p-radhakrishnan-greets-people-on-independence-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B0-%E0%A4%9D%E0%A4%A8-%E0%A4%91%E0%A4%A8-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F-%E0%A4%A1-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%A7-%E0%A4%B9-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%86%E0%A4%B3%E0%A4%82%E0%A4%A6-%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1KAarj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%A7-%E0%A4%B2-26-34-%E0%A4%B2-%E0%A4%96-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%85%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1JoWkD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2-%E0%A4%91%E0%A4%97%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%A7-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%B2-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1KrMRe</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/mukhyamantri-ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%AA-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KuMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bom26-mh-2ndld-meat-ban.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3538927-political-strife-over-maratha-quota-intensifies-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3538922-clashes-over-maratha-quota-a-political-tug-of-war</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-pigeon-feeding-dispute-jain-community-vs-marathi-integration-committee-tense-protests-police-detain-hundreds/articleshow/123294170.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://www.pratahkal.com/Encyc/2025/8/12/big-action-by-rpf-grp-big-secret-of-theft-exposed.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://www.hindisaamana.com/rokhthok-conspiracy-to-make-maharashtra-vegetarian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://www.amnesty.org/en/latest/research/2025/08/open-letter-to-government-of-maharashtra-withhold-assent-maharashtra-special-public-security-bill/</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/truce-talks-us-china-agree-to-extend-their-tariff-truce-for-another-90-days/julyaugust-developments/slideshow/123250425.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/the-eyes-that-saw-independence-day-1947/articleshow/123312887.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/concord-biotech-sai-life-sciences-among-9-stocks-that-closed-above-vwap-on-august-11/trend-watch/slideshow/123248478.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/bhiwani-woman-teacher-murder-triggers-protests-villagers-block-delhipilani-road-demand-arrests/articleshow/123345021.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/golden-crossovers-metropolis-healthcare-dixon-tech-among-5-stocks-signal-further-bullishness-on-august-12/bullish-breakout/slideshow/123248692.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/new-updates/kalyan-dombivli-meat-shop-ban-on-independence-day-sparks-political-row-kdmc-official-says-its-a-routine-order-since-1988/articleshow/123220004.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/wealth/save/ppf-sukanya-samriddhi-yojana-new-rules-you-must-know/closing-a-sukanya-samriddhi-account-before-maturity/slideshow/123233624.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/treasury-yields-dip-ahead-of-key-inflation-data/treasury-yields-ease-before-inflation-data/slideshow/123251840.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/max-financial-titan-among-8-stocks-showing-rsi-trending-up-on-august-8/saregama-india/slideshow/123226556.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/pb-fintech-supreme-industries-among-11-stocks-with-white-marubozu-pattern-on-august-11/adani-enterprises/slideshow/123249237.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/14/bom5-mh-meat-ban-security.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/pune/anna-hazares-stir-sparks-debate-again-banners-demanding-action-appear-in-pune/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-political-row-erupts-at-savitribai-phule-pune-university-over-voice-of-devendra-elocution-competition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-lokmanya-nagar-redevelopment-hits-impasse-residents-blame-political-meddling/</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/videos/why-did-mutton-politics-happen-on-15th-august-in-maharashtra-aimim-ncp-organized-a-non-veg-party-981146</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-eknath-shinde-aditya-thackeray-on-one-stage-sa-9506059.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/meat-sale-banned-on-aug-15-security-tightened-in-kalyan/855124/</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/dahi-handi-event-organized-by-bjp-leaders-in-mumbai-municipal-elections-operation-sindoor-are-the-topics/856127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>https://apnnews.in/top-news/eknath-shinde-faction-minister-bharat-gogawale-angry-he-will-stay-away-from-cabinet-meeting/</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>https://indiplomacy.com/2025/08/13/maharashtra-and-singapore-strengthen-maritime-and-industrial-ties-with-landmark-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/woman-accuses-ex-husband-of-sharing-intimate-pics-to-ruin-engagement/articleshow/123309891.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-to-celebrate-independence-day-with-social-initiatives-and-community-engagement/articleshow/123312038.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/goa/war-on-cyber-cons-goa-police-to-use-memes-reels/articleshow/123311003.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ganesh-mandals-in-mumbai-seek-abolition-of-rs-2000-penalty-for-digging-public-roads/articleshow/123302643.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/top-news/maharashtra-police-bharti-2025-approval-for-15000-police-recruitment-in-maharashtra-cm-fadnavis-takes-4-big-decisions-88282</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/pune-residents-experienced-the-thrill-of-punit-balan-groups-joint-dj-mukta-dahihandi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>https://www.punjabnewsexpress.com/punjab/news/union-home-minister-amit-shah-to-participate-in-the-350th-martyrdom-anniversary-celebrations-of-sri-guru-tegh-bahadur-sa-294387</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>https://thelivenagpur.com/2025/08/11/khan-academy-and-maharashtra-government-to-empower-62000-schools-with-free-digital-tools/</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>https://globalprimenews.com/2025/08/14/capitaland-investment-signs-landmark-mou-with-maharashtra-government/</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>https://thelivenagpur.com/2025/08/11/historic-sword-of-raghuji-bhosale-secured-by-maharashtra-government-in-london/</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bom19-mh-meat-ban-fadnavis.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>https://indiacsr.in/national-stem-challenge-2025-central-zone-winners-announced/</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/maharashtra-singapore-investment-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%B6-3-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%81%E0%A4%82%E0%A4%A4%E0%A4%B5%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B0/ar-AA1Kq8BL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-on-devendra-fadnavis-says-government-came-to-power-by-cutting-water-buffalo-at-kamakhya-temple-and-even-ate-it-as-prasad-and-fadnavis-says-become-a-vegetarian-stop-this-nonsense-1376830</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-bharti-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B5%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%AA-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B7-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%81%E0%A4%A6-%E0%A4%A6%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1Ks1KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-fadnavis-government-has-increased-ration-shopkeepers-margin-amount-20-rupee-88298</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/free-digital-learning-%E0%A4%96-%E0%A4%A8-%E0%A4%85%E0%A4%95%E0%A5%85%E0%A4%A1%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3/ar-AA1KCLdZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/devendra-fadnavis-dahi-handi-speech-maharashtra-politics-on-bmc-elections-news-on-agrowon-ssp-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-decision-devendra-fadnavis-home-ministry-15-thousand-police-recruitment/articleshow/123252638.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-recruitment-%E0%A4%A4%E0%A4%B0%E0%A5%81%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B2-%E0%A4%B2-%E0%A4%97-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A5%A7%E0%A5%AB-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Km5x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-independence-day-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news/912247/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-14-august-2025-eknath-shinde-aditya-thackeray-bdd-chawl-mumbai-devendra-fadnavis-ajit-pawar-arjun-tendulkar-maharashtra-weather-today-mumbai-rain-shivsena-ubt-mns-alliance-1376992</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/big-decision-in-cabinet-on-state-police-state-to-soon-recruit-14000-posts-maharashtra-police-recruitment-2025-1467605.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>https://globalprimenews.com/2025/08/14/credai-mchi-change-of-guard-2025-ceremony-in-presence-of-honorable-cm-of-maharashtra-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/singapore-should-cooperate-for-development-by-adding-a-new-dimension-to-maritime-cooperation-between-maharasht.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/states-progress-in-agriculture-and-energy-sectors-rat16</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/there-will-be-a-capitaland-data-center-in-navi-mumbai-an-investment-of-rs-19200-crores-will-come-and-the-economy-will-benefit-maharashtra-news-mhs25081301777</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-disha-abhiyan-unprecedented-changes-in-education-for-students-with-intellectual-disabilities/articleshow/123230486.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/santosh-juvekar-thankful-to-ashish-shelar-for-bringing-back-raghuji-bhosale-sword-in-india/articleshow/123270658.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/cabinet-decisions-jumbo-police-recruitment-in-maharashtra-fadnavis-government-gives-green-light-to-fill-15-thousand-posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-approves-recruitment-of-15000-police-in-state-article-152450966</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/i-feel-jealous-of-devendra-fadnavis-uddhav-thackerays-attack-on-fadnavis/128759/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/chandrashekhar-bawankule-on-uddhav-thackeray-thackerays-criticism-of-fadnavis-bawankules-attack-on-thackeray/128784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/maharashtra-police-recruitment-2025-15000-vacancies-with-special-age-relaxation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>https://news34.in/2025/08/chandrapur-development-schemes-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-f-21/911866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B6-%E0%A4%95%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%86%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%A8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%A6%E0%A5%81%E0%A4%96-%E0%A4%B5-%E0%A4%A2%E0%A4%B2/ar-AA1Ksebj</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A6-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97-%E0%A4%B1%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AE-%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B8-%E0%A4%A7%E0%A4%B2%E0%A4%82-%E0%A4%A4-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%A2%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A4%A6-%E0%A4%A6-%E0%A4%96%E0%A4%B5%E0%A4%B2/ar-AA1K55hg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/nagpur/raghuji-raje-sword-in-london-is-in-the-possession-of-the-government-88219</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/maharashtra-police-bharti-cabinet-decision-what-are-the-recruitment-for-the-posts-omr-system-used-for-written-examination-1456438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/pune/pune-accident-news-death-toll-rises-to-10-in-pimpri-chinchwad-accident-88376</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/poet-saumitra-fears-homelessness-appeals-for-help-from-chief-minister-maharashtra-news-mhs25081106242</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/independence-day-2025-chhagan-bhujbal-refuse-to-hoist-flag-in-gondia-due-to-girish-mahajan/articleshow/123296100.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/chhatrapati-sambhajinagar-the-common-citizen-is-the-focal-point-guardian-minister-sanjay-shirsat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/maharashtra-is-making-a-fool-of-itself-sanjay-raut-questions-the-government-on-the-august-15-meat-ban/128932/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/chairman-ram-shindes-follow-up-is-successful-punyashloka-ahilyadevis-national-monument-at-chondi-approved-under-the-development-plan/129292/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/vijay-vadettiwar-on-devendra-fadanvis-vijay-vadettiwars-aggressive-criticism-of-the-decision-to-close-meat-fish-shops/128933/</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/india/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/international/global-trends/us-news-xfg-stratus-covid-variant-in-us-8-key-facts-risky-states-symptoms-prevention/covid-cases-are-increasing-in-us/slideshow/123347536.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/ar-AA1KtpKo</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519-amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/same-sex-couple-moves-hc-against-gift-tax-rules/articleshow/123325951.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/pune/punes-street-food-crisis-1500-poisoning-cases-in-six-months-students-worst-hit/</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/mumbai/bombay-high-court-bans-djs-in-ganeshotsav-and-other-processions-in-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/new-rules-for-admission-to-the-ministry-online-registration-mandatory-effective-from-august-15.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-on-ban-on-meat-eating/</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/the-government-will-decide-on-a-special-policy-regarding-backward-class-housing-societies-in-the-state-assembly-deputy-speaker-annasaheb-bansode/</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B2%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A5%80%E0%A4%9A%E0%A4%BE-%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/113758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cm-bhagwant-mann-writes-to-union-minister-shivraj-singh-chouhan-dont-drop-road-bridge-projects/articleshow/123317920.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment-125081101371_1.html?isa=yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/3-model-village-heads-from-gujarat-get-invited-to-i-day-celebrations-in-delhi/articleshow/123310840.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-junior-minister-yogesh-kadam-seeks-more-decision-making-powers-and-access-to-cabinet-meetings/articleshow/123284395.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/fishermen-must-prioritise-safety-hebbalkar/articleshow/123309750.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/divyansh-bhardwaj-bags-best-sarpanch-in-raj/articleshow/123312215.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>https://theindianawaaz.com/india-celebrates-79th-independence-day-with-patriotic-fervour-and-statewide-announcements-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mumbai-gets-2-bridges-and-a-promenade-101755198444321.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>https://munsifdaily.com/rapid-redevelopment-essential-for-a-slum-free/</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>https://www.newsonair.gov.in/hi/ndependence-day-celebrated-with-patriotic-fervour-and-gaiety-across-the-country/</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/news/india/cji-gavai-launches-bombay-hcs-4th-bench-in-kolhapur/articleshow/123351073.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-death-toll-rises-to-10-in-pimpri-chinchwad-accident/articleshow/123247989.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/7-must-visit-forts-and-memorials-honoring-indias-freedom-struggle/pratapgad-fort-maharashtra/slideshow/123236622.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/no-need-to-worry-about-us-tariffs-duty-hike-on-shrimp-chance-to-boost-indian-market-nitesh-rane/articleshow/123240165.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/7-devotees-died-as-pickup-overturned-in-pune-pm-modi-expressed-grief/</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>https://hindi.newsdanka.com/politics/independence-day-2025-pm-modi-longest-speech-ever/111404/</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>https://breakingmaharashtra.in/?p=39156</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-labour-dept-simplifies-access-to-welfare-schemes/articleshow/123289483.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chennai/tn-govt-will-not-let-down-sanitary-workers-stalin/articleshow/123311969.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/breaking-party-line-mithun-likens-lakshmir-bhandar-to-alms-tmc-hits-back/articleshow/123289871.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chennai/the-time-has-come-tamil-nadu-cm-mk-stalin-urges-legal-battle-to-reclaim-states-powers/articleshow/123317272.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/varanasi/cm-grid-scheme-reviewed-directions-to-expedite-work/articleshow/123289376.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/vijayawada/naidu-to-launch-free-bus-scheme-for-women-today/articleshow/123309861.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/msedcl-achieves-milestone-of-1gw-domestic-rooftop-solar-capacity/articleshow/123302393.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/pmo-team-reviews-pm-shri-scheme-in-jaisalmer/articleshow/123289381.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/mha-warns-states-of-foreigners-obtaining-indian-identity-docus/articleshow/123325780.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/delhi/prayaas-scheme-to-promote-research-innovation-among-classes-ix-xi-students/articleshow/123306112.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/tn-launches-door-delivery-of-ration-items-to-elderly-differently-abled.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/farmers-day-events-held-across-thiruvananthapuram-district/articleshow/123348556.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/hubballi/hubballi-nk-region-celebrate-independence-day-with-fervour/articleshow/123325559.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/13/dcm132-biz-briefs-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/ls-passes-two-tax-bills-amid-din-without-debate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>https://ommcomnews.com/india-news/maha-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/solapur-mumbai-flight-service-to-begin-soon/</t>
         </is>
       </c>
     </row>

--- a/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A802"/>
+  <dimension ref="A1:A775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,133 +466,133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-23589010</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-23589010</t>
+          <t>https://www.msn.com/en-in/money/topstories/business-as-usual-won-t-work-devendra-fadnavis-on-rising-property-prices-in-mumbai/ar-AA1KELqU?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/money/topstories/business-as-usual-won-t-work-devendra-fadnavis-on-rising-property-prices-in-mumbai/ar-AA1KELqU?ocid=finance-verthp-feeds</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
+          <t>https://infra.economictimes.indiatimes.com/news/ports-shipping/devendra-fadnavis-and-singapores-yong-collaborate-on-indias-largest-container-port/123274805</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/ports-shipping/devendra-fadnavis-and-singapores-yong-collaborate-on-indias-largest-container-port/123274805</t>
+          <t>http://www.msn.com/en-in/weather/climate-change/gives-me-sleepless-nights-climate-change-a-major-economic-risk-for-maharashtra-says-cm-devendra-fadnavis/ar-AA1CxKxh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/weather/climate-change/gives-me-sleepless-nights-climate-change-a-major-economic-risk-for-maharashtra-says-cm-devendra-fadnavis/ar-AA1CxKxh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
+          <t>http://www.msn.com/en-in/news/India/devendra-fadnavis-infrastructure-work-shouldn-t-drag-on-for-years/ar-AA1JUyyJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/devendra-fadnavis-infrastructure-work-shouldn-t-drag-on-for-years/ar-AA1JUyyJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
+          <t>https://www.msn.com/en-in/news/other/maharashtra-cm-devendra-fadnavis-asks-dhananjay-munde-to-resign-as-minister-report/ar-AA1AbOok?ocid=BingNewsVerp</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/maharashtra-cm-devendra-fadnavis-asks-dhananjay-munde-to-resign-as-minister-report/ar-AA1AbOok?ocid=BingNewsVerp</t>
+          <t>https://www.ndtv.com/video/devendra-fadnavis-rejects-election-rigging-claims-calls-opposition-allegations-fabricated-978678</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/devendra-fadnavis-rejects-election-rigging-claims-calls-opposition-allegations-fabricated-978678</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/more-maharashtra-civic-bodies-order-closure-of-slaughterhouses-on-aug-15-chief-minister-fadnavis-says-govt-played-no-role/articleshow/123289673.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/more-maharashtra-civic-bodies-order-closure-of-slaughterhouses-on-aug-15-chief-minister-fadnavis-says-govt-played-no-role/articleshow/123289673.cms</t>
+          <t>https://www.msn.com/en-in/autos/photos/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra/ar-AA1KmsuB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/photos/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra/ar-AA1KmsuB</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya/ar-AA1Kz9Qg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya/ar-AA1Kz9Qg</t>
+          <t>http://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/india/did-you-use-vote-riggers-fadnavis-asks-sharad-pawar/articleshow/123224044.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/did-you-use-vote-riggers-fadnavis-asks-sharad-pawar/articleshow/123224044.cms</t>
+          <t>http://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-vows-to-bring-elephant-home-mahadevi/ar-AA1JYQ3u?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-vows-to-bring-elephant-home-mahadevi/ar-AA1JYQ3u?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/videoshow/123305295.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/videoshow/123305295.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-cm-fadnavis-urges-ganesh-mandals-to-promote-operation-sindoor-and-swadeshi-goods-23589371</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-cm-fadnavis-urges-ganesh-mandals-to-promote-operation-sindoor-and-swadeshi-goods-23589371</t>
+          <t>https://www.tribuneindia.com/news/business/ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra/</t>
         </is>
       </c>
     </row>
@@ -662,112 +662,112 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-125081100764_1.html</t>
+          <t>https://timesofindia.indiatimes.com/india/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/articleshow/123290009.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.business-standard.com/politics/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-125081100764_1.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-to-inaugurate-dabbawallahs-museum-in-bandra-today/ar-AA1KvJtc</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-appeals-to-aviation-ministry-to-shift-radars-in-mumbai-to-allow-redevelopment/ar-AA1IrbnT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-to-inaugurate-dabbawallahs-museum-in-bandra-today/ar-AA1KvJtc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-prominent-in-indian-s-unstoppable-growth-story-cm-fadnavis-125081500462_1.html</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-appeals-to-aviation-ministry-to-shift-radars-in-mumbai-to-allow-redevelopment/ar-AA1IrbnT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/mmr-region-can-become-1-5-trillion-growth-hub-says-maharashtra-cm-125081500149_1.html</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-prominent-in-indian-s-unstoppable-growth-story-cm-fadnavis-125081500462_1.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.business-standard.com/india-news/mmr-region-can-become-1-5-trillion-growth-hub-says-maharashtra-cm-125081500149_1.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes-101755198744381.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-broke-handi-of-corruption-mahayuti-sounds-poll-bugle-101755369969997.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes-101755198744381.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-opens-key-projects-on-independence-day-by-maharashtra-cm-devendra-fadnavis-to-cut-traffic-travel-time-and-give-scenic-commutes-heres-how-article-152469772</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-broke-handi-of-corruption-mahayuti-sounds-poll-bugle-101755369969997.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/civic-bodies-are-only-following-the-meat-ban-imposed-by-congress-in-1988-cm-101755112861436.html</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-opens-key-projects-on-independence-day-by-maharashtra-cm-devendra-fadnavis-to-cut-traffic-travel-time-and-give-scenic-commutes-heres-how-article-152469772</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/india/rahul-gandhi-has-no-evidence-of-vote-chori-he-is-living-in-an-illusion-devendra-fadnavis-9503697.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/civic-bodies-are-only-following-the-meat-ban-imposed-by-congress-in-1988-cm-101755112861436.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/real-estate/third-and-fourth-mumbai-to-power-1-5-trillion-mmr-economy-city-can-surpass-dubai-in-10-years-devendra-fadnavis-101755244116021.html</t>
+          <t>https://www.news18.com/videos/india/rahul-gandhi-has-no-evidence-of-vote-chori-he-is-living-in-an-illusion-devendra-fadnavis-9503697.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/11/most-financial-fraud-platforms-run-by-foreign-operators-cm-fadnavis-.html</t>
+          <t>https://www.hindustantimes.com/real-estate/third-and-fourth-mumbai-to-power-1-5-trillion-mmr-economy-city-can-surpass-dubai-in-10-years-devendra-fadnavis-101755244116021.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/11/most-financial-fraud-platforms-run-by-foreign-operators-cm-fadnavis-.html</t>
         </is>
       </c>
     </row>
@@ -893,28 +893,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbais-dharavi-redevelopment-project-use-dharavi-land-50-50-for-rehabilitation-units-and-for-sale-buildings-directs-maharashtra-chief-minister-fadnavis/articleshow/123222610.cms</t>
+          <t>https://globalprimenews.com/2025/08/14/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-and-union-minister-gajendra-singh-shekhawat/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/eknath-shinde-won-political-lottery-maharashtra-bjp-mla-ganesh-naik-mahayuti-101755432617411.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbais-dharavi-redevelopment-project-use-dharavi-land-50-50-for-rehabilitation-units-and-for-sale-buildings-directs-maharashtra-chief-minister-fadnavis/articleshow/123222610.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/-third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation/2834267</t>
+          <t>https://www.hindustantimes.com/india-news/eknath-shinde-won-political-lottery-maharashtra-bjp-mla-ganesh-naik-mahayuti-101755432617411.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/08/14/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-and-union-minister-gajendra-singh-shekhawat/</t>
+          <t>https://www.ptinews.com/story/business/-third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation/2834267</t>
         </is>
       </c>
     </row>
@@ -928,2688 +928,2688 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/india/devendra-fadnavis-at-cnn-news18-townhall-on-student-mental-health-tricolour-true-freedom-9503816.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/actor-complains-about-redevelopment-project-fraud-cm-intervenes-101755026135161.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-coastal-road-to-remain-open-24-hours-from-aug-15-cm-fadnavis-warns-against-turning-the-stretch-into-a-racetrack/articleshow/123306484.cms</t>
+          <t>https://www.news18.com/videos/india/devendra-fadnavis-at-cnn-news18-townhall-on-student-mental-health-tricolour-true-freedom-9503816.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/dahi-handi-festivities-kick-starts-maharasthra-local-body-poll-campaign-3683995</t>
+          <t>https://zeenews.india.com/mobility/mumbai-coastal-road-to-be-open-24-hours-from-i-day-maha-cm-2946068.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-coastal-road-to-remain-open-24-hours-from-aug-15-cm-fadnavis-warns-against-turning-the-stretch-into-a-racetrack/articleshow/123306484.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.deccanherald.com/india/maharashtra/dahi-handi-festivities-kick-starts-maharasthra-local-body-poll-campaign-3683995</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/cmfadnavisinaugurates-first-phase-of-worli-bdd-chawl-redevelopment</t>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/mumbai-development-fadnavis-inaugurates-projects/32017320250814</t>
+          <t>https://www.newsband.in/article_detail/cmfadnavisinaugurates-first-phase-of-worli-bdd-chawl-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
+          <t>https://money.rediff.com/news/market/mumbai-development-fadnavis-inaugurates-projects/32017320250814</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/maharashtra-cm-devendra-fadnavis-comments-on-the-kabutar-khana-issue-cnn-news18-townhall-n18s-9503954.html</t>
+          <t>https://www.ptinews.com/story/national/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
+          <t>https://www.ptinews.com/editor-detail/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/from-160-sq-ft-to-sky-high-towers-fadnavis-delivers-bdd-chawl-homes-years-after-launching-project-3680811</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-cm-devendra-fadnavis-comments-on-the-kabutar-khana-issue-cnn-news18-townhall-n18s-9503954.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/bmc-in-focus-ballots-on-the-horizon-hear-it-straight-from-cm-of-maharashtra-devendra-fadnavis-9503385.html</t>
+          <t>https://www.ptinews.com/detail/national/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli20250814181439</t>
+          <t>https://www.deccanherald.com/india/maharashtra/from-160-sq-ft-to-sky-high-towers-fadnavis-delivers-bdd-chawl-homes-years-after-launching-project-3680811</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/maharashtra-chief-minster-devendra-fadnavis-attacks-rahul-gandhi-on-alleged-vote-chori-ruckus-9503712.html</t>
+          <t>https://www.news18.com/short-videos/trending/bmc-in-focus-ballots-on-the-horizon-hear-it-straight-from-cm-of-maharashtra-devendra-fadnavis-9503385.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/worlis-bdd-chawl-redevelopment-556-people-to-get-key-from-cm-fadnavis-on-august-14-says-mhada-23589353</t>
+          <t>https://www.aninews.in/news/business/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli20250814181439</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-chief-minster-devendra-fadnavis-attacks-rahul-gandhi-on-alleged-vote-chori-ruckus-9503712.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/aaditya-thackeray-greets-maharashtra-cm-devendra-fadnavis-warmly-at-cnn-news18-townhall-n18s-9503626.html</t>
+          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/worlis-bdd-chawl-redevelopment-556-people-to-get-key-from-cm-fadnavis-on-august-14-says-mhada-23589353</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year/ar-AA1KtMtq</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/like-munnabhai-mbbs-rahul-gandhi-is-living-in-an-illusion-maharashtra-cm-devendra-fadnavis-9504355.html</t>
+          <t>https://www.news18.com/short-videos/trending/aaditya-thackeray-greets-maharashtra-cm-devendra-fadnavis-warmly-at-cnn-news18-townhall-n18s-9503626.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/promote-operation-sindoor-swadeshi-at-ganesh-pandals-maharashtra-cm-23589390</t>
+          <t>https://www.aninews.in/news/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.msn.com/en-in/news/India/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year/ar-AA1KtMtq</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mahayuti-hands-over-keys-to-redeveloped-worli-bdd-chawl-flats-23589547</t>
+          <t>https://www.news18.com/short-videos/trending/like-munnabhai-mbbs-rahul-gandhi-is-living-in-an-illusion-maharashtra-cm-devendra-fadnavis-9504355.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/marathi-is-compulsory-ye-maharashtra-ki-ghajini-hain-devendra-fadnavis-attacks-ubt-govt-on-nep-9503705.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/promote-operation-sindoor-swadeshi-at-ganesh-pandals-maharashtra-cm-23589390</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/BJP-may-have--panna-pramukhs--but-we-have-workers-at-the-grassroots-level--Raj-Thackeray/2823246</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/projects-tenders/bdd-chawl-development</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mahayuti-hands-over-keys-to-redeveloped-worli-bdd-chawl-flats-23589547</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/big-political-voices-devendra-fadnavis-aaditya-thackeray-more-all-under-one-roof-n18s-9503158.html</t>
+          <t>https://www.news18.com/short-videos/trending/marathi-is-compulsory-ye-maharashtra-ki-ghajini-hain-devendra-fadnavis-attacks-ubt-govt-on-nep-9503705.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.ptinews.com/editor-detail/BJP-may-have--panna-pramukhs--but-we-have-workers-at-the-grassroots-level--Raj-Thackeray/2823246</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-7-killed-after-pickup-van-falls-down-slope-cm-fadnavis-announces-financial-assistance-of-rs-4-lakh20250811192235</t>
+          <t>https://www.constructionweekonline.in/projects-tenders/bdd-chawl-development</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/savitribai-phule-pune-university-withdraws-voice-of-devendra-competition-notice-after-nsui-objection/ar-AA1Kqjjv</t>
+          <t>https://www.news18.com/short-videos/trending/big-political-voices-devendra-fadnavis-aaditya-thackeray-more-all-under-one-roof-n18s-9503158.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom30-mh-rains-mumbai-ld-cm.html</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-7-killed-after-pickup-van-falls-down-slope-cm-fadnavis-announces-financial-assistance-of-rs-4-lakh20250811192235</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://tennews.in/chawl-redevelopment-project-maha-cm-fadnavis-hands-over-556-flats-at-worli-in-phase-1/</t>
+          <t>https://www.msn.com/en-in/news/India/savitribai-phule-pune-university-withdraws-voice-of-devendra-competition-notice-after-nsui-objection/ar-AA1Kqjjv</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://tennews.in/viksit-maharashtra-making-special-contribution-in-realising-dream-of-viksit-bharat-says-cm-fadnavis/</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278510817/mmr-region-has-potential-to-become-15-trillion-dollars-says-maharashtra-cm</t>
+          <t>https://tennews.in/chawl-redevelopment-project-maha-cm-fadnavis-hands-over-556-flats-at-worli-in-phase-1/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://tennews.in/viksit-maharashtra-making-special-contribution-in-realising-dream-of-viksit-bharat-says-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278515875/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-nda-vp-nomination</t>
+          <t>https://www.bignewsnetwork.com/news/278510817/mmr-region-has-potential-to-become-15-trillion-dollars-says-maharashtra-cm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/devendra-fadnavis-led-maharashtra-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers-7055240.html</t>
+          <t>https://www.bignewsnetwork.com/news/278515875/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-nda-vp-nomination</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3543870-maharashtra-cm-fadnavis-predicts-imminent-change-in-bmc-at-dahi-handi-celebrations</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/maharashtra-meat-shop-ban-controversy-devendra-fadnavis-ajit-pawar-aaditya-thackeray-independence-day-2025-1794498</t>
+          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3545017-fadnavis-congratulates-radhakrishnan-ndas-new-vice-presidential-candidate</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.devdiscourse.com/article/business/3540239-ibms-new-mumbai-hub-a-quantum-leap-for-maharashtras-future</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/socially/india/news/maharashtra-meat-ban-on-independence-day-2025-aaditya-thackeray-terms-august-15-meat-ban-wrong-cm-devendra-fadnavis-distances-govt-from-decision-watch-video-7058930.html</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/fadnavis-presents-shawl-to-cp-radhakrishnan-on-nda-s-vp-nomination-7063864.html</t>
+          <t>https://www.latestly.com/india/news/devendra-fadnavis-led-maharashtra-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers-7055240.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/education/jobs/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra-1794239</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/in-operation-sindoor-under-the-leadership-of-pm-modi-maharashtra-cm-devendra-fadnavis-47149/</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-his-deputies-congratulate-governor-radhakrishnan-over-vp-nomination-9670364</t>
+          <t>https://www.devdiscourse.com/article/headlines/3542998-tripura-and-maharashtra-cms-celebrate-indias-79th-independence-day-with-patriotic-fervor</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3542847-diwali-comes-early-new-gst-reforms-announced-on-independence-day</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli-7058938.html</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3541262-worlis-rebirthed-bdd-chawls-mumbais-new-gold-standard</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/law-advocates-cm-fadnavis-high-court/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3542407-maharashtras-mega-city-vision-building-beyond-dubai</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day/</t>
+          <t>https://www.latestly.com/socially/india/news/maharashtra-meat-ban-on-independence-day-2025-aaditya-thackeray-terms-august-15-meat-ban-wrong-cm-devendra-fadnavis-distances-govt-from-decision-watch-video-7058930.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3540668-fadnavis-calls-for-operation-sindoor-awareness-during-ganesh-festival</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-uddhav-thackeray-claims-and-big-attack-says-cm-devendra-fadnavis-shielding-corrupt-ministers-24009940.html</t>
+          <t>https://www.latestly.com/quickly/agency-news/fadnavis-presents-shawl-to-cp-radhakrishnan-on-nda-s-vp-nomination-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-and-ajit-pawar-faction-assigned-flag-hoisting-duties-in-maharashtra-eknath-shinde-out/articleshow/123242552.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3542411-maharashtras-pivotal-role-in-indias-growth-story</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%95-%E0%A4%87%E0%A4%A4%E0%A4%A8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%B9%E0%A5%88-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AC%E0%A4%A8-%E0%A4%AE-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9C%E0%A4%AE%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%B0/ar-AA1IVb2V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.newsx.com/india/in-operation-sindoor-under-the-leadership-of-pm-modi-maharashtra-cm-devendra-fadnavis-47149/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/krishna-janmashtami-2025-maharashtra-cm-devendra-fadnavis-target-congress-shiv-sena-uddhav-thackeray-sharad-pawar-bmc-2996712</t>
+          <t>https://www.devdiscourse.com/article/business/3542420-maharashtras-unstoppable-growth-under-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/photo/fadnavis-made-big-announcement-for-dharavi-it-will-be-built-like-a-new-city-1550</t>
+          <t>https://www.devdiscourse.com/article/headlines/3542847-diwali-comes-early-new-gst-reforms-announced-on-independence-day</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.latestly.com/agency-news/business-news-maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli-7058938.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/august-15-meat-ban-row-maharashtra-cm-devendra-fadnavis-said-govt-not-interested-in-regulating-people-food-choices-know-all/articleshow/123294081.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3544716-maharashtras-legal-leap-ensuring-advocate-safety-and-expanding-justice</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-has-world-s-best-technology-to-curb-cyber-crime-devendra-fadnavis-11078</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-handover-556-flats-in-worli-bdd-chawl-redevelopment-project-ann-2995711</t>
+          <t>https://www.5dariyanews.com/news/464628-Cooperation-of-IBM-is-necessary-to-achieve-goal-of-Viksit-Maharashtra-Devendra-Fadnavis</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
+          <t>https://www.devdiscourse.com/article/politics/3543787-mumbais-dahi-handi-a-festival-of-change-and-celebration</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%AE%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%96-%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%9C-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%A1%E0%A4%BC/ar-AA1G9764?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-police-recruitment-2025-devendra-fadnavis-cabinet-approves-recruitment-of-15000-post-2994374</t>
+          <t>https://lawchakra.in/legal-updates/law-advocates-cm-fadnavis-high-court/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-calls-uddhav-thackeray-politics-ghajini-but-why-ws-l-9506496.html</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/maha-cm-breaks-parivartan-operation-sindoor-handi-targeting-mva-in-aaditya-thackerays-worli-constituency-135690000.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-and-aaditya-thackeray-will-on-one-stage-with-devendra-fadnavis-201755068550172.html</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ganeshotsav-2025-cm-devendra-fadnavis-appeals-to-ganpati-mandals-operation-sindoor-show-indigenous-tableaux/articleshow/123286430.cms</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97%E0%A4%A2%E0%A4%BC%E0%A4%9A-%E0%A4%B0-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%82%E0%A4%9F-%E0%A4%B9-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%94%E0%A4%B0-%E0%A4%9F-%E0%A4%89%E0%A4%A8%E0%A4%B6-%E0%A4%AA-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A5%87%E0%A4%A1-%E0%A4%95-%E0%A4%B0-%E0%A4%A1-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%96-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B5-%E0%A4%95-%E0%A4%A8-%E0%A4%82%E0%A4%B5/ar-AA1J3wnZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jagran.com/politics/national-uddhav-thackeray-claims-and-big-attack-says-cm-devendra-fadnavis-shielding-corrupt-ministers-24009940.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-and-ajit-pawar-faction-assigned-flag-hoisting-duties-in-maharashtra-eknath-shinde-out/articleshow/123242552.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis-2025-08-13</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%95-%E0%A4%87%E0%A4%A4%E0%A4%A8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%B9%E0%A5%88-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AC%E0%A4%A8-%E0%A4%AE-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9C%E0%A4%AE%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%B0/ar-AA1IVb2V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-in-a-protest-organised-against-mahayuti-government-accused-devendra-fadnavis-of-protecting-the-corrupt-ministers/articleshow/123248772.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/august-15-meat-ban-row-maharashtra-cm-devendra-fadnavis-said-govt-not-interested-in-regulating-people-food-choices-know-all/articleshow/123294081.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/nagpur-why-no-action-was-taken-against-those-who-guaranteed-160-seats-devendra-fadnavis-hits-back-at-sharad-pawar-9496304.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cm-devendra-fadnavis-reply-on-15th-august-meat-ban-controversy-9078739</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%AE%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%96-%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%9C-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%A1%E0%A4%BC/ar-AA1G9764?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-meeting-on-ganeshotsav-2025-he-also-directs-on-eid-e-milad-festival-ann-2995187</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-calls-uddhav-thackeray-politics-ghajini-but-why-ws-l-9506496.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-municipal-body-looted-devendra-fadnavis-target-uddhav-thackeray-bmc-elections-9516480.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/bdd-chawl-redevelopment-scheme-cm-devendra-fadnavis-give-mhada-houses/articleshow/123310540.cms</t>
+          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-and-aaditya-thackeray-will-on-one-stage-with-devendra-fadnavis-201755068550172.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ganeshotsav-2025-cm-devendra-fadnavis-appeals-to-ganpati-mandals-operation-sindoor-show-indigenous-tableaux/articleshow/123286430.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-government-of-maharashtra-gave-permission-for-school-buses-pratap-sarnaik-ann-2994680</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-fadnavis-calls-for-promotion-of-indigenous-sports-sports-minister-kokate-inaugurates-khelo-mahakumbh/articleshow/123286194.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis-2025-08-13</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-in-a-protest-organised-against-mahayuti-government-accused-devendra-fadnavis-of-protecting-the-corrupt-ministers/articleshow/123248772.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-meat-ban-order-cm-devendra-fadnavis-backs-decision-ajit-pawar-says-this-wrong-2995176</t>
+          <t>https://hindi.news18.com/news/maharashtra/nagpur-why-no-action-was-taken-against-those-who-guaranteed-160-seats-devendra-fadnavis-hits-back-at-sharad-pawar-9496304.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/good-news-for-the-youth-devendra-fadnavis-cabinet-approved-recruitment-for-15-thousand-posts/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/uddhav-thackeray-targets-shindes-tainted-ministers-puts-moral-pressure-on-cm-fadnavis-amid-brewing-cold-war-ntc-rpti-2308276-2025-08-12</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cm-devendra-fadnavis-reply-on-15th-august-meat-ban-controversy-9078739</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/abu-asim-azmi-demands-cm-devendra-fadnavis-to-take-action-in-jamner-murder-case-2995099</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-municipal-body-looted-devendra-fadnavis-target-uddhav-thackeray-bmc-elections-9516480.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-protest-many-places-against-cm-fadnavis-corrupt-minister-uddhav-chief-minister-protecting-everyone-2025-08-11</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/bdd-chawl-redevelopment-scheme-cm-devendra-fadnavis-give-mhada-houses/articleshow/123310540.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-vegetarians-are-impotent-nonsense-talk-cm-devendra-fadnavis-reaction-on-slaughterhouse-meat-shops-9506829.html</t>
+          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/congress-leader-balasaheb-thorat-again-expressed-fear-of-rigging-in-maharashtra-assembly-election-2993690</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-fadnavis-calls-for-promotion-of-indigenous-sports-sports-minister-kokate-inaugurates-khelo-mahakumbh/articleshow/123286194.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16?src=top-subnav</t>
+          <t>https://www.agniban.com/good-news-for-the-youth-devendra-fadnavis-cabinet-approved-recruitment-for-15-thousand-posts/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%A6%E0%A4%B0%E0%A4%B5-%E0%A4%9C-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-ac-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%AC-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1KyN36</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-protest-many-places-against-cm-fadnavis-corrupt-minister-uddhav-chief-minister-protecting-everyone-2025-08-11</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-govt-approves-recruitment-of-15000-police-personnel-know-cabinet-meeting-decisions/articleshow/123260370.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-vegetarians-are-impotent-nonsense-talk-cm-devendra-fadnavis-reaction-on-slaughterhouse-meat-shops-9506829.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/cm-fadnavis-told-how-dharavi-is-being-redeveloped-says-this-is-the-center-of-economic-development-9084680</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%A6%E0%A4%B0%E0%A4%B5-%E0%A4%9C-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-ac-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%AC-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1KyN36</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-govt-approves-recruitment-of-15000-police-personnel-know-cabinet-meeting-decisions/articleshow/123260370.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/sclr-extension-mumbai-opening-eastern-western-expressway-highway-link-mumbai/articleshow/123308994.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-cm-fadnavis-advised-mumbaikars-not-to-sell-their-houses-24013649.html</t>
+          <t>https://ndtv.in/india/cm-fadnavis-told-how-dharavi-is-being-redeveloped-says-this-is-the-center-of-economic-development-9084680</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-slams-sharad-pawar-over-august-15-meat-sale-ban-says-its-pawar-governments-decision/articleshow/123286747.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/sclr-extension-mumbai-opening-eastern-western-expressway-highway-link-mumbai/articleshow/123308994.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/whom-did-chief-minister-devendra-fadnavis-target-regarding-bmc-125081600082_1.html</t>
+          <t>https://www.jagran.com/news/national-cm-fadnavis-advised-mumbaikars-not-to-sell-their-houses-24013649.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%95%E0%A4%88-%E0%A4%9C%E0%A4%97%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%95-%E0%A4%AC%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1Kiekp</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-slams-sharad-pawar-over-august-15-meat-sale-ban-says-its-pawar-governments-decision/articleshow/123286747.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-maharashtra-cyber-crime-control-cm-fadnavis-lauds-garud-drishti-initiative-24009491.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%95%E0%A4%88-%E0%A4%9C%E0%A4%97%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%95-%E0%A4%AC%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1Kiekp</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1JArmJ</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/whom-did-chief-minister-devendra-fadnavis-target-regarding-bmc-125081600082_1.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bdd-chawl-redevelopment-flats-ready-in-worli-cm-fadnavis-inaugurates-them-11129</t>
+          <t>https://www.jagran.com/news/national-maharashtra-cyber-crime-control-cm-fadnavis-lauds-garud-drishti-initiative-24009491.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/nagpur-what-is-garuda-vision-of-maharashtra-police-done-patent-communal-violence-cyber-fraud-check-social-media-post-10-crore-recovery-ws-kl-9498865.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1JArmJ</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O</t>
+          <t>https://hindi.news18.com/news/maharashtra/nagpur-what-is-garuda-vision-of-maharashtra-police-done-patent-communal-violence-cyber-fraud-check-social-media-post-10-crore-recovery-ws-kl-9498865.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/India/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-556-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%82%E0%A4%AA-bdd-%E0%A4%9A-%E0%A4%B2-%E0%A4%95-%E0%A4%9A-%E0%A4%AC-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B0-%E0%A4%B0-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%88-%E0%A4%A6%E0%A5%82%E0%A4%B0/ar-AA1KxhQD</t>
+          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.pratahkal.com/Encyc/2025/8/16/cm-fadnavis-praised-the-army-on-independence-day.html</t>
+          <t>https://www.msn.com/hi-in/news/India/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-556-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%82%E0%A4%AA-bdd-%E0%A4%9A-%E0%A4%B2-%E0%A4%95-%E0%A4%9A-%E0%A4%AC-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B0-%E0%A4%B0-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%88-%E0%A4%A6%E0%A5%82%E0%A4%B0/ar-AA1KxhQD</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/bjp-leader-targets-maratha-reservation-activist-jarange-for-his-remarks-against-fadnavis/854383/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KfkTJ</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/cm-fadnavis-inaugurated-mumbai-dabbawala-international-experience-center-dabbawalas-will-get-their-own-house-9088159</t>
+          <t>https://www.pratahkal.com/Encyc/2025/8/16/cm-fadnavis-praised-the-army-on-independence-day.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-chhagan-bhujbal-skips-gondia-flag-hoisting-amid-guardian-minister-row-bjp-mangal-prabhat-deputed-know-all/articleshow/123305574.cms</t>
+          <t>https://ndtv.in/maharashtra-news/cm-fadnavis-inaugurated-mumbai-dabbawala-international-experience-center-dabbawalas-will-get-their-own-house-9088159</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/aimim-leader-imtiaz-jaleel-organised-a-biryani-party-at-his-home-to-protest-against-civic-bodys-meat-ban-also-targeted-cm-devendra-fadnavis/articleshow/123329000.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-chhagan-bhujbal-skips-gondia-flag-hoisting-amid-guardian-minister-row-bjp-mangal-prabhat-deputed-know-all/articleshow/123305574.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/independence-day-meat-ban-row-sanjay-raut-slams-cm-fadnavis-said-shivaji-maharaj-was-not-eat-only-rice-and-ghee-know-all/articleshow/123274873.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/aimim-leader-imtiaz-jaleel-organised-a-biryani-party-at-his-home-to-protest-against-civic-bodys-meat-ban-also-targeted-cm-devendra-fadnavis/articleshow/123329000.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://bhasha.ptinews.com/detail/2830925</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/independence-day-meat-ban-row-sanjay-raut-slams-cm-fadnavis-said-shivaji-maharaj-was-not-eat-only-rice-and-ghee-know-all/articleshow/123274873.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-mahayuti-eknath-shinde-missing-devendra-fadnavis-govt-cabinet-meeting-sa-9502234.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE-%E0%A4%9F-%E0%A4%95-%E0%A4%A6%E0%A5%81%E0%A4%95-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%87%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%A8-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%9A-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Ksgnw</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/dispute-over-guardian-minister-post-deepens-in-mahayuti-government-eknath-shinde-distances-himself-from-cabinet-meeting/articleshow/123270600.cms</t>
+          <t>https://bhasha.ptinews.com/detail/2830925</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/public-security-act-is-a-direct-attack-on-fundamental-rights-opposition-parties-in-the-field-11142</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-mahayuti-eknath-shinde-missing-devendra-fadnavis-govt-cabinet-meeting-sa-9502234.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/uddhav-thackeray-roared-with-jan-akrosh-andolan-in-dadar-lashed-out-at-shinde-fadnavis-government-1541</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/cm-fadnavis-handed-over-the-keys-of-new-houses-to-bdd-chawl-residents/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/dispute-over-guardian-minister-post-deepens-in-mahayuti-government-eknath-shinde-distances-himself-from-cabinet-meeting/articleshow/123270600.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/ganeshotsav-2025-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%88%E0%A4%A6-%E0%A4%8F-%E0%A4%AE-%E0%A4%B2-%E0%A4%A6-%E0%A4%95-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1KskuP</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-15000-policemen-recruitment-soon-fadnavis-cabinet-approved-four-important-proposals-19856957</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://mandalnews.com/amravati/cm-fadnavis-handed-over-the-keys-of-new-houses-to-bdd-chawl-residents/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-inaugurates-bombay-high-court-new-circuit-bench-at-kolhapur-cm-fadnavis-and-dcm-eknath-shinde-also-present-know-all/articleshow/123346652.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/ganeshotsav-2025-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%88%E0%A4%A6-%E0%A4%8F-%E0%A4%AE-%E0%A4%B2-%E0%A4%A6-%E0%A4%95-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1KskuP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-not-reached-devendra-fadnavis-govt-cabinet-meeting-201754983032466.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-police-bharti-2025-mega-recruitment-drive-hire-15000-personnel-various-posts-announced-check-details-go-to-this-link-and-see-b507/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-inaugurates-bombay-high-court-new-circuit-bench-at-kolhapur-cm-fadnavis-and-dcm-eknath-shinde-also-present-know-all/articleshow/123346652.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%B5-%E0%A4%A6-%E0%A4%9C-%E0%A4%8F-%E0%A4%AF-%E0%A4%A6%E0%A5%82%E0%A4%B8%E0%A4%B0%E0%A5%87/ar-AA1KrMtV</t>
+          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-not-reached-devendra-fadnavis-govt-cabinet-meeting-201754983032466.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-police-bharti-2025-mega-recruitment-drive-hire-15000-personnel-various-posts-announced-check-details-go-to-this-link-and-see-b507/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-unhappy-eknath-shinde-skips-cabinet-meeting-know-what-is-going-in-mahayuti-amid-guardian-minister-row/articleshow/123283685.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%B5-%E0%A4%A6-%E0%A4%9C-%E0%A4%8F-%E0%A4%AF-%E0%A4%A6%E0%A5%82%E0%A4%B8%E0%A4%B0%E0%A5%87/ar-AA1KrMtV</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/committee-formed-to-give-suggestions-to-help-sectors-affected-by-us-tariffs-fadnavis/854538/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-unhappy-eknath-shinde-skips-cabinet-meeting-know-what-is-going-in-mahayuti-amid-guardian-minister-row/articleshow/123283685.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/aimim-and-ncp-sp-leaders-held-a-chicken-mutton-party-in-protest-against-meat-ban-in-maharashtra-9092115</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-faction-minister-bharat-gogawale-angry-he-will-stay-away-from-cabinet-meeting-2994340</t>
+          <t>https://ndtv.in/maharashtra-news/aimim-and-ncp-sp-leaders-held-a-chicken-mutton-party-in-protest-against-meat-ban-in-maharashtra-9092115</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-leader-parinay-fuke-hits-out-at-maratha-quota-activist-manoj-jarange-for-remarks-against-devendra-fadnavis-2994554</t>
+          <t>https://www.jagran.com/politics/national-maharashtra-meat-ban-protest-opposition-condemns-independence-day-shop-closure-24014311.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-maharashtra-meat-ban-protest-opposition-condemns-independence-day-shop-closure-24014311.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://www.newsonair.gov.in/hi/garuda-drishti-device-is-playing-an-important-role-in-monitoring-social-media-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/garuda-drishti-device-is-playing-an-important-role-in-monitoring-social-media-chief-minister-fadnavis/</t>
+          <t>https://hindi.theprint.in/india/a-middle-path-should-be-found-in-the-matter-of-feeding-pigeons-fadnavis/854960/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/news/india/cji-br-gavai-praise-devendra-fadnavis-govt-said-maharashtra-government-always-leader-judiciary-infrastructure-2997155</t>
+          <t>https://www.agniban.com/protests-at-many-places-against-cm-fadnavis-corrupt-ministers-uddhav-said-chief-minister-is-protecting-everyone/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/a-middle-path-should-be-found-in-the-matter-of-feeding-pigeons-fadnavis/854960/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%A7-%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%87-%E0%A4%B9%E0%A5%88-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0/ar-AA1KvM5B</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maharashtra-cm-fadnavis-is-protecting-corrupt-ministers-uddhav/853904/</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-meat-ban-cm-devendra-fadnavis-says-govt-wont-decide-who-eats-what-201755168216321.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/jarange-has-lost-credibility-his-remote-control-is-in-sharad-pawars-hands-bjp-leader/854582/</t>
+          <t>https://www.agniban.com/fadnavis-clarification-on-meat-ban-in-maharashtra-government-will-not-decide-who-should-eat-what/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/pune-university-withdraws-voice-of-devendra-contest-notification-after-nsui-objects/854442/</t>
+          <t>https://www.livehindustan.com/maharashtra/i-pity-devendra-fadnavis-why-did-uddhav-thackeray-say-this-after-taking-the-names-of-these-3-ministers-201754912659397.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/protests-at-many-places-against-cm-fadnavis-corrupt-ministers-uddhav-said-chief-minister-is-protecting-everyone/</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-politics-saamna-editorial-devendra-fadnavis-eknath-shinde-ajit-pawar-uddhav-thackeray-sanjay-raut-201755148013599.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%A7-%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%87-%E0%A4%B9%E0%A5%88-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0/ar-AA1KvM5B</t>
+          <t>https://www.5dariyanews.com/hindi/news/310952-Devendra-Fadnavis-taunts-the-opposition-the-pot-of-sin-has-been-broken-in-the-Municipal-Corporation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-meat-ban-cm-devendra-fadnavis-says-govt-wont-decide-who-eats-what-201755168216321.html</t>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/fadnavis-clarification-on-meat-ban-in-maharashtra-government-will-not-decide-who-should-eat-what/</t>
+          <t>https://www.hindisaamana.com/fadnavis-reprimands-shindes-osd/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/maharashtra-politics-uddhav-thackeray-attacks-devendra-fadnavis-for-not-acting-against-corrupt-ministers-frvd-2308298-2025-08-12</t>
+          <t>https://www.hindisaamana.com/home-minister-fadnavis-is-not-worried-the-protectors-of-law-are-committing-suicide-in-4-days-3-policemen-committed-their-lives/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/i-pity-devendra-fadnavis-why-did-uddhav-thackeray-say-this-after-taking-the-names-of-these-3-ministers-201754912659397.html</t>
+          <t>https://hindi.newsdanka.com/news-update/devendra-fadnavis-hoists-tricolour-maharashtra-engine-of-indias-progress/111395/amp</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/on-janmashtami-enthusiasm-for-dahi-handi-in-mumbai-a-unique-display-in-the-presence-of-cm-fadnavis-ytvd-2311680-2025-08-16</t>
+          <t>https://hindi.latestly.com/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-politics-saamna-editorial-devendra-fadnavis-eknath-shinde-ajit-pawar-uddhav-thackeray-sanjay-raut-201755148013599.html</t>
+          <t>https://bharatexpress.com/india/c-p-radhakrishnan-becomes-ndas-vice-presidential-candidate-maharashtra-chief-minister-devendra-fadnavis-congratulates-him-552637</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://samacharnama.com/states/maharashtra-news/paul-tixs-ghajini-devendra-fadnavis-lashes-out-at-uddhav/cid17238362.htm</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/fadnavis-reprimands-shindes-osd/</t>
+          <t>https://www.rokthoklekhani.com/article/43041/flats-of-worli-bdd-chawl-redevelopment-project-inaugurated-by-cm</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/home-minister-fadnavis-is-not-worried-the-protectors-of-law-are-committing-suicide-in-4-days-3-policemen-committed-their-lives/</t>
+          <t>https://jantaserishta.com/local/maharashtra/maharashtra-7-killed-as-pickup-van-falls-off-slope-cm-fadnavis-announces-rs-4-lakh-aid-4206354</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/news-update/devendra-fadnavis-hoists-tricolour-maharashtra-engine-of-indias-progress/111395/amp</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
+          <t>https://bharatexpress.com/india/maharashtra-cm-devendra-fadnavis-independence-day-wishes-three-languages-reply-to-opposition-551631</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/c-p-radhakrishnan-becomes-ndas-vice-presidential-candidate-maharashtra-chief-minister-devendra-fadnavis-congratulates-him-552637</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/cm-fadnavis-arrived-at-dahi-handi-on-operation-sindoor-theme/article-101120</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/paul-tixs-ghajini-devendra-fadnavis-lashes-out-at-uddhav/cid17238362.htm</t>
+          <t>https://jantaserishta.com/local/maharashtra/mmr-region-has-15-trillion-potential-maharashtra-cm-4213325</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43041/flats-of-worli-bdd-chawl-redevelopment-project-inaugurated-by-cm</t>
+          <t>https://bharat24live.com/news/maharashtra-cabinet-approves-recruitment-for-15000-police-posts-in-2025</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/maharashtra-7-killed-as-pickup-van-falls-off-slope-cm-fadnavis-announces-rs-4-lakh-aid-4206354</t>
+          <t>https://www.rokthoklekhani.com/tag/29359/mumbai%3A-rapid-redeevelopment-is-necessary-for-a-slum--free-mumbai---chief-minister-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/fadnavis-ka-vipaksh-par-tanz-mahanagar-palika-mein-toot-chuki-hai-paap-ki-haandi--20250816171044/</t>
+          <t>https://hindi.latestly.com/quickly/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.rokthoklekhani.com/tag/29261/other-places-should</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://indiagroundreport.com/mumbai-dabbawalas-in-mumbai-will-get-500-square-feet-house-for-rs-25-50-lakh-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/maharashtra-cm-devendra-fadnavis-independence-day-wishes-three-languages-reply-to-opposition-551631</t>
+          <t>https://joindia.co.in/news/fadnaviss-retort-on-sharad-pawars-160-seat-offer-statement-said-this-story-is-like-salim-javeds-script/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/cm-fadnavis-arrived-at-dahi-handi-on-operation-sindoor-theme/article-101120</t>
+          <t>https://www.primetvindia.com/nda-declared-c-p-radhakrishnan-as-the-candidate-for-the-post-of-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mmr-region-has-15-trillion-potential-maharashtra-cm-4213325</t>
+          <t>https://www.msn.com/en-in/news/India/guaranteed-victory-claim-row-erupts-in-maharashtra-did-you-use-vote-riggers-devendra-fadnavis-asks-sharad-pawar/ar-AA1Khn2c</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://bharat24live.com/news/maharashtra-cabinet-approves-recruitment-for-15000-police-posts-in-2025</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832775</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/tag/29359/mumbai%3A-rapid-redeevelopment-is-necessary-for-a-slum--free-mumbai---chief-minister-devendra-fadnavis</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sppu-withdraws-voice-of-devendra-contest-notice-after-protest-101755032437944.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/quickly/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
+          <t>https://www.msn.com/en-in/news/India/credai-mchi-appoints-sukhraj-nahar-as-18th-president-in-presence-of-cm-devendra-fadnavis/ar-AA1KxDEc</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/tag/29261/other-places-should</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-to-inaugurate-slew-of-projects-today-metro-3-may-launch-by-aug-end-101754936573343.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-dabbawalas-in-mumbai-will-get-500-square-feet-house-for-rs-25-50-lakh-chief-minister/</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/farmers-compensation-pending-sharad-pawar-to-discuss-with-chief-minister-4216652</t>
+          <t>https://www.newsband.in/article_detail/new-psa-terminal-at-jnpa-to-be-opened-soon-fadnavis-</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/fadnaviss-retort-on-sharad-pawars-160-seat-offer-statement-said-this-story-is-like-salim-javeds-script/</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos--106878</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/guaranteed-victory-claim-row-erupts-in-maharashtra-did-you-use-vote-riggers-devendra-fadnavis-asks-sharad-pawar/ar-AA1Khn2c</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832775</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-14-news-updates-live-updates-weather-update-mumbai-monsoon-18331384</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sppu-withdraws-voice-of-devendra-contest-notice-after-protest-101755032437944.html</t>
+          <t>https://www.thehansindia.com/news/national/viksit-maharashtra-making-special-contribution-in-realising-dream-of-viksit-bharat-says-cm-fadnavis-997311</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/credai-mchi-appoints-sukhraj-nahar-as-18th-president-in-presence-of-cm-devendra-fadnavis/ar-AA1KxDEc</t>
+          <t>https://zeenews.india.com/india/maharashtra-7-dead-as-pickup-van-falls-cm-fadnavis-announces-4-lakh-aid-2944690.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-to-inaugurate-slew-of-projects-today-metro-3-may-launch-by-aug-end-101754936573343.html</t>
+          <t>https://www.ptinews.com/editor-detail/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-13-news-updates-live-updates-weather-update-mumbai-monsoon-18331383</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/new-psa-terminal-at-jnpa-to-be-opened-soon-fadnavis-</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-ubt-protests-in-nagpur-seeking-sacking-of-corrupt-maharashtra-ministers/2812465</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-deputy-cm-ajit-pawar-led-ncp-questions-meat-ban-on-august-15-bjp-cites-1988-order-23589362</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos--106878</t>
+          <t>http://www.uniindia.com/photoes/631755.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.bignewsnetwork.com/news/278509383/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-14-news-updates-live-updates-weather-update-mumbai-monsoon-18331384</t>
+          <t>https://newsarenaindia.com/states/maha-govt-not-keen-on-regulating-people-s-food-choices-fadnavis/53228</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-7-dead-as-pickup-van-falls-cm-fadnavis-announces-4-lakh-aid-2944690.html</t>
+          <t>https://www.punekarnews.in/congresss-ramesh-chennithala-questions-cm-fadnaviss-remarks-on-rahul-gandhis-allegations-against-election-commission/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/bhiwandi-will-be-developed-as-an-urban-city-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-ubt-protests-in-nagpur-seeking-sacking-of-corrupt-maharashtra-ministers/2812465</t>
+          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-speech-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A4%B0%E0%A4%95%E0%A5%81%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A4%E0%A4%B0%E0%A4%A3-marathi-news/vi-AA1KFM8O?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-deputy-cm-ajit-pawar-led-ncp-questions-meat-ban-on-august-15-bjp-cites-1988-order-23589362</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-statement-that-kolhapur-has-become-centralized-due-to-the-circuit-bench/912997/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/631755.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/underground-road-plan-to-ease-central-pune-traffic-cm-devendra-fadnavis-meeting-9101801</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278509383/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.apnnews.com/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-after-president-trump-who-is-the-clown-in-politics-it-is-devendra-fadnavis-raut-criticizes-the-chief-minister/912795/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6622494</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/congresss-ramesh-chennithala-questions-cm-fadnaviss-remarks-on-rahul-gandhis-allegations-against-election-commission/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/bhiwandi-will-be-developed-as-an-urban-city-devendra-fadnavis.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-speech-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A4%B0%E0%A4%95%E0%A5%81%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A4%E0%A4%B0%E0%A4%A3-marathi-news/vi-AA1KFM8O?ocid=hpmsn</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-statement-that-kolhapur-has-become-centralized-due-to-the-circuit-bench/912997/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/underground-road-plan-to-ease-central-pune-traffic-cm-devendra-fadnavis-meeting-9101801</t>
+          <t>https://www.saamana.com/after-donald-trump-devendra-fadnavis-is-biggest-joker-in-politics-sanjay-raut-criticized/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/only-then-will-the-dream-of-a-slum-free-mumbai-be-realized-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-after-president-trump-who-is-the-clown-in-politics-it-is-devendra-fadnavis-raut-criticizes-the-chief-minister/912795/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-challenges-uddhav-and-raj-thackeray-over-mumbai-municipal-corporation-bmc-elections-during-dahi-handi-festival/articleshow/123333235.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announced-it-park-to-be-set-up-in-solapur-for-employment-generation-1460220.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-believes-that-maharashtra-will-lead-the-countrys-development-system-amy-95-5307598/</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devedra-fadnavis-challenges-opposition-over-upcoming-municipal-elections-at-dahi-handi-2025/articleshow/123340653.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288/amp/1</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/solapur-news-mla-vijay-kumar-deshmukh-expressed-regret-over-chief-minister-devendra-fadnavis-neglect-of-solapur-in-the-last-two-years-1377700</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raj-thackeray-uddhav-thackeray-shiv-sena-ubt-mns-reunite-for-best-employees-credit-society-election-against-bjp-devendra-fadnavis-samruddhi-panel/articleshow/123328116.cms</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.mymahanagar.com/photo-gallery/dahi-handi-2025-tembhinaka-dahihandi-cm-devendrad-fadnavis-political-statement-on-bmc-election/912700/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/after-donald-trump-devendra-fadnavis-is-biggest-joker-in-politics-sanjay-raut-criticized/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cm-devendra-fadnavis-criticizes-thackeray-group-saying-we-broke-the-pot-of-sin-in-municipal-corporation/912631/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/only-then-will-the-dream-of-a-slum-free-mumbai-be-realized-chief-minister-devendra-fadnavis.html</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-stated-bandra-versova-sea-link-will-be-extended-up-to-vadhavan-port-local18-1459825.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-challenges-uddhav-and-raj-thackeray-over-mumbai-municipal-corporation-bmc-elections-during-dahi-handi-festival/articleshow/123333235.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://deshdoot.com/fadnavis-targets-thackeray-camp-we-broke-the-pot-of-corruption-in-bmc-now-development-will-flow/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announced-it-park-to-be-set-up-in-solapur-for-employment-generation-1460220.html</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A6%E0%A4%B9-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%95-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F/ar-AA1KD8k2</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devedra-fadnavis-challenges-opposition-over-upcoming-municipal-elections-at-dahi-handi-2025/articleshow/123340653.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9A-%E0%A4%AB-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KE0LG</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-strong-answer-to-uddhav-thackeray-said-he-stole-public-mandate-and-now-teaching-us-scj-81-5296450/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288/amp/1</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/dahi-handi-2025-tembhinaka-dahihandi-cm-devendrad-fadnavis-political-statement-on-bmc-election/912700/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%96%E0%A5%87%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%86%E0%A4%B2-%E0%A4%9A-%E0%A4%AC-%E0%A4%A1-%E0%A4%A1-%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1KcLlH</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raj-thackeray-uddhav-thackeray-shiv-sena-ubt-mns-reunite-for-best-employees-credit-society-election-against-bjp-devendra-fadnavis-samruddhi-panel/articleshow/123328116.cms</t>
+          <t>https://marathi.ndtv.com/cities/jain-muni-nileshchandra-appeal-to-cm-devendra-fadnavis-over-dadar-kabutar-khana-issue-9075708</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.msn.com/mr-in/news/other/third-mumbai-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A6%E0%A5%81%E0%A4%AC%E0%A4%88%E0%A4%AA%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%86%E0%A4%A3-%E0%A4%86%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B7%E0%A4%95-%E0%A4%B9-%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KDOAo</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/operation-sindoor-broke-the-yoke-of-pakistans-sins.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-mumbai-dahihandi-mahapalik-dahihandi-and-challage-to-uddhav-thackeray-bmc-election-1377445</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mumbai-within-59-minutes-metro-local-railway-bus-roadways-to-become-congestion-free/articleshow/123316080.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/police-bharati-maharashtra-cabinet-decisions-today-under-cm-devendra-fadnavis-15000-police-bharti-know-details-in-marathi-1376621</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/emotional-moment-as-bdd-residents-get-their-dream-home-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-india-independence-day-cm-fadnavis-dy-cms-opposition-leaders-hoist-flag-across-maharashtra-delhi-rahul-gandhi-in-rain-1377336</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-and-ajit-pawar-battle-over-additional-municipal-corporations-in-pune/articleshow/123235053.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-stated-bandra-versova-sea-link-will-be-extended-up-to-vadhavan-port-local18-1459825.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/11/gopinath-munde-taught-chief-minister-devendra-fadnavis-to-struggle-without-compromising-with-power-home-minist.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B5%E0%A4%B2%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%8A%E0%A4%A8%E0%A4%B9-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%98%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%82%E0%A4%AE%E0%A4%A4-%E0%A4%95%E0%A4%B6-%E0%A4%95-%E0%A4%AF/ar-AA1KA4bi?cvid=709e293f49bb433db28c9ad0d1e1c64d</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://marathi.ndtv.com/maharashtra/worli-bdd-chawl-redevelopment-program-cm-devendra-fadnavis-speech-dharavi-project-9083348</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A6%E0%A4%B9-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%95-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F/ar-AA1KD8k2</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-news-controversy-over-state-level-oratory-competition-on-the-occasion-of-chief-minister-devendra-fadnavis/articleshow/123257068.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9A-%E0%A4%AB-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KE0LG</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/congress-sangli-leader-prithviraj-patil-resigns-to-join-bjp-in-presence-of-devendra-fadnavis/articleshow/123269760.cms</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/harshvardhan-sapkal-on-devendra-fadanvis-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%9A%E0%A5%87-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%87/ar-AA1KbAUb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%82%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF/ar-AA1KyPVX</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/fadnavis-targets-thackeray-camp-we-broke-the-pot-of-corruption-in-bmc-now-development-will-flow/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-calling-vegetarians-impotent-is-foolish-chief-minister-devendra-fadnavis/911740/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jaimaharashtranews.com/video-story/vvvtqkxjy3fptfd3cnjbsi1qyun0dhf3lklevjzry3qwaktr/ac686946/cdf73399/ed2025af/8051239e/videodetails/4</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%96%E0%A5%87%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%86%E0%A4%B2-%E0%A4%9A-%E0%A4%AC-%E0%A4%A1-%E0%A4%A1-%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1KcLlH</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B2-%E0%A4%A8-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%87%E0%A4%B6%E0%A4%B5%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AD-%E0%A4%A4-%E0%A4%96-%E0%A4%8A%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A5%AC%E0%A5%AB-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%A8/ar-AA1KqsEZ</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/jain-muni-nileshchandra-appeal-to-cm-devendra-fadnavis-over-dadar-kabutar-khana-issue-9075708</t>
+          <t>https://marathi.abplive.com/news/maharashtra/manoj-jarange-patil-criticizes-on-chief-minister-devendra-fadnavis-on-maratha-reservation-nanded-1377172</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-uddhav-thackeray-before-criticizing-devendra-fadnavis-look-in-the-mirror-public-not-forgotten-rs-100-crore-recovery-case-maharashtra-politics-marathi-news-1376412</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-big-announcement-for-mumbai-dabewala-will-give-a-500-square-feet-house-for-25-lakhs-1458046.html</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/third-mumbai-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A6%E0%A5%81%E0%A4%AC%E0%A4%88%E0%A4%AA%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%86%E0%A4%A3-%E0%A4%86%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B7%E0%A4%95-%E0%A4%B9-%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KDOAo</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-mns-raj-thackeray-over-mumbai-municipal-bmc-elections/articleshow/123306829.cms</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/operation-sindoor-broke-the-yoke-of-pakistans-sins.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ubt-leader-sanjay-raut-talk-on-cm-devendra-fadnavis-in-press-conference/articleshow/123271049.cms</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mumbai-within-59-minutes-metro-local-railway-bus-roadways-to-become-congestion-free/articleshow/123316080.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-ubt-mns-aim-to-prevent-mumbai-from-gujarati-people-says-sanjay-raut/articleshow/123340988.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/emotional-moment-as-bdd-residents-get-their-dream-home-maha-mtb.html</t>
+          <t>https://www.saamana.com/sanjay-raut-media-briefing-in-nashik-slams-pm-modi-devendra-fadnavis-and-bjp-on-independence/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-vice-presidential-election-nda-nominates-cp-radhakrishnan-rajnath-singh-calls-kharge-for-unopposed-poll-india-alliance-to-meet-1377786</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-and-ajit-pawar-battle-over-additional-municipal-corporations-in-pune/articleshow/123235053.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/11/gopinath-munde-taught-chief-minister-devendra-fadnavis-to-struggle-without-compromising-with-power-home-minist.html</t>
+          <t>https://prahaar.in/2025/08/18/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B5%E0%A4%B2%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%8A%E0%A4%A8%E0%A4%B9-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%98%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%82%E0%A4%AE%E0%A4%A4-%E0%A4%95%E0%A4%B6-%E0%A4%95-%E0%A4%AF/ar-AA1KA4bi?cvid=709e293f49bb433db28c9ad0d1e1c64d</t>
+          <t>https://news18marathi.com/maharashtra/pankaja-munde-emotional-speech-at-latur-gopinath-munde-statue-inauguration-latur-1455554.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/worli-bdd-chawl-redevelopment-program-cm-devendra-fadnavis-speech-dharavi-project-9083348</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-news-controversy-over-state-level-oratory-competition-on-the-occasion-of-chief-minister-devendra-fadnavis/articleshow/123257068.cms</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/congress-sangli-leader-prithviraj-patil-resigns-to-join-bjp-in-presence-of-devendra-fadnavis/articleshow/123269760.cms</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/devendra-fadnavis-appeal-to-public-ganeshotsav-committees-958689.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/third-mumbai-can-be-bigger-and-more-attractive-than-dubai-says-cm-devendra-fadnavis-article-152473589</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-slams-cm-devendra-fadnavis-and-mahayuti-government-in-mumbai-speech-1376389</t>
+          <t>https://www.dainikprabhat.com/alandi-news-universal-thoughts-in-dnyaneshwari-are-the-root-of-indian-culture-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%82%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF/ar-AA1KyPVX</t>
+          <t>https://vishwanewsmarathi.com/devendra-fadnavis-is-not-the-chief-but-a-thief-minister-thackerays-attack/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-calling-vegetarians-impotent-is-foolish-chief-minister-devendra-fadnavis/911740/</t>
+          <t>https://vishwanewsmarathi.com/rightful-houses-for-workers-of-solapur-houses-distributed-by-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-thackeray-group-morcha-kabutar-khana-thalak-batmya-monday-11-august-2025-1466781.html</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B2-%E0%A4%A8-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%87%E0%A4%B6%E0%A4%B5%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AD-%E0%A4%A4-%E0%A4%96-%E0%A4%8A%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A5%AC%E0%A5%AB-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%A8/ar-AA1KqsEZ</t>
+          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-big-announcement-for-solapur-residents-will-thousands-of-youth-get-employment/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/manoj-jarange-patil-criticizes-on-chief-minister-devendra-fadnavis-on-maratha-reservation-nanded-1377172</t>
+          <t>https://www.dainikprabhat.com/houses-in-mumbai-are-worth-gold-keep-them-safe-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-big-announcement-for-mumbai-dabewala-will-give-a-500-square-feet-house-for-25-lakhs-1458046.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-mns-raj-thackeray-over-mumbai-municipal-bmc-elections/articleshow/123306829.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/it-park-will-be-set-up-in-solapur-says-cm-devendra-fadnavis-article-152478385</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ubt-leader-sanjay-raut-talk-on-cm-devendra-fadnavis-in-press-conference/articleshow/123271049.cms</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-ubt-mns-aim-to-prevent-mumbai-from-gujarati-people-says-sanjay-raut/articleshow/123340988.cms</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-public-awareness-should-be-created-about-vermilion-and-swadeshi-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-vice-presidential-election-nda-nominates-cp-radhakrishnan-rajnath-singh-calls-kharge-for-unopposed-poll-india-alliance-to-meet-1377786</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-committee-formed-for-those-industries-chief-minister-devendra-fadnavis-gave-information/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-media-briefing-in-nashik-slams-pm-modi-devendra-fadnavis-and-bjp-on-independence/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-dabbawalas-will-get-500-square-feet-house-in-25-lakh-50-thousand-cm-devendra-fadnavis-big-annoucement-for-dabbawala-article-152466274</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.dainikprabhat.com/devendra-fadanvis-cant-bear-it-cant-even-say-it-devendra-fadnaviss-attack-on-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/08/18/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/the-historic-sword-of-the-brave-maratha-sardar-raghuji-bhosale-is-in-the-possession-of-the-government-when-will-it-be-brought-to-mumbai/129289/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/pankaja-munde-emotional-speech-at-latur-gopinath-munde-statue-inauguration-latur-1455554.html</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-orders-give-preference-to-locals-in-railway-bogie-factory/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-government-s-cabinet-approves-recruitment-of-15000-police-officers-125081200048_1.html</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/devendra-fadanvis-chief-minister-devendra-fadanvis-clear-opinion-on-tariff-said-the-industries-that-will-be-affected/128946/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://www.thodkyaat.com/manoj-jaranges-ultimatum-to-government-threatens-chalo-mumbai-on-august-29/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/we-broke-the-pot-of-sin-chief-minister-fadnavis/</t>
+          <t>https://marathi.ndtv.com/cities/chief-minister-devendra-fadnavis-announces-that-mumbai-dabbawalas-will-get-houses-worth-rs-25-50-lakh-9087324</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/third-mumbai-can-be-bigger-and-more-attractive-than-dubai-says-cm-devendra-fadnavis-article-152473589</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/alandi-news-universal-thoughts-in-dnyaneshwari-are-the-root-of-indian-culture-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/cm-devendra-fadnavis-takes-big-decision-transfer-7-ias-officer-in-state-88422</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/devendra-fadnavis-is-not-the-chief-but-a-thief-minister-thackerays-attack/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-dahi-handi-2025-live-updates-16-august-heavy-rain-alert-mumbai-thane-rain-updates-kvg-85-5307740/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.loksatta.com/photos/news/5301075/marathi-ekikaran-samiti-agitation-at-kabutar-khana-mumbai-what-did-they-say/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/rightful-houses-for-workers-of-solapur-houses-distributed-by-chief-minister-fadnavis/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-12-political-news-in-marathi-931564</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-nagpur-high-speed-rail-project-parallel-lines-to-samruddhi-mahamarg-know-detail-by-cm-devendra-fadnavis-article-152450605</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-big-announcement-for-solapur-residents-will-thousands-of-youth-get-employment/</t>
+          <t>https://lokmanthan.com/give-priority-to-locals-for-employment-in-railway-bogie-factory-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/houses-in-mumbai-are-worth-gold-keep-them-safe-devendra-fadnavis/</t>
+          <t>http://www.msn.com/en-in/news/India/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav/ar-AA1KiaOZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/seat-sharing-formula-for-mumbai-civic-election-will-depend-on-party-strength-says-cm-fadnavis/articleshow/123288144.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/it-park-will-be-set-up-in-solapur-says-cm-devendra-fadnavis-article-152478385</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-savvy-maharashtra-cm-fadnavis-gives-ipads-to-ministers-to-ensure-cabinet-agenda-secrecy/articleshow/123242160.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-public-awareness-should-be-created-about-vermilion-and-swadeshi-devendra-fadnavis/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/mumbais-journey-to-become-slum-free-cm-fadnavis-emphasizes-rapid-redevelopment/123320003</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-committee-formed-for-those-industries-chief-minister-devendra-fadnavis-gave-information/</t>
+          <t>https://www.ptinews.com/editor-detail/We-missed-the-bus-earlier--no-compromise-on-Mumbai-s-development-now--Fadnavis/2823252</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-dabbawalas-will-get-500-square-feet-house-in-25-lakh-50-thousand-cm-devendra-fadnavis-big-annoucement-for-dabbawala-article-152466274</t>
+          <t>https://www.ptinews.com/editor-detail/Quota-activist-Jarange-lost-credibility--his-remote-control-is-in-Sharad-Pawar-s-hands--BJP-MLC/2816227</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadanvis-cant-bear-it-cant-even-say-it-devendra-fadnaviss-attack-on-rahul-gandhi/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/the-historic-sword-of-the-brave-maratha-sardar-raghuji-bhosale-is-in-the-possession-of-the-government-when-will-it-be-brought-to-mumbai/129289/</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/pune-university-withdraws-voice-of-devendra-competition-notice-after-objection-from-nsui/123300501</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-orders-give-preference-to-locals-in-railway-bogie-factory/</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-government-s-cabinet-approves-recruitment-of-15000-police-officers-125081200048_1.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/devendra-fadanvis-chief-minister-devendra-fadanvis-clear-opinion-on-tariff-said-the-industries-that-will-be-affected/128946/</t>
+          <t>https://www.latestly.com/agency-news/india-news-newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis-7056055.html</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/manoj-jaranges-ultimatum-to-government-threatens-chalo-mumbai-on-august-29/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%9D%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%A8%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B2-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A4%9A-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A4%82-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%AE-%E0%A4%A6-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%B2/ar-AA1KwUDj</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chief-minister-devendra-fadnavis-announces-that-mumbai-dabbawalas-will-get-houses-worth-rs-25-50-lakh-9087324</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/now-we-have-to-build-a-dahi-handi-of-self-reliance-chief-ministers-statement-at-shivraj-pratishthans-dahi-hand.html</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/11-years-of-modi-government-indias-development-and-global-trust.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/cm-devendra-fadnavis-takes-big-decision-transfer-7-ias-officer-in-state-88422</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/support-modi-government-in-its-journey-of-development-minister-shri-mangalprabhat-lodha.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5301075/marathi-ekikaran-samiti-agitation-at-kabutar-khana-mumbai-what-did-they-say/</t>
+          <t>https://www.loksatta.com/maharashtra/sindhudurg-district-uddhav-thackeray-shiv-sena-agitation-against-state-government-css-98-5296933/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-12-political-news-in-marathi-931564</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-nagpur-high-speed-rail-project-parallel-lines-to-samruddhi-mahamarg-know-detail-by-cm-devendra-fadnavis-article-152450605</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/since-2014-the-modi-government-has-taken-a-firm-step-away-from-past-practices-and-given-top-priority-to-nation.html</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/give-priority-to-locals-for-employment-in-railway-bogie-factory-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/in-2014-power-changed-in-india-but-the-potential-change-in-foreign-policy-that-accompanied-the-change-in-power.html</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/articleshow/123290009.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/there-is-no-shortage-of-athletes-in-our-country-the-most-populous-in-the-world.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav/ar-AA1KiaOZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/the-governments-that-came-to-power-in-the-post-independence-era-gave-the-slogan-of-poverty-eradication.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-savvy-maharashtra-cm-fadnavis-gives-ipads-to-ministers-to-ensure-cabinet-agenda-secrecy/articleshow/123242160.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/government-policies-have-given-new-energy-to-the-startup-culture-in-india.html</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://breakingmaharashtra.in/?p=39156</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/actor-complains-about-redevelopment-project-fraud-cm-intervenes-101755026135161.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/many-workers-including-former-nagsevaks-of-bahujan-vikas-aaghadi-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/mumbais-journey-to-become-slum-free-cm-fadnavis-emphasizes-rapid-redevelopment/123320003</t>
+          <t>https://dainikekmat.com/%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%A6%E0%A4%BF%E0%A4%A8%E0%A5%80%E0%A4%9A-%E0%A4%AE%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A4%BE/113567/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/We-missed-the-bus-earlier--no-compromise-on-Mumbai-s-development-now--Fadnavis/2823252</t>
+          <t>http://www.msn.com/en-in/news/India/script-by-salim-javed-fadnavis-mocks-rahul-s-vote-chori-claims-says-congress-chief-is-speaking-fiction/ar-AA1Ka5DS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/17/bom26-mh-vp-candidate-ld-fadnavis.html</t>
+          <t>https://www.deccanherald.com/opinion/election-commission-and-the-trust-it-must-rebuild-3678073</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Quota-activist-Jarange-lost-credibility--his-remote-control-is-in-Sharad-Pawar-s-hands--BJP-MLC/2816227</t>
+          <t>http://www.msn.com/en-in/news/India/uddhav-thackeray-s-last-row-seat-at-rahul-gandhi-dinner-meet-gets-bjp-taunt/ar-AA1Kc4YH?cvid=6e808800d5b0453f91562cfa362d3523&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ex-mla-from-maharashtra-says-he-too-was-offered-voter-fraud-services/articleshow/123349170.cms</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/pune-university-withdraws-voice-of-devendra-competition-notice-after-objection-from-nsui/123300501</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
+          <t>https://timesofindia.indiatimes.com/city/indore/cm-leads-tiranga-rally-in-indore-criticises-rahul-gandhi/articleshow/123289456.cms</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statement-in-pune-court-apprehending-threat-to-rahuls-life-being-withdrawn-congress-spokespersons/articleshow/123289899.cms</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis-7056055.html</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/my-bihar-yatra-is-to-save-democracy-says-rahul/articleshow/123308887.cms</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/script-by-salim-javed-fadnavis-mocks-rahul-s-vote-chori-claims-says-congress-chief-is-speaking-fiction/ar-AA1Ka5DS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/surrendered-maoist-commander-returns-home-to-celebrate-i-day/articleshow/123339065.cms</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/election-commission-and-the-trust-it-must-rebuild-3678073</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/uddhav-thackeray-s-last-row-seat-at-rahul-gandhi-dinner-meet-gets-bjp-taunt/ar-AA1Kc4YH?cvid=6e808800d5b0453f91562cfa362d3523&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.news18.com/videos/india/fight-to-save-constitution-says-rahul-gandhi-as-police-detain-opposition-mps-amid-protest-9498093.html</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ex-mla-from-maharashtra-says-he-too-was-offered-voter-fraud-services/articleshow/123349170.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://m.economictimes.com/news/india/red-fort-2025-guest-list-vips-special-guests-and-leaders-joining-the-ceremony/historical-significance/slideshow/123258949.cms</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/indore/cm-leads-tiranga-rally-in-indore-criticises-rahul-gandhi/articleshow/123289456.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bailey-bridges-set-to-bring-year-round-connectivity-to-14-gadchiroli-villages/articleshow/123339082.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statement-in-pune-court-apprehending-threat-to-rahuls-life-being-withdrawn-congress-spokespersons/articleshow/123289899.cms</t>
+          <t>https://www.business-standard.com/india-news/rahul-gandhi-kharge-extend-greetings-to-nation-on-79th-independence-day-125081500455_1.html</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/patna/my-bihar-yatra-is-to-save-democracy-says-rahul/articleshow/123308887.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/guwahati/himanta-calls-rahul-traitor-slams-priyankas-proposed-visit-to-dhubri/articleshow/123080085.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/surrendered-maoist-commander-returns-home-to-celebrate-i-day/articleshow/123339065.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/bjp-mla-wants-daily-screening-of-at-least-1-marathi-film-in-all-theatres-across-maharashtra-writes-to-cm-cultural-minister/articleshow/123311633.cms</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tricolour-rises-in-maoist-hq-foothills-kawandes-first-tryst-with-independence-day/articleshow/123310883.cms</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/india/fight-to-save-constitution-says-rahul-gandhi-as-police-detain-opposition-mps-amid-protest-9498093.html</t>
+          <t>https://arunachal24.in/rahul-gandhi-alleges-massive-voter-fraud-accuses-election-commission-of-collusion-with-bjp/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/cong-prepares-for-rahuls-yatra-evades-question-on-oppn-cm-face/articleshow/123285236.cms</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/red-fort-2025-guest-list-vips-special-guests-and-leaders-joining-the-ceremony/historical-significance/slideshow/123258949.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bailey-bridges-set-to-bring-year-round-connectivity-to-14-gadchiroli-villages/articleshow/123339082.cms</t>
+          <t>https://m.economictimes.com/news/india/9-indian-monuments-and-places-that-tell-the-story-of-freedom/red-fort-delhi/slideshow/123275019.cms</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/rahul-gandhi-kharge-extend-greetings-to-nation-on-79th-independence-day-125081500455_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/guwahati/himanta-calls-rahul-traitor-slams-priyankas-proposed-visit-to-dhubri/articleshow/123080085.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/bjp-mla-wants-daily-screening-of-at-least-1-marathi-film-in-all-theatres-across-maharashtra-writes-to-cm-cultural-minister/articleshow/123311633.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cji-gavai-to-inaugurate-bombay-high-courts-circuit-bench-at-kolhapur-today/articleshow/123338656.cms</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tricolour-rises-in-maoist-hq-foothills-kawandes-first-tryst-with-independence-day/articleshow/123310883.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://arunachal24.in/rahul-gandhi-alleges-massive-voter-fraud-accuses-election-commission-of-collusion-with-bjp/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/patna/cong-prepares-for-rahuls-yatra-evades-question-on-oppn-cm-face/articleshow/123285236.cms</t>
+          <t>https://www.zoomnews.in/en/news-detail/evm-tampering-sir-vote-theft-is-rahuls-conflict-with-ec-increasing-1.html</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%B5%E0%A4%B9-%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%87%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4-%E0%A4%AE-%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%87%E0%A4%82%E0%A4%A1-%E0%A4%AF-%E0%A4%AC%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%AC%E0%A5%88%E0%A4%A0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4%E0%A4%82%E0%A4%9C/ar-AA1K9Ujk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/9-indian-monuments-and-places-that-tell-the-story-of-freedom/red-fort-delhi/slideshow/123275019.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-doubtful-voters-made-rahul-gandhi-win-raebareli-2025-08-13-1155872</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/160-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%9F%E0%A4%B2%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%AF-%E0%A4%A6/ar-AA1KcU3e?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-india-block-s-show-of-strength-will-march-to-the-election-commission-office-under-led-of-rahul-gandhi-2025-08-11-1155278</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cji-gavai-to-inaugurate-bombay-high-courts-circuit-bench-at-kolhapur-today/articleshow/123338656.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-march-on-vote-theft-could-rahul-gandhi-become-in-charge-2025-08-11-1155436</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.indiatv.in/video/kurukshetra/will-the-election-commission-take-rahul-gandhi-to-court-over-vote-theft-allegations-2025-08-12-1155626</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.zoomnews.in/en/news-detail/evm-tampering-sir-vote-theft-is-rahuls-conflict-with-ec-increasing-1.html</t>
+          <t>https://bharatexpress.com/india/independence-day-2025-rahul-gandhi-congratulated-on-79th-independence-day-said-it-is-the-duty-of-all-of-us-to-protect-the-pride-and-honor-of-the-precious-heritage-551556</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%B5%E0%A4%B9-%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%87%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4-%E0%A4%AE-%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%87%E0%A4%82%E0%A4%A1-%E0%A4%AF-%E0%A4%AC%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%AC%E0%A5%88%E0%A4%A0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4%E0%A4%82%E0%A4%9C/ar-AA1K9Ujk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A%E0%A5%87-5-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%A6-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B3-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1K51qk</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-doubtful-voters-made-rahul-gandhi-win-raebareli-2025-08-13-1155872</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-india-independence-day-cm-fadnavis-dy-cms-opposition-leaders-hoist-flag-across-maharashtra-delhi-rahul-gandhi-in-rain-1377336</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/160-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%9F%E0%A4%B2%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%AF-%E0%A4%A6/ar-AA1KcU3e?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-first-side-every-claim-of-rahul-gandhi-is-unacceptable-shehzad-poonawala-amy-95-5297251/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-india-block-s-show-of-strength-will-march-to-the-election-commission-office-under-led-of-rahul-gandhi-2025-08-11-1155278</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-criticizes-india-aghadi-and-uddhav-thackerays-protest/910941/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-march-on-vote-theft-could-rahul-gandhi-become-in-charge-2025-08-11-1155436</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/karnataka-supporters-protest-after-rajannas-ouster-doubts-were-cast-on-rahul-gandhis-claim-of-vote-rigging.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/will-the-election-commission-take-rahul-gandhi-to-court-over-vote-theft-allegations-2025-08-12-1155626</t>
+          <t>https://www.msn.com/mr-in/news/other/harshvardhan-sapkal-on-devendra-fadanvis-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%9A%E0%A5%87-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%87/ar-AA1KbAUb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.loksatta.com/desh-videsh/minta-devi-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%BE%E0%A4%9D%E0%A4%BE-%E0%A4%AB%E0%A5%8B%E0%A4%9F-5300887/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/independence-day-2025-rahul-gandhi-congratulated-on-79th-independence-day-said-it-is-the-duty-of-all-of-us-to-protect-the-pride-and-honor-of-the-precious-heritage-551556</t>
+          <t>https://www.loksatta.com/desh-videsh/i-had-the-experience-of-having-tea-with-dead-people-rahul-gandhi-criticizes-election-commission-by-sharing-video-gkt-96-5302274/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A%E0%A5%87-5-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%A6-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B3-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1K51qk</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5297490/india-alliance-parliament-protest-rahul-gandhi-election-commission-photos-viral-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-first-side-every-claim-of-rahul-gandhi-is-unacceptable-shehzad-poonawala-amy-95-5297251/</t>
+          <t>https://www.loksatta.com/politics/bjp-says-sonia-gandhis-name-added-to-voter-list-list-before-indian-citizenship-sdp-92-5301499/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-criticizes-india-aghadi-and-uddhav-thackerays-protest/910941/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-should-have-experimented-with-them-both-hasan-mushrif-counterattack-also-criticizes-rahul-gandhi-1376392</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/rahul-gandhi-the-king-of-fake-news-keshav-upadhyays-criticism.html</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/minta-devi-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%BE%E0%A4%9D%E0%A4%BE-%E0%A4%AB%E0%A5%8B%E0%A4%9F-5300887/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/rahul-gandhi-claims-life-threat-in-pune-court-over-voter-fraud-issue-vvg94</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/i-had-the-experience-of-having-tea-with-dead-people-rahul-gandhi-criticizes-election-commission-by-sharing-video-gkt-96-5302274/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/11/rahul-gandhi-is-a-puppet-of-anti-india-forces-union-minister-shivraj-singh-chouhans-attack.html</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5297490/india-alliance-parliament-protest-rahul-gandhi-election-commission-photos-viral-spl-93/</t>
+          <t>https://www.loksatta.com/desh-videsh/anurag-thakur-criticizes-bjp-over-vote-rigging-issue-amy-95-5302546/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/karnataka-supporters-protest-after-rajannas-ouster-doubts-were-cast-on-rahul-gandhis-claim-of-vote-rigging.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/central-election-commissions-press-conference-today-rahul-gandhis-allegations-likely-to-be-answered.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-says-sonia-gandhis-name-added-to-voter-list-list-before-indian-citizenship-sdp-92-5301499/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/fear-and-run-away-rahul-gandhis-role-in-swatantryaveer-savarkar-defamation-case.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.mymahanagar.com/editorial/agralekha/the-revelation-made-by-sharad-pawar-is-likely-to-undermine-rahul-gandhis-efforts/911074/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/rahul-gandhi-the-king-of-fake-news-keshav-upadhyays-criticism.html</t>
+          <t>https://www.loksatta.com/desh-videsh/maneka-gandhi-expresses-her-opinion-on-supreme-court-order-on-stray-dogs-amy-95-5299752/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/rahul-gandhi-claims-life-threat-in-pune-court-over-voter-fraud-issue-vvg94</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5295848/monsoon-tips-for-immunity-these-10-best-fruits-to-stay-healthy-and-energised-svk-05/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/navimumbai/in-uran-maritime-conference-cm-fadnavis-on-jnpa-and-port-of-singapore-to-build-indias-largest-port-rds-00-5299525/</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5296622/how-to-beat-afternoon-sleepiness-and-boost-energy-with-simple-breathing-exercises-instead-of-coffee-svk-05/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/anurag-thakur-criticizes-bjp-over-vote-rigging-issue-amy-95-5302546/</t>
+          <t>https://www.loksatta.com/desh-videsh/bihar-list-of-voters-dispute-big-deabte-in-supreme-court-what-sc-said-and-what-kapil-sibbal-claims-scj-81-5298737/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/business/finance/nobel-laureate-abhijit-on-trump-50-per-cent-tariff-us-trade-does-russian-oil-import-worth-it-marathi-news-rak-94-5295923/</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5299053/liver-damage-symptoms-on-feet-liver-failure-signs-on-body-solution-expert-advice-dvr-99/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5295848/monsoon-tips-for-immunity-these-10-best-fruits-to-stay-healthy-and-energised-svk-05/</t>
+          <t>https://www.loksatta.com/sampadkiya/features/many-fake-voters-in-voter-list-democracy-bjp-congress-research-team-amy-95-5297141/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5296622/how-to-beat-afternoon-sleepiness-and-boost-energy-with-simple-breathing-exercises-instead-of-coffee-svk-05/</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5297669/5-biggest-gold-mines-in-india-kolar-hutti-sonbhadra-ramagiri-gold-field-know-the-details-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/bihar-list-of-voters-dispute-big-deabte-in-supreme-court-what-sc-said-and-what-kapil-sibbal-claims-scj-81-5298737/</t>
+          <t>https://www.loksatta.com/photos/picture-gallery-others/5298318/how-did-the-netherlands-end-the-problem-of-stray-dogs-what-measures-takern-for-stray-dogs-in-indian-cities-including-mumbai-aam-93/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5299053/liver-damage-symptoms-on-feet-liver-failure-signs-on-body-solution-expert-advice-dvr-99/</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5298525/mumbai-ganpati-bappa-maha-aagman-sohala-sunday-10-august-2025-lalbaug-parel-photos-sdn-96/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5297669/5-biggest-gold-mines-in-india-kolar-hutti-sonbhadra-ramagiri-gold-field-know-the-details-spl-93/</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5298218/surya-gochar-in-singh-rashi-leo-virgo-and-aquarius-will-get-new-job-and-success-in-business-sap-20/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/picture-gallery-others/5298318/how-did-the-netherlands-end-the-problem-of-stray-dogs-what-measures-takern-for-stray-dogs-in-indian-cities-including-mumbai-aam-93/</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5302433/ncp-has-entrusted-suraj-chavan-with-a-big-responsibility-appointed-as-ncps-regional-general-secretary-gkt-96/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5298525/mumbai-ganpati-bappa-maha-aagman-sohala-sunday-10-august-2025-lalbaug-parel-photos-sdn-96/</t>
+          <t>https://www.loksatta.com/photos/news/5302284/dhananjay-munde-government-bungalow-row-karuna-munde-slams-says-he-have-many-flats-in-mumbai-kvg-85/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5298218/surya-gochar-in-singh-rashi-leo-virgo-and-aquarius-will-get-new-job-and-success-in-business-sap-20/</t>
+          <t>https://www.loksatta.com/mumbai/borivali-religious-events-in-sanjay-gandhi-national-park-sparks-outrage-from-environmentalist-mumbai-print-news-rds-00-5296674/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5302433/ncp-has-entrusted-suraj-chavan-with-a-big-responsibility-appointed-as-ncps-regional-general-secretary-gkt-96/</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5301397/mukesh-ambanis-wealth-on-twelth-of-indias-gdp-check-indias-top-10-wealthiest-families-kvg-85/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5302284/dhananjay-munde-government-bungalow-row-karuna-munde-slams-says-he-have-many-flats-in-mumbai-kvg-85/</t>
+          <t>https://www.loksatta.com/thane/jitendra-awhad-sharad-pawar-ncp-protest-against-election-commission-in-mumbra-css-98-5299492/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5301397/mukesh-ambanis-wealth-on-twelth-of-indias-gdp-check-indias-top-10-wealthiest-families-kvg-85/</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5302315/these-special-bollywood-movies-still-rule-the-hearts-of-the-people-today-how-many-of-these-have-you-seen-scj-81/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/jitendra-awhad-sharad-pawar-ncp-protest-against-election-commission-in-mumbra-css-98-5299492/</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5302393/jui-gadkari-shares-his-bond-with-madhubhau-aka-narayan-jadhav-in-serial-and-real-life-ssm-00/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5302315/these-special-bollywood-movies-still-rule-the-hearts-of-the-people-today-how-many-of-these-have-you-seen-scj-81/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-river-flood-study-causes-of-flooding-solutions-rain-koyna-dam-ssb-93-5300066/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5302393/jui-gadkari-shares-his-bond-with-madhubhau-aka-narayan-jadhav-in-serial-and-real-life-ssm-00/</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5299829/maharashtrachi-hasyajatra-fame-nimish-kulkarni-also-part-of-chala-hawa-yeu-dya-2-with-gaurav-more-ssm-00/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5299829/maharashtrachi-hasyajatra-fame-nimish-kulkarni-also-part-of-chala-hawa-yeu-dya-2-with-gaurav-more-ssm-00/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nandurbar/padmakar-valvi-to-join-ajit-pawar-led-ncp-after-leaving-bjp-congress-in-nandurbar/articleshow/123273982.cms</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nandurbar/padmakar-valvi-to-join-ajit-pawar-led-ncp-after-leaving-bjp-congress-in-nandurbar/articleshow/123273982.cms</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5293131/hsrp-number-plate-deadline-and-fine-only-a-few-days-left-to-install-hsrp-number-plates-otherwise-you-will-have-to-pay-a-heavy-fine-gkt-96/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5293131/hsrp-number-plate-deadline-and-fine-only-a-few-days-left-to-install-hsrp-number-plates-otherwise-you-will-have-to-pay-a-heavy-fine-gkt-96/</t>
+          <t>https://www.loksatta.com/manoranjan/bollywood/jaya-bhaduri-father-said-mera-parivar-barbad-ho-gaya-after-daughter-married-to-amitabh-bachchan-hrc-97-5297540/</t>
         </is>
       </c>
     </row>
@@ -3637,42 +3637,42 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/karnataka-netas-unite-to-oppose-fadnavis-over-almatti-height/ar-AA1GbrxF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/other/government-is-beggar-maharashtra-minister-manikrao-kokate-sparks-row-with-fresh-remark-cm-fadnavis-terms-it-inappropriate/ar-AA1J47YX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pcmc/pune-news-illegal-construction-on-pavana-river-flood-line-sparks-controversy/</t>
+          <t>http://www.msn.com/en-in/news/India/karnataka-netas-unite-to-oppose-fadnavis-over-almatti-height/ar-AA1GbrxF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3541769-meat-ban-controversy-on-independence-day-ignites-debate-in-maharashtra</t>
+          <t>http://www.msn.com/en-in/news/india/eknath-shinde-slams-uddhav-thackeray-amid-fadnavis-meet-buzz-changed-colours-like-a-chameleon/ar-AA1IS5La?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/politics/maharashtra-federation-demands-national-meat-sale-calendar-amid-non-veg-row/story</t>
+          <t>https://punemirror.com/city/pcmc/pune-news-illegal-construction-on-pavana-river-flood-line-sparks-controversy/</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE-%E0%A4%9F-%E0%A4%95-%E0%A4%A6%E0%A5%81%E0%A4%95-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%87%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%A8-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%9A-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Ksgnw</t>
+          <t>https://www.devdiscourse.com/article/politics/3538922-clashes-over-maratha-quota-a-political-tug-of-war</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://hindi.newsbytesapp.com/news/india/maharashtra-meat-ban-on-independence-day-whats-the-controversy/story</t>
+          <t>https://www.devdiscourse.com/article/law-order/3541769-meat-ban-controversy-on-independence-day-ignites-debate-in-maharashtra</t>
         </is>
       </c>
     </row>
@@ -3700,1820 +3700,1820 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/shiv-sena-tensions-flare-over-raigad-nashik-flag-hoisting-guardian-minister-dispute-ntcpmm-dskc-2308822-2025-08-12</t>
+          <t>https://www.hindisaamana.com/cold-war-on-guardian-minister-controversy-shinde-stays-away-from-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/cold-war-on-guardian-minister-controversy-shinde-stays-away-from-cabinet-meeting/</t>
+          <t>https://www.theindiadaily.com/india/there-is-uproar-in-maharashtra-over-meat-ban-opposition-opened-front-warned-of-protest-outside-kdmc-office-news-89830</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/there-is-uproar-in-maharashtra-over-meat-ban-opposition-opened-front-warned-of-protest-outside-kdmc-office-news-89830</t>
+          <t>https://www.hindisaamana.com/political-temperature-rises-in-mahayuti-dissatisfaction-rising-in-shinde-faction/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/political-temperature-rises-in-mahayuti-dissatisfaction-rising-in-shinde-faction/</t>
+          <t>https://bharatexpress.com/legal/supreme-court-hearing-on-elephant-mahadevi-transfer-to-vantara-jamnagar-controversy-549836</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/legal/supreme-court-hearing-on-elephant-mahadevi-transfer-to-vantara-jamnagar-controversy-549836</t>
+          <t>https://www.travelandleisureasia.com/in/news/nagpur-pune-vande-bharat-express-becomes-longest-in-india/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.travelandleisureasia.com/in/news/nagpur-pune-vande-bharat-express-becomes-longest-in-india/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pm-flags-off-nagpur-pune-vande-bharat-cm-attends-nagpur-launch-101754853627589.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pm-flags-off-nagpur-pune-vande-bharat-cm-attends-nagpur-launch-101754853627589.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ngp-pune-vande-bharat-oversubscribed-waiting-list-crosses-150-for-sunday-journey/articleshow/123339056.cms</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ngp-pune-vande-bharat-oversubscribed-waiting-list-crosses-150-for-sunday-journey/articleshow/123339056.cms</t>
+          <t>https://www.newsonair.gov.in/pm-narendra-modi-flags-off-three-vande-bharat-trains-from-ksr-railway-station-in-bengaluru/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/pm-narendra-modi-flags-off-three-vande-bharat-trains-from-ksr-railway-station-in-bengaluru/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/14/palak-excels-as-nagpur-eves-get-better-of-thane.html</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/14/palak-excels-as-nagpur-eves-get-better-of-thane.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/maharashtra-govt-singapore-partner-for-350-bedded-multi-speciality-hospital-in-city.html</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/maharashtra-govt-singapore-partner-for-350-bedded-multi-speciality-hospital-in-city.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/rtmnu-to-shift-examination-deptt-to-maharajbag-campus.html</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/rtmnu-to-shift-examination-deptt-to-maharajbag-campus.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/shriram-urban-cooperative-bank-posts-net-profit-of-rs-12995-lakh-.html</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/shriram-urban-cooperative-bank-posts-net-profit-of-rs-12995-lakh-.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/nagpur-pune-vande-bharat-express-timings-route-stops-ticket-price-train-number-schedule-and-more-9062515</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/nagpur-pune-vande-bharat-express-timings-route-stops-ticket-price-train-number-schedule-and-more-9062515</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-new-railway-route-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0-100-%E0%A4%95-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%9A-%E0%A4%B6-%E0%A4%AB-%E0%A4%B0%E0%A4%B8/ar-AA1KfxgY</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-new-railway-route-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0-100-%E0%A4%95-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%9A-%E0%A4%B6-%E0%A4%AB-%E0%A4%B0%E0%A4%B8/ar-AA1KfxgY</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-ajit-pawar-baramati-kabutar-khana-issue-mumbai-megablock-maharashtra-rain-sunday-10th-august-2025-1466332.html</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-pune-nagpur-news-live-11-august-kabutar-khana-dadar-latest-news-pune-st-bus-metro-breaking-news-sud-02-5295305/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-nagpur-high-speed-rail-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A4%E0%A5%87-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B5%E0%A4%98%E0%A5%8D%E0%A4%AF-2-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%A4-%E0%A4%96%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1KmwMT</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-nagpur-high-speed-rail-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A4%E0%A5%87-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B5%E0%A4%98%E0%A5%8D%E0%A4%AF-2-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%A4-%E0%A4%96%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1KmwMT</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-live-updates-political-crime-sports-national-international-breaking-news-955926.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-live-updates-political-crime-sports-national-international-breaking-news-955926.html</t>
+          <t>https://trak.in/stories/3rd-mumbai-being-developed-by-govt-says-maharashtra-cm/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/st-receives-record-income-of-rs-137-crore-in-four-days-from-beloved-sisters-information-from-transport-ministe.html</t>
+          <t>https://marathi.ndtv.com/cities/ajit-pawar-on-dharavi-redevelopment-project-in-bdd-mhada-home-distribution-9083170</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/3rd-mumbai-being-developed-by-govt-says-maharashtra-cm/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/drps-big-scheme-for-businessmen-in-dharavi-drppl-nmdpl-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/photo/fadnavis-made-a-big-announcement-about-dharavi-it-will-be-built-like-a-new-city-1550</t>
+          <t>https://www.msn.com/en-in/news/India/ensure-timely-completion-of-5-000-mw-solar-agri-feeder-scheme-by-sep-2025-fadnavis/ar-AA1JA6xO</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ajit-pawar-on-dharavi-redevelopment-project-in-bdd-mhada-home-distribution-9083170</t>
+          <t>https://m.economictimes.com/news/india/pm-modis-independence-day-speeches-highlights-a-look-back-from-2025-to-2014/2025-the-era-of-self-reliant-bharat-103-minutes/slideshow/123319643.cms</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/drps-big-scheme-for-businessmen-in-dharavi-drppl-nmdpl-maha-mtb.html</t>
+          <t>https://www.mypunepulse.com/pune-pmc-dismantles-traffic-circle-at-sm-ghule-chowk-in-mohamadwadi-after-residents-protest/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ensure-timely-completion-of-5-000-mw-solar-agri-feeder-scheme-by-sep-2025-fadnavis/ar-AA1JA6xO</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/pm-modis-independence-day-speeches-highlights-a-look-back-from-2025-to-2014/2025-the-era-of-self-reliant-bharat-103-minutes/slideshow/123319643.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/disturbing-that-pms-i-day-speech-didnt-have-nehrus-mention-pawar/articleshow/123339182.cms</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
+          <t>https://newsarenaindia.com/states/sharad-pawar-slams-pm-modi-for-ignoring-nehru-in-i-day-speech/53504</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-pmc-dismantles-traffic-circle-at-sm-ghule-chowk-in-mohamadwadi-after-residents-protest/</t>
+          <t>http://www.msn.com/hi-in/news/other/devendra-fadnavis-on-sharad-pawar-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%A6%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1KdfSS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/fadnavis-says-maharashtra-has-access-to-top-global-tech-to-fight-cybercrime/ar-AA1KhsyI</t>
+          <t>https://www.loksatta.com/mumbai/list-of-spokespersons-of-ncp-sharad-pawar-group-announced-mumbai-print-news-css-98-5299884/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/disturbing-that-pms-i-day-speech-didnt-have-nehrus-mention-pawar/articleshow/123339182.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-thackeray-group-called-him-a-thief-minister-devendra-fadnavis-criticized-uddhav-thackeray-calling-him-a-mandate-thief/911143/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/states/sharad-pawar-slams-pm-modi-for-ignoring-nehru-in-i-day-speech/53504</t>
+          <t>https://www.saamana.com/sanjay-raut-criticized-devendra-fadnavis-over-ban-on-non-veg-on-15th-august/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis-9652523</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-comment-on-manoj-jarange-patil-protest-for-maratha-reservation-in-mumbai-on-august-29-1470254.html/amp</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/devendra-fadnavis-on-sharad-pawar-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%A6%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1KdfSS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-bhaskar-jadhav-comment-on-brahman-samaj-1376769</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/list-of-spokespersons-of-ncp-sharad-pawar-group-announced-mumbai-print-news-css-98-5299884/</t>
+          <t>https://jantaserishta.com/local/maharashtra/farmers-compensation-pending-sharad-pawar-to-discuss-with-chief-minister-4216652</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-alleges-that-the-public-safety-act-is-meant-for-bunch-of-thought/</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-thackeray-group-called-him-a-thief-minister-devendra-fadnavis-criticized-uddhav-thackeray-calling-him-a-mandate-thief/911143/</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-politics-obc-leader-laxman-hake-criticizes-pawar-family-he-warns-devendra-fadnavis-over-maratha-vs-obc-conflict-amid-manoj-jarange-agitation-in-mumbai-maharashtra-news-mhs25081700653</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/agralekha/the-revelation-made-by-sharad-pawar-is-likely-to-undermine-rahul-gandhis-efforts/911074/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%88%E0%A4%B8-%E0%A4%91%E0%A4%AB-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%88-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/ar-AA1KkbZY</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-comment-on-manoj-jarange-patil-protest-for-maratha-reservation-in-mumbai-on-august-29-1470254.html/amp</t>
+          <t>http://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-bhaskar-jadhav-comment-on-brahman-samaj-1376769</t>
+          <t>https://www.lokmat.com/maharashtra/dhananjay-munde-praises-cm-devendra-fadnavis-in-a-public-meeting-is-he-try-to-grab-a-ministerial-position-again-discussion-in-politics-a-a719/amp/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-alleges-that-the-public-safety-act-is-meant-for-bunch-of-thought/</t>
+          <t>https://www.lokmat.com/pune/pune-news-maharashtra-will-have-to-face-a-maratha-vs-obc-conflict-warns-haake-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/can-you-get-reservation-by-criticizing-fadnavis-vikhe-patils-direct-question-97495/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-kabutar-khana-rain-updates-bdd-flats-pranjal-khewalkar-case-thalak-batmya-14th-august-2025-1469014.html</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/those-who-came-to-power-by-cutting-reds-teach-wisdom-rauts-target-97526/</t>
+          <t>https://www.dainikprabhat.com/manoj-jaranges-remote-in-sharad-pawars-hands/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/sharad-pawar-high-level-inquiry-by-election-commission-demand-by-bjp-mla-prashant-bamb-957164.html</t>
+          <t>https://www.thodkyaat.com/sanjay-raut-slams-devendra-fadnavis-over-ban-on-meat-sales-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%88%E0%A4%B8-%E0%A4%91%E0%A4%AB-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%88-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/ar-AA1KkbZY</t>
+          <t>https://www.ainvest.com/news/ibm-maharashtra-collaborate-quantum-computing-initiatives-2508/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/rohit-pawar-criticizes-on-savitribai-phule-pune-university-administration-on-the-issue-of-voice-of-devendra-1376510</t>
+          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/parinay-fuke-criticized-on-manoj-jarange-patil-said-manoj-jarange-remote-is-in-sharad-pawar-hand-criticism-over-cm-devendra-fadnavis-maratha-reservation-1376608</t>
+          <t>https://www.business-standard.com/companies/news/ibm-mumbai-client-centre-maharashtra-quantum-initiative-support-125081301837_1.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-maharashtra-will-have-to-face-a-maratha-vs-obc-conflict-warns-haake-a-a1008/</t>
+          <t>https://www.itvoice.in/ibm-unveils-new-india-client-experience-centre-in-mumbai-and-announces-plans-to-support-government-of-maharashtras-quantum-initiatives</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/manoj-jaranges-remote-in-sharad-pawars-hands/</t>
+          <t>https://economictimes.indiatimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/sanjay-raut-slams-devendra-fadnavis-over-ban-on-meat-sales-on-august-15/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.ainvest.com/news/ibm-maharashtra-collaborate-quantum-computing-initiatives-2508/</t>
+          <t>https://m.economictimes.com/news/india/independence-day-at-red-fort-where-to-book-and-what-to-carry/event-timings/slideshow/123258257.cms</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/chhattisgarh-cm-sai-flags-off-sbi-cyber-security-awareness-van-in-raipur-launches-statewide-drive-against-online-fraud/articleshow/123334545.cms</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/companies/news/ibm-mumbai-client-centre-maharashtra-quantum-initiative-support-125081301837_1.html</t>
+          <t>https://www.jansatta.com/national/maharashtra-politics-uddhav-thackeray-shivsena-bmc-elections-mns-shivena-ubt-raj-thackeray-bmc-elections-news-bjp-shivsena-ubt/4096856/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.itvoice.in/ibm-unveils-new-india-client-experience-centre-in-mumbai-and-announces-plans-to-support-government-of-maharashtras-quantum-initiatives</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-alleges-vote-theft-holds-candle-march-protest-in-nagpur/articleshow/123312003.cms</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/politicians-must-not-hate-any-community-while-ensuring-welfare-of-their-own-fadnavis/articleshow/123244376.cms</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>http://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/independence-day-at-red-fort-where-to-book-and-what-to-carry/event-timings/slideshow/123258257.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/political-buzz-on-janmashtami-festivities-in-mumbai-ahead-of-local-body-polls-3683780</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/chhattisgarh-cm-sai-flags-off-sbi-cyber-security-awareness-van-in-raipur-launches-statewide-drive-against-online-fraud/articleshow/123334545.cms</t>
+          <t>https://www.msn.com/en-in/news/India/mumbai-bahujan-vikas-aaghadi-bva-leaders-cross-over-to-bjp-mahesh-patil-among-new-joinees/ar-AA1KqIKK</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3537336-inclusivity-and-legacy-remembering-gopinath-mundes-vision</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-politics-uddhav-thackeray-shivsena-bmc-elections-mns-shivena-ubt-raj-thackeray-bmc-elections-news-bjp-shivsena-ubt/4096856/</t>
+          <t>https://www.devdiscourse.com/article/politics/3544879-maharashtra-leaders-celebrate-cp-radhakrishnans-vice-presidential-nomination</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-alleges-vote-theft-holds-candle-march-protest-in-nagpur/articleshow/123312003.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3543985-mumbai-dahi-handi-honoring-indias-brave-soldiers</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/politicians-must-not-hate-any-community-while-ensuring-welfare-of-their-own-fadnavis/articleshow/123244376.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/maharashtra/ratnagiri-news-ncp-sharad-pawar-group-leader-prashant-yadav-join-bjp-9083531</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis/2719488/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%86%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%95/ar-AA1KEzpJ</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/political-buzz-on-janmashtami-festivities-in-mumbai-ahead-of-local-body-polls-3683780</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-gets-a-setback-in-konkan-big-leader-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/eknath-shinde-slams-uddhav-thackeray-amid-fadnavis-meet-buzz-changed-colours-like-a-chameleon/ar-AA1IS5La?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary-says-cji-gavai-3684747</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-bahujan-vikas-aaghadi-bva-leaders-cross-over-to-bjp-mahesh-patil-among-new-joinees/ar-AA1KqIKK</t>
+          <t>https://indiplomacy.com/2025/08/15/singapore-deepens-infrastructure-ties-in-maharashtra-with-major-investments/</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
+          <t>https://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ratnagiri-news-ncp-sharad-pawar-group-leader-prashant-yadav-join-bjp-9083531</t>
+          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/versova-bandra-sea-link-on-track-for-two-year-completion-maha-cm/123321974</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%86%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%95/ar-AA1KEzpJ</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/submit-proposal-to-convert-circuit-bench-in-kolhapur-into-permanent-bench-cji-bhushan-gavai-to-hc/articleshow/123349240.cms</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-gets-a-setback-in-konkan-big-leader-joins-bjp/</t>
+          <t>https://www.msn.com/en-in/autos/news/2025-maharashtra-ev-policy-gets-green-signal-subsidies-to-toll-waiver-everything-you-must-know/ar-AA1DTk4A?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary-says-cji-gavai-3684747</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/17/lokmat-global-economic-convention-to-be-held-on-august-18-in-london.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://indiplomacy.com/2025/08/15/singapore-deepens-infrastructure-ties-in-maharashtra-with-major-investments/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjAzNDk=/maharashtra-must-fix-tendering-to-speed-up-infrastructure-work-cm</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment/2812408</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/versova-bandra-sea-link-on-track-for-two-year-completion-maha-cm/123321974</t>
+          <t>https://www.devdiscourse.com/article/business/3538840-maharashtras-digital-leap-rapid-growth-in-data-and-infrastructure</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/submit-proposal-to-convert-circuit-bench-in-kolhapur-into-permanent-bench-cji-bhushan-gavai-to-hc/articleshow/123349240.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3544027-transforming-bhiwandi-a-vision-for-modern-urban-development</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/news/2025-maharashtra-ev-policy-gets-green-signal-subsidies-to-toll-waiver-everything-you-must-know/ar-AA1DTk4A?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thenewsmill.com/2025/08/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/17/lokmat-global-economic-convention-to-be-held-on-august-18-in-london.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3544738-maharashtras-commitment-to-judiciary-kolhapur-gets-a-new-bench</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjAzNDk=/maharashtra-must-fix-tendering-to-speed-up-infrastructure-work-cm</t>
+          <t>https://agrowon.esakal.com/agro-special/will-the-political-power-of-farmers-survive-article-on-agrowon-rat16</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment/2812408</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3538840-maharashtras-digital-leap-rapid-growth-in-data-and-infrastructure</t>
+          <t>https://www.ndtv.com/video/meet-sanjay-india-s-robotic-war-dog-are-robodogs-the-future-of-warfare-978929</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bes21-mp-vote-theft-campaign-cong.html</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3544738-maharashtras-commitment-to-judiciary-kolhapur-gets-a-new-bench</t>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/wayanad-voters-refute-anurag-singh-thakurs-fraud-claims/articleshow/123311455.cms</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/will-the-political-power-of-farmers-survive-article-on-agrowon-rat16</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/des117-hr-rahul-saini.html</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/119-voters-from-one-single-house-cong-alleges-vote-theft-in-chandrapur/articleshow/123312033.cms</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/meet-sanjay-india-s-robotic-war-dog-are-robodogs-the-future-of-warfare-978929</t>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/ec-acting-like-bjp-agent-hebbalkar/articleshow/123325268.cms</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bes21-mp-vote-theft-campaign-cong.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/119-voters-in-one-house-cong-alleges-vote-theft/articleshow/123310094.cms</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kozhikode/wayanad-voters-refute-anurag-singh-thakurs-fraud-claims/articleshow/123311455.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-maharashtra-cm-prithviraj-chavan-backs-stir-over-alleged-bogus-voting-in-karad-south-during-2024-assembly-polls/articleshow/123311995.cms</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/des117-hr-rahul-saini.html</t>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/119-voters-from-one-single-house-cong-alleges-vote-theft-in-chandrapur/articleshow/123312033.cms</t>
+          <t>https://humenglish.com/world/vote-chori-protest-rahul-gandhi-arrested-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/ec-acting-like-bjp-agent-hebbalkar/articleshow/123325268.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/119-voters-in-one-house-cong-alleges-vote-theft/articleshow/123310094.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/sonia-gandhi-was-a-voter-before-becoming-an-indian-citizen-bjp-alleges-that-it-is-congresss-voter-scam.html</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-maharashtra-cm-prithviraj-chavan-backs-stir-over-alleged-bogus-voting-in-karad-south-during-2024-assembly-polls/articleshow/123311995.cms</t>
+          <t>https://www.jagran.com/news/national-debate-erupts-over-closing-meat-shops-in-maharashtra-on-independence-day-24012549.html</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-slams-mahayuti-govt-signals-bmc-shakeup-4214626</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://humenglish.com/world/vote-chori-protest-rahul-gandhi-arrested-in-new-delhi/</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/vice-president-election-2025-pm-modi-gives-big-joy-to-rss-by-nominating-cp-radhakrishnan-ahead-of-100-years-celebration-know-all/articleshow/123377347.cms</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/sonia-gandhi-was-a-voter-before-becoming-an-indian-citizen-bjp-alleges-that-it-is-congresss-voter-scam.html</t>
+          <t>https://www.msn.com/en-in/news/India/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes/ar-AA1Kyjju</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/political-turmoil-in-maharashtra-uddhavs-public-outrage-questions-over-dhanakar-the-dove-seed-controversy-ytvd-2308283-2025-08-12</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-debate-erupts-over-closing-meat-shops-in-maharashtra-on-independence-day-24012549.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/idontknowhomeminister-goes-viral-g-parameshwara-tells-trolls-to-find-out-who-is-the-best/articleshow/123338015.cms</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/fadnavis-slams-mahayuti-govt-signals-bmc-shakeup-4214626</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-maratha-royal-raghuji-bhonsle-returns-home-on-aug-18-after-200-years/articleshow/123244523.cms</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/bastar-kids-visit-city-from-remote-areas-on-edu-expedition/articleshow/123289148.cms</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/vice-president-election-2025-pm-modi-gives-big-joy-to-rss-by-nominating-cp-radhakrishnan-ahead-of-100-years-celebration-know-all/articleshow/123377347.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-says-govt-will-take-steps-to-increase-number-of-loudspeaker-days-for-ganeshotsav/articleshow/123284079.cms</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes/ar-AA1Kyjju</t>
+          <t>https://www.msn.com/en-in/news/India/we-missed-the-bus-earlier-no-compromise-on-mumbais-development-now-fadnavis/ar-AA1KxlQf</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmcs-pot-of-sins-broken-says-maharashtra-cm-devendra-fadnavis-23589784</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/idontknowhomeminister-goes-viral-g-parameshwara-tells-trolls-to-find-out-who-is-the-best/articleshow/123338015.cms</t>
+          <t>http://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-maratha-royal-raghuji-bhonsle-returns-home-on-aug-18-after-200-years/articleshow/123244523.cms</t>
+          <t>http://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-orders-partial-rollback-of-ban-on-feeding-pigeons/ar-AA1JYREe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/bastar-kids-visit-city-from-remote-areas-on-edu-expedition/articleshow/123289148.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year-101755112441600.html</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-says-govt-will-take-steps-to-increase-number-of-loudspeaker-days-for-ganeshotsav/articleshow/123284079.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/museum-to-honour-dabbawalas-to-be-inaugurated-in-mumbai-3677005</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/we-missed-the-bus-earlier-no-compromise-on-mumbais-development-now-fadnavis/ar-AA1KxlQf</t>
+          <t>https://www.businessworld.in/article/ibm-opens-new-mumbai-office-as-gateway-to-viksit-bharat-567381</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/seat-sharing-formula-for-mumbai-civic-election-will-depend-on-party-strength-says-cm-fadnavis/articleshow/123288144.cms</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/Maharashtra-prominent-player-in-Indian%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-orders-partial-rollback-of-ban-on-feeding-pigeons/ar-AA1JYREe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/business/as-chawl-residents-move-into-modern-homes-fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year-101755112441600.html</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/museum-to-honour-dabbawalas-to-be-inaugurated-in-mumbai-3677005</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/ibm-opens-new-mumbai-office-as-gateway-to-viksit-bharat-567381</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/record-10-tier-human-pyramids-lend-thrill-to-mumbais-rainy-dahi-handi-in-poll-year/articleshow/123337445.cms</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-gives-go-ahead-for-recruiment-of-over-15000-constables/articleshow/123261279.cms</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Maharashtra-prominent-player-in-Indian%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
+          <t>https://www.msn.com/en-in/news/India/mumbai-gets-5-km-sea-facing-promenade-coastal-road-to-stay-open-24x7/ar-AA1Kxl74</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/as-chawl-residents-move-into-modern-homes-fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
+          <t>https://www.businessworld.in/article/fadnavis-singapore-leaders-review-phase-2-of-bharat-mumbai-container-terminal-567159</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day20250815151854</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/record-10-tier-human-pyramids-lend-thrill-to-mumbais-rainy-dahi-handi-in-poll-year/articleshow/123337445.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-gives-go-ahead-for-recruiment-of-over-15000-constables/articleshow/123261279.cms</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-gets-5-km-sea-facing-promenade-coastal-road-to-stay-open-24x7/ar-AA1Kxl74</t>
+          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-singapore-leaders-review-phase-2-of-bharat-mumbai-container-terminal-567159</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3543920-thrills-and-politics-dahi-handi-festival-amidst-mumbai-rains</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-13-news-updates-live-updates-weather-update-mumbai-monsoon-18331383</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3540648-mumbai-unveils-new-coastal-promenade-a-green-oasis-by-the-sea</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://www.socialnews.xyz/2025/08/16/mumbai-worli-parivartan-dahi-handi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cabinet-recruitment-police-10184591/lite/</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day20250815151854</t>
+          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%95%E0%A4%AC%E0%A5%82%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%A8-%E0%A4%AF%E0%A4%AE-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JYvBC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-eknath-shinde-aditya-thackeray-on-one-stage-sa-9506059.html</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://marathi.ndtv.com/maharashtra/the-dream-of-mumbai-within-59-minutes-will-be-soon-filfilled-cm-devendra-fadnavis-9089297</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/16/mumbai-worli-parivartan-dahi-handi-gallery/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-on-plan-of-slum-free-mumbai-89066</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/national-stem-challenge-grand-finale-set-for-august-18-19-in-mumbai/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://marathi.abplive.com/web-stories/news/flag-hoisting-on-the-occasion-of-independence-at-high-cout-with-the-presence-of-cm-devendra-fadnavis-1377273</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%95%E0%A4%AC%E0%A5%82%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%A8-%E0%A4%AF%E0%A4%AE-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JYvBC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-announces-that-coastal-road-will-be-open-24-hours-from-august-15/912175/amp</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/the-dream-of-mumbai-within-59-minutes-will-be-soon-filfilled-cm-devendra-fadnavis-9089297</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sclr-to-weh-connector-chembur-to-mumbai-airport-cable-bridge-inaugurated-by-devendra-fadnavis/articleshow/123317604.cms</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/entertainment/actor-kishor-kadam-appeals-to-cm-devendra-fadnavis-to-save-mumbai-residence-details-9065124</t>
+          <t>https://www.mymahanagar.com/mahamumbai/kishor-kadam-seeks-help-from-cm-devendra-fadnavis-to-save-his-house-in-mumbai/911132/</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-on-plan-of-slum-free-mumbai-89066</t>
+          <t>https://news18marathi.com/maharashtra/aaditya-thackeray-welcome-cm-devendra-fadnavis-in-mumbai-maharashtra-politics-news-1457232.html</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-bdd-says-houses-in-mumbai-are-worth-as-much-as-gold-do-not-sell-houses-remember-you-want-to-pass-this-house-on-to-the-next-generation-1377083</t>
+          <t>https://marathi.abplive.com/news/mumbai/mumbai-lagbaghcha-raja-area-firefighters-charage-1-25-lakh-per-day-cm-devendra-fadnavis-assures-ganesh-mandal-of-mumbai-1376931</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://marathi.indiatimes.com/editorial/editorial-on-pune-municipal-corporation-issue-cm-devendra-fadnavis-ajit-pawar/articleshow/123227690.cms</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/news/flag-hoisting-on-the-occasion-of-independence-at-high-cout-with-the-presence-of-cm-devendra-fadnavis-1377273</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-big-statement-on-slaughter-houses-closed-on-independence-day/articleshow/123293008.cms</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-12-hour-electricity-for-farmers-in-the-state-and-steel-hub-in-gadchiroli-chief-minister-assures-on-independence-day-in-mumbai-1377256</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/mumbai-mumbai-worli-largest-dahi-handi-tower-in-mumbai-the-sacrifice-of-sambhaji-maharaj-chhaava-and-kavi-kalash-cm-devendra-fadnavis-clap-1377434</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-announces-that-coastal-road-will-be-open-24-hours-from-august-15/912175/amp</t>
+          <t>https://hindi.latestly.com/india/mumbai-to-receive-several-projects-ahead-of-bmc-elections-metro-3-phase-3-likely-to-be-launched-by-end-of-august-ask-chatgpt-2726817.html</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sclr-to-weh-connector-chembur-to-mumbai-airport-cable-bridge-inaugurated-by-devendra-fadnavis/articleshow/123317604.cms</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/we-broke-the-pot-of-sin-in-mumbai-municipal-corporation-fadnavis-taunts-thackeray-961442.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis-4212867</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/aaditya-thackeray-welcome-cm-devendra-fadnavis-in-mumbai-maharashtra-politics-news-1457232.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-experienced-ai-cricket-simulator-during-the-visit-4210440</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://jantaserishta.com/local/maharashtra/newly-built-capitaland-data-centre-in-mumbai-will-put-india-ahead-in-digital-revolution-fadnavis-4210177</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/worli-bdd-chawl-redevelopment-program-keys-distribution-cm-devendra-fadnavis-speech-today-1469211.html</t>
+          <t>https://www.marathiebatmya.com/mumbai/cm-fadnavis-said-dream-of-mumbai-within-59-minutes-will-soon-be-fulfilled/</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/editorial/editorial-on-pune-municipal-corporation-issue-cm-devendra-fadnavis-ajit-pawar/articleshow/123227690.cms</t>
+          <t>https://joindia.co.in/news/mumbais-development-gets-new-momentum-many-big-projects-of-mmrda-inaugurated-coastal-road-will-be-open-24-hours-from-august-15/</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-big-statement-on-slaughter-houses-closed-on-independence-day/articleshow/123293008.cms</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-rapid-redevelopment-is-needed-for-a-slum-free-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/the-flag-hoisting-will-be-done-by-fadnavis-in-mumbai-and-radhakrishnan-in-pune-15226401</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/mumbai-to-receive-several-projects-ahead-of-bmc-elections-metro-3-phase-3-likely-to-be-launched-by-end-of-august-ask-chatgpt-2726817.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/flag-hoisting-flag-hoisting-ceremony-completed-in-mumbai-thane-and-beed-by-the-chief-minister-and-deputy-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-gets-emotional-after-seeing-the-encampment-on-dahihandi-tower/129236/</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis-4212867</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/eknath-shinde-claims-that-not-a-single-pothole-will-be-seen-in-mumbai-in-the-next-one-and-a-half-years/129057/</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/newly-built-capitaland-data-centre-in-mumbai-will-put-india-ahead-in-digital-revolution-fadnavis-4210177</t>
+          <t>https://www.timemaharashtra.com/politics/politics-in-the-dahi-handi-festival-in-mumbai-fadnavis-hints-at-change/129241/</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/cm-fadnavis-said-dream-of-mumbai-within-59-minutes-will-soon-be-fulfilled/</t>
+          <t>https://www.timemaharashtra.com/politics/cm-devendra-fadnavis-chief-minister-devendra-fadnavis-should-not-be-influenced-by-my-voice-manoj-jarange-patil/128997/</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/mumbais-development-gets-new-momentum-many-big-projects-of-mmrda-inaugurated-coastal-road-will-be-open-24-hours-from-august-15/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-rapid-redevelopment-is-needed-for-a-slum-free-mumbai/</t>
+          <t>https://m.economictimes.com/news/india/cji-gavai-inaugurates-bombay-hcs-4th-bench-in-kolhapur/amp_articleshow/123345149.cms</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/i-day-navroz-and-janmashtami-bring-cheer-to-festive-weekend/articleshow/123309219.cms</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/new-delhi-weather-alert-rainfall-humidity-and-a-cooler-day-ahead-on-august-15-2025/articleshow/123314541.cms</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/flag-hoisting-flag-hoisting-ceremony-completed-in-mumbai-thane-and-beed-by-the-chief-minister-and-deputy-chief-minister/</t>
+          <t>https://timesofindia.indiatimes.com/city/ranchi/school-celebrates-dahi-handi-event/articleshow/123350561.cms</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-gets-emotional-after-seeing-the-encampment-on-dahihandi-tower/129236/</t>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/committee-seeks-deputation-of-physical-education-teachers-to-rural-schools-twice-a-week/articleshow/123325270.cms</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/politics-in-the-dahi-handi-festival-in-mumbai-fadnavis-hints-at-change/129241/</t>
+          <t>https://ddnews.gov.in/en/india-singapore-green-digital-maritime-corridor-takes-center-stage-at-mumbai-dialogue-ahead-of-india-maritime-week-2025/</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/cm-devendra-fadnavis-chief-minister-devendra-fadnavis-should-not-be-influenced-by-my-voice-manoj-jarange-patil/128997/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/kolkata-weather-forecast-patchy-rain-and-humidity-expected-on-august-15-2025/articleshow/123314563.cms</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/mumbai-dabbawalas-to-get-500-sq-ft-homes-at-%E2%82%B925-50-lakh-cm-devendra-fadnavis-announce/</t>
+          <t>https://hindi.newsdanka.com/business/india-maritime-week-2025-preparations-green-digital-corridors/111129/</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/maratha-leader-manoj-jarange-patil-aggressive-for-mumbai-march/articleshow/123323428.cms</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://pudhari.news/maharashtra/marathwada/latur/latur-news-chief-minister-knows-about-art-he-stopped-a-convoy-of-vehicles-and-met-a-young-child-artist-ar84</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/cji-gavai-inaugurates-bombay-hcs-4th-bench-in-kolhapur/amp_articleshow/123345149.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rcnv-team-youth-installs-new-interact-rotaract-leaders-with-green-initiatives/articleshow/123311304.cms</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/i-day-navroz-and-janmashtami-bring-cheer-to-festive-weekend/articleshow/123309219.cms</t>
+          <t>https://www.constructionweekonline.in/business/sukhraj-nahar-becomes-credai-mchi-president</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/new-delhi-weather-alert-rainfall-humidity-and-a-cooler-day-ahead-on-august-15-2025/articleshow/123314541.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/belapur-lake-faces-environmental-threat-warns-citizens-forum/articleshow/123312125.cms</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ranchi/school-celebrates-dahi-handi-event/articleshow/123350561.cms</t>
+          <t>https://indiacsr.in/welspun-living-cultivating-community-value-through-strategic-csr-initiatives/</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/committee-seeks-deputation-of-physical-education-teachers-to-rural-schools-twice-a-week/articleshow/123325270.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/india-singapore-green-digital-maritime-corridor-takes-center-stage-at-mumbai-dialogue-ahead-of-india-maritime-week-2025/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/970-nashik-district-women-voluntarily-opt-out-of-ladki-bahin-scheme/articleshow/123266291.cms</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/kolkata-weather-forecast-patchy-rain-and-humidity-expected-on-august-15-2025/articleshow/123314563.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/pawar-defends-scrutiny-of-ladki-bahin-scheme-beneficiaries/articleshow/123308892.cms</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/business/india-maritime-week-2025-preparations-green-digital-corridors/111129/</t>
+          <t>https://punemirror.com/state/maharashtra-governor-governor-c-p-radhakrishnan-greets-people-on-independence-day/</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/maratha-leader-manoj-jarange-patil-aggressive-for-mumbai-march/articleshow/123323428.cms</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/latur/latur-news-chief-minister-knows-about-art-he-stopped-a-convoy-of-vehicles-and-met-a-young-child-artist-ar84</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B0-%E0%A4%9D%E0%A4%A8-%E0%A4%91%E0%A4%A8-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F-%E0%A4%A1-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%A7-%E0%A4%B9-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%86%E0%A4%B3%E0%A4%82%E0%A4%A6-%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1KAarj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/sukhraj-nahar-becomes-credai-mchi-president</t>
+          <t>http://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%A7-%E0%A4%B2-26-34-%E0%A4%B2-%E0%A4%96-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%85%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1JoWkD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/welspun-living-cultivating-community-value-through-strategic-csr-initiatives/</t>
+          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2-%E0%A4%91%E0%A4%97%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%A7-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%B2-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1KrMRe</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
+          <t>https://www.msn.com/mr-in/news/other/mukhyamantri-ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%AA-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KuMO3</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/970-nashik-district-women-voluntarily-opt-out-of-ladki-bahin-scheme/articleshow/123266291.cms</t>
+          <t>https://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/pawar-defends-scrutiny-of-ladki-bahin-scheme-beneficiaries/articleshow/123308892.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-pigeon-feeding-dispute-jain-community-vs-marathi-integration-committee-tense-protests-police-detain-hundreds/articleshow/123294170.cms</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://punemirror.com/state/maharashtra-governor-governor-c-p-radhakrishnan-greets-people-on-independence-day/</t>
+          <t>https://www.pratahkal.com/Encyc/2025/8/12/big-action-by-rpf-grp-big-secret-of-theft-exposed.html</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.hindisaamana.com/rokhthok-conspiracy-to-make-maharashtra-vegetarian/</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B0-%E0%A4%9D%E0%A4%A8-%E0%A4%91%E0%A4%A8-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F-%E0%A4%A1-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%A7-%E0%A4%B9-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%86%E0%A4%B3%E0%A4%82%E0%A4%A6-%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1KAarj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amnesty.org/en/latest/research/2025/08/open-letter-to-government-of-maharashtra-withhold-assent-maharashtra-special-public-security-bill/</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://m.economictimes.com/markets/stocks/news/truce-talks-us-china-agree-to-extend-their-tariff-truce-for-another-90-days/julyaugust-developments/slideshow/123250425.cms</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%A7-%E0%A4%B2-26-34-%E0%A4%B2-%E0%A4%96-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%85%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1JoWkD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/the-eyes-that-saw-independence-day-1947/articleshow/123312887.cms</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2-%E0%A4%91%E0%A4%97%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%A7-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%B2-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1KrMRe</t>
+          <t>https://m.economictimes.com/markets/stocks/news/concord-biotech-sai-life-sciences-among-9-stocks-that-closed-above-vwap-on-august-11/trend-watch/slideshow/123248478.cms</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mukhyamantri-ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%AA-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KuMO3</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/bhiwani-woman-teacher-murder-triggers-protests-villagers-block-delhipilani-road-demand-arrests/articleshow/123345021.cms</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k</t>
+          <t>https://m.economictimes.com/markets/stocks/news/golden-crossovers-metropolis-healthcare-dixon-tech-among-5-stocks-signal-further-bullishness-on-august-12/bullish-breakout/slideshow/123248692.cms</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bom26-mh-2ndld-meat-ban.html</t>
+          <t>https://m.economictimes.com/news/new-updates/kalyan-dombivli-meat-shop-ban-on-independence-day-sparks-political-row-kdmc-official-says-its-a-routine-order-since-1988/articleshow/123220004.cms</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3538927-political-strife-over-maratha-quota-intensifies-in-maharashtra</t>
+          <t>https://m.economictimes.com/wealth/save/ppf-sukanya-samriddhi-yojana-new-rules-you-must-know/closing-a-sukanya-samriddhi-account-before-maturity/slideshow/123233624.cms</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3538922-clashes-over-maratha-quota-a-political-tug-of-war</t>
+          <t>https://m.economictimes.com/markets/stocks/news/treasury-yields-dip-ahead-of-key-inflation-data/treasury-yields-ease-before-inflation-data/slideshow/123251840.cms</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-pigeon-feeding-dispute-jain-community-vs-marathi-integration-committee-tense-protests-police-detain-hundreds/articleshow/123294170.cms</t>
+          <t>https://m.economictimes.com/markets/stocks/news/max-financial-titan-among-8-stocks-showing-rsi-trending-up-on-august-8/saregama-india/slideshow/123226556.cms</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>https://www.pratahkal.com/Encyc/2025/8/12/big-action-by-rpf-grp-big-secret-of-theft-exposed.html</t>
+          <t>https://m.economictimes.com/markets/stocks/news/pb-fintech-supreme-industries-among-11-stocks-with-white-marubozu-pattern-on-august-11/adani-enterprises/slideshow/123249237.cms</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/rokhthok-conspiracy-to-make-maharashtra-vegetarian/</t>
+          <t>https://punemirror.com/city/pune/bjps-mahesh-landge-cow-protection-groups-clash-with-ajit-pawar-over-crackdown-on-vigilantes/</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>https://www.amnesty.org/en/latest/research/2025/08/open-letter-to-government-of-maharashtra-withhold-assent-maharashtra-special-public-security-bill/</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/truce-talks-us-china-agree-to-extend-their-tariff-truce-for-another-90-days/julyaugust-developments/slideshow/123250425.cms</t>
+          <t>https://punemirror.com/city/pune/anna-hazares-stir-sparks-debate-again-banners-demanding-action-appear-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/the-eyes-that-saw-independence-day-1947/articleshow/123312887.cms</t>
+          <t>https://www.punekarnews.in/pune-political-row-erupts-at-savitribai-phule-pune-university-over-voice-of-devendra-elocution-competition/</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/concord-biotech-sai-life-sciences-among-9-stocks-that-closed-above-vwap-on-august-11/trend-watch/slideshow/123248478.cms</t>
+          <t>https://www.punekarnews.in/pune-lokmanya-nagar-redevelopment-hits-impasse-residents-blame-political-meddling/</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/bhiwani-woman-teacher-murder-triggers-protests-villagers-block-delhipilani-road-demand-arrests/articleshow/123345021.cms</t>
+          <t>https://ndtv.in/videos/why-did-mutton-politics-happen-on-15th-august-in-maharashtra-aimim-ncp-organized-a-non-veg-party-981146</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/golden-crossovers-metropolis-healthcare-dixon-tech-among-5-stocks-signal-further-bullishness-on-august-12/bullish-breakout/slideshow/123248692.cms</t>
+          <t>https://hindi.newsdanka.com/politics/independence-day-2025-pm-modi-longest-speech-ever/111404/</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/new-updates/kalyan-dombivli-meat-shop-ban-on-independence-day-sparks-political-row-kdmc-official-says-its-a-routine-order-since-1988/articleshow/123220004.cms</t>
+          <t>https://indiplomacy.com/2025/08/13/maharashtra-and-singapore-strengthen-maritime-and-industrial-ties-with-landmark-agreements/</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/wealth/save/ppf-sukanya-samriddhi-yojana-new-rules-you-must-know/closing-a-sukanya-samriddhi-account-before-maturity/slideshow/123233624.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/woman-accuses-ex-husband-of-sharing-intimate-pics-to-ruin-engagement/articleshow/123309891.cms</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/treasury-yields-dip-ahead-of-key-inflation-data/treasury-yields-ease-before-inflation-data/slideshow/123251840.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-to-celebrate-independence-day-with-social-initiatives-and-community-engagement/articleshow/123312038.cms</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/max-financial-titan-among-8-stocks-showing-rsi-trending-up-on-august-8/saregama-india/slideshow/123226556.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/war-on-cyber-cons-goa-police-to-use-memes-reels/articleshow/123311003.cms</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/pb-fintech-supreme-industries-among-11-stocks-with-white-marubozu-pattern-on-august-11/adani-enterprises/slideshow/123249237.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ganesh-mandals-in-mumbai-seek-abolition-of-rs-2000-penalty-for-digging-public-roads/articleshow/123302643.cms</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+          <t>https://www.marathijagran.com/top-news/maharashtra-police-bharti-2025-approval-for-15000-police-recruitment-in-maharashtra-cm-fadnavis-takes-4-big-decisions-88282</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/14/bom5-mh-meat-ban-security.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/pune-residents-experienced-the-thrill-of-punit-balan-groups-joint-dj-mukta-dahihandi.html</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/anna-hazares-stir-sparks-debate-again-banners-demanding-action-appear-in-pune/</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-political-row-erupts-at-savitribai-phule-pune-university-over-voice-of-devendra-elocution-competition/</t>
+          <t>https://www.punjabnewsexpress.com/punjab/news/union-home-minister-amit-shah-to-participate-in-the-350th-martyrdom-anniversary-celebrations-of-sri-guru-tegh-bahadur-sa-294387</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-lokmanya-nagar-redevelopment-hits-impasse-residents-blame-political-meddling/</t>
+          <t>https://thelivenagpur.com/2025/08/11/khan-academy-and-maharashtra-government-to-empower-62000-schools-with-free-digital-tools/</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>https://ndtv.in/videos/why-did-mutton-politics-happen-on-15th-august-in-maharashtra-aimim-ncp-organized-a-non-veg-party-981146</t>
+          <t>https://globalprimenews.com/2025/08/14/capitaland-investment-signs-landmark-mou-with-maharashtra-government/</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-eknath-shinde-aditya-thackeray-on-one-stage-sa-9506059.html</t>
+          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/meat-sale-banned-on-aug-15-security-tightened-in-kalyan/855124/</t>
+          <t>https://thelivenagpur.com/2025/08/11/historic-sword-of-raghuji-bhosale-secured-by-maharashtra-government-in-london/</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/dahi-handi-event-organized-by-bjp-leaders-in-mumbai-municipal-elections-operation-sindoor-are-the-topics/856127/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>https://apnnews.in/top-news/eknath-shinde-faction-minister-bharat-gogawale-angry-he-will-stay-away-from-cabinet-meeting/</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>https://indiplomacy.com/2025/08/13/maharashtra-and-singapore-strengthen-maritime-and-industrial-ties-with-landmark-agreements/</t>
+          <t>https://indiacsr.in/national-stem-challenge-2025-central-zone-winners-announced/</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/woman-accuses-ex-husband-of-sharing-intimate-pics-to-ruin-engagement/articleshow/123309891.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-to-celebrate-independence-day-with-social-initiatives-and-community-engagement/articleshow/123312038.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/war-on-cyber-cons-goa-police-to-use-memes-reels/articleshow/123311003.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-bharti-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B5%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%AA-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B7-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%81%E0%A4%A6-%E0%A4%A6%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1Ks1KV</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ganesh-mandals-in-mumbai-seek-abolition-of-rs-2000-penalty-for-digging-public-roads/articleshow/123302643.cms</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/governments-big-announcement-mega-recruitment-announced-for-15000-posts-in-the-police-department/39848</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/top-news/maharashtra-police-bharti-2025-approval-for-15000-police-recruitment-in-maharashtra-cm-fadnavis-takes-4-big-decisions-88282</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/pune-residents-experienced-the-thrill-of-punit-balan-groups-joint-dj-mukta-dahihandi.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-fadnavis-government-has-increased-ration-shopkeepers-margin-amount-20-rupee-88298</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.msn.com/mr-in/news/other/free-digital-learning-%E0%A4%96-%E0%A4%A8-%E0%A4%85%E0%A4%95%E0%A5%85%E0%A4%A1%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3/ar-AA1KCLdZ</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/punjab/news/union-home-minister-amit-shah-to-participate-in-the-350th-martyrdom-anniversary-celebrations-of-sri-guru-tegh-bahadur-sa-294387</t>
+          <t>https://agrowon.esakal.com/agro-special/devendra-fadnavis-dahi-handi-speech-maharashtra-politics-on-bmc-elections-news-on-agrowon-ssp-25</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/11/khan-academy-and-maharashtra-government-to-empower-62000-schools-with-free-digital-tools/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-decision-devendra-fadnavis-home-ministry-15-thousand-police-recruitment/articleshow/123252638.cms</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/08/14/capitaland-investment-signs-landmark-mou-with-maharashtra-government/</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/the-flag-hoisting-will-be-done-by-fadnavis-in-mumbai-and-radhakrishnan-in-pune-15226401</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-recruitment-%E0%A4%A4%E0%A4%B0%E0%A5%81%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B2-%E0%A4%B2-%E0%A4%97-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A5%A7%E0%A5%AB-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Km5x7</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/11/historic-sword-of-raghuji-bhosale-secured-by-maharashtra-government-in-london/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-independence-day-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news/912247/amp</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bom19-mh-meat-ban-fadnavis.html</t>
+          <t>https://www.tv9marathi.com/videos/big-decision-in-cabinet-on-state-police-state-to-soon-recruit-14000-posts-maharashtra-police-recruitment-2025-1467605.html/amp</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://globalprimenews.com/2025/08/14/credai-mchi-change-of-guard-2025-ceremony-in-presence-of-honorable-cm-of-maharashtra-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/singapore-should-cooperate-for-development-by-adding-a-new-dimension-to-maritime-cooperation-between-maharasht.html</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/national-stem-challenge-2025-central-zone-winners-announced/</t>
+          <t>https://agrowon.esakal.com/agro-special/states-progress-in-agriculture-and-energy-sectors-rat16</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-12-august-2025-marathi-batmya-maharashtra-weather-update-dadar-kabutarkhana-ban-pune-khed-pickup-accident/liveblog/123248711.cms</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/maharashtra-singapore-investment-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%B6-3-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%81%E0%A4%82%E0%A4%A4%E0%A4%B5%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B0/ar-AA1Kq8BL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/santosh-juvekar-thankful-to-ashish-shelar-for-bringing-back-raghuji-bhosale-sword-in-india/articleshow/123270658.cms</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-on-devendra-fadnavis-says-government-came-to-power-by-cutting-water-buffalo-at-kamakhya-temple-and-even-ate-it-as-prasad-and-fadnavis-says-become-a-vegetarian-stop-this-nonsense-1376830</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-bharti-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B5%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%AA-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B7-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%81%E0%A4%A6-%E0%A4%A6%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1Ks1KV</t>
+          <t>https://civicmirror.in/maharashtra/cabinet-decisions-jumbo-police-recruitment-in-maharashtra-fadnavis-government-gives-green-light-to-fill-15-thousand-posts/</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-fadnavis-government-has-increased-ration-shopkeepers-margin-amount-20-rupee-88298</t>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-approves-recruitment-of-15000-police-in-state-article-152450966</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.timemaharashtra.com/politics/i-feel-jealous-of-devendra-fadnavis-uddhav-thackerays-attack-on-fadnavis/128759/</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/free-digital-learning-%E0%A4%96-%E0%A4%A8-%E0%A4%85%E0%A4%95%E0%A5%85%E0%A4%A1%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3/ar-AA1KCLdZ</t>
+          <t>https://www.thodkyaat.com/maharashtra-police-recruitment-2025-15000-vacancies-with-special-age-relaxation/</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/devendra-fadnavis-dahi-handi-speech-maharashtra-politics-on-bmc-elections-news-on-agrowon-ssp-25</t>
+          <t>https://news34.in/2025/08/chandrapur-development-schemes-2025/</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-decision-devendra-fadnavis-home-ministry-15-thousand-police-recruitment/articleshow/123252638.cms</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-f-21/911866/</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-recruitment-%E0%A4%A4%E0%A4%B0%E0%A5%81%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B2-%E0%A4%B2-%E0%A4%97-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A5%A7%E0%A5%AB-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Km5x7</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B6-%E0%A4%95%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%86%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%A8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%A6%E0%A5%81%E0%A4%96-%E0%A4%B5-%E0%A4%A2%E0%A4%B2/ar-AA1Ksebj</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-independence-day-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news/912247/amp</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-14-august-2025-eknath-shinde-aditya-thackeray-bdd-chawl-mumbai-devendra-fadnavis-ajit-pawar-arjun-tendulkar-maharashtra-weather-today-mumbai-rain-shivsena-ubt-mns-alliance-1376992</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A6-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97-%E0%A4%B1%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AE-%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B8-%E0%A4%A7%E0%A4%B2%E0%A4%82-%E0%A4%A4-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%A2%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A4%A6-%E0%A4%A6-%E0%A4%96%E0%A4%B5%E0%A4%B2/ar-AA1K55hg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/big-decision-in-cabinet-on-state-police-state-to-soon-recruit-14000-posts-maharashtra-police-recruitment-2025-1467605.html/amp</t>
+          <t>https://www.marathijagran.com/maharashtra/nagpur/raghuji-raje-sword-in-london-is-in-the-possession-of-the-government-88219</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/08/14/credai-mchi-change-of-guard-2025-ceremony-in-presence-of-honorable-cm-of-maharashtra-devendra-fadnavis/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-police-bharti-cabinet-decision-what-are-the-recruitment-for-the-posts-omr-system-used-for-written-examination-1456438.html</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/singapore-should-cooperate-for-development-by-adding-a-new-dimension-to-maritime-cooperation-between-maharasht.html</t>
+          <t>https://www.marathijagran.com/maharashtra/pune/pune-accident-news-death-toll-rises-to-10-in-pimpri-chinchwad-accident-88376</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/states-progress-in-agriculture-and-energy-sectors-rat16</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/independence-day-2025-chhagan-bhujbal-refuse-to-hoist-flag-in-gondia-due-to-girish-mahajan/articleshow/123296100.cms</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/there-will-be-a-capitaland-data-center-in-navi-mumbai-an-investment-of-rs-19200-crores-will-come-and-the-economy-will-benefit-maharashtra-news-mhs25081301777</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-disha-abhiyan-unprecedented-changes-in-education-for-students-with-intellectual-disabilities/articleshow/123230486.cms</t>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/santosh-juvekar-thankful-to-ashish-shelar-for-bringing-back-raghuji-bhosale-sword-in-india/articleshow/123270658.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/cabinet-decisions-jumbo-police-recruitment-in-maharashtra-fadnavis-government-gives-green-light-to-fill-15-thousand-posts/</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-approves-recruitment-of-15000-police-in-state-article-152450966</t>
+          <t>https://civicmirror.in/maharashtra/chhatrapati-sambhajinagar-the-common-citizen-is-the-focal-point-guardian-minister-sanjay-shirsat/</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/i-feel-jealous-of-devendra-fadnavis-uddhav-thackerays-attack-on-fadnavis/128759/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
         </is>
       </c>
     </row>
@@ -5527,516 +5527,327 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-police-recruitment-2025-15000-vacancies-with-special-age-relaxation/</t>
+          <t>https://www.timemaharashtra.com/politics/maharashtra-is-making-a-fool-of-itself-sanjay-raut-questions-the-government-on-the-august-15-meat-ban/128932/</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/08/chandrapur-development-schemes-2025/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/chairman-ram-shindes-follow-up-is-successful-punyashloka-ahilyadevis-national-monument-at-chondi-approved-under-the-development-plan/129292/amp/</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-f-21/911866/</t>
+          <t>https://www.timemaharashtra.com/politics/vijay-vadettiwar-on-devendra-fadanvis-vijay-vadettiwars-aggressive-criticism-of-the-decision-to-close-meat-fish-shops/128933/</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B6-%E0%A4%95%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%86%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%A8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%A6%E0%A5%81%E0%A4%96-%E0%A4%B5-%E0%A4%A2%E0%A4%B2/ar-AA1Ksebj</t>
+          <t>https://www.msn.com/en-in/news/india/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A6-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97-%E0%A4%B1%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AE-%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B8-%E0%A4%A7%E0%A4%B2%E0%A4%82-%E0%A4%A4-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%A2%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A4%A6-%E0%A4%A6-%E0%A4%96%E0%A4%B5%E0%A4%B2/ar-AA1K55hg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519-amp.html</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nagpur/raghuji-raje-sword-in-london-is-in-the-possession-of-the-government-88219</t>
+          <t>https://m.economictimes.com/news/international/global-trends/us-news-xfg-stratus-covid-variant-in-us-8-key-facts-risky-states-symptoms-prevention/covid-cases-are-increasing-in-us/slideshow/123347536.cms</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-police-bharti-cabinet-decision-what-are-the-recruitment-for-the-posts-omr-system-used-for-written-examination-1456438.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/pune/pune-accident-news-death-toll-rises-to-10-in-pimpri-chinchwad-accident-88376</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/ar-AA1KtpKo</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://punemirror.com/city/pune/punes-street-food-crisis-1500-poisoning-cases-in-six-months-students-worst-hit/</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/poet-saumitra-fears-homelessness-appeals-for-help-from-chief-minister-maharashtra-news-mhs25081106242</t>
+          <t>https://punemirror.com/city/mumbai/bombay-high-court-bans-djs-in-ganeshotsav-and-other-processions-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/independence-day-2025-chhagan-bhujbal-refuse-to-hoist-flag-in-gondia-due-to-girish-mahajan/articleshow/123296100.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/new-rules-for-admission-to-the-ministry-online-registration-mandatory-effective-from-august-15.html</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-on-ban-on-meat-eating/</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://civicmirror.in/maharashtra/the-government-will-decide-on-a-special-policy-regarding-backward-class-housing-societies-in-the-state-assembly-deputy-speaker-annasaheb-bansode/</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B2%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A5%80%E0%A4%9A%E0%A4%BE-%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/113758/</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cm-bhagwant-mann-writes-to-union-minister-shivraj-singh-chouhan-dont-drop-road-bridge-projects/articleshow/123317920.cms</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/chhatrapati-sambhajinagar-the-common-citizen-is-the-focal-point-guardian-minister-sanjay-shirsat/</t>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment-125081101371_1.html?isa=yes</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+          <t>https://timesofindia.indiatimes.com/city/mysuru/agri-minister-reaffirms-support-for-farmers/articleshow/123325241.cms</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/maharashtra-is-making-a-fool-of-itself-sanjay-raut-questions-the-government-on-the-august-15-meat-ban/128932/</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/3-model-village-heads-from-gujarat-get-invited-to-i-day-celebrations-in-delhi/articleshow/123310840.cms</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/chairman-ram-shindes-follow-up-is-successful-punyashloka-ahilyadevis-national-monument-at-chondi-approved-under-the-development-plan/129292/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-junior-minister-yogesh-kadam-seeks-more-decision-making-powers-and-access-to-cabinet-meetings/articleshow/123284395.cms</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/vijay-vadettiwar-on-devendra-fadanvis-vijay-vadettiwars-aggressive-criticism-of-the-decision-to-close-meat-fish-shops/128933/</t>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/fishermen-must-prioritise-safety-hebbalkar/articleshow/123309750.cms</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/divyansh-bhardwaj-bags-best-sarpanch-in-raj/articleshow/123312215.cms</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/global-trends/us-news-xfg-stratus-covid-variant-in-us-8-key-facts-risky-states-symptoms-prevention/covid-cases-are-increasing-in-us/slideshow/123347536.cms</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/ar-AA1KtpKo</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mumbai-gets-2-bridges-and-a-promenade-101755198444321.html</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3541547-mumbai-redefines-urban-living-bdd-chawl-project-unveils-new-homes</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519-amp.html</t>
+          <t>https://www.newsonair.gov.in/hi/ndependence-day-celebrated-with-patriotic-fervour-and-gaiety-across-the-country/</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/same-sex-couple-moves-hc-against-gift-tax-rules/articleshow/123325951.cms</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/punes-street-food-crisis-1500-poisoning-cases-in-six-months-students-worst-hit/</t>
+          <t>https://economictimes.indiatimes.com/news/india/cji-gavai-launches-bombay-hcs-4th-bench-in-kolhapur/articleshow/123351073.cms</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/mumbai/bombay-high-court-bans-djs-in-ganeshotsav-and-other-processions-in-mumbai/</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-death-toll-rises-to-10-in-pimpri-chinchwad-accident/articleshow/123247989.cms</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/new-rules-for-admission-to-the-ministry-online-registration-mandatory-effective-from-august-15.html</t>
+          <t>https://m.economictimes.com/news/india/7-must-visit-forts-and-memorials-honoring-indias-freedom-struggle/pratapgad-fort-maharashtra/slideshow/123236622.cms</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-on-ban-on-meat-eating/</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/no-need-to-worry-about-us-tariffs-duty-hike-on-shrimp-chance-to-boost-indian-market-nitesh-rane/articleshow/123240165.cms</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/the-government-will-decide-on-a-special-policy-regarding-backward-class-housing-societies-in-the-state-assembly-deputy-speaker-annasaheb-bansode/</t>
+          <t>https://ddnews.gov.in/7-devotees-died-as-pickup-overturned-in-pune-pm-modi-expressed-grief/</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B2%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A5%80%E0%A4%9A%E0%A4%BE-%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/113758/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/tn-launches-door-delivery-of-ration-items-to-elderly-differently-abled.html</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cm-bhagwant-mann-writes-to-union-minister-shivraj-singh-chouhan-dont-drop-road-bridge-projects/articleshow/123317920.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-labour-dept-simplifies-access-to-welfare-schemes/articleshow/123289483.cms</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/content/press-releases-ani/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment-125081101371_1.html?isa=yes</t>
+          <t>https://timesofindia.indiatimes.com/city/chennai/tn-govt-will-not-let-down-sanitary-workers-stalin/articleshow/123311969.cms</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/3-model-village-heads-from-gujarat-get-invited-to-i-day-celebrations-in-delhi/articleshow/123310840.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/breaking-party-line-mithun-likens-lakshmir-bhandar-to-alms-tmc-hits-back/articleshow/123289871.cms</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-junior-minister-yogesh-kadam-seeks-more-decision-making-powers-and-access-to-cabinet-meetings/articleshow/123284395.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/msedcl-achieves-milestone-of-1gw-domestic-rooftop-solar-capacity/articleshow/123302393.cms</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/fishermen-must-prioritise-safety-hebbalkar/articleshow/123309750.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/visakhapatnam/independence-day-2-police-officers-from-andhra-pradesh-to-receive-presidents-medal-for-distinguished-service/articleshow/123302786.cms</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/jaipur/divyansh-bhardwaj-bags-best-sarpanch-in-raj/articleshow/123312215.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-ring-road-plan-pmrda-holds-preliminary-talks-with-villages-for-upcoming-town-planning-schemes/articleshow/123320219.cms</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/india-celebrates-79th-independence-day-with-patriotic-fervour-and-statewide-announcements-2/</t>
+          <t>https://timesofindia.indiatimes.com/city/hubballi/hubballi-nk-region-celebrate-independence-day-with-fervour/articleshow/123325559.cms</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/13/dcm132-biz-briefs-6.html</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mumbai-gets-2-bridges-and-a-promenade-101755198444321.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/ls-passes-two-tax-bills-amid-din-without-debate.html</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>https://munsifdaily.com/rapid-redevelopment-essential-for-a-slum-free/</t>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/ndependence-day-celebrated-with-patriotic-fervour-and-gaiety-across-the-country/</t>
+          <t>https://www.mypunepulse.com/pune-records-19195-consumers-generating-89-mw-rooftop-solar-power-under-pm-suryaghar-muft-bijli-yojana-msedcl/</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>https://economictimes.indiatimes.com/news/india/cji-gavai-launches-bombay-hcs-4th-bench-in-kolhapur/articleshow/123351073.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-death-toll-rises-to-10-in-pimpri-chinchwad-accident/articleshow/123247989.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/7-must-visit-forts-and-memorials-honoring-indias-freedom-struggle/pratapgad-fort-maharashtra/slideshow/123236622.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/no-need-to-worry-about-us-tariffs-duty-hike-on-shrimp-chance-to-boost-indian-market-nitesh-rane/articleshow/123240165.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>https://ddnews.gov.in/7-devotees-died-as-pickup-overturned-in-pune-pm-modi-expressed-grief/</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>https://hindi.newsdanka.com/politics/independence-day-2025-pm-modi-longest-speech-ever/111404/</t>
-        </is>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>https://breakingmaharashtra.in/?p=39156</t>
-        </is>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-labour-dept-simplifies-access-to-welfare-schemes/articleshow/123289483.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chennai/tn-govt-will-not-let-down-sanitary-workers-stalin/articleshow/123311969.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/breaking-party-line-mithun-likens-lakshmir-bhandar-to-alms-tmc-hits-back/articleshow/123289871.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chennai/the-time-has-come-tamil-nadu-cm-mk-stalin-urges-legal-battle-to-reclaim-states-powers/articleshow/123317272.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/varanasi/cm-grid-scheme-reviewed-directions-to-expedite-work/articleshow/123289376.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/vijayawada/naidu-to-launch-free-bus-scheme-for-women-today/articleshow/123309861.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/msedcl-achieves-milestone-of-1gw-domestic-rooftop-solar-capacity/articleshow/123302393.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/jaipur/pmo-team-reviews-pm-shri-scheme-in-jaisalmer/articleshow/123289381.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/mha-warns-states-of-foreigners-obtaining-indian-identity-docus/articleshow/123325780.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/prayaas-scheme-to-promote-research-innovation-among-classes-ix-xi-students/articleshow/123306112.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/tn-launches-door-delivery-of-ration-items-to-elderly-differently-abled.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/farmers-day-events-held-across-thiruvananthapuram-district/articleshow/123348556.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/hubballi/hubballi-nk-region-celebrate-independence-day-with-fervour/articleshow/123325559.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/13/dcm132-biz-briefs-6.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/ls-passes-two-tax-bills-amid-din-without-debate.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
-        <is>
-          <t>https://ommcomnews.com/india-news/maha-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
-        <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
-        </is>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
-        </is>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
         <is>
           <t>https://www.mypunepulse.com/solapur-mumbai-flight-service-to-begin-soon/</t>
         </is>

--- a/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A775"/>
+  <dimension ref="A1:A842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/photos/sharad-pawar-is-hallucinating-devendra-fadnavis-slams-ncp-sp-chief-over-financial-aid-claim/ar-AA1tnzDv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/money/topstories/business-as-usual-won-t-work-devendra-fadnavis-on-rising-property-prices-in-mumbai/ar-AA1KELqU?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
@@ -466,14 +466,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-23589010</t>
+          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/money/topstories/business-as-usual-won-t-work-devendra-fadnavis-on-rising-property-prices-in-mumbai/ar-AA1KELqU?ocid=finance-verthp-feeds</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-23589010</t>
         </is>
       </c>
     </row>
@@ -494,35 +494,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/weather/climate-change/gives-me-sleepless-nights-climate-change-a-major-economic-risk-for-maharashtra-says-cm-devendra-fadnavis/ar-AA1CxKxh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
+          <t>http://www.msn.com/en-in/news/India/devendra-fadnavis-infrastructure-work-shouldn-t-drag-on-for-years/ar-AA1JUyyJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/devendra-fadnavis-infrastructure-work-shouldn-t-drag-on-for-years/ar-AA1JUyyJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/autos/photos/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra/ar-AA1KmsuB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/maharashtra-cm-devendra-fadnavis-asks-dhananjay-munde-to-resign-as-minister-report/ar-AA1AbOok?ocid=BingNewsVerp</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/more-maharashtra-civic-bodies-order-closure-of-slaughterhouses-on-aug-15-chief-minister-fadnavis-says-govt-played-no-role/articleshow/123289673.cms</t>
         </is>
       </c>
     </row>
@@ -536,42 +536,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/more-maharashtra-civic-bodies-order-closure-of-slaughterhouses-on-aug-15-chief-minister-fadnavis-says-govt-played-no-role/articleshow/123289673.cms</t>
+          <t>http://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/photos/devendra-fadnavis-cabinet-approves-15000-police-vacancies-in-maharashtra/ar-AA1KmsuB</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmcs-pot-of-sins-broken-says-maharashtra-cm-devendra-fadnavis-23589784</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya/ar-AA1Kz9Qg</t>
+          <t>https://timesofindia.indiatimes.com/india/did-you-use-vote-riggers-fadnavis-asks-sharad-pawar/articleshow/123224044.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/india/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/did-you-use-vote-riggers-fadnavis-asks-sharad-pawar/articleshow/123224044.cms</t>
+          <t>http://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-vows-to-bring-elephant-home-mahadevi/ar-AA1JYQ3u?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-vows-to-bring-elephant-home-mahadevi/ar-AA1JYQ3u?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-cm-fadnavis-urges-ganesh-mandals-to-promote-operation-sindoor-and-swadeshi-goods-23589371</t>
         </is>
       </c>
     </row>
@@ -585,105 +585,105 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-cm-fadnavis-urges-ganesh-mandals-to-promote-operation-sindoor-and-swadeshi-goods-23589371</t>
+          <t>http://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-flays-congress-mp-praniti-shinde-for-calling-operation-sindoor-tamasha/ar-AA1JB0sg?cvid=B8A9EB465BAC4119AEF858223F6989C3&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis/articleshow/123261137.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/redeveloping-dharavi-is-like-building-a-new-city-maharashtra-cm-devendra-fadnavis-23589541</t>
+          <t>https://www.ndtv.com/video/maharashtra-cm-devendra-fadnavis-participates-in-flag-hoisting-ceremony-on-i-day-980963</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-takes-major-leap-in-urban-infrastructure-as-cm-devendra-fadnavis-inaugurates-four-landmark-mmrda-projects-23589505</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-leader-hits-out-at-maratha-quota-activist-jarange-for-remarks-against-fadnavis/articleshow/123261137.cms</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/maharashtra-cm-devendra-fadnavis-participates-in-flag-hoisting-ceremony-on-i-day-980963</t>
+          <t>https://www.msn.com/en-in/news/India/devendra-fadnavis-says-work-on-offshore-vadhvan-airport-likely-to-commence-next-year/ar-AA1IqAAe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-takes-major-leap-in-urban-infrastructure-as-cm-devendra-fadnavis-inaugurates-four-landmark-mmrda-projects-23589505</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya-says-no-one-can-stop-indias-development-23589603</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-has-access-to-worlds-best-tech-to-curb-cyber-crime-says-devendra-fadnavis-23588979</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/redeveloping-dharavi-is-like-building-a-new-city-maharashtra-cm-devendra-fadnavis-23589541</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmcs-pot-of-sins-broken-says-maharashtra-cm-devendra-fadnavis-23589784</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-hoists-indian-flag-at-mantralaya-says-no-one-can-stop-indias-development-23589603</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-appeals-to-aviation-ministry-to-shift-radars-in-mumbai-to-allow-redevelopment/ar-AA1IrbnT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/articleshow/123290009.cms</t>
+          <t>https://www.ptinews.com/story/business/as-chawl-residents-move-into-modern-homes-fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-125081100764_1.html</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-prominent-in-indian-s-unstoppable-growth-story-cm-fadnavis-125081500462_1.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.business-standard.com/india-news/mmr-region-can-become-1-5-trillion-growth-hub-says-maharashtra-cm-125081500149_1.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://www.msn.com/en-in/news/India/credai-mchi-appoints-sukhraj-nahar-as-18th-president-in-presence-of-cm-devendra-fadnavis/ar-AA1KxDEc</t>
         </is>
       </c>
     </row>
@@ -697,56 +697,56 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-chief-minister-devendra-fadnavis-appeals-to-aviation-ministry-to-shift-radars-in-mumbai-to-allow-redevelopment/ar-AA1IrbnT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/Fadnavis--his-deputies-congratulate-Governor-Radhakrishnan-over-VP-nomination/2831355</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-prominent-in-indian-s-unstoppable-growth-story-cm-fadnavis-125081500462_1.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/mmr-region-can-become-1-5-trillion-growth-hub-says-maharashtra-cm-125081500149_1.html</t>
+          <t>https://www.ptinews.com/story/national/govt-positive-about-bringing-in-law-to-protect-advocates:-fadnavis/2830765</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-opens-key-projects-on-independence-day-by-maharashtra-cm-devendra-fadnavis-to-cut-traffic-travel-time-and-give-scenic-commutes-heres-how-article-152469772</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes-101755198744381.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-savvy-maharashtra-cm-fadnavis-gives-ipads-to-ministers-to-ensure-cabinet-agenda-secrecy/articleshow/123222699.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-broke-handi-of-corruption-mahayuti-sounds-poll-bugle-101755369969997.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes-101755198744381.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-opens-key-projects-on-independence-day-by-maharashtra-cm-devendra-fadnavis-to-cut-traffic-travel-time-and-give-scenic-commutes-heres-how-article-152469772</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/fadnavis-fires-first-poll-salvo-ubt-mns-share-stage-in-dadar/articleshow/123336574.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/civic-bodies-are-only-following-the-meat-ban-imposed-by-congress-in-1988-cm-101755112861436.html</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/real-estate/third-and-fourth-mumbai-to-power-1-5-trillion-mmr-economy-city-can-surpass-dubai-in-10-years-devendra-fadnavis-101755244116021.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/civic-bodies-are-only-following-the-meat-ban-imposed-by-congress-in-1988-cm-101755112861436.html</t>
         </is>
       </c>
     </row>
@@ -774,112 +774,112 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/we-missed-the-bus-earlier,-no-compromise-on-mumbai's-development-now:-fadnavis/2823252</t>
+          <t>https://www.hindustantimes.com/real-estate/third-and-fourth-mumbai-to-power-1-5-trillion-mmr-economy-city-can-surpass-dubai-in-10-years-devendra-fadnavis-101755244116021.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/maharashtra-prominent-player-in-india%E2%80%99s-unstoppable-growth-story:-fadnavis/2824090/0</t>
+          <t>http://www.msn.com/en-in/news/India/script-by-salim-javed-fadnavis-mocks-rahul-s-vote-chori-claims-says-congress-chief-is-speaking-fiction/ar-AA1Ka5DS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sea-stroll-anytime-5-25-km-mumbai-coastal-road-promenade-opens-to-public-from-today-23589539</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sppu-withdraws-voice-of-devendra-contest-notice-after-protest-101755032437944.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-at-mantralaya-in-mumbai-106920</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://www.business-standard.com/politics/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav-thackeray-125081100764_1.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/activists-politicians-question-parvati-janata-vasahat-tdr-approval-101755033157676.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-at-mantralaya-in-mumbai-106920</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/articleshow/123309898.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-broke-handi-of-corruption-mahayuti-sounds-poll-bugle-101755369969997.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.businesstoday.in/india/story/business-as-usual-wont-work-devendra-fadnavis-on-rising-property-prices-in-mumbai-489712-2025-08-17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/articleshow/123309898.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519.html</t>
+          <t>https://www.ptinews.com/story/national/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-of-looters-fadnavis/2828031</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/As-chawl-residents-move-into-modern-homes--Fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra20250813190131</t>
+          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
@@ -907,56 +907,56 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/eknath-shinde-won-political-lottery-maharashtra-bjp-mla-ganesh-naik-mahayuti-101755432617411.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/-third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation/2834267</t>
+          <t>https://www.hindustantimes.com/india-news/eknath-shinde-won-political-lottery-maharashtra-bjp-mla-ganesh-naik-mahayuti-101755432617411.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-maharashtra-cm-devendra-fadnavis-inaugurates-flats-under-worlis-bdd-chawl-redevelopment-hands-over-keys-23589461</t>
+          <t>https://www.ptinews.com/story/business/-third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation/2834267</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/actor-complains-about-redevelopment-project-fraud-cm-intervenes-101755026135161.html</t>
+          <t>https://www.news18.com/videos/india/devendra-fadnavis-at-cnn-news18-townhall-on-student-mental-health-tricolour-true-freedom-9503816.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/india/devendra-fadnavis-at-cnn-news18-townhall-on-student-mental-health-tricolour-true-freedom-9503816.html</t>
+          <t>https://www.ptinews.com/story/national/we-missed-the-bus-earlier-no-compromise-on-mumbai-s-development-now-fadnavis/2823255</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/mobility/mumbai-coastal-road-to-be-open-24-hours-from-i-day-maha-cm-2946068.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-maharashtra-cm-devendra-fadnavis-inaugurates-flats-under-worlis-bdd-chawl-redevelopment-hands-over-keys-23589461</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-coastal-road-to-remain-open-24-hours-from-aug-15-cm-fadnavis-warns-against-turning-the-stretch-into-a-racetrack/articleshow/123306484.cms</t>
+          <t>https://zeenews.india.com/mobility/mumbai-coastal-road-to-be-open-24-hours-from-i-day-maha-cm-2946068.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/dahi-handi-festivities-kick-starts-maharasthra-local-body-poll-campaign-3683995</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-coastal-road-to-remain-open-24-hours-from-aug-15-cm-fadnavis-warns-against-turning-the-stretch-into-a-racetrack/articleshow/123306484.cms</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
@@ -991,77 +991,77 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mahayuti-hands-over-keys-to-redeveloped-worli-bdd-chawl-flats-23589547</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/mumbai-development-fadnavis-inaugurates-projects/32017320250814</t>
+          <t>https://www.ptinews.com/editor-detail/Maharashtra-prominent-player-in-India%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
+          <t>https://money.rediff.com/news/market/mumbai-development-fadnavis-inaugurates-projects/32017320250814</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832583</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/maharashtra-cm-devendra-fadnavis-comments-on-the-kabutar-khana-issue-cnn-news18-townhall-n18s-9503954.html</t>
+          <t>https://lokmat.news18.com/short-videos/trending/aaditya-thackeray-stands-to-welcome-cm-devendra-fadnavis-marathi-news-n18s-1070291.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
+          <t>https://www.aninews.in/news/business/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli20250814181439</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/from-160-sq-ft-to-sky-high-towers-fadnavis-delivers-bdd-chawl-homes-years-after-launching-project-3680811</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-cm-devendra-fadnavis-comments-on-the-kabutar-khana-issue-cnn-news18-townhall-n18s-9503954.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/bmc-in-focus-ballots-on-the-horizon-hear-it-straight-from-cm-of-maharashtra-devendra-fadnavis-9503385.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/from-160-sq-ft-to-sky-high-towers-fadnavis-delivers-bdd-chawl-homes-years-after-launching-project-3680811</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli20250814181439</t>
+          <t>https://www.news18.com/short-videos/trending/bmc-in-focus-ballots-on-the-horizon-hear-it-straight-from-cm-of-maharashtra-devendra-fadnavis-9503385.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/maharashtra-chief-minster-devendra-fadnavis-attacks-rahul-gandhi-on-alleged-vote-chori-ruckus-9503712.html</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+          <t>https://www.news18.com/short-videos/trending/maharashtra-chief-minster-devendra-fadnavis-attacks-rahul-gandhi-on-alleged-vote-chori-ruckus-9503712.html</t>
         </is>
       </c>
     </row>
@@ -1075,28 +1075,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://theprint.in/india/spread-awareness-on-operation-sindoor-during-ganesh-festival-fadnavis/2720722/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/aaditya-thackeray-greets-maharashtra-cm-devendra-fadnavis-warmly-at-cnn-news18-townhall-n18s-9503626.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
+          <t>https://www.news18.com/short-videos/trending/aaditya-thackeray-greets-maharashtra-cm-devendra-fadnavis-warmly-at-cnn-news18-townhall-n18s-9503626.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year/ar-AA1KtMtq</t>
+          <t>https://www.aninews.in/news/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
         </is>
       </c>
     </row>
@@ -1117,63 +1117,63 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.news18.com/short-videos/trending/marathi-is-compulsory-ye-maharashtra-ki-ghajini-hain-devendra-fadnavis-attacks-ubt-govt-on-nep-9503705.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mahayuti-hands-over-keys-to-redeveloped-worli-bdd-chawl-flats-23589547</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-14-news-updates-live-updates-weather-update-mumbai-monsoon-18331384</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/marathi-is-compulsory-ye-maharashtra-ki-ghajini-hain-devendra-fadnavis-attacks-ubt-govt-on-nep-9503705.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-deputy-cm-ajit-pawar-led-ncp-questions-meat-ban-on-august-15-bjp-cites-1988-order-23589362</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/BJP-may-have--panna-pramukhs--but-we-have-workers-at-the-grassroots-level--Raj-Thackeray/2823246</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-13-news-updates-live-updates-weather-update-mumbai-monsoon-18331383</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/projects-tenders/bdd-chawl-development</t>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/fadnavis-orders-equal-land-split-in-dharavi-project/77583</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.news18.com/short-videos/trending/big-political-voices-devendra-fadnavis-aaditya-thackeray-more-all-under-one-roof-n18s-9503158.html</t>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.news18.com/short-videos/trending/big-political-voices-devendra-fadnavis-aaditya-thackeray-more-all-under-one-roof-n18s-9503158.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-7-killed-after-pickup-van-falls-down-slope-cm-fadnavis-announces-financial-assistance-of-rs-4-lakh20250811192235</t>
+          <t>https://www.constructionweekonline.in/projects-tenders/bdd-chawl-development</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/savitribai-phule-pune-university-withdraws-voice-of-devendra-competition-notice-after-nsui-objection/ar-AA1Kqjjv</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
@@ -1201,35 +1201,35 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278510817/mmr-region-has-potential-to-become-15-trillion-dollars-says-maharashtra-cm</t>
+          <t>http://www.uniindia.com/photoes/631755.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://www.bignewsnetwork.com/news/278510817/mmr-region-has-potential-to-become-15-trillion-dollars-says-maharashtra-cm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278515875/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-nda-vp-nomination</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3543870-maharashtra-cm-fadnavis-predicts-imminent-change-in-bmc-at-dahi-handi-celebrations</t>
+          <t>https://www.bignewsnetwork.com/news/278515875/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-nda-vp-nomination</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3543870-maharashtra-cm-fadnavis-predicts-imminent-change-in-bmc-at-dahi-handi-celebrations</t>
         </is>
       </c>
     </row>
@@ -1243,21 +1243,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3540239-ibms-new-mumbai-hub-a-quantum-leap-for-maharashtras-future</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://menafn.com/1109923897/Maharashtra-CM-Devendra-Fadnavis-Intervenes-In-August-15-Meat-Ban-Row-Says-Govt-Not-Interested-In</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/devendra-fadnavis-led-maharashtra-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers-7055240.html</t>
+          <t>https://news.abplive.com/news/india/bjp-parinay-fuke-slams-maratha-quota-activist-manoj-jarange-over-remarks-against-cm-fadnavis-1794286</t>
         </is>
       </c>
     </row>
@@ -1271,14 +1271,14 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://news.abplive.com/cities/maharashtra-meat-shop-ban-controversy-devendra-fadnavis-ajit-pawar-aaditya-thackeray-independence-day-2025-1794498</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3542998-tripura-and-maharashtra-cms-celebrate-indias-79th-independence-day-with-patriotic-fervor</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
@@ -1292,133 +1292,133 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.latestly.com/socially/india/news/maharashtra-meat-ban-on-independence-day-2025-aaditya-thackeray-terms-august-15-meat-ban-wrong-cm-devendra-fadnavis-distances-govt-from-decision-watch-video-7058930.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3541262-worlis-rebirthed-bdd-chawls-mumbais-new-gold-standard</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3540668-fadnavis-calls-for-operation-sindoor-awareness-during-ganesh-festival</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.latestly.com/quickly/agency-news/fadnavis-presents-shawl-to-cp-radhakrishnan-on-nda-s-vp-nomination-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3542407-maharashtras-mega-city-vision-building-beyond-dubai</t>
+          <t>https://www.devdiscourse.com/article/business/3542411-maharashtras-pivotal-role-in-indias-growth-story</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/socially/india/news/maharashtra-meat-ban-on-independence-day-2025-aaditya-thackeray-terms-august-15-meat-ban-wrong-cm-devendra-fadnavis-distances-govt-from-decision-watch-video-7058930.html</t>
+          <t>https://www.newsx.com/india/in-operation-sindoor-under-the-leadership-of-pm-modi-maharashtra-cm-devendra-fadnavis-47149/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3540668-fadnavis-calls-for-operation-sindoor-awareness-during-ganesh-festival</t>
+          <t>https://www.latestly.com/agency-news/business-news-maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli-7058938.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/fadnavis-presents-shawl-to-cp-radhakrishnan-on-nda-s-vp-nomination-7063864.html</t>
+          <t>https://www.punekarnews.in/congresss-ramesh-chennithala-questions-cm-fadnaviss-remarks-on-rahul-gandhis-allegations-against-election-commission/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3542411-maharashtras-pivotal-role-in-indias-growth-story</t>
+          <t>https://www.devdiscourse.com/article/headlines/3542847-diwali-comes-early-new-gst-reforms-announced-on-independence-day</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/in-operation-sindoor-under-the-leadership-of-pm-modi-maharashtra-cm-devendra-fadnavis-47149/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3544716-maharashtras-legal-leap-ensuring-advocate-safety-and-expanding-justice</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3542420-maharashtras-unstoppable-growth-under-fadnavis</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3542847-diwali-comes-early-new-gst-reforms-announced-on-independence-day</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli-7058938.html</t>
+          <t>https://www.latestly.com/agency-news/business-news-ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra-7057337.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3544716-maharashtras-legal-leap-ensuring-advocate-safety-and-expanding-justice</t>
+          <t>https://english.newsnationtv.com/business/ibms-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra20250813190131</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/464628-Cooperation-of-IBM-is-necessary-to-achieve-goal-of-Viksit-Maharashtra-Devendra-Fadnavis</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3543787-mumbais-dahi-handi-a-festival-of-change-and-celebration</t>
+          <t>https://english.newsnationtv.com/national/general-news/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis20250813090909</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://lawchakra.in/legal-updates/law-advocates-cm-fadnavis-high-court/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/law-advocates-cm-fadnavis-high-court/</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day/</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
@@ -1432,70 +1432,70 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-uddhav-thackeray-claims-and-big-attack-says-cm-devendra-fadnavis-shielding-corrupt-ministers-24009940.html</t>
+          <t>https://www.newsroomodisha.com/nda-vice-president-nominee-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-and-ajit-pawar-faction-assigned-flag-hoisting-duties-in-maharashtra-eknath-shinde-out/articleshow/123242552.cms</t>
+          <t>https://english.publictv.in/maharashtra-7-killed-after-pickup-van-falls-down-slope-cm-fadnavis-announces-financial-assistance-of-rs-4-lakh/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%95-%E0%A4%87%E0%A4%A4%E0%A4%A8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%B9%E0%A5%88-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AC%E0%A4%A8-%E0%A4%AE-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9C%E0%A4%AE%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%B0/ar-AA1IVb2V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/august-15-meat-ban-row-maharashtra-cm-devendra-fadnavis-said-govt-not-interested-in-regulating-people-food-choices-know-all/articleshow/123294081.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-and-ajit-pawar-faction-assigned-flag-hoisting-duties-in-maharashtra-eknath-shinde-out/articleshow/123242552.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%AE%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%96-%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%9C-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%A1%E0%A4%BC/ar-AA1G9764?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-calls-uddhav-thackeray-politics-ghajini-but-why-ws-l-9506496.html</t>
+          <t>https://www.abplive.com/states/maharashtra/krishna-janmashtami-2025-maharashtra-cm-devendra-fadnavis-target-congress-shiv-sena-uddhav-thackeray-sharad-pawar-bmc-2996712</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-has-world-s-best-technology-to-curb-cyber-crime-devendra-fadnavis-11078</t>
         </is>
       </c>
     </row>
@@ -1509,4345 +1509,4814 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ganeshotsav-2025-cm-devendra-fadnavis-appeals-to-ganpati-mandals-operation-sindoor-show-indigenous-tableaux/articleshow/123286430.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%96%E0%A5%81%E0%A4%B6%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B2%E0%A4%97-%E0%A4%88-%E0%A4%AE%E0%A5%81%E0%A4%B9%E0%A4%B0/ar-AA1KmvrX</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis-2025-08-13</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/august-15-meat-ban-row-maharashtra-cm-devendra-fadnavis-said-govt-not-interested-in-regulating-people-food-choices-know-all/articleshow/123294081.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-in-a-protest-organised-against-mahayuti-government-accused-devendra-fadnavis-of-protecting-the-corrupt-ministers/articleshow/123248772.cms</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/nagpur-why-no-action-was-taken-against-those-who-guaranteed-160-seats-devendra-fadnavis-hits-back-at-sharad-pawar-9496304.html</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-handover-556-flats-in-worli-bdd-chawl-redevelopment-project-ann-2995711</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cm-devendra-fadnavis-reply-on-15th-august-meat-ban-controversy-9078739</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ganeshotsav-2025-cm-devendra-fadnavis-appeals-to-ganpati-mandals-operation-sindoor-show-indigenous-tableaux/articleshow/123286430.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-municipal-body-looted-devendra-fadnavis-target-uddhav-thackeray-bmc-elections-9516480.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-calls-uddhav-thackeray-politics-ghajini-but-why-ws-l-9506496.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/bdd-chawl-redevelopment-scheme-cm-devendra-fadnavis-give-mhada-houses/articleshow/123310540.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-in-a-protest-organised-against-mahayuti-government-accused-devendra-fadnavis-of-protecting-the-corrupt-ministers/articleshow/123248772.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-fadnavis-calls-for-promotion-of-indigenous-sports-sports-minister-kokate-inaugurates-khelo-mahakumbh/articleshow/123286194.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-inaugurates-cycling-tracks-on-mumbai-coatal-road-ac-local-trains-project-underway-2995915</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.indiatv.in/maharashtra/dahi-handi-festival-themed-on-operation-sindoor-organised-in-ghatkopar-area-of-mumbai-cm-fadnavis-2025-08-16-1156327</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/good-news-for-the-youth-devendra-fadnavis-cabinet-approved-recruitment-for-15-thousand-posts/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis-2025-08-13</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-protest-many-places-against-cm-fadnavis-corrupt-minister-uddhav-chief-minister-protecting-everyone-2025-08-11</t>
+          <t>https://hindi.news18.com/news/maharashtra/nagpur-why-no-action-was-taken-against-those-who-guaranteed-160-seats-devendra-fadnavis-hits-back-at-sharad-pawar-9496304.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-vegetarians-are-impotent-nonsense-talk-cm-devendra-fadnavis-reaction-on-slaughterhouse-meat-shops-9506829.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-municipal-body-looted-devendra-fadnavis-target-uddhav-thackeray-bmc-elections-9516480.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%A6%E0%A4%B0%E0%A4%B5-%E0%A4%9C-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-ac-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%AC-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1KyN36</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cm-devendra-fadnavis-reply-on-15th-august-meat-ban-controversy-9078739</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-govt-approves-recruitment-of-15000-police-personnel-know-cabinet-meeting-decisions/articleshow/123260370.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-meeting-on-ganeshotsav-2025-he-also-directs-on-eid-e-milad-festival-ann-2995187</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/bdd-chawl-redevelopment-scheme-cm-devendra-fadnavis-give-mhada-houses/articleshow/123310540.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/cm-fadnavis-told-how-dharavi-is-being-redeveloped-says-this-is-the-center-of-economic-development-9084680</t>
+          <t>https://www.amarujala.com/india-news/change-imminent-in-bmc-mahayuti-govt-has-broken-pot-of-sins-say-cm-fadnavis-2025-08-16</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-fadnavis-calls-for-promotion-of-indigenous-sports-sports-minister-kokate-inaugurates-khelo-mahakumbh/articleshow/123286194.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/sclr-extension-mumbai-opening-eastern-western-expressway-highway-link-mumbai/articleshow/123308994.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-government-of-maharashtra-gave-permission-for-school-buses-pratap-sarnaik-ann-2994680</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-cm-fadnavis-advised-mumbaikars-not-to-sell-their-houses-24013649.html</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-slams-sharad-pawar-over-august-15-meat-sale-ban-says-its-pawar-governments-decision/articleshow/123286747.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-meat-ban-order-cm-devendra-fadnavis-backs-decision-ajit-pawar-says-this-wrong-2995176</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%95%E0%A4%88-%E0%A4%9C%E0%A4%97%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%95-%E0%A4%AC%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1Kiekp</t>
+          <t>https://www.jagran.com/news/national-maharashtra-cyber-crime-control-cm-fadnavis-lauds-garud-drishti-initiative-24009491.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/whom-did-chief-minister-devendra-fadnavis-target-regarding-bmc-125081600082_1.html</t>
+          <t>https://www.abplive.com/states/maharashtra/abu-asim-azmi-demands-cm-devendra-fadnavis-to-take-action-in-jamner-murder-case-2995099</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-maharashtra-cyber-crime-control-cm-fadnavis-lauds-garud-drishti-initiative-24009491.html</t>
+          <t>https://www.agniban.com/good-news-for-the-youth-devendra-fadnavis-cabinet-approved-recruitment-for-15-thousand-posts/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1JArmJ</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-protest-many-places-against-cm-fadnavis-corrupt-minister-uddhav-chief-minister-protecting-everyone-2025-08-11</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/nagpur-what-is-garuda-vision-of-maharashtra-police-done-patent-communal-violence-cyber-fraud-check-social-media-post-10-crore-recovery-ws-kl-9498865.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-vegetarians-are-impotent-nonsense-talk-cm-devendra-fadnavis-reaction-on-slaughterhouse-meat-shops-9506829.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O</t>
+          <t>https://www.abplive.com/states/maharashtra/congress-leader-balasaheb-thorat-again-expressed-fear-of-rigging-in-maharashtra-assembly-election-2993690</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/India/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-556-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%82%E0%A4%AA-bdd-%E0%A4%9A-%E0%A4%B2-%E0%A4%95-%E0%A4%9A-%E0%A4%AC-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B0-%E0%A4%B0-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%88-%E0%A4%A6%E0%A5%82%E0%A4%B0/ar-AA1KxhQD</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KfkTJ</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%B5%E0%A4%B9-%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%87%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4-%E0%A4%AE-%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%87%E0%A4%82%E0%A4%A1-%E0%A4%AF-%E0%A4%AC%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%AC%E0%A5%88%E0%A4%A0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4%E0%A4%82%E0%A4%9C/ar-AA1K9Ujk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.pratahkal.com/Encyc/2025/8/16/cm-fadnavis-praised-the-army-on-independence-day.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/cm-fadnavis-inaugurated-mumbai-dabbawala-international-experience-center-dabbawalas-will-get-their-own-house-9088159</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-govt-approves-recruitment-of-15000-police-personnel-know-cabinet-meeting-decisions/articleshow/123260370.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-chhagan-bhujbal-skips-gondia-flag-hoisting-amid-guardian-minister-row-bjp-mangal-prabhat-deputed-know-all/articleshow/123305574.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/aimim-leader-imtiaz-jaleel-organised-a-biryani-party-at-his-home-to-protest-against-civic-bodys-meat-ban-also-targeted-cm-devendra-fadnavis/articleshow/123329000.cms</t>
+          <t>https://ndtv.in/india/cm-fadnavis-told-how-dharavi-is-being-redeveloped-says-this-is-the-center-of-economic-development-9084680</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/independence-day-meat-ban-row-sanjay-raut-slams-cm-fadnavis-said-shivaji-maharaj-was-not-eat-only-rice-and-ghee-know-all/articleshow/123274873.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/sclr-extension-mumbai-opening-eastern-western-expressway-highway-link-mumbai/articleshow/123308994.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE-%E0%A4%9F-%E0%A4%95-%E0%A4%A6%E0%A5%81%E0%A4%95-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%87%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%A8-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%9A-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Ksgnw</t>
+          <t>https://www.jagran.com/news/national-cm-fadnavis-advised-mumbaikars-not-to-sell-their-houses-24013649.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://bhasha.ptinews.com/detail/2830925</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-mahayuti-eknath-shinde-missing-devendra-fadnavis-govt-cabinet-meeting-sa-9502234.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-slams-sharad-pawar-over-august-15-meat-sale-ban-says-its-pawar-governments-decision/articleshow/123286747.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%95%E0%A4%88-%E0%A4%9C%E0%A4%97%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%95-%E0%A4%AC%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1Kiekp</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/dispute-over-guardian-minister-post-deepens-in-mahayuti-government-eknath-shinde-distances-himself-from-cabinet-meeting/articleshow/123270600.cms</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/whom-did-chief-minister-devendra-fadnavis-target-regarding-bmc-125081600082_1.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-15000-policemen-recruitment-soon-fadnavis-cabinet-approved-four-important-proposals-19856957</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/cm-fadnavis-handed-over-the-keys-of-new-houses-to-bdd-chawl-residents/</t>
+          <t>https://www.indiatv.in/maharashtra/devendra-fadnavis-government-cabinet-approval-15-thousand-policemen-recruited-in-maharashtra-2025-08-12-1155549</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/ganeshotsav-2025-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%88%E0%A4%A6-%E0%A4%8F-%E0%A4%AE-%E0%A4%B2-%E0%A4%A6-%E0%A4%95-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1KskuP</t>
+          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://www.msn.com/hi-in/news/India/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-556-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%82%E0%A4%AA-bdd-%E0%A4%9A-%E0%A4%B2-%E0%A4%95-%E0%A4%9A-%E0%A4%AC-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B0-%E0%A4%B0-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%88-%E0%A4%A6%E0%A5%82%E0%A4%B0/ar-AA1KxhQD</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-inaugurates-bombay-high-court-new-circuit-bench-at-kolhapur-cm-fadnavis-and-dcm-eknath-shinde-also-present-know-all/articleshow/123346652.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE-%E0%A4%9F-%E0%A4%95-%E0%A4%A6%E0%A5%81%E0%A4%95-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A5%87%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%A8-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%9A-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Ksgnw</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-not-reached-devendra-fadnavis-govt-cabinet-meeting-201754983032466.html</t>
+          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%95%E0%A4%AC%E0%A5%82%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%A8-%E0%A4%AF%E0%A4%AE-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JYvBC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-police-bharti-2025-mega-recruitment-drive-hire-15000-personnel-various-posts-announced-check-details-go-to-this-link-and-see-b507/</t>
+          <t>https://ndtv.in/maharashtra-news/cm-fadnavis-inaugurated-mumbai-dabbawala-international-experience-center-dabbawalas-will-get-their-own-house-9088159</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%B5-%E0%A4%A6-%E0%A4%9C-%E0%A4%8F-%E0%A4%AF-%E0%A4%A6%E0%A5%82%E0%A4%B8%E0%A4%B0%E0%A5%87/ar-AA1KrMtV</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/aimim-leader-imtiaz-jaleel-organised-a-biryani-party-at-his-home-to-protest-against-civic-bodys-meat-ban-also-targeted-cm-devendra-fadnavis/articleshow/123329000.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/independence-day-meat-ban-row-sanjay-raut-slams-cm-fadnavis-said-shivaji-maharaj-was-not-eat-only-rice-and-ghee-know-all/articleshow/123274873.cms</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-unhappy-eknath-shinde-skips-cabinet-meeting-know-what-is-going-in-mahayuti-amid-guardian-minister-row/articleshow/123283685.cms</t>
+          <t>https://bhasha.ptinews.com/detail/2830925</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-mahayuti-eknath-shinde-missing-devendra-fadnavis-govt-cabinet-meeting-sa-9502234.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/aimim-and-ncp-sp-leaders-held-a-chicken-mutton-party-in-protest-against-meat-ban-in-maharashtra-9092115</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-maharashtra-meat-ban-protest-opposition-condemns-independence-day-shop-closure-24014311.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/dispute-over-guardian-minister-post-deepens-in-mahayuti-government-eknath-shinde-distances-himself-from-cabinet-meeting/articleshow/123270600.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/public-security-act-is-a-direct-attack-on-fundamental-rights-opposition-parties-in-the-field-11142</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/garuda-drishti-device-is-playing-an-important-role-in-monitoring-social-media-chief-minister-fadnavis/</t>
+          <t>https://www.msn.com/hi-in/news/other/ganeshotsav-2025-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%88%E0%A4%A6-%E0%A4%8F-%E0%A4%AE-%E0%A4%B2-%E0%A4%A6-%E0%A4%95-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1KskuP</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/a-middle-path-should-be-found-in-the-matter-of-feeding-pigeons-fadnavis/854960/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/protests-at-many-places-against-cm-fadnavis-corrupt-ministers-uddhav-said-chief-minister-is-protecting-everyone/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-inaugurates-bombay-high-court-new-circuit-bench-at-kolhapur-cm-fadnavis-and-dcm-eknath-shinde-also-present-know-all/articleshow/123346652.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%A7-%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%87-%E0%A4%B9%E0%A5%88-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0/ar-AA1KvM5B</t>
+          <t>https://www.livehindustan.com/maharashtra/eknath-shinde-not-reached-devendra-fadnavis-govt-cabinet-meeting-201754983032466.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-meat-ban-cm-devendra-fadnavis-says-govt-wont-decide-who-eats-what-201755168216321.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/fadnavis-clarification-on-meat-ban-in-maharashtra-government-will-not-decide-who-should-eat-what/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-5-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0%E0%A5%8D%E0%A4%B2-%E0%A4%82%E0%A4%97-%E0%A4%B8%E0%A5%8D%E0%A4%A5%E0%A4%B2-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%87%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4/ar-AA1K4uF3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/i-pity-devendra-fadnavis-why-did-uddhav-thackeray-say-this-after-taking-the-names-of-these-3-ministers-201754912659397.html</t>
+          <t>https://www.ucnnews.live/nagpur/flag-hoisting-at-the-divisional-commissioner-s-office-by-the-guardian-minister-presented-a-roadmap-to-make-the-sub-capital-developed-and-safe-1755239784945</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-politics-saamna-editorial-devendra-fadnavis-eknath-shinde-ajit-pawar-uddhav-thackeray-sanjay-raut-201755148013599.html</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-police-bharti-2025-mega-recruitment-drive-hire-15000-personnel-various-posts-announced-check-details-go-to-this-link-and-see-b507/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/310952-Devendra-Fadnavis-taunts-the-opposition-the-pot-of-sin-has-been-broken-in-the-Municipal-Corporation</t>
+          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%B5-%E0%A4%A6-%E0%A4%9C-%E0%A4%8F-%E0%A4%AF-%E0%A4%A6%E0%A5%82%E0%A4%B8%E0%A4%B0%E0%A5%87/ar-AA1KrMtV</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-unhappy-eknath-shinde-skips-cabinet-meeting-know-what-is-going-in-mahayuti-amid-guardian-minister-row/articleshow/123283685.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/fadnavis-reprimands-shindes-osd/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/home-minister-fadnavis-is-not-worried-the-protectors-of-law-are-committing-suicide-in-4-days-3-policemen-committed-their-lives/</t>
+          <t>https://ndtv.in/maharashtra-news/aimim-and-ncp-sp-leaders-held-a-chicken-mutton-party-in-protest-against-meat-ban-in-maharashtra-9092115</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/news-update/devendra-fadnavis-hoists-tricolour-maharashtra-engine-of-indias-progress/111395/amp</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-leader-parinay-fuke-hits-out-at-maratha-quota-activist-manoj-jarange-for-remarks-against-devendra-fadnavis-2994554</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
+          <t>https://thecsrjournal.in/maharashtra-police-bharti-recruitment-15000-posts-approved-hindi/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/c-p-radhakrishnan-becomes-ndas-vice-presidential-candidate-maharashtra-chief-minister-devendra-fadnavis-congratulates-him-552637</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-politics-why-is-cm-fadnavis-not-taking-action-against-controversial-ministers-compulsion-1360683.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/paul-tixs-ghajini-devendra-fadnavis-lashes-out-at-uddhav/cid17238362.htm</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43041/flats-of-worli-bdd-chawl-redevelopment-project-inaugurated-by-cm</t>
+          <t>https://www.abplive.com/news/india/cji-br-gavai-praise-devendra-fadnavis-govt-said-maharashtra-government-always-leader-judiciary-infrastructure-2997155</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/maharashtra-7-killed-as-pickup-van-falls-off-slope-cm-fadnavis-announces-rs-4-lakh-aid-4206354</t>
+          <t>https://hindi.theprint.in/india/a-middle-path-should-be-found-in-the-matter-of-feeding-pigeons-fadnavis/854960/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.newsonair.gov.in/hi/garuda-drishti-device-is-playing-an-important-role-in-monitoring-social-media-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/eknath-shinde-and-bharat-gogavale-did-not-attend-cm-fadnavis-cabinet-meeting-why-are-they-angry-1360801.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/maharashtra-cm-devendra-fadnavis-independence-day-wishes-three-languages-reply-to-opposition-551631</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/cm-fadnavis-issued-instructions-regarding-ganeshotsav-and-eid-e-milad-he-mention-operation-sindoor-1361833.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/cm-fadnavis-arrived-at-dahi-handi-on-operation-sindoor-theme/article-101120</t>
+          <t>https://www.agniban.com/protests-at-many-places-against-cm-fadnavis-corrupt-ministers-uddhav-said-chief-minister-is-protecting-everyone/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mmr-region-has-15-trillion-potential-maharashtra-cm-4213325</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%A7-%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%87-%E0%A4%B9%E0%A5%88-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0/ar-AA1KvM5B</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://bharat24live.com/news/maharashtra-cabinet-approves-recruitment-for-15000-police-posts-in-2025</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-meat-ban-cm-devendra-fadnavis-says-govt-wont-decide-who-eats-what-201755168216321.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/tag/29359/mumbai%3A-rapid-redeevelopment-is-necessary-for-a-slum--free-mumbai---chief-minister-devendra-fadnavis</t>
+          <t>https://www.ucnnews.live/politics/-15-000-posts-in-the-state-police-force-for-the-recruitment-of-police-the-cabinet-approved-the-proposal-see-major-verdicts-1754985934867</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/quickly/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95-%E0%A4%A8%E0%A5%82%E0%A4%A8-%E0%A4%B2-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KGky3</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/tag/29261/other-places-should</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/maharashtra-politics-uddhav-thackeray-attacks-devendra-fadnavis-for-not-acting-against-corrupt-ministers-frvd-2308298-2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-dabbawalas-in-mumbai-will-get-500-square-feet-house-for-rs-25-50-lakh-chief-minister/</t>
+          <t>https://www.livehindustan.com/maharashtra/i-pity-devendra-fadnavis-why-did-uddhav-thackeray-say-this-after-taking-the-names-of-these-3-ministers-201754912659397.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/fadnaviss-retort-on-sharad-pawars-160-seat-offer-statement-said-this-story-is-like-salim-javeds-script/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B5-%E0%A4%86%E0%A4%B8%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA-%E0%A4%AA-%E0%A4%95-%E0%A4%98%E0%A4%A1%E0%A4%BC-%E0%A4%AB-%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%AF-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KDcsH</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-politics-saamna-editorial-devendra-fadnavis-eknath-shinde-ajit-pawar-uddhav-thackeray-sanjay-raut-201755148013599.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.primetvindia.com/nda-declared-c-p-radhakrishnan-as-the-candidate-for-the-post-of-vice-president/</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/guaranteed-victory-claim-row-erupts-in-maharashtra-did-you-use-vote-riggers-devendra-fadnavis-asks-sharad-pawar/ar-AA1Khn2c</t>
+          <t>https://www.prabhasakshi.com/national/committee-formed-to-give-suggestions-to-help-the-sectors-affected-by-us-tariffs-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832775</t>
+          <t>https://mpbreakingnews.in/maharashtra/fadnavis-mumbai-bmc-elections-dharavi-project-54-801314</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sppu-withdraws-voice-of-devendra-contest-notice-after-protest-101755032437944.html</t>
+          <t>https://www.hindisaamana.com/home-minister-fadnavis-is-not-worried-the-protectors-of-law-are-committing-suicide-in-4-days-3-policemen-committed-their-lives/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/credai-mchi-appoints-sukhraj-nahar-as-18th-president-in-presence-of-cm-devendra-fadnavis/ar-AA1KxDEc</t>
+          <t>https://hindi.newsdanka.com/news-update/devendra-fadnavis-hoists-tricolour-maharashtra-engine-of-indias-progress/111395/amp</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-to-inaugurate-slew-of-projects-today-metro-3-may-launch-by-aug-end-101754936573343.html</t>
+          <t>https://hindi.latestly.com/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
+          <t>https://mpbreakingnews.in/maharashtra/kalyan-meat-shop-ban-devendra-fadnavis-political-protest-54-802580</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/new-psa-terminal-at-jnpa-to-be-opened-soon-fadnavis-</t>
+          <t>https://samacharnama.com/states/maharashtra-news/paul-tixs-ghajini-devendra-fadnavis-lashes-out-at-uddhav/cid17238362.htm</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
+          <t>https://bharatexpress.com/india/c-p-radhakrishnan-becomes-ndas-vice-presidential-candidate-maharashtra-chief-minister-devendra-fadnavis-congratulates-him-552637</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos--106878</t>
+          <t>https://www.rokthoklekhani.com/article/43041/flats-of-worli-bdd-chawl-redevelopment-project-inaugurated-by-cm</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.newsnationtv.com/maharashtra-bombay-high-court-mein-chal-rahe-kabutarkhana-vivad-par-kya-bole-cm-fadnavis--20250813193234/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-14-news-updates-live-updates-weather-update-mumbai-monsoon-18331384</t>
+          <t>https://jantaserishta.com/local/maharashtra/maharashtra-7-killed-as-pickup-van-falls-off-slope-cm-fadnavis-announces-rs-4-lakh-aid-4206354</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/viksit-maharashtra-making-special-contribution-in-realising-dream-of-viksit-bharat-says-cm-fadnavis-997311</t>
+          <t>https://www.newsnationtv.com/fadnavis-ka-vipaksh-par-tanz-mahanagar-palika-mein-toot-chuki-hai-paap-ki-haandi--20250816171044/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-7-dead-as-pickup-van-falls-cm-fadnavis-announces-4-lakh-aid-2944690.html</t>
+          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Health-concerns--religious-feelings-to-be-considered-while-resolving-pigeon-feeding-row--Fadnavis/2819045</t>
+          <t>https://bharatexpress.com/india/maharashtra-cm-devendra-fadnavis-independence-day-wishes-three-languages-reply-to-opposition-551631</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-august-13-news-updates-live-updates-weather-update-mumbai-monsoon-18331383</t>
+          <t>https://mpbreakingnews.in/maharashtra/raigad-guardian-minister-bharat-gogawale-aditi-tatkare-maharashtra-politics-54-800763</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-ubt-protests-in-nagpur-seeking-sacking-of-corrupt-maharashtra-ministers/2812465</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/cm-fadnavis-arrived-at-dahi-handi-on-operation-sindoor-theme/article-101120</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-deputy-cm-ajit-pawar-led-ncp-questions-meat-ban-on-august-15-bjp-cites-1988-order-23589362</t>
+          <t>https://jantaserishta.com/local/maharashtra/bjp-led-mahayuti-has-broken-the-pot-of-sins-change-in-bmc-is-inevitable-fadnavis-4214994</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/631755.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-slams-mahayuti-govt-signals-bmc-shakeup-4214626</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278509383/maharashtra-cm-devendra-fadnavis-hands-over-keys-to-owners-of-bdd-chawl-redevelopment-project-in-worli</t>
+          <t>https://hindi.latestly.com/india/mumbai-to-receive-several-projects-ahead-of-bmc-elections-metro-3-phase-3-likely-to-be-launched-by-end-of-august-ask-chatgpt-2726817.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/states/maha-govt-not-keen-on-regulating-people-s-food-choices-fadnavis/53228</t>
+          <t>https://bharat24live.com/news/maharashtra-cabinet-approves-recruitment-for-15000-police-posts-in-2025</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/congresss-ramesh-chennithala-questions-cm-fadnaviss-remarks-on-rahul-gandhis-allegations-against-election-commission/</t>
+          <t>https://www.rokthoklekhani.com/tag/29359/mumbai%3A-rapid-redeevelopment-is-necessary-for-a-slum--free-mumbai---chief-minister-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/bhiwandi-will-be-developed-as-an-urban-city-devendra-fadnavis.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-hoisted-the-tricolor-on-independence-day-attended-the-bombay-high-court-ceremony-4212924</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-speech-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A4%B0%E0%A4%95%E0%A5%81%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A4%E0%A4%B0%E0%A4%A3-marathi-news/vi-AA1KFM8O?ocid=hpmsn</t>
+          <t>https://jantaserishta.com/local/maharashtra/dahi-handi-event-in-ghatkopar-honours-soldiers-involved-in-operation-sindoor-fadnavis-4215202</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-statement-that-kolhapur-has-become-centralized-due-to-the-circuit-bench/912997/</t>
+          <t>https://hindi.latestly.com/quickly/india/mumbai-good-news-for-worli-bdd-chawl-residents-556-new-homes-keys-to-be-handed-over-today-by-cm-devendra-fadnavis-2728000.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/underground-road-plan-to-ease-central-pune-traffic-cm-devendra-fadnavis-meeting-9101801</t>
+          <t>https://www.rokthoklekhani.com/tag/29261/other-places-should</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://bharat24live.com/news/maharashtra-government-announces-2-da-hike-for-employees-to-pay-8-months-arrears</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-after-president-trump-who-is-the-clown-in-politics-it-is-devendra-fadnavis-raut-criticizes-the-chief-minister/912795/</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://joindia.co.in/news/fadnaviss-retort-on-sharad-pawars-160-seat-offer-statement-said-this-story-is-like-salim-javeds-script/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.primetvindia.com/nda-declared-c-p-radhakrishnan-as-the-candidate-for-the-post-of-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.msn.com/en-in/news/India/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-prominent-player-in-india%E2%80%99s-unstoppable-growth-story:-fadnavis/2824090/0</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/after-donald-trump-devendra-fadnavis-is-biggest-joker-in-politics-sanjay-raut-criticized/</t>
+          <t>https://www.ptinews.com/story/business/we-missed-the-bus-earlier,-no-compromise-on-mumbai's-development-now:-fadnavis/2823252</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/only-then-will-the-dream-of-a-slum-free-mumbai-be-realized-chief-minister-devendra-fadnavis.html</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-challenges-uddhav-and-raj-thackeray-over-mumbai-municipal-corporation-bmc-elections-during-dahi-handi-festival/articleshow/123333235.cms</t>
+          <t>https://www.ptinews.com/detail/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/pune-univ-wing-drops-voice-of-devendra-contest-circular/articleshow/123265802.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announced-it-park-to-be-set-up-in-solapur-for-employment-generation-1460220.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos--106878</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devedra-fadnavis-challenges-opposition-over-upcoming-municipal-elections-at-dahi-handi-2025/articleshow/123340653.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/dahi-handi-festivities-kick-starts-maharasthra-local-body-poll-campaign-3683995</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288/amp/1</t>
+          <t>https://zeenews.india.com/india/maharashtra-7-dead-as-pickup-van-falls-cm-fadnavis-announces-4-lakh-aid-2944690.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raj-thackeray-uddhav-thackeray-shiv-sena-ubt-mns-reunite-for-best-employees-credit-society-election-against-bjp-devendra-fadnavis-samruddhi-panel/articleshow/123328116.cms</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/dahi-handi-2025-tembhinaka-dahihandi-cm-devendrad-fadnavis-political-statement-on-bmc-election/912700/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sea-stroll-anytime-5-25-km-mumbai-coastal-road-promenade-opens-to-public-from-today-23589539</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-stated-bandra-versova-sea-link-will-be-extended-up-to-vadhavan-port-local18-1459825.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/bhiwandi-will-be-developed-as-an-urban-city-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-speech-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A4%B0%E0%A4%95%E0%A5%81%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A4%E0%A4%B0%E0%A4%A3-marathi-news/vi-AA1KFM8O?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/fadnavis-targets-thackeray-camp-we-broke-the-pot-of-corruption-in-bmc-now-development-will-flow/</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-statement-that-kolhapur-has-become-centralized-due-to-the-circuit-bench/912997/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A6%E0%A4%B9-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%95-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F/ar-AA1KD8k2</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9A-%E0%A4%AB-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KE0LG</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%96%E0%A5%87%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%86%E0%A4%B2-%E0%A4%9A-%E0%A4%AC-%E0%A4%A1-%E0%A4%A1-%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1KcLlH</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/jain-muni-nileshchandra-appeal-to-cm-devendra-fadnavis-over-dadar-kabutar-khana-issue-9075708</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/third-mumbai-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A6%E0%A5%81%E0%A4%AC%E0%A4%88%E0%A4%AA%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%86%E0%A4%A3-%E0%A4%86%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B7%E0%A4%95-%E0%A4%B9-%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1KDOAo</t>
+          <t>https://marathi.ndtv.com/maharashtra/underground-road-plan-to-ease-central-pune-traffic-cm-devendra-fadnavis-meeting-9101801</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/operation-sindoor-broke-the-yoke-of-pakistans-sins.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mumbai-within-59-minutes-metro-local-railway-bus-roadways-to-become-congestion-free/articleshow/123316080.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/emotional-moment-as-bdd-residents-get-their-dream-home-maha-mtb.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://www.loksatta.com/navimumbai/cm-devendra-fadnavis-set-up-high-level-committee-to-review-industries-affected-after-us-tariff-on-india-zws-70-5299657/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-and-ajit-pawar-battle-over-additional-municipal-corporations-in-pune/articleshow/123235053.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/11/gopinath-munde-taught-chief-minister-devendra-fadnavis-to-struggle-without-compromising-with-power-home-minist.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-after-president-trump-who-is-the-clown-in-politics-it-is-devendra-fadnavis-raut-criticizes-the-chief-minister/912795/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B5%E0%A4%B2%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%8A%E0%A4%A8%E0%A4%B9-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%98%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%82%E0%A4%AE%E0%A4%A4-%E0%A4%95%E0%A4%B6-%E0%A4%95-%E0%A4%AF/ar-AA1KA4bi?cvid=709e293f49bb433db28c9ad0d1e1c64d</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/worli-bdd-chawl-redevelopment-program-cm-devendra-fadnavis-speech-dharavi-project-9083348</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announced-it-park-to-be-set-up-in-solapur-for-employment-generation-1460220.html</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-news-controversy-over-state-level-oratory-competition-on-the-occasion-of-chief-minister-devendra-fadnavis/articleshow/123257068.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/police-bharati-maharashtra-cabinet-decisions-today-under-cm-devendra-fadnavis-15000-police-bharti-know-details-in-marathi-1376621</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/congress-sangli-leader-prithviraj-patil-resigns-to-join-bjp-in-presence-of-devendra-fadnavis/articleshow/123269760.cms</t>
+          <t>https://www.lokmat.com/shorts/maharashtra/dabbawalas-to-get-500-sq-ft-homes-for-25-50-lakh/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%82%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF/ar-AA1KyPVX</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A6%E0%A4%B9-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%95-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F/ar-AA1KD8k2</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-calling-vegetarians-impotent-is-foolish-chief-minister-devendra-fadnavis/911740/</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-believes-that-maharashtra-will-lead-the-countrys-development-system-amy-95-5307598/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/video-story/vvvtqkxjy3fptfd3cnjbsi1qyun0dhf3lklevjzry3qwaktr/ac686946/cdf73399/ed2025af/8051239e/videodetails/4</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B2-%E0%A4%A8-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%87%E0%A4%B6%E0%A4%B5%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AD-%E0%A4%A4-%E0%A4%96-%E0%A4%8A%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A5%AC%E0%A5%AB-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%A8/ar-AA1KqsEZ</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%82%E0%A4%A1-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9A-%E0%A4%AB-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KE0LG</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/manoj-jarange-patil-criticizes-on-chief-minister-devendra-fadnavis-on-maratha-reservation-nanded-1377172</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-big-announcement-for-mumbai-dabewala-will-give-a-500-square-feet-house-for-25-lakhs-1458046.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%96%E0%A5%87%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%86%E0%A4%B2-%E0%A4%9A-%E0%A4%AC-%E0%A4%A1-%E0%A4%A1-%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1KcLlH</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-mns-raj-thackeray-over-mumbai-municipal-bmc-elections/articleshow/123306829.cms</t>
+          <t>https://www.saamana.com/after-donald-trump-devendra-fadnavis-is-biggest-joker-in-politics-sanjay-raut-criticized/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ubt-leader-sanjay-raut-talk-on-cm-devendra-fadnavis-in-press-conference/articleshow/123271049.cms</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-uddhav-thackeray-before-criticizing-devendra-fadnavis-look-in-the-mirror-public-not-forgotten-rs-100-crore-recovery-case-maharashtra-politics-marathi-news-1376412</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-ubt-mns-aim-to-prevent-mumbai-from-gujarati-people-says-sanjay-raut/articleshow/123340988.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mumbai-within-59-minutes-metro-local-railway-bus-roadways-to-become-congestion-free/articleshow/123316080.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-media-briefing-in-nashik-slams-pm-modi-devendra-fadnavis-and-bjp-on-independence/</t>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-vice-presidential-election-nda-nominates-cp-radhakrishnan-rajnath-singh-calls-kharge-for-unopposed-poll-india-alliance-to-meet-1377786</t>
+          <t>https://news18marathi.com/maharashtra/aaditya-thackeray-welcome-cm-devendra-fadnavis-in-mumbai-maharashtra-politics-news-1457232.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-and-ajit-pawar-battle-over-additional-municipal-corporations-in-pune/articleshow/123235053.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/08/18/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/pankaja-munde-emotional-speech-at-latur-gopinath-munde-statue-inauguration-latur-1455554.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-congress-leader-prithviraj-patil-to-join-bjp-in-maharashtra-citing-sangli-development-cm-fadnavis-to-attend-ceremony-1376508</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/11/gopinath-munde-taught-chief-minister-devendra-fadnavis-to-struggle-without-compromising-with-power-home-minist.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://marathi.ndtv.com/cities/jain-muni-nileshchandra-appeal-to-cm-devendra-fadnavis-over-dadar-kabutar-khana-issue-9075708</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadnavis-stated-bandra-versova-sea-link-will-be-extended-up-to-vadhavan-port-local18-1459825.html</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/third-mumbai-can-be-bigger-and-more-attractive-than-dubai-says-cm-devendra-fadnavis-article-152473589</t>
+          <t>https://www.msn.com/mr-in/news/other/harshvardhan-sapkal-on-devendra-fadanvis-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%9A%E0%A5%87-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%87/ar-AA1KbAUb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/alandi-news-universal-thoughts-in-dnyaneshwari-are-the-root-of-indian-culture-chief-minister-devendra-fadnavis/</t>
+          <t>https://marathi.ndtv.com/maharashtra/worli-bdd-chawl-redevelopment-program-cm-devendra-fadnavis-speech-dharavi-project-9083348</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/devendra-fadnavis-is-not-the-chief-but-a-thief-minister-thackerays-attack/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-news-controversy-over-state-level-oratory-competition-on-the-occasion-of-chief-minister-devendra-fadnavis/articleshow/123257068.cms</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-challenges-uddhav-and-raj-thackeray-over-mumbai-municipal-corporation-bmc-elections-during-dahi-handi-festival/articleshow/123333235.cms</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/rightful-houses-for-workers-of-solapur-houses-distributed-by-chief-minister-fadnavis/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/congress-sangli-leader-prithviraj-patil-resigns-to-join-bjp-in-presence-of-devendra-fadnavis/articleshow/123269760.cms</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/only-then-will-the-dream-of-a-slum-free-mumbai-be-realized-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-big-announcement-for-solapur-residents-will-thousands-of-youth-get-employment/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%82%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF/ar-AA1KyPVX</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/houses-in-mumbai-are-worth-gold-keep-them-safe-devendra-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-calling-vegetarians-impotent-is-foolish-chief-minister-devendra-fadnavis/911740/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/it-park-will-be-set-up-in-solapur-says-cm-devendra-fadnavis-article-152478385</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bdd-chawl-redevelopment-worli-phase-one-key-distribution-event-brings-maharashtra-political-leaders-devendra-fadnavis-eknath-shinde-aaditya-thackeray-on-one-stage-1376797</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-public-awareness-should-be-created-about-vermilion-and-swadeshi-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/navimumbai/in-uran-maritime-conference-cm-fadnavis-on-jnpa-and-port-of-singapore-to-build-indias-largest-port-rds-00-5299525/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-committee-formed-for-those-industries-chief-minister-devendra-fadnavis-gave-information/</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B2-%E0%A4%A8-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%87%E0%A4%B6%E0%A4%B5%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AD-%E0%A4%A4-%E0%A4%96-%E0%A4%8A%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A5%AC%E0%A5%AB-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%A8/ar-AA1KqsEZ</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-dabbawalas-will-get-500-square-feet-house-in-25-lakh-50-thousand-cm-devendra-fadnavis-big-annoucement-for-dabbawala-article-152466274</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-f-20/911111/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadanvis-cant-bear-it-cant-even-say-it-devendra-fadnaviss-attack-on-rahul-gandhi/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devedra-fadnavis-challenges-opposition-over-upcoming-municipal-elections-at-dahi-handi-2025/articleshow/123340653.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/the-historic-sword-of-the-brave-maratha-sardar-raghuji-bhosale-is-in-the-possession-of-the-government-when-will-it-be-brought-to-mumbai/129289/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-big-announcement-for-mumbai-dabewala-will-give-a-500-square-feet-house-for-25-lakhs-1458046.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-orders-give-preference-to-locals-in-railway-bogie-factory/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-mns-raj-thackeray-over-mumbai-municipal-bmc-elections/articleshow/123306829.cms</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-government-s-cabinet-approves-recruitment-of-15000-police-officers-125081200048_1.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ubt-leader-sanjay-raut-talk-on-cm-devendra-fadnavis-in-press-conference/articleshow/123271049.cms</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/devendra-fadanvis-chief-minister-devendra-fadanvis-clear-opinion-on-tariff-said-the-industries-that-will-be-affected/128946/</t>
+          <t>https://www.mymahanagar.com/photo-gallery/dahi-handi-2025-tembhinaka-dahihandi-cm-devendrad-fadnavis-political-statement-on-bmc-election/912700/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/manoj-jaranges-ultimatum-to-government-threatens-chalo-mumbai-on-august-29/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-dahi-handi-2025-live-updates-16-august-heavy-rain-alert-mumbai-thane-rain-updates-kvg-85-5307740/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chief-minister-devendra-fadnavis-announces-that-mumbai-dabbawalas-will-get-houses-worth-rs-25-50-lakh-9087324</t>
+          <t>https://www.saamana.com/sanjay-raut-media-briefing-in-nashik-slams-pm-modi-devendra-fadnavis-and-bjp-on-independence/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%97%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-10-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%A8%E0%A4%82-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3/ar-AA1Kn5AI</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/cm-devendra-fadnavis-takes-big-decision-transfer-7-ias-officer-in-state-88422</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-vice-presidential-election-nda-nominates-cp-radhakrishnan-rajnath-singh-calls-kharge-for-unopposed-poll-india-alliance-to-meet-1377786</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-dahi-handi-2025-live-updates-16-august-heavy-rain-alert-mumbai-thane-rain-updates-kvg-85-5307740/</t>
+          <t>https://prahaar.in/2025/08/18/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5301075/marathi-ekikaran-samiti-agitation-at-kabutar-khana-mumbai-what-did-they-say/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ratnagiri/nitesh-rane-indirectly-said-that-bjp-will-fight-independently-local-body-elections-in-konkan/articleshow/123308028.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-12-political-news-in-marathi-931564</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-nagpur-high-speed-rail-project-parallel-lines-to-samruddhi-mahamarg-know-detail-by-cm-devendra-fadnavis-article-152450605</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/give-priority-to-locals-for-employment-in-railway-bogie-factory-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/cm-fadnavis-shielding-corrupt-ministers-claims-uddhav/ar-AA1KiaOZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://vishwanewsmarathi.com/devendra-fadnavis-is-not-the-chief-but-a-thief-minister-thackerays-attack/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/seat-sharing-formula-for-mumbai-civic-election-will-depend-on-party-strength-says-cm-fadnavis/articleshow/123288144.cms</t>
+          <t>https://mpbreakingnews.in/marathi/national-internation/devendra-fadnavis-met-governor-c-p-radhakrishnan-what-did-fadnavis-shinde-say-about-the-vice-presidential-candidacy-05-692576</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-savvy-maharashtra-cm-fadnavis-gives-ipads-to-ministers-to-ensure-cabinet-agenda-secrecy/articleshow/123242160.cms</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/mumbais-journey-to-become-slum-free-cm-fadnavis-emphasizes-rapid-redevelopment/123320003</t>
+          <t>https://www.dainikprabhat.com/houses-in-mumbai-are-worth-gold-keep-them-safe-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/We-missed-the-bus-earlier--no-compromise-on-Mumbai-s-development-now--Fadnavis/2823252</t>
+          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-big-announcement-for-solapur-residents-will-thousands-of-youth-get-employment/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Quota-activist-Jarange-lost-credibility--his-remote-control-is-in-Sharad-Pawar-s-hands--BJP-MLC/2816227</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/pune-university-withdraws-voice-of-devendra-competition-notice-after-objection-from-nsui/123300501</t>
+          <t>https://vishwanewsmarathi.com/rightful-houses-for-workers-of-solapur-houses-distributed-by-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/it-park-will-be-set-up-in-solapur-says-cm-devendra-fadnavis-article-152478385</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-7063864.html</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis-7056055.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/third-mumbai-can-be-bigger-and-more-attractive-than-dubai-says-cm-devendra-fadnavis-article-152473589</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%9D%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%A8%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B2-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A4%9A-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A4%82-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%AE-%E0%A4%A6-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%B2/ar-AA1KwUDj</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/now-we-have-to-build-a-dahi-handi-of-self-reliance-chief-ministers-statement-at-shivraj-pratishthans-dahi-hand.html</t>
+          <t>https://www.dainikprabhat.com/alandi-news-universal-thoughts-in-dnyaneshwari-are-the-root-of-indian-culture-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/11-years-of-modi-government-indias-development-and-global-trust.html</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-committee-formed-for-those-industries-chief-minister-devendra-fadnavis-gave-information/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/support-modi-government-in-its-journey-of-development-minister-shri-mangalprabhat-lodha.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/india-showed-power-to-world-through-operation-sindoor-maharashtra-contribution-in-development-of-india-devendra-fadnavis-05-692150</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sindhudurg-district-uddhav-thackeray-shiv-sena-agitation-against-state-government-css-98-5296933/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadanvis-cant-bear-it-cant-even-say-it-devendra-fadnaviss-attack-on-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-dabbawalas-will-get-500-square-feet-house-in-25-lakh-50-thousand-cm-devendra-fadnavis-big-annoucement-for-dabbawala-article-152466274</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/since-2014-the-modi-government-has-taken-a-firm-step-away-from-past-practices-and-given-top-priority-to-nation.html</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/in-2014-power-changed-in-india-but-the-potential-change-in-foreign-policy-that-accompanied-the-change-in-power.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/santacruz-chembur-link-road-cable-stayed-bridge-to-open-for-traffic-from-tomorrow-august-14-article-152451074</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/there-is-no-shortage-of-athletes-in-our-country-the-most-populous-in-the-world.html</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-orders-give-preference-to-locals-in-railway-bogie-factory/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/the-governments-that-came-to-power-in-the-post-independence-era-gave-the-slogan-of-poverty-eradication.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/cabinet-decision-recruitment-of-15-thousand-policemen-increase-in-margins-of-fair-price-shopkeepers-034645.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/government-policies-have-given-new-energy-to-the-startup-culture-in-india.html</t>
+          <t>https://www.thodkyaat.com/manoj-jaranges-ultimatum-to-government-threatens-chalo-mumbai-on-august-29/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://breakingmaharashtra.in/?p=39156</t>
+          <t>https://marathi.ndtv.com/cities/chief-minister-devendra-fadnavis-announces-that-mumbai-dabbawalas-will-get-houses-worth-rs-25-50-lakh-9087324</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/many-workers-including-former-nagsevaks-of-bahujan-vikas-aaghadi-of-vasai-virar-join-bjp/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%A6%E0%A4%BF%E0%A4%A8%E0%A5%80%E0%A4%9A-%E0%A4%AE%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A4%BE/113567/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/cm-devendra-fadnavis-takes-big-decision-transfer-7-ias-officer-in-state-88422</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/script-by-salim-javed-fadnavis-mocks-rahul-s-vote-chori-claims-says-congress-chief-is-speaking-fiction/ar-AA1Ka5DS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/mr/!state/dahi-handi-2025-mumbai-municipal-corporation-will-break-the-mold-of-change-in-the-elections-chief-minister-devendra-fadnavis-maharashtra-news-mhs25081603443</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/election-commission-and-the-trust-it-must-rebuild-3678073</t>
+          <t>https://marathi.abplive.com/news/india/sanjay-raut-sharp-attack-said-devendra-fadnavis-is-the-beneficiary-of-the-election-commission-robbery-three-and-a-half-lakh-votes-were-stolen-in-nitin-gadkari-constituency-1376351</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/uddhav-thackeray-s-last-row-seat-at-rahul-gandhi-dinner-meet-gets-bjp-taunt/ar-AA1Kc4YH?cvid=6e808800d5b0453f91562cfa362d3523&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.navarashtra.com/maharashtra/devendra-fadnavis-on-rapid-redevelopment-is-necessary-for-a-slum-free-mumbai-960291.html</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ex-mla-from-maharashtra-says-he-too-was-offered-voter-fraud-services/articleshow/123349170.cms</t>
+          <t>https://www.loksatta.com/photos/news/5301075/marathi-ekikaran-samiti-agitation-at-kabutar-khana-mumbai-what-did-they-say/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-12-political-news-in-marathi-931564</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/indore/cm-leads-tiranga-rally-in-indore-criticises-rahul-gandhi/articleshow/123289456.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mumbai-nagpur-high-speed-rail-project-parallel-lines-to-samruddhi-mahamarg-know-detail-by-cm-devendra-fadnavis-article-152450605</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statement-in-pune-court-apprehending-threat-to-rahuls-life-being-withdrawn-congress-spokespersons/articleshow/123289899.cms</t>
+          <t>https://lokmanthan.com/give-priority-to-locals-for-employment-in-railway-bogie-factory-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/patna/my-bihar-yatra-is-to-save-democracy-says-rahul/articleshow/123308887.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/politicians-must-not-hate-any-community-while-ensuring-welfare-of-their-own-fadnavis/articleshow/123244376.cms</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/surrendered-maoist-commander-returns-home-to-celebrate-i-day/articleshow/123339065.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/articleshow/123290009.cms</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-says-govt-will-take-steps-to-increase-number-of-loudspeaker-days-for-ganeshotsav/articleshow/123284079.cms</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/india/fight-to-save-constitution-says-rahul-gandhi-as-police-detain-opposition-mps-amid-protest-9498093.html</t>
+          <t>http://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year-101755112441600.html</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/red-fort-2025-guest-list-vips-special-guests-and-leaders-joining-the-ceremony/historical-significance/slideshow/123258949.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-to-inaugurate-slew-of-projects-today-metro-3-may-launch-by-aug-end-101754936573343.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bailey-bridges-set-to-bring-year-round-connectivity-to-14-gadchiroli-villages/articleshow/123339082.cms</t>
+          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/rahul-gandhi-kharge-extend-greetings-to-nation-on-79th-independence-day-125081500455_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/seat-sharing-formula-for-mumbai-civic-election-will-depend-on-party-strength-says-cm-fadnavis/articleshow/123288144.cms</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/guwahati/himanta-calls-rahul-traitor-slams-priyankas-proposed-visit-to-dhubri/articleshow/123080085.cms</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/bjp-mla-wants-daily-screening-of-at-least-1-marathi-film-in-all-theatres-across-maharashtra-writes-to-cm-cultural-minister/articleshow/123311633.cms</t>
+          <t>https://www.newsband.in/article_detail/new-psa-terminal-at-jnpa-to-be-opened-soon-fadnavis-</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tricolour-rises-in-maoist-hq-foothills-kawandes-first-tryst-with-independence-day/articleshow/123310883.cms</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/mumbais-journey-to-become-slum-free-cm-fadnavis-emphasizes-rapid-redevelopment/123320003</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://arunachal24.in/rahul-gandhi-alleges-massive-voter-fraud-accuses-election-commission-of-collusion-with-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/patna/cong-prepares-for-rahuls-yatra-evades-question-on-oppn-cm-face/articleshow/123285236.cms</t>
+          <t>https://www.business-standard.com/companies/news/ibm-mumbai-client-centre-maharashtra-quantum-initiative-support-125081301837_1.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/vasai-virar-ex-civic-chief-set-up-gang-took-bribe-to-spare-illegal-buildings-ed-to-court-23589547</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/9-indian-monuments-and-places-that-tell-the-story-of-freedom/red-fort-delhi/slideshow/123275019.cms</t>
+          <t>https://www.ptinews.com/story/national/Change-imminent-in-BMC--Mahayuti-govt-has-broken-pot-of-sins-of-looters--Fadnavis/2828031</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.ptinews.com/detail/south,states/Maharashtra-government-not-interested-in-regulating-people-s-food-choices--CM-Fadnavis/2818929</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
+          <t>https://www.indiatvnews.com/maharashtra/ajit-pawar-aaditya-thackeray-slam-august-15-independence-day-meat-ban-orders-in-maharashtra-call-it-wrong-in-state-devendra-fadnavis-2025-08-13-1003355</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cji-gavai-to-inaugurate-bombay-high-courts-circuit-bench-at-kolhapur-today/articleshow/123338656.cms</t>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment-125081101371_1.html?isa=yes</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.zoomnews.in/en/news-detail/evm-tampering-sir-vote-theft-is-rahuls-conflict-with-ec-increasing-1.html</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%B5%E0%A4%B9-%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%87%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4-%E0%A4%AE-%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%87%E0%A4%82%E0%A4%A1-%E0%A4%AF-%E0%A4%AC%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%AC%E0%A5%88%E0%A4%A0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4%E0%A4%82%E0%A4%9C/ar-AA1K9Ujk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3544027-transforming-bhiwandi-a-vision-for-modern-urban-development</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-doubtful-voters-made-rahul-gandhi-win-raebareli-2025-08-13-1155872</t>
+          <t>https://thenewsmill.com/2025/08/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/160-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%9F%E0%A4%B2%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%AF-%E0%A4%A6/ar-AA1KcU3e?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-on-devendra-fadnavis-says-government-came-to-power-by-cutting-water-buffalo-at-kamakhya-temple-and-even-ate-it-as-prasad-and-fadnavis-says-become-a-vegetarian-stop-this-nonsense-1376830</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-india-block-s-show-of-strength-will-march-to-the-election-commission-office-under-led-of-rahul-gandhi-2025-08-11-1155278</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-march-on-vote-theft-could-rahul-gandhi-become-in-charge-2025-08-11-1155436</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-kabutar-khana-rain-updates-bdd-flats-pranjal-khewalkar-case-thalak-batmya-14th-august-2025-1469014.html</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/will-the-election-commission-take-rahul-gandhi-to-court-over-vote-theft-allegations-2025-08-12-1155626</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%9D%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%A8%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B2-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A4%9A-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A4%82-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%AE-%E0%A4%A6-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%B2/ar-AA1KwUDj</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/now-we-have-to-build-a-dahi-handi-of-self-reliance-chief-ministers-statement-at-shivraj-pratishthans-dahi-hand.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/independence-day-2025-rahul-gandhi-congratulated-on-79th-independence-day-said-it-is-the-duty-of-all-of-us-to-protect-the-pride-and-honor-of-the-precious-heritage-551556</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/11-years-of-modi-government-indias-development-and-global-trust.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A%E0%A5%87-5-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%A6-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B3-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1K51qk</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/support-modi-government-in-its-journey-of-development-minister-shri-mangalprabhat-lodha.html</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-india-independence-day-cm-fadnavis-dy-cms-opposition-leaders-hoist-flag-across-maharashtra-delhi-rahul-gandhi-in-rain-1377336</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-first-side-every-claim-of-rahul-gandhi-is-unacceptable-shehzad-poonawala-amy-95-5297251/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/since-2014-the-modi-government-has-taken-a-firm-step-away-from-past-practices-and-given-top-priority-to-nation.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-criticizes-india-aghadi-and-uddhav-thackerays-protest/910941/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/narendra-modi-is-the-name-of-the-strong-walls-standing-between-the-western-market-mafia-and-indias-sovereignty.html</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/karnataka-supporters-protest-after-rajannas-ouster-doubts-were-cast-on-rahul-gandhis-claim-of-vote-rigging.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/in-2014-power-changed-in-india-but-the-potential-change-in-foreign-policy-that-accompanied-the-change-in-power.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/harshvardhan-sapkal-on-devendra-fadanvis-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%9A%E0%A5%87-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%87/ar-AA1KbAUb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/there-is-no-shortage-of-athletes-in-our-country-the-most-populous-in-the-world.html</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/minta-devi-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%BE%E0%A4%9D%E0%A4%BE-%E0%A4%AB%E0%A5%8B%E0%A4%9F-5300887/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/about-the-fourth-chief-director-of-the-rashtra-sevika-samiti-pramilatai-medhe.html</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/i-had-the-experience-of-having-tea-with-dead-people-rahul-gandhi-criticizes-election-commission-by-sharing-video-gkt-96-5302274/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/pm-modi-hoists-the-tricolour-flag-at-the-ramparts-of-red-fort-on-79th-independence-day-2025.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5297490/india-alliance-parliament-protest-rahul-gandhi-election-commission-photos-viral-spl-93/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/narendra-modi-took-oath-as-prime-minister-in-2014-after-that-the-development-festival-of-the-entire-society-be.html</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-says-sonia-gandhis-name-added-to-voter-list-list-before-indian-citizenship-sdp-92-5301499/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/after-the-formation-of-a-stable-majority-government-under-the-leadership-of-narendra-modi-in-2014-indias-econo.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://breakingmaharashtra.in/?p=39156</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/rahul-gandhi-the-king-of-fake-news-keshav-upadhyays-criticism.html</t>
+          <t>https://www.deccanherald.com/opinion/election-commission-and-the-trust-it-must-rebuild-3678073</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/rahul-gandhi-claims-life-threat-in-pune-court-over-voter-fraud-issue-vvg94</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ex-mla-from-maharashtra-says-he-too-was-offered-voter-fraud-services/articleshow/123349170.cms</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/11/rahul-gandhi-is-a-puppet-of-anti-india-forces-union-minister-shivraj-singh-chouhans-attack.html</t>
+          <t>http://www.msn.com/en-in/news/India/uddhav-thackeray-s-last-row-seat-at-rahul-gandhi-dinner-meet-gets-bjp-taunt/ar-AA1Kc4YH?cvid=6e808800d5b0453f91562cfa362d3523&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/anurag-thakur-criticizes-bjp-over-vote-rigging-issue-amy-95-5302546/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/central-election-commissions-press-conference-today-rahul-gandhis-allegations-likely-to-be-answered.html</t>
+          <t>https://timesofindia.indiatimes.com/city/indore/cm-leads-tiranga-rally-in-indore-criticises-rahul-gandhi/articleshow/123289456.cms</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/fear-and-run-away-rahul-gandhis-role-in-swatantryaveer-savarkar-defamation-case.html</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/my-bihar-yatra-is-to-save-democracy-says-rahul/articleshow/123308887.cms</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/agralekha/the-revelation-made-by-sharad-pawar-is-likely-to-undermine-rahul-gandhis-efforts/911074/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statement-in-pune-court-apprehending-threat-to-rahuls-life-being-withdrawn-congress-spokespersons/articleshow/123289899.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/maneka-gandhi-expresses-her-opinion-on-supreme-court-order-on-stray-dogs-amy-95-5299752/</t>
+          <t>https://m.economictimes.com/news/india/live-rahul-gandhi-tejashwi-yadav-at-voter-adhikar-rally-nawada-bihar/videoshow/123379809.cms</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5295848/monsoon-tips-for-immunity-these-10-best-fruits-to-stay-healthy-and-energised-svk-05/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/live-rahul-gandhis-vote-adhikar-yatra-starts-from-sasaram-in-bihar/videoshow/123343047.cms</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5296622/how-to-beat-afternoon-sleepiness-and-boost-energy-with-simple-breathing-exercises-instead-of-coffee-svk-05/</t>
+          <t>https://m.economictimes.com/news/india/red-fort-2025-guest-list-vips-special-guests-and-leaders-joining-the-ceremony/historical-significance/slideshow/123258949.cms</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/bihar-list-of-voters-dispute-big-deabte-in-supreme-court-what-sc-said-and-what-kapil-sibbal-claims-scj-81-5298737/</t>
+          <t>https://www.business-standard.com/india-news/rahul-gandhi-kharge-extend-greetings-to-nation-on-79th-independence-day-125081500455_1.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5299053/liver-damage-symptoms-on-feet-liver-failure-signs-on-body-solution-expert-advice-dvr-99/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/live-ec-to-hold-press-conference-today-as-rahul-gandhi-takes-out-voter-adhikar-yatra-in-bihar/videoshow/123344763.cms</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/features/many-fake-voters-in-voter-list-democracy-bjp-congress-research-team-amy-95-5297141/</t>
+          <t>https://timesofindia.indiatimes.com/city/guwahati/himanta-calls-rahul-traitor-slams-priyankas-proposed-visit-to-dhubri/articleshow/123080085.cms</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5297669/5-biggest-gold-mines-in-india-kolar-hutti-sonbhadra-ramagiri-gold-field-know-the-details-spl-93/</t>
+          <t>https://arunachal24.in/rahul-gandhi-alleges-massive-voter-fraud-accuses-election-commission-of-collusion-with-bjp/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/picture-gallery-others/5298318/how-did-the-netherlands-end-the-problem-of-stray-dogs-what-measures-takern-for-stray-dogs-in-indian-cities-including-mumbai-aam-93/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tricolour-rises-in-maoist-hq-foothills-kawandes-first-tryst-with-independence-day/articleshow/123310883.cms</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5298525/mumbai-ganpati-bappa-maha-aagman-sohala-sunday-10-august-2025-lalbaug-parel-photos-sdn-96/</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/cong-prepares-for-rahuls-yatra-evades-question-on-oppn-cm-face/articleshow/123285236.cms</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/lifestyle-gallery/5298218/surya-gochar-in-singh-rashi-leo-virgo-and-aquarius-will-get-new-job-and-success-in-business-sap-20/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5302433/ncp-has-entrusted-suraj-chavan-with-a-big-responsibility-appointed-as-ncps-regional-general-secretary-gkt-96/</t>
+          <t>https://m.economictimes.com/news/india/9-indian-monuments-and-places-that-tell-the-story-of-freedom/red-fort-delhi/slideshow/123275019.cms</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5302284/dhananjay-munde-government-bungalow-row-karuna-munde-slams-says-he-have-many-flats-in-mumbai-kvg-85/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/borivali-religious-events-in-sanjay-gandhi-national-park-sparks-outrage-from-environmentalist-mumbai-print-news-rds-00-5296674/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5301397/mukesh-ambanis-wealth-on-twelth-of-indias-gdp-check-indias-top-10-wealthiest-families-kvg-85/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cji-gavai-to-inaugurate-bombay-high-courts-circuit-bench-at-kolhapur-today/articleshow/123338656.cms</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/jitendra-awhad-sharad-pawar-ncp-protest-against-election-commission-in-mumbra-css-98-5299492/</t>
+          <t>https://tennews.in/maha-cm-should-sack-corrupt-ministers-and-not-succumb-to-pressure-uddhav-thackeray/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5302315/these-special-bollywood-movies-still-rule-the-hearts-of-the-people-today-how-many-of-these-have-you-seen-scj-81/</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5302393/jui-gadkari-shares-his-bond-with-madhubhau-aka-narayan-jadhav-in-serial-and-real-life-ssm-00/</t>
+          <t>https://www.bundle.app/en/breaking-news/sharad-pawars-160-seats-offer-claim-follows-rahul-gandhis-big-charge-D07F5552-1EE6-4753-BCA7-5D187905264A</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-river-flood-study-causes-of-flooding-solutions-rain-koyna-dam-ssb-93-5300066/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5299829/maharashtrachi-hasyajatra-fame-nimish-kulkarni-also-part-of-chala-hawa-yeu-dya-2-with-gaurav-more-ssm-00/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-doubtful-voters-made-rahul-gandhi-win-raebareli-2025-08-13-1155872</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nandurbar/padmakar-valvi-to-join-ajit-pawar-led-ncp-after-leaving-bjp-congress-in-nandurbar/articleshow/123273982.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-march-on-vote-theft-could-rahul-gandhi-become-in-charge-2025-08-11-1155436</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/todays-photo-3/5293131/hsrp-number-plate-deadline-and-fine-only-a-few-days-left-to-install-hsrp-number-plates-otherwise-you-will-have-to-pay-a-heavy-fine-gkt-96/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-has-tea-with-dead-voters-from-bihar-2025-08-15-1156071</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/manoranjan/bollywood/jaya-bhaduri-father-said-mera-parivar-barbad-ho-gaya-after-daughter-married-to-amitabh-bachchan-hrc-97-5297540/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/will-the-election-commission-take-rahul-gandhi-to-court-over-vote-theft-allegations-2025-08-12-1155626</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/rahul-gandhi-clashes-in-delhi-over-ghost-in-voter-list-opposition-mps-including-rahul-gandhi-akhilesh-yadav-arrested/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis/ar-AA1KrS1p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-2025-08-14-1156052</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/mumbai-pigeons-kabootarkhanas-mumbais-pigeon-feeding-ban-how-a-public-health-move-clashed-with-faith-9077531</t>
+          <t>https://bharatexpress.com/india/independence-day-2025-wishes-rahul-gandhi-arvind-kejriwal-rekha-gupta-manish-sisodia-551510</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/government-is-beggar-maharashtra-minister-manikrao-kokate-sparks-row-with-fresh-remark-cm-fadnavis-terms-it-inappropriate/ar-AA1J47YX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A%E0%A5%87-5-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%A6-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B3-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1K51qk</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/karnataka-netas-unite-to-oppose-fadnavis-over-almatti-height/ar-AA1GbrxF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-india-independence-day-cm-fadnavis-dy-cms-opposition-leaders-hoist-flag-across-maharashtra-delhi-rahul-gandhi-in-rain-1377336</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/eknath-shinde-slams-uddhav-thackeray-amid-fadnavis-meet-buzz-changed-colours-like-a-chameleon/ar-AA1IS5La?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-first-side-every-claim-of-rahul-gandhi-is-unacceptable-shehzad-poonawala-amy-95-5297251/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pcmc/pune-news-illegal-construction-on-pavana-river-flood-line-sparks-controversy/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/karnataka-supporters-protest-after-rajannas-ouster-doubts-were-cast-on-rahul-gandhis-claim-of-vote-rigging.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3538922-clashes-over-maratha-quota-a-political-tug-of-war</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-should-have-experimented-with-them-both-hasan-mushrif-counterattack-also-criticizes-rahul-gandhi-1376392</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3541769-meat-ban-controversy-on-independence-day-ignites-debate-in-maharashtra</t>
+          <t>https://www.loksatta.com/desh-videsh/minta-devi-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%BE%E0%A4%9D%E0%A4%BE-%E0%A4%AB%E0%A5%8B%E0%A4%9F-5300887/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/maharashtra/mumbai-fadnavis-mumbai-need-not-be-made-like-singapore-or-shanghai-mumbai-has-own-character-which-better-announce-bmc-election-date-ws-l-9506968.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/jain-muni-nileshchandra-threatens-for-hunger-strike-from-august-13-against-closure-of-the-kabutarkhana-in-mumbai-bombay-high-court-know-all/articleshow/123229693.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/rahul-gandhi-the-king-of-fake-news-keshav-upadhyays-criticism.html</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%97-%E0%A4%B2-%E0%A4%9F-%E0%A4%AA-%E0%A4%A6-%E0%A4%A2%E0%A4%BC-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%B9%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B2%E0%A4%AE-%E0%A4%A8-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AC%E0%A4%AF-%E0%A4%A8/ar-AA1IpDnk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/rahul-gandhi-claims-life-threat-in-pune-court-over-voter-fraud-issue-vvg94</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/cold-war-on-guardian-minister-controversy-shinde-stays-away-from-cabinet-meeting/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/central-election-commissions-press-conference-today-rahul-gandhis-allegations-likely-to-be-answered.html</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/there-is-uproar-in-maharashtra-over-meat-ban-opposition-opened-front-warned-of-protest-outside-kdmc-office-news-89830</t>
+          <t>https://www.loksatta.com/desh-videsh/anurag-thakur-criticizes-bjp-over-vote-rigging-issue-amy-95-5302546/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/political-temperature-rises-in-mahayuti-dissatisfaction-rising-in-shinde-faction/</t>
+          <t>https://www.loksatta.com/maharashtra/asim-sarode-called-shiv-sena-shinde-group-alibaba-chalis-cho-backed-uddhav-thackeray-constitutional-stance-sud-02-5298749/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/legal/supreme-court-hearing-on-elephant-mahadevi-transfer-to-vantara-jamnagar-controversy-549836</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/fear-and-run-away-rahul-gandhis-role-in-swatantryaveer-savarkar-defamation-case.html</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.travelandleisureasia.com/in/news/nagpur-pune-vande-bharat-express-becomes-longest-in-india/</t>
+          <t>https://www.mymahanagar.com/editorial/agralekha/the-revelation-made-by-sharad-pawar-is-likely-to-undermine-rahul-gandhis-efforts/911074/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pm-flags-off-nagpur-pune-vande-bharat-cm-attends-nagpur-launch-101754853627589.html</t>
+          <t>https://www.loksatta.com/desh-videsh/maneka-gandhi-expresses-her-opinion-on-supreme-court-order-on-stray-dogs-amy-95-5299752/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ngp-pune-vande-bharat-oversubscribed-waiting-list-crosses-150-for-sunday-journey/articleshow/123339056.cms</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5296622/how-to-beat-afternoon-sleepiness-and-boost-energy-with-simple-breathing-exercises-instead-of-coffee-svk-05/</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/pm-narendra-modi-flags-off-three-vande-bharat-trains-from-ksr-railway-station-in-bengaluru/</t>
+          <t>https://www.loksatta.com/desh-videsh/bihar-list-of-voters-dispute-big-deabte-in-supreme-court-what-sc-said-and-what-kapil-sibbal-claims-scj-81-5298737/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://www.loksatta.com/sampadkiya/features/many-fake-voters-in-voter-list-democracy-bjp-congress-research-team-amy-95-5297141/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/14/palak-excels-as-nagpur-eves-get-better-of-thane.html</t>
+          <t>https://www.loksatta.com/photos/picture-gallery-others/5298318/how-did-the-netherlands-end-the-problem-of-stray-dogs-what-measures-takern-for-stray-dogs-in-indian-cities-including-mumbai-aam-93/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/maharashtra-govt-singapore-partner-for-350-bedded-multi-speciality-hospital-in-city.html</t>
+          <t>https://www.loksatta.com/photos/lifestyle-gallery/5298218/surya-gochar-in-singh-rashi-leo-virgo-and-aquarius-will-get-new-job-and-success-in-business-sap-20/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/rtmnu-to-shift-examination-deptt-to-maharajbag-campus.html</t>
+          <t>https://www.loksatta.com/photos/news/5302284/dhananjay-munde-government-bungalow-row-karuna-munde-slams-says-he-have-many-flats-in-mumbai-kvg-85/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/shriram-urban-cooperative-bank-posts-net-profit-of-rs-12995-lakh-.html</t>
+          <t>https://www.loksatta.com/thane/jitendra-awhad-sharad-pawar-ncp-protest-against-election-commission-in-mumbra-css-98-5299492/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/nagpur-pune-vande-bharat-express-timings-route-stops-ticket-price-train-number-schedule-and-more-9062515</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5302315/these-special-bollywood-movies-still-rule-the-hearts-of-the-people-today-how-many-of-these-have-you-seen-scj-81/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-new-railway-route-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0-100-%E0%A4%95-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%9A-%E0%A4%B6-%E0%A4%AB-%E0%A4%B0%E0%A4%B8/ar-AA1KfxgY</t>
+          <t>https://www.loksatta.com/pune/planning-department-to-restrict-to-use-10-percent-of-the-total-funds-of-dpc-for-procurement-pune-print-news-apk-13-zws-70-5298202/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-ajit-pawar-baramati-kabutar-khana-issue-mumbai-megablock-maharashtra-rain-sunday-10th-august-2025-1466332.html</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5299829/maharashtrachi-hasyajatra-fame-nimish-kulkarni-also-part-of-chala-hawa-yeu-dya-2-with-gaurav-more-ssm-00/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-nagpur-high-speed-rail-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A4%E0%A5%87-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B5%E0%A4%98%E0%A5%8D%E0%A4%AF-2-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%A4-%E0%A4%96%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1KmwMT</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nandurbar/padmakar-valvi-to-join-ajit-pawar-led-ncp-after-leaving-bjp-congress-in-nandurbar/articleshow/123273982.cms</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-live-updates-political-crime-sports-national-international-breaking-news-955926.html</t>
+          <t>https://www.mumbailive.com/mr/politics/maharashtra-election-commission-issues-notice-to-congress-leader-rahul-gandhi-for-allegations-of-voter-fraud-89540</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/3rd-mumbai-being-developed-by-govt-says-maharashtra-cm/</t>
+          <t>https://www.saamana.com/file-affidavit-in-seven-days-or-apologise-eci-ultimatum-on-rahul-gandhi-vote-theft-allegations/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ajit-pawar-on-dharavi-redevelopment-project-in-bdd-mhada-home-distribution-9083170</t>
+          <t>https://www.loksatta.com/thane/senior-citizen-looted-in-kalyan-west-siddheshwar-aali-area-css-98-5296201/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/16/drps-big-scheme-for-businessmen-in-dharavi-drppl-nmdpl-maha-mtb.html</t>
+          <t>https://www.loksatta.com/nashik/university-likely-to-include-students-service-at-the-kumbh-mela-subject-in-curriculum-zws-70-5299041/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ensure-timely-completion-of-5-000-mw-solar-agri-feeder-scheme-by-sep-2025-fadnavis/ar-AA1JA6xO</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/in-which-democracy-does-vote-jihad-fit-question-from-minister-nitesh-rane/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/pm-modis-independence-day-speeches-highlights-a-look-back-from-2025-to-2014/2025-the-era-of-self-reliant-bharat-103-minutes/slideshow/123319643.cms</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-government-not-interested-in-regulating-people-s-food-choices-cm-fadnavis/ar-AA1KrS1p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-pmc-dismantles-traffic-circle-at-sm-ghule-chowk-in-mohamadwadi-after-residents-protest/</t>
+          <t>https://www.ndtv.com/india-news/mumbai-pigeons-kabootarkhanas-mumbais-pigeon-feeding-ban-how-a-public-health-move-clashed-with-faith-9077531</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.msn.com/en-in/news/India/karnataka-netas-unite-to-oppose-fadnavis-over-almatti-height/ar-AA1GbrxF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/disturbing-that-pms-i-day-speech-didnt-have-nehrus-mention-pawar/articleshow/123339182.cms</t>
+          <t>http://www.msn.com/en-in/news/india/eknath-shinde-slams-uddhav-thackeray-amid-fadnavis-meet-buzz-changed-colours-like-a-chameleon/ar-AA1IS5La?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/states/sharad-pawar-slams-pm-modi-for-ignoring-nehru-in-i-day-speech/53504</t>
+          <t>https://punemirror.com/city/pcmc/pune-news-illegal-construction-on-pavana-river-flood-line-sparks-controversy/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/devendra-fadnavis-on-sharad-pawar-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%A6%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1KdfSS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/politics/3539923-controversy-over-maharashtras-kabutar-jihad-congress-hits-back-at-bjp</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/list-of-spokespersons-of-ncp-sharad-pawar-group-announced-mumbai-print-news-css-98-5299884/</t>
+          <t>https://www.msn.com/en-in/news/India/maha-govt-not-keen-on-regulating-peoples-food-choices-fadnavis/ar-AA1KsooX</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3541769-meat-ban-controversy-on-independence-day-ignites-debate-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-thackeray-group-called-him-a-thief-minister-devendra-fadnavis-criticized-uddhav-thackeray-calling-him-a-mandate-thief/911143/</t>
+          <t>https://www.newsbytesapp.com/news/politics/maharashtra-federation-demands-national-meat-sale-calendar-amid-non-veg-row/story</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-criticized-devendra-fadnavis-over-ban-on-non-veg-on-15th-august/</t>
+          <t>https://hindi.newsbytesapp.com/news/india/maharashtra-meat-ban-on-independence-day-whats-the-controversy/story</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-comment-on-manoj-jarange-patil-protest-for-maratha-reservation-in-mumbai-on-august-29-1470254.html/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1JArmJ</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-bhaskar-jadhav-comment-on-brahman-samaj-1376769</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/shiv-sena-tensions-flare-over-raigad-nashik-flag-hoisting-guardian-minister-dispute-ntcpmm-dskc-2308822-2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/farmers-compensation-pending-sharad-pawar-to-discuss-with-chief-minister-4216652</t>
+          <t>https://ndtv.in/videos/why-did-mutton-politics-happen-on-15th-august-in-maharashtra-aimim-ncp-organized-a-non-veg-party-981146</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-alleges-that-the-public-safety-act-is-meant-for-bunch-of-thought/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9B-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1JMr77?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-politics-obc-leader-laxman-hake-criticizes-pawar-family-he-warns-devendra-fadnavis-over-maratha-vs-obc-conflict-amid-manoj-jarange-agitation-in-mumbai-maharashtra-news-mhs25081700653</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/jain-muni-nileshchandra-threatens-for-hunger-strike-from-august-13-against-closure-of-the-kabutarkhana-in-mumbai-bombay-high-court-know-all/articleshow/123229693.cms</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%88%E0%A4%B8-%E0%A4%91%E0%A4%AB-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%88-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/ar-AA1KkbZY</t>
+          <t>https://www.agniban.com/controversy-over-the-tomb-in-fatehpur-owaisi-said-if-the-attackers-were-muslims/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mpbreakingnews.in/maharashtra/maharashtra-politics-eknath-shinde-bharat-gogawale-aditi-tatkare-54-800703</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/dhananjay-munde-praises-cm-devendra-fadnavis-in-a-public-meeting-is-he-try-to-grab-a-ministerial-position-again-discussion-in-politics-a-a719/amp/</t>
+          <t>https://www.theindiadaily.com/india/there-is-uproar-in-maharashtra-over-meat-ban-opposition-opened-front-warned-of-protest-outside-kdmc-office-news-89830</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-maharashtra-will-have-to-face-a-maratha-vs-obc-conflict-warns-haake-a-a1008/</t>
+          <t>https://www.hindisaamana.com/political-temperature-rises-in-mahayuti-dissatisfaction-rising-in-shinde-faction/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-kabutar-khana-rain-updates-bdd-flats-pranjal-khewalkar-case-thalak-batmya-14th-august-2025-1469014.html</t>
+          <t>https://bharatexpress.com/legal/supreme-court-hearing-on-elephant-mahadevi-transfer-to-vantara-jamnagar-controversy-549836</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/manoj-jaranges-remote-in-sharad-pawars-hands/</t>
+          <t>https://bharatexpress.com/legal/supreme-court-allows-amendment-of-petition-in-kolhapurs-mahadevi-elephant-case-hearing-will-be-held-on-august-25-551046</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/sanjay-raut-slams-devendra-fadnavis-over-ban-on-meat-sales-on-august-15/</t>
+          <t>https://www.travelandleisureasia.com/in/news/nagpur-pune-vande-bharat-express-becomes-longest-in-india/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.ainvest.com/news/ibm-maharashtra-collaborate-quantum-computing-initiatives-2508/</t>
+          <t>https://www.msn.com/en-in/news/India/breaking-news-pm-modi-flags-off-12th-vande-bharat-express-nagpur-to-pune-abp-news/vi-AA1KhGS6</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pm-flags-off-nagpur-pune-vande-bharat-cm-attends-nagpur-launch-101754853627589.html</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/companies/news/ibm-mumbai-client-centre-maharashtra-quantum-initiative-support-125081301837_1.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/14/palak-excels-as-nagpur-eves-get-better-of-thane.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.itvoice.in/ibm-unveils-new-india-client-experience-centre-in-mumbai-and-announces-plans-to-support-government-of-maharashtras-quantum-initiatives</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/maharashtra-govt-singapore-partner-for-350-bedded-multi-speciality-hospital-in-city.html</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://currentaffairs.adda247.com/indias-longest-route-vande-bharat-express-launched-on-this-corridor/</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/nagpur-pune-vande-bharat-express-timings-route-stops-ticket-price-train-number-schedule-and-more-9062515</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/independence-day-at-red-fort-where-to-book-and-what-to-carry/event-timings/slideshow/123258257.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-new-railway-route-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0-100-%E0%A4%95-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%9A-%E0%A4%B6-%E0%A4%AB-%E0%A4%B0%E0%A4%B8/ar-AA1KfxgY</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/chhattisgarh-cm-sai-flags-off-sbi-cyber-security-awareness-van-in-raipur-launches-statewide-drive-against-online-fraud/articleshow/123334545.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-nagpur-high-speed-rail-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%A4%E0%A5%87-%E0%A4%A8-%E0%A4%97%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B5%E0%A4%98%E0%A5%8D%E0%A4%AF-2-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%A4-%E0%A4%96%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1KmwMT</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/vikhe-patil-on-vandhe-bharat-express-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%95-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B5%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1Ki4Gy</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-politics-uddhav-thackeray-shivsena-bmc-elections-mns-shivena-ubt-raj-thackeray-bmc-elections-news-bjp-shivsena-ubt/4096856/</t>
+          <t>https://trak.in/stories/3rd-mumbai-being-developed-by-govt-says-maharashtra-cm/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-alleges-vote-theft-holds-candle-march-protest-in-nagpur/articleshow/123312003.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/mhada-hands-over-556-flats-in-worli-bdd-chawl-redevelopment.html</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/politicians-must-not-hate-any-community-while-ensuring-welfare-of-their-own-fadnavis/articleshow/123244376.cms</t>
+          <t>https://marathi.ndtv.com/cities/ajit-pawar-on-dharavi-redevelopment-project-in-bdd-mhada-home-distribution-9083170</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/drps-big-scheme-for-businessmen-in-dharavi-drppl-nmdpl-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/political-buzz-on-janmashtami-festivities-in-mumbai-ahead-of-local-body-polls-3683780</t>
+          <t>https://www.msn.com/en-in/news/India/ensure-timely-completion-of-5-000-mw-solar-agri-feeder-scheme-by-sep-2025-fadnavis/ar-AA1JA6xO</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-bahujan-vikas-aaghadi-bva-leaders-cross-over-to-bjp-mahesh-patil-among-new-joinees/ar-AA1KqIKK</t>
+          <t>https://m.economictimes.com/news/india/pm-modis-independence-day-speeches-highlights-a-look-back-from-2025-to-2014/2025-the-era-of-self-reliant-bharat-103-minutes/slideshow/123319643.cms</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3537336-inclusivity-and-legacy-remembering-gopinath-mundes-vision</t>
+          <t>https://m.economictimes.com/news/india/bjp-leader-anurag-thakur-press-meet-in-bjp-hq-new-delhi/videoshow/123276786.cms</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3544879-maharashtra-leaders-celebrate-cp-radhakrishnans-vice-presidential-nomination</t>
+          <t>https://thelivenagpur.com/2025/08/15/bawankule-hoists-tricolour-calls-for-prosperous-and-safe-nagpur/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3543985-mumbai-dahi-handi-honoring-indias-brave-soldiers</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
+          <t>https://www.zoomnews.in/en/news-detail/evm-tampering-sir-vote-theft-is-rahuls-conflict-with-ec-increasing-1.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ratnagiri-news-ncp-sharad-pawar-group-leader-prashant-yadav-join-bjp-9083531</t>
+          <t>https://www.msn.com/en-in/news/India/guaranteed-win-through-evms-sanjay-raut-echoes-sharad-pawar-s-160-seats-claim-says-same-people-approached-uddhav-thackeray-twice/ar-AA1Kfsqp</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%86%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%95/ar-AA1KEzpJ</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/disturbing-that-pms-i-day-speech-didnt-have-nehrus-mention-pawar/articleshow/123339182.cms</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-gets-a-setback-in-konkan-big-leader-joins-bjp/</t>
+          <t>https://newsarenaindia.com/states/sharad-pawar-slams-pm-modi-for-ignoring-nehru-in-i-day-speech/53504</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary-says-cji-gavai-3684747</t>
+          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-on-sharad-pawar-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-160-%E0%A4%B8-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%82%E0%A4%9F-%E0%A4%A6%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1KdfSS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://indiplomacy.com/2025/08/15/singapore-deepens-infrastructure-ties-in-maharashtra-with-major-investments/</t>
+          <t>https://www.loksatta.com/politics/sharad-pawar-nagpur-tour-political-strategy-print-politics-news-ocd-94-5298098/</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/news/tesla-debuts-in-india-picks-mumbai-cm-devendra-fadnavis-says-city-ideal-for-ev-push-4-charging-spots-lineup/ar-AA1IGIiB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-thackeray-group-called-him-a-thief-minister-devendra-fadnavis-criticized-uddhav-thackeray-calling-him-a-mandate-thief/911143/</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/versova-bandra-sea-link-on-track-for-two-year-completion-maha-cm/123321974</t>
+          <t>https://www.loksatta.com/mumbai/list-of-spokespersons-of-ncp-sharad-pawar-group-announced-mumbai-print-news-css-98-5299884/</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/submit-proposal-to-convert-circuit-bench-in-kolhapur-into-permanent-bench-cji-bhushan-gavai-to-hc/articleshow/123349240.cms</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/news/2025-maharashtra-ev-policy-gets-green-signal-subsidies-to-toll-waiver-everything-you-must-know/ar-AA1DTk4A?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-chandan-nagar-police-station-inaugurated-by-ajit-pawar-devendra-fadnavis-ashapura-jewelers-robbery-in-hours/articleshow/123227257.cms</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/17/lokmat-global-economic-convention-to-be-held-on-august-18-in-london.html</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-comment-on-manoj-jarange-patil-protest-for-maratha-reservation-in-mumbai-on-august-29-1470254.html/amp</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjAzNDk=/maharashtra-must-fix-tendering-to-speed-up-infrastructure-work-cm</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment/2812408</t>
+          <t>https://marathi.abplive.com/tv-show/zero-hour/zero-hour-bhaskar-jadhav-comment-on-brahman-samaj-1376769</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3538840-maharashtras-digital-leap-rapid-growth-in-data-and-infrastructure</t>
+          <t>https://jantaserishta.com/local/maharashtra/farmers-compensation-pending-sharad-pawar-to-discuss-with-chief-minister-4216652</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3544027-transforming-bhiwandi-a-vision-for-modern-urban-development</t>
+          <t>https://www.marathiebatmya.com/political/harshwardhan-sapkal-alleges-that-the-public-safety-act-is-meant-for-bunch-of-thought/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/newly-inaugurated-capitaland-data-centre-in-mumbai-keeps-india-ahead-in-digital-revolution-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%88%E0%A4%B8-%E0%A4%91%E0%A4%AB-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%88-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/ar-AA1KkbZY</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3544738-maharashtras-commitment-to-judiciary-kolhapur-gets-a-new-bench</t>
+          <t>https://www.loksatta.com/mumbai/sharad-pawar-criticize-maharashtra-public-security-bill-mumbai-print-news-css-98-5304810/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/will-the-political-power-of-farmers-survive-article-on-agrowon-rat16</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-parinay-phuke-said-when-elections-come-manoj-jarange-patil-spoils-the-atmosphere-and-his-remote-key-in-sharad-pawar-hands-a-a719/amp/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://marathi.abplive.com/news/maharashtra/rohit-pawar-criticizes-on-savitribai-phule-pune-university-administration-on-the-issue-of-voice-of-devendra-1376510</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/meet-sanjay-india-s-robotic-war-dog-are-robodogs-the-future-of-warfare-978929</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%95-%E0%A4%B5-%E0%A4%AF%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B5%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%AA%E0%A4%9C-%E0%A4%A6%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%A4-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A4%A1-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%AE-%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%A4%E0%A4%B0/ar-AA1Ki9tC</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bes21-mp-vote-theft-campaign-cong.html</t>
+          <t>https://marathi.abplive.com/news/parinay-fuke-criticized-on-manoj-jarange-patil-said-manoj-jarange-remote-is-in-sharad-pawar-hand-criticism-over-cm-devendra-fadnavis-maratha-reservation-1376608</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kozhikode/wayanad-voters-refute-anurag-singh-thakurs-fraud-claims/articleshow/123311455.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/radhakrishna-vikhe-patil-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1KitOb</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/13/des117-hr-rahul-saini.html</t>
+          <t>https://www.lokmat.com/pune/pune-news-maharashtra-will-have-to-face-a-maratha-vs-obc-conflict-warns-haake-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/119-voters-from-one-single-house-cong-alleges-vote-theft-in-chandrapur/articleshow/123312033.cms</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5300621/sanjay-raut-criticized-devendra-fadanvis-and-bjp-government/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/ec-acting-like-bjp-agent-hebbalkar/articleshow/123325268.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-live-news-today-11-august-2025-marathi-batmya-weather-update-heavy-rain-konkan-vidarbha-orange-alert-thane-metro-news/liveblog/123227006.cms</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/119-voters-in-one-house-cong-alleges-vote-theft/articleshow/123310094.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/rahul-gandhi-vote-theft-allegation-%E0%A4%96-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%9A-%E0%A4%AE%E0%A4%A4%E0%A4%9A-%E0%A4%B0-%E0%A4%9A-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%B9-%E0%A4%96-%E0%A4%9F-%E0%A4%B0%E0%A4%A1%E0%A5%87%E0%A4%AA%E0%A4%A3/ar-AA1Kuhrn</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-maharashtra-cm-prithviraj-chavan-backs-stir-over-alleged-bogus-voting-in-karad-south-during-2024-assembly-polls/articleshow/123311995.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-big-statement-on-slaughter-houses-closed-on-independence-day/articleshow/123293008.cms</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-pigeon-feed-controversy-public-health-a-priority-280965/</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://humenglish.com/world/vote-chori-protest-rahul-gandhi-arrested-in-new-delhi/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-shivsena-ubt-on-meat-ban-on-independence-day-15-august/911513/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://www.dainikprabhat.com/manoj-jaranges-remote-in-sharad-pawars-hands/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/14/sonia-gandhi-was-a-voter-before-becoming-an-indian-citizen-bjp-alleges-that-it-is-congresss-voter-scam.html</t>
+          <t>https://www.thodkyaat.com/sanjay-raut-slams-devendra-fadnavis-over-ban-on-meat-sales-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-debate-erupts-over-closing-meat-shops-in-maharashtra-on-independence-day-24012549.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/fadnavis-slams-mahayuti-govt-signals-bmc-shakeup-4214626</t>
+          <t>https://www.ainvest.com/news/ibm-maharashtra-collaborate-quantum-computing-initiatives-2508/</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://m.economictimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/vice-president-election-2025-pm-modi-gives-big-joy-to-rss-by-nominating-cp-radhakrishnan-ahead-of-100-years-celebration-know-all/articleshow/123377347.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/cm-fadnavis-urges-bdd-chawl-residents-not-to-sell-new-homes/ar-AA1Kyjju</t>
+          <t>https://www.itvoice.in/ibm-unveils-new-india-client-experience-centre-in-mumbai-and-announces-plans-to-support-government-of-maharashtras-quantum-initiatives</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://economictimes.indiatimes.com/tech/technology/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/articleshow/123286355.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/idontknowhomeminister-goes-viral-g-parameshwara-tells-trolls-to-find-out-who-is-the-best/articleshow/123338015.cms</t>
+          <t>https://m.economictimes.com/news/india/independence-day-at-red-fort-where-to-book-and-what-to-carry/event-timings/slideshow/123258257.cms</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-maratha-royal-raghuji-bhonsle-returns-home-on-aug-18-after-200-years/articleshow/123244523.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/bastar-kids-visit-city-from-remote-areas-on-edu-expedition/articleshow/123289148.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/chhattisgarh-cm-sai-flags-off-sbi-cyber-security-awareness-van-in-raipur-launches-statewide-drive-against-online-fraud/articleshow/123334545.cms</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-says-govt-will-take-steps-to-increase-number-of-loudspeaker-days-for-ganeshotsav/articleshow/123284079.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/we-missed-the-bus-earlier-no-compromise-on-mumbais-development-now-fadnavis/ar-AA1KxlQf</t>
+          <t>http://www.msn.com/en-in/news/India/maharashtra-news-will-uddhav-and-raj-thackeray-join-hands-for-maharashtra-s-local-elections/ar-AA1KvJOD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmcs-pot-of-sins-broken-says-maharashtra-cm-devendra-fadnavis-23589784</t>
+          <t>https://www.jansatta.com/national/maharashtra-politics-uddhav-thackeray-shivsena-bmc-elections-mns-shivena-ubt-raj-thackeray-bmc-elections-news-bjp-shivsena-ubt/4096856/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/fadnavis-asks-real-estate-industry-why-housing-prices-are-rising-in-mumbai-despite-concessions/ar-AA1KxRR7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-alleges-vote-theft-holds-candle-march-protest-in-nagpur/articleshow/123312003.cms</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-orders-partial-rollback-of-ban-on-feeding-pigeons/ar-AA1JYREe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ganesh-mandals-asked-by-cm-to-have-operation-sindoor-as-theme-this-year-101755112441600.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/political-buzz-on-janmashtami-festivities-in-mumbai-ahead-of-local-body-polls-3683780</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/museum-to-honour-dabbawalas-to-be-inaugurated-in-mumbai-3677005</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bva-leaders-cross-over-to-bjp-mahesh-patil-among-new-joinees/articleshow/123274391.cms</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/ibm-opens-new-mumbai-office-as-gateway-to-viksit-bharat-567381</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://marathi.ndtv.com/maharashtra/ratnagiri-news-ncp-sharad-pawar-group-leader-prashant-yadav-join-bjp-9083531</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Maharashtra-prominent-player-in-Indian%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bjp-mla-ramesh-karad-criticizes-congress-leader-dheeraj-deshmukh-1376456</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/as-chawl-residents-move-into-modern-homes-fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%86%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%95/ar-AA1KEzpJ</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-gets-a-setback-in-konkan-big-leader-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%97-%E0%A4%97-%E0%A4%B5%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%A4-%E0%A4%B0%E0%A4%A1%E0%A4%97-%E0%A4%A3%E0%A5%87-%E0%A4%A6%E0%A5%88%E0%A4%A8-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%A8-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%B5%E0%A4%B0-%E0%A4%B9%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AC-%E0%A4%B2/ar-AA1KtVOK</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/record-10-tier-human-pyramids-lend-thrill-to-mumbais-rainy-dahi-handi-in-poll-year/articleshow/123337445.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary-says-cji-gavai-3684747</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-gives-go-ahead-for-recruiment-of-over-15000-constables/articleshow/123261279.cms</t>
+          <t>https://indiplomacy.com/2025/08/15/singapore-deepens-infrastructure-ties-in-maharashtra-with-major-investments/</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-gets-5-km-sea-facing-promenade-coastal-road-to-stay-open-24x7/ar-AA1Kxl74</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra-govt-at-forefront-of-efforts-to-provide-infrastructure-for-judiciary--says-cji-gavai/2830846</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-singapore-leaders-review-phase-2-of-bharat-mumbai-container-terminal-567159</t>
+          <t>https://www.msn.com/en-in/autos/news/2025-maharashtra-ev-policy-gets-green-signal-subsidies-to-toll-waiver-everything-you-must-know/ar-AA1DTk4A?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/versova-bandra-sea-link-on-track-for-two-year-completion-maha-cm/123321974</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day20250815151854</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/submit-proposal-to-convert-circuit-bench-in-kolhapur-into-permanent-bench-cji-bhushan-gavai-to-hc/articleshow/123349240.cms</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/17/lokmat-global-economic-convention-to-be-held-on-august-18-in-london.html</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://propnewstime.com/getdetailsStories/MjAzNDk=/maharashtra-must-fix-tendering-to-speed-up-infrastructure-work-cm</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
+          <t>https://www.ptinews.com/editor-detail/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment/2812408</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3543920-thrills-and-politics-dahi-handi-festival-amidst-mumbai-rains</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3540648-mumbai-unveils-new-coastal-promenade-a-green-oasis-by-the-sea</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/leaders-review-phase-2-of-bharat-mumbai-container-terminal/77640</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/16/mumbai-worli-parivartan-dahi-handi-gallery/</t>
+          <t>https://agrowon.esakal.com/agro-special/will-the-political-power-of-farmers-survive-article-on-agrowon-rat16</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%95%E0%A4%AC%E0%A5%82%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%A8-%E0%A4%AF%E0%A4%AE-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JYvBC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ndtv.com/video/meet-sanjay-india-s-robotic-war-dog-are-robodogs-the-future-of-warfare-978929</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-eknath-shinde-aditya-thackeray-on-one-stage-sa-9506059.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/actor-complains-about-redevelopment-project-fraud-cm-intervenes-101755026135161.html</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/the-dream-of-mumbai-within-59-minutes-will-be-soon-filfilled-cm-devendra-fadnavis-9089297</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/bes21-mp-vote-theft-campaign-cong.html</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-on-plan-of-slum-free-mumbai-89066</t>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/wayanad-voters-refute-anurag-singh-thakurs-fraud-claims/articleshow/123311455.cms</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/119-voters-from-one-single-house-cong-alleges-vote-theft-in-chandrapur/articleshow/123312033.cms</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/news/flag-hoisting-on-the-occasion-of-independence-at-high-cout-with-the-presence-of-cm-devendra-fadnavis-1377273</t>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/ec-acting-like-bjp-agent-hebbalkar/articleshow/123325268.cms</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-announces-that-coastal-road-will-be-open-24-hours-from-august-15/912175/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/119-voters-in-one-house-cong-alleges-vote-theft/articleshow/123310094.cms</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sclr-to-weh-connector-chembur-to-mumbai-airport-cable-bridge-inaugurated-by-devendra-fadnavis/articleshow/123317604.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-maharashtra-cm-prithviraj-chavan-backs-stir-over-alleged-bogus-voting-in-karad-south-during-2024-assembly-polls/articleshow/123311995.cms</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/kishor-kadam-seeks-help-from-cm-devendra-fadnavis-to-save-his-house-in-mumbai/911132/</t>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/aaditya-thackeray-welcome-cm-devendra-fadnavis-in-mumbai-maharashtra-politics-news-1457232.html</t>
+          <t>https://humenglish.com/world/vote-chori-protest-rahul-gandhi-arrested-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/mumbai-lagbaghcha-raja-area-firefighters-charage-1-25-lakh-per-day-cm-devendra-fadnavis-assures-ganesh-mandal-of-mumbai-1376931</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/editorial/editorial-on-pune-municipal-corporation-issue-cm-devendra-fadnavis-ajit-pawar/articleshow/123227690.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/14/sonia-gandhi-was-a-voter-before-becoming-an-indian-citizen-bjp-alleges-that-it-is-congresss-voter-scam.html</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-big-statement-on-slaughter-houses-closed-on-independence-day/articleshow/123293008.cms</t>
+          <t>https://mpbreakingnews.in/maharashtra/nawab-malik-ajit-pawar-bmc-election-maharashtra-politics-54-801354</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/mumbai-mumbai-worli-largest-dahi-handi-tower-in-mumbai-the-sacrifice-of-sambhaji-maharaj-chhaava-and-kavi-kalash-cm-devendra-fadnavis-clap-1377434</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.capitaland.com/en/about-capitaland/newsroom/news-releases/international/2025/august/CLI_signs_MoU_with_Maharashtra_Government_for_plans_to_invest_over_INR19,200_crores_by_2030_to_expand_in_Mumbai_and_Pune.html</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/mumbai-to-receive-several-projects-ahead-of-bmc-elections-metro-3-phase-3-likely-to-be-launched-by-end-of-august-ask-chatgpt-2726817.html</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/idontknowhomeminister-goes-viral-g-parameshwara-tells-trolls-to-find-out-who-is-the-best/articleshow/123338015.cms</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis-4212867</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-maratha-royal-raghuji-bhonsle-returns-home-on-aug-18-after-200-years/articleshow/123244523.cms</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-experienced-ai-cricket-simulator-during-the-visit-4210440</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/newly-built-capitaland-data-centre-in-mumbai-will-put-india-ahead-in-digital-revolution-fadnavis-4210177</t>
+          <t>https://www.msn.com/en-in/lifestyle/smart-living/navi-mumbai-airport-work-in-full-swing-panel-to-suggest-ways-to-help-us-tariffs-hit-sectors-cm/ar-AA1KnAoG</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/cm-fadnavis-said-dream-of-mumbai-within-59-minutes-will-soon-be-fulfilled/</t>
+          <t>https://www.msn.com/en-in/news/India/we-missed-the-bus-earlier-no-compromise-on-mumbais-development-now-fadnavis/ar-AA1KxlQf</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/mumbais-development-gets-new-momentum-many-big-projects-of-mmrda-inaugurated-coastal-road-will-be-open-24-hours-from-august-15/</t>
+          <t>http://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-orders-partial-rollback-of-ban-on-feeding-pigeons/ar-AA1JYREe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-rapid-redevelopment-is-needed-for-a-slum-free-mumbai/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/museum-to-honour-dabbawalas-to-be-inaugurated-in-mumbai-3677005</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.businessworld.in/article/ibm-opens-new-mumbai-office-as-gateway-to-viksit-bharat-567381</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://www.ptinews.com/story/national/Maharashtra-prominent-player-in-Indian%E2%80%99s-unstoppable-growth-story--Fadnavis/2824090</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/flag-hoisting-flag-hoisting-ceremony-completed-in-mumbai-thane-and-beed-by-the-chief-minister-and-deputy-chief-minister/</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-gets-emotional-after-seeing-the-encampment-on-dahihandi-tower/129236/</t>
+          <t>https://www.ptinews.com/detail/business/As-chawl-residents-move-into-modern-homes--Fadnavis-urges-them-to-treat-new-possession-as-gold/2821434</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/eknath-shinde-claims-that-not-a-single-pothole-will-be-seen-in-mumbai-in-the-next-one-and-a-half-years/129057/</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/politics-in-the-dahi-handi-festival-in-mumbai-fadnavis-hints-at-change/129241/</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/cm-devendra-fadnavis-chief-minister-devendra-fadnavis-should-not-be-influenced-by-my-voice-manoj-jarange-patil/128997/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-fadanvis-inaugurates-santacruz-chembur-link-road-extension-and-kalanagar-flyover-arm-in-mumbai/articleshow/123307771.cms</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/record-10-tier-human-pyramids-lend-thrill-to-mumbais-rainy-dahi-handi-in-poll-year/articleshow/123337445.cms</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/cji-gavai-inaugurates-bombay-hcs-4th-bench-in-kolhapur/amp_articleshow/123345149.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-gives-go-ahead-for-recruiment-of-over-15000-constables/articleshow/123261279.cms</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/i-day-navroz-and-janmashtami-bring-cheer-to-festive-weekend/articleshow/123309219.cms</t>
+          <t>https://www.msn.com/en-in/news/India/mumbai-gets-5-km-sea-facing-promenade-coastal-road-to-stay-open-24x7/ar-AA1Kxl74</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/new-delhi-weather-alert-rainfall-humidity-and-a-cooler-day-ahead-on-august-15-2025/articleshow/123314541.cms</t>
+          <t>https://www.businessworld.in/article/fadnavis-singapore-leaders-review-phase-2-of-bharat-mumbai-container-terminal-567159</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ranchi/school-celebrates-dahi-handi-event/articleshow/123350561.cms</t>
+          <t>https://ommcomnews.com/india-news/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/committee-seeks-deputation-of-physical-education-teachers-to-rural-schools-twice-a-week/articleshow/123325270.cms</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/india-singapore-green-digital-maritime-corridor-takes-center-stage-at-mumbai-dialogue-ahead-of-india-maritime-week-2025/</t>
+          <t>https://www.indiatvnews.com/maharashtra/mumbai-rains-live-updates-traffic-snarl-waterlogging-local-train-status-imd-forecast-today-schools-closed-maharashtra-weather-red-orange-alert-1003991</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/kolkata-weather-forecast-patchy-rain-and-humidity-expected-on-august-15-2025/articleshow/123314563.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-hoists-tricolour-flag-attends-hoisting-ceremony-of-bombay-high-court-on-the-occasion-of-indian-independence-day20250815151854</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/business/india-maritime-week-2025-preparations-green-digital-corridors/111129/</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/maratha-leader-manoj-jarange-patil-aggressive-for-mumbai-march/articleshow/123323428.cms</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/latur/latur-news-chief-minister-knows-about-art-he-stopped-a-convoy-of-vehicles-and-met-a-young-child-artist-ar84</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rcnv-team-youth-installs-new-interact-rotaract-leaders-with-green-initiatives/articleshow/123311304.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278507102/ibm-new-mumbai-office-inaugurated-by-cm-fadnavis-with-a-vision-for-a-quantum-driven-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/sukhraj-nahar-becomes-credai-mchi-president</t>
+          <t>https://www.devdiscourse.com/article/law-order/3545578-mumbai-braces-for-more-rain-after-torrential-downpour</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/belapur-lake-faces-environmental-threat-warns-citizens-forum/articleshow/123312125.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/16/mumbai-worli-parivartan-dahi-handi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/welspun-living-cultivating-community-value-through-strategic-csr-initiatives/</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/970-nashik-district-women-voluntarily-opt-out-of-ladki-bahin-scheme/articleshow/123266291.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%AA%E0%A5%81%E0%A4%82%E0%A4%B8%E0%A4%95-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82%E0%A4%90%E0%A4%B8-%E0%A4%AC%E0%A4%95%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%9F-%E0%A4%AC%E0%A5%88%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%B2%E0%A4%9A%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1Kue0T</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/pawar-defends-scrutiny-of-ladki-bahin-scheme-beneficiaries/articleshow/123308892.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/the-dream-of-mumbai-within-59-minutes-will-be-soon-filfilled-cm-devendra-fadnavis-9089297</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://punemirror.com/state/maharashtra-governor-governor-c-p-radhakrishnan-greets-people-on-independence-day/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-bdd-says-houses-in-mumbai-are-worth-as-much-as-gold-do-not-sell-houses-remember-you-want-to-pass-this-house-on-to-the-next-generation-1377083</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B0-%E0%A4%9D%E0%A4%A8-%E0%A4%91%E0%A4%A8-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%9F-%E0%A4%A1-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%A7-%E0%A4%B9-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%86%E0%A4%B3%E0%A4%82%E0%A4%A6-%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1KAarj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/entertainment/actor-kishor-kadam-post-appeal-to-cm-devendra-fadnavis-to-save-his-mumbai-residence-entertainment-marathi-news-1376444</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%A7-%E0%A4%B2-26-34-%E0%A4%B2-%E0%A4%96-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%85%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1JoWkD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-mumbai-dahihandi-mahapalik-dahihandi-and-challage-to-uddhav-thackeray-bmc-election-1377445</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2-%E0%A4%91%E0%A4%97%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%A7-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%B2-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1KrMRe</t>
+          <t>https://marathi.abplive.com/web-stories/news/flag-hoisting-on-the-occasion-of-independence-at-high-cout-with-the-presence-of-cm-devendra-fadnavis-1377273</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mukhyamantri-ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%AA-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KuMO3</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/making-up-stories-cm-fadnavis-reacts-to-sharad-pawars-claim-of-160-seat-offer-before-maha-polls/ar-AA1Kgb5k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/mumbai/cm-devendra-fadnavis-warns-developers-to-reduce-prices-of-house-homes-flats-mumbai-print-news-css-98-5306672/</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-pigeon-feeding-dispute-jain-community-vs-marathi-integration-committee-tense-protests-police-detain-hundreds/articleshow/123294170.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-12-hour-electricity-for-farmers-in-the-state-and-steel-hub-in-gadchiroli-chief-minister-assures-on-independence-day-in-mumbai-1377256</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://www.pratahkal.com/Encyc/2025/8/12/big-action-by-rpf-grp-big-secret-of-theft-exposed.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-announces-that-coastal-road-will-be-open-24-hours-from-august-15/912175/</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/rokhthok-conspiracy-to-make-maharashtra-vegetarian/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sclr-to-weh-connector-chembur-to-mumbai-airport-cable-bridge-inaugurated-by-devendra-fadnavis/articleshow/123317604.cms</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>https://www.amnesty.org/en/latest/research/2025/08/open-letter-to-government-of-maharashtra-withhold-assent-maharashtra-special-public-security-bill/</t>
+          <t>https://www.msn.com/mr-in/news/other/uddhav-thackeray-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9A-%E0%A4%AB-%E0%A4%AE-%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%B9%E0%A5%87-%E0%A4%A4%E0%A4%B0-%E0%A4%A5-%E0%A4%AB-%E0%A4%AE-%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1KivGW</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/truce-talks-us-china-agree-to-extend-their-tariff-truce-for-another-90-days/julyaugust-developments/slideshow/123250425.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/kishor-kadam-seeks-help-from-cm-devendra-fadnavis-to-save-his-house-in-mumbai/911132/</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/the-eyes-that-saw-independence-day-1947/articleshow/123312887.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raj-thackeray-uddhav-thackeray-shiv-sena-ubt-mns-reunite-for-best-employees-credit-society-election-against-bjp-devendra-fadnavis-samruddhi-panel/articleshow/123328116.cms</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/concord-biotech-sai-life-sciences-among-9-stocks-that-closed-above-vwap-on-august-11/trend-watch/slideshow/123248478.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/mumbai-lagbaghcha-raja-area-firefighters-charage-1-25-lakh-per-day-cm-devendra-fadnavis-assures-ganesh-mandal-of-mumbai-1376931</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/bhiwani-woman-teacher-murder-triggers-protests-villagers-block-delhipilani-road-demand-arrests/articleshow/123345021.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/16/emotional-moment-as-bdd-residents-get-their-dream-home-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/golden-crossovers-metropolis-healthcare-dixon-tech-among-5-stocks-signal-further-bullishness-on-august-12/bullish-breakout/slideshow/123248692.cms</t>
+          <t>https://marathi.indiatimes.com/editorial/editorial-on-pune-municipal-corporation-issue-cm-devendra-fadnavis-ajit-pawar/articleshow/123227690.cms</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/new-updates/kalyan-dombivli-meat-shop-ban-on-independence-day-sparks-political-row-kdmc-official-says-its-a-routine-order-since-1988/articleshow/123220004.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/mumbai-mumbai-worli-largest-dahi-handi-tower-in-mumbai-the-sacrifice-of-sambhaji-maharaj-chhaava-and-kavi-kalash-cm-devendra-fadnavis-clap-1377434</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/wealth/save/ppf-sukanya-samriddhi-yojana-new-rules-you-must-know/closing-a-sukanya-samriddhi-account-before-maturity/slideshow/123233624.cms</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/treasury-yields-dip-ahead-of-key-inflation-data/treasury-yields-ease-before-inflation-data/slideshow/123251840.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/singapore-should-cooperate-for-development-by-adding-a-new-dimension-to-maritime-cooperation-between-maharasht.html</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/max-financial-titan-among-8-stocks-showing-rsi-trending-up-on-august-8/saregama-india/slideshow/123226556.cms</t>
+          <t>https://news18marathi.com/maharashtra/uddhav-thackeray-criticizes-cm-devendra-fadnavis-announces-anti-corruption-movement-ws-l-1455373.html</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/pb-fintech-supreme-industries-among-11-stocks-with-white-marubozu-pattern-on-august-11/adani-enterprises/slideshow/123249237.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/bjps-mahesh-landge-cow-protection-groups-clash-with-ajit-pawar-over-crackdown-on-vigilantes/</t>
+          <t>https://www.lokmat.com/latur/manoj-jarange-patil-said-that-the-chief-minister-should-give-reservatio-we-are-not-coming-to-mumbai-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+          <t>https://jantaserishta.com/local/maharashtra/rapid-redevelopment-essential-for-a-slum-free-mumbai-cm-fadnavis-4212867</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/anna-hazares-stir-sparks-debate-again-banners-demanding-action-appear-in-pune/</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-political-row-erupts-at-savitribai-phule-pune-university-over-voice-of-devendra-elocution-competition/</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-experienced-ai-cricket-simulator-during-the-visit-4210440</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-lokmanya-nagar-redevelopment-hits-impasse-residents-blame-political-meddling/</t>
+          <t>https://www.marathiebatmya.com/mumbai/cm-fadnavis-said-dream-of-mumbai-within-59-minutes-will-soon-be-fulfilled/</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>https://ndtv.in/videos/why-did-mutton-politics-happen-on-15th-august-in-maharashtra-aimim-ncp-organized-a-non-veg-party-981146</t>
+          <t>https://joindia.co.in/news/mumbais-development-gets-new-momentum-many-big-projects-of-mmrda-inaugurated-coastal-road-will-be-open-24-hours-from-august-15/</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/independence-day-2025-pm-modi-longest-speech-ever/111404/</t>
+          <t>https://marathi.asianetnews.com/maharashtra/cm-devendra-fadnavis-flag-hoisting-in-mumbai-read-important-points/articleshow-a7935co</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>https://indiplomacy.com/2025/08/13/maharashtra-and-singapore-strengthen-maritime-and-industrial-ties-with-landmark-agreements/</t>
+          <t>https://marathi.asianetnews.com/mumbai/raghuji-bhosale-sword-in-mumbai-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow-5d2azb4</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/woman-accuses-ex-husband-of-sharing-intimate-pics-to-ruin-engagement/articleshow/123309891.cms</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-rapid-redevelopment-is-needed-for-a-slum-free-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-to-celebrate-independence-day-with-social-initiatives-and-community-engagement/articleshow/123312038.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/war-on-cyber-cons-goa-police-to-use-memes-reels/articleshow/123311003.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ganesh-mandals-in-mumbai-seek-abolition-of-rs-2000-penalty-for-digging-public-roads/articleshow/123302643.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/chief-minister-devendra-fadnavis-gets-emotional-after-seeing-the-encampment-on-dahihandi-tower/129236/</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/top-news/maharashtra-police-bharti-2025-approval-for-15000-police-recruitment-in-maharashtra-cm-fadnavis-takes-4-big-decisions-88282</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/eknath-shinde-claims-that-not-a-single-pothole-will-be-seen-in-mumbai-in-the-next-one-and-a-half-years/129057/</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/17/pune-residents-experienced-the-thrill-of-punit-balan-groups-joint-dj-mukta-dahihandi.html</t>
+          <t>https://www.timemaharashtra.com/politics/politics-in-the-dahi-handi-festival-in-mumbai-fadnavis-hints-at-change/129241/</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://m.economictimes.com/news/india/worlds-highest-railway-bridge-witnesses-grand-tiranga-rally-in-jk-ahead-of-independence-day/videoshow/123301830.cms</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/punjab/news/union-home-minister-amit-shah-to-participate-in-the-350th-martyrdom-anniversary-celebrations-of-sri-guru-tegh-bahadur-sa-294387</t>
+          <t>https://ddnews.gov.in/en/india-singapore-green-digital-maritime-corridor-takes-center-stage-at-mumbai-dialogue-ahead-of-india-maritime-week-2025/</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/11/khan-academy-and-maharashtra-government-to-empower-62000-schools-with-free-digital-tools/</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/bangalore-weather-update-rainy-days-ahead-with-cool-temperatures/articleshow/123314539.cms</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/08/14/capitaland-investment-signs-landmark-mou-with-maharashtra-government/</t>
+          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519-amp.html</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/lucknows-anglo-indian-legacyshowcased-at-storytelling-event/articleshow/123351337.cms</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/11/historic-sword-of-raghuji-bhosale-secured-by-maharashtra-government-in-london/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/16/bom14-mh-dahi-handi-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mysuru/kodagu-freedom-fighters-honoured-during-i-day-event/articleshow/123349934.cms</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
+          <t>https://punemirror.com/entertainment/43rd-india-day-parade-new-york-bollywood-icons-vijay-deverakonda-rashmika-mandana-named-co-grand-marshals/</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/national-stem-challenge-2025-central-zone-winners-announced/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/kolkata-weather-forecast-patchy-rain-and-humidity-expected-on-august-15-2025/articleshow/123314563.cms</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://timesofindia.indiatimes.com/city/chennai/chennai-weather-update-cooler-temperatures-and-rain-showers-expected/articleshow/123340697.cms</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://indiashippingnews.com/green-digital-maritime-corridors-dialogue-at-jnpa-sets-stage-for-india-maritime-week-2025-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-bharti-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B5%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%AA-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B7-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%81%E0%A4%A6-%E0%A4%A6%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1Ks1KV</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/des121-up-dgp-iday.html</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/governments-big-announcement-mega-recruitment-announced-for-15000-posts-in-the-police-department/39848</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/13/mes34-tl-tourist-police.html</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3543979-dahi-handi-festival-a-political-arena-amidst-fervent-celebrations</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-fadnavis-government-has-increased-ration-shopkeepers-margin-amount-20-rupee-88298</t>
+          <t>https://hindi.newsdanka.com/business/india-maritime-week-2025-preparations-green-digital-corridors/111129/</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/free-digital-learning-%E0%A4%96-%E0%A4%A8-%E0%A4%85%E0%A4%95%E0%A5%85%E0%A4%A1%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3/ar-AA1KCLdZ</t>
+          <t>https://pudhari.news/maharashtra/marathwada/latur/latur-news-chief-minister-knows-about-art-he-stopped-a-convoy-of-vehicles-and-met-a-young-child-artist-ar84</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/devendra-fadnavis-dahi-handi-speech-maharashtra-politics-on-bmc-elections-news-on-agrowon-ssp-25</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rcnv-team-youth-installs-new-interact-rotaract-leaders-with-green-initiatives/articleshow/123311304.cms</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-decision-devendra-fadnavis-home-ministry-15-thousand-police-recruitment/articleshow/123252638.cms</t>
+          <t>https://www.constructionweekonline.in/business/sukhraj-nahar-becomes-credai-mchi-president</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/the-flag-hoisting-will-be-done-by-fadnavis-in-mumbai-and-radhakrishnan-in-pune-15226401</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/belapur-lake-faces-environmental-threat-warns-citizens-forum/articleshow/123312125.cms</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-recruitment-%E0%A4%A4%E0%A4%B0%E0%A5%81%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B2-%E0%A4%B2-%E0%A4%97-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A5%A7%E0%A5%AB-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Km5x7</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/970-nashik-district-women-voluntarily-opt-out-of-ladki-bahin-scheme/articleshow/123266291.cms</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-independence-day-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news/912247/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/pawar-defends-scrutiny-of-ladki-bahin-scheme-beneficiaries/articleshow/123308892.cms</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/big-decision-in-cabinet-on-state-police-state-to-soon-recruit-14000-posts-maharashtra-police-recruitment-2025-1467605.html/amp</t>
+          <t>https://punemirror.com/state/maharashtra-governor-governor-c-p-radhakrishnan-greets-people-on-independence-day/</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/08/14/credai-mchi-change-of-guard-2025-ceremony-in-presence-of-honorable-cm-of-maharashtra-devendra-fadnavis/</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/singapore-should-cooperate-for-development-by-adding-a-new-dimension-to-maritime-cooperation-between-maharasht.html</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/states-progress-in-agriculture-and-energy-sectors-rat16</t>
+          <t>https://www.msn.com/mr-in/news/other/mukhyamantri-ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%AA-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KuMO3</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-12-august-2025-marathi-batmya-maharashtra-weather-update-dadar-kabutarkhana-ban-pune-khed-pickup-accident/liveblog/123248711.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/eknath-shinde-alandi-pune-news-ladki-bhahin-yojana-will-never-be-closed-says-eknath-shinde-1377303</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/santosh-juvekar-thankful-to-ashish-shelar-for-bringing-back-raghuji-bhosale-sword-in-india/articleshow/123270658.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2-%E0%A4%91%E0%A4%97%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%A7-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%B2-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1KrMRe</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/sambhaji-nagar/ladki-bahin-yojana-1-lakh-4-thousand-sisters-application-rejected-by-state-government-on-rules-and-regulation-basis-in-ladki-bahin-yojana-your-name-is-not-in-the-list-is-it-1469031.html</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/cabinet-decisions-jumbo-police-recruitment-in-maharashtra-fadnavis-government-gives-green-light-to-fill-15-thousand-posts/</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-approves-recruitment-of-15000-police-in-state-article-152450966</t>
+          <t>https://www.mymahanagar.com/maharashtra/government-employees-ganesh-chaturthi-gift-to-government-employees-in-the-state-two-percent-increase-in-dearness-allowance/911032/</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/i-feel-jealous-of-devendra-fadnavis-uddhav-thackerays-attack-on-fadnavis/128759/</t>
+          <t>https://www.msn.com/en-in/autos/photos/sharad-pawar-is-hallucinating-devendra-fadnavis-slams-ncp-sp-chief-over-financial-aid-claim/ar-AA1tnzDv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-police-recruitment-2025-15000-vacancies-with-special-age-relaxation/</t>
+          <t>https://www.devdiscourse.com/article/politics/3538927-political-strife-over-maratha-quota-intensifies-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/08/chandrapur-development-schemes-2025/</t>
+          <t>https://hindi.theprint.in/india/bjp-and-ncp-spoke-in-different-tones-on-ban-on-meat-sale-on-august-15/854981/</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-f-21/911866/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-chhagan-bhujbal-skips-gondia-flag-hoisting-amid-guardian-minister-row-bjp-mangal-prabhat-deputed-know-all/articleshow/123305574.cms</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B6-%E0%A4%95%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%86%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%A8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%A6%E0%A5%81%E0%A4%96-%E0%A4%B5-%E0%A4%A2%E0%A4%B2/ar-AA1Ksebj</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-pigeon-feeding-dispute-jain-community-vs-marathi-integration-committee-tense-protests-police-detain-hundreds/articleshow/123294170.cms</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.hindisaamana.com/rokhthok-conspiracy-to-make-maharashtra-vegetarian/</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A6-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97-%E0%A4%B1%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AE-%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B8-%E0%A4%A7%E0%A4%B2%E0%A4%82-%E0%A4%A4-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%A2%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A4%A6-%E0%A4%A6-%E0%A4%96%E0%A4%B5%E0%A4%B2/ar-AA1K55hg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amnesty.org/en/latest/research/2025/08/open-letter-to-government-of-maharashtra-withhold-assent-maharashtra-special-public-security-bill/</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nagpur/raghuji-raje-sword-in-london-is-in-the-possession-of-the-government-88219</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/give-affidavit-or-apologise-no-third-option-cec-gyanesh-kumar-on-rahuls-vote-theft-allegations/videoshow/123346794.cms</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-police-bharti-cabinet-decision-what-are-the-recruitment-for-the-posts-omr-system-used-for-written-examination-1456438.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/spanish-child-castellers-form-human-pyramid-in-siddhivinayak-temple-courtyard/articleshow/123324754.cms</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/pune/pune-accident-news-death-toll-rises-to-10-in-pimpri-chinchwad-accident-88376</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/activists-politicians-question-parvati-janata-vasahat-tdr-approval-101755033157676.html</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://timesofindia.indiatimes.com/city/patna/dy-cm-threatens-legal-action-against-tejashwi-over-false-allegations/articleshow/123285022.cms</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/independence-day-2025-chhagan-bhujbal-refuse-to-hoist-flag-in-gondia-due-to-girish-mahajan/articleshow/123296100.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/the-eyes-that-saw-independence-day-1947/articleshow/123312887.cms</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/dont-reduce-grandfather-to-a-muslim-hating-kasai-says-gopal-patthas-kin-sends-notice-to-agnihotri/articleshow/123351366.cms</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/bhiwani-woman-teacher-murder-triggers-protests-villagers-block-delhipilani-road-demand-arrests/articleshow/123345021.cms</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://m.economictimes.com/news/new-updates/kalyan-dombivli-meat-shop-ban-on-independence-day-sparks-political-row-kdmc-official-says-its-a-routine-order-since-1988/articleshow/123220004.cms</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/chhatrapati-sambhajinagar-the-common-citizen-is-the-focal-point-guardian-minister-sanjay-shirsat/</t>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/dharmasthala-mass-burial-sit-probe-transparent-says-dinesh-gundu-rao-minister-accuses-bjp-of-twisting-facts-for-political-mileage/articleshow/123321254.cms</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/chandrashekhar-bawankule-on-uddhav-thackeray-thackerays-criticism-of-fadnavis-bawankules-attack-on-thackeray/128784/</t>
+          <t>https://punemirror.com/city/pune/anna-hazares-stir-sparks-debate-again-banners-demanding-action-appear-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/maharashtra-is-making-a-fool-of-itself-sanjay-raut-questions-the-government-on-the-august-15-meat-ban/128932/</t>
+          <t>https://www.punekarnews.in/pune-political-row-erupts-at-savitribai-phule-pune-university-over-voice-of-devendra-elocution-competition/</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/chairman-ram-shindes-follow-up-is-successful-punyashloka-ahilyadevis-national-monument-at-chondi-approved-under-the-development-plan/129292/amp/</t>
+          <t>https://www.punekarnews.in/pune-lokmanya-nagar-redevelopment-hits-impasse-residents-blame-political-meddling/</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/vijay-vadettiwar-on-devendra-fadanvis-vijay-vadettiwars-aggressive-criticism-of-the-decision-to-close-meat-fish-shops/128933/</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8/</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-of-11-aug-2025-daily-astrology-in-hindi-bhavishyavani-with-acharya-indu-prakash-2025-08-11-1155277</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-varsity-withdraws-notification-for-competition-named-after-cm-fadnavis-101754995999519-amp.html</t>
+          <t>https://www.bbc.com/hindi/live/c23pr7x3kmgt</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/global-trends/us-news-xfg-stratus-covid-variant-in-us-8-key-facts-risky-states-symptoms-prevention/covid-cases-are-increasing-in-us/slideshow/123347536.cms</t>
+          <t>https://www.tv9hindi.com/india/happy-independence-day-2025-live-updates-india-pm-narendra-modi-speech-latest-news-in-hindi-3437605.html</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://mpbreakingnews.in/maharashtra/eknath-shinde-aaditya-thackeray-bdd-redevelopment-mumbai-politics-54-801357</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/ar-AA1KtpKo</t>
+          <t>https://apnnews.in/top-news/eknath-shinde-faction-minister-bharat-gogawale-angry-he-will-stay-away-from-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/punes-street-food-crisis-1500-poisoning-cases-in-six-months-students-worst-hit/</t>
+          <t>https://hindi.newsdanka.com/politics/independence-day-2025-pm-modi-longest-speech-ever/111404/</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/mumbai/bombay-high-court-bans-djs-in-ganeshotsav-and-other-processions-in-mumbai/</t>
+          <t>https://samacharnama.com/states/bihar-news/fake-voters-vs-transparent-elections-political-battle/cid17236691.htm</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/12/new-rules-for-admission-to-the-ministry-online-registration-mandatory-effective-from-august-15.html</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/woman-accuses-ex-husband-of-sharing-intimate-pics-to-ruin-engagement/articleshow/123309891.cms</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-on-ban-on-meat-eating/</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/war-on-cyber-cons-goa-police-to-use-memes-reels/articleshow/123311003.cms</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/the-government-will-decide-on-a-special-policy-regarding-backward-class-housing-societies-in-the-state-assembly-deputy-speaker-annasaheb-bansode/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ganesh-mandals-in-mumbai-seek-abolition-of-rs-2000-penalty-for-digging-public-roads/articleshow/123302643.cms</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B2%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A5%80%E0%A4%9A%E0%A4%BE-%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/113758/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/17/pune-residents-experienced-the-thrill-of-punit-balan-groups-joint-dj-mukta-dahihandi.html</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cm-bhagwant-mann-writes-to-union-minister-shivraj-singh-chouhan-dont-drop-road-bridge-projects/articleshow/123317920.cms</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/content/press-releases-ani/chief-minister-of-maharashtra-felicitates-abhay-bhutada-for-strengthening-pune-police-with-advanced-equipment-125081101371_1.html?isa=yes</t>
+          <t>https://globalprimenews.com/2025/08/14/capitaland-investment-signs-landmark-mou-with-maharashtra-government/</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mysuru/agri-minister-reaffirms-support-for-farmers/articleshow/123325241.cms</t>
+          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/3-model-village-heads-from-gujarat-get-invited-to-i-day-celebrations-in-delhi/articleshow/123310840.cms</t>
+          <t>https://thelivenagpur.com/2025/08/11/historic-sword-of-raghuji-bhosale-secured-by-maharashtra-government-in-london/</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-junior-minister-yogesh-kadam-seeks-more-decision-making-powers-and-access-to-cabinet-meetings/articleshow/123284395.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mangaluru/fishermen-must-prioritise-safety-hebbalkar/articleshow/123309750.cms</t>
+          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/jaipur/divyansh-bhardwaj-bags-best-sarpanch-in-raj/articleshow/123312215.cms</t>
+          <t>https://www.newsonair.gov.in/independence-day-celebrated-with-patriotic-fervour-gaiety-across-the-country/</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mumbai-gets-2-bridges-and-a-promenade-101755198444321.html</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-police-bharti-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-15-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%AD%E0%A4%B0%E0%A4%A4-%E0%A4%B5%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%AA-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B7-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%81%E0%A4%A6-%E0%A4%A6%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1Ks1KV</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3541547-mumbai-redefines-urban-living-bdd-chawl-project-unveils-new-homes</t>
+          <t>https://www.marathijagran.com/top-news/maharashtra-police-bharti-2025-approval-for-15000-police-recruitment-in-maharashtra-cm-fadnavis-takes-4-big-decisions-88282</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/ndependence-day-celebrated-with-patriotic-fervour-and-gaiety-across-the-country/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-empowers-districts-to-attract-private-capital-in-1-trillion-economy-push/articleshow/123326420.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/devendra-fadnavis-dahi-handi-speech-maharashtra-politics-on-bmc-elections-news-on-agrowon-ssp-25</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/india/cji-gavai-launches-bombay-hcs-4th-bench-in-kolhapur/articleshow/123351073.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-fadnavis-government-has-increased-ration-shopkeepers-margin-amount-20-rupee-88298</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-death-toll-rises-to-10-in-pimpri-chinchwad-accident/articleshow/123247989.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/free-digital-learning-%E0%A4%96-%E0%A4%A8-%E0%A4%85%E0%A4%95%E0%A5%85%E0%A4%A1%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3/ar-AA1KCLdZ</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/7-must-visit-forts-and-memorials-honoring-indias-freedom-struggle/pratapgad-fort-maharashtra/slideshow/123236622.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-decision-devendra-fadnavis-home-ministry-15-thousand-police-recruitment/articleshow/123252638.cms</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/no-need-to-worry-about-us-tariffs-duty-hike-on-shrimp-chance-to-boost-indian-market-nitesh-rane/articleshow/123240165.cms</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/the-flag-hoisting-will-be-done-by-fadnavis-in-mumbai-and-radhakrishnan-in-pune-15226401</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/7-devotees-died-as-pickup-overturned-in-pune-pm-modi-expressed-grief/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/13/tn-launches-door-delivery-of-ration-items-to-elderly-differently-abled.html</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-assembly-monsoon-session-2025-independence-day-maharashtra-assembly-monsoon-session-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news/912247/amp</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-labour-dept-simplifies-access-to-welfare-schemes/articleshow/123289483.cms</t>
+          <t>https://www.tv9marathi.com/videos/big-decision-in-cabinet-on-state-police-state-to-soon-recruit-14000-posts-maharashtra-police-recruitment-2025-1467605.html/amp</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chennai/tn-govt-will-not-let-down-sanitary-workers-stalin/articleshow/123311969.cms</t>
+          <t>https://globalprimenews.com/2025/08/14/credai-mchi-change-of-guard-2025-ceremony-in-presence-of-honorable-cm-of-maharashtra-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/breaking-party-line-mithun-likens-lakshmir-bhandar-to-alms-tmc-hits-back/articleshow/123289871.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/states-progress-in-agriculture-and-energy-sectors-rat16</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/msedcl-achieves-milestone-of-1gw-domestic-rooftop-solar-capacity/articleshow/123302393.cms</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-police-bharti-cabinet-decision-what-are-the-recruitment-for-the-posts-omr-system-used-for-written-examination-1456438.html</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/visakhapatnam/independence-day-2-police-officers-from-andhra-pradesh-to-receive-presidents-medal-for-distinguished-service/articleshow/123302786.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-disha-abhiyan-unprecedented-changes-in-education-for-students-with-intellectual-disabilities/articleshow/123230486.cms</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-ring-road-plan-pmrda-holds-preliminary-talks-with-villages-for-upcoming-town-planning-schemes/articleshow/123320219.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-12-august-2025-marathi-batmya-maharashtra-weather-update-dadar-kabutarkhana-ban-pune-khed-pickup-accident/liveblog/123248711.cms</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hubballi/hubballi-nk-region-celebrate-independence-day-with-fervour/articleshow/123325559.cms</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/santosh-juvekar-thankful-to-ashish-shelar-for-bringing-back-raghuji-bhosale-sword-in-india/articleshow/123270658.cms</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/13/dcm132-biz-briefs-6.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/ls-passes-two-tax-bills-amid-din-without-debate.html</t>
+          <t>https://civicmirror.in/maharashtra/ganeshotsav-2025-operation-sindoor-swadeshi-performances-chief-minister-devendra-fadnavis-appeals-to-the-mandals/</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://marathi.oneindia.com/maharashtra/manoj-jarange-warns-maharashtra-government-034725.html</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-approves-recruitment-of-15000-police-in-state-article-152450966</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-records-19195-consumers-generating-89-mw-rooftop-solar-power-under-pm-suryaghar-muft-bijli-yojana-msedcl/</t>
+          <t>https://civicmirror.in/maharashtra/with-the-cooperation-of-everyone-the-face-of-beed-district-will-be-changed-by-carrying-out-all-round-development-deputy-chief-minister-ajit-pawar/</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/i-feel-jealous-of-devendra-fadnavis-uddhav-thackerays-attack-on-fadnavis/128759/</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/maharashtra-police-recruitment-2025-15000-vacancies-with-special-age-relaxation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%B6-%E0%A4%95%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%86%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%A8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%A6%E0%A5%81%E0%A4%96-%E0%A4%B5-%E0%A4%A2%E0%A4%B2/ar-AA1Ksebj</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/independence-day-2025-15-august-non-veg-ban-in-maharashtra-sanjay-raut-slams-devendra-fadnavis-1376835</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/pune/pune-accident-news-death-toll-rises-to-10-in-pimpri-chinchwad-accident-88376</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/independence-day-2025-chhagan-bhujbal-refuse-to-hoist-flag-in-gondia-due-to-girish-mahajan/articleshow/123296100.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/maharashtra-is-making-a-fool-of-itself-sanjay-raut-questions-the-government-on-the-august-15-meat-ban/128932/</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-not-interested-in-deciding-who-eats-what-cm-fadnavis/ar-AA1KtpKo</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cabinet-gives-nod-to-denotify-land-pooling-policy/articleshow/123317921.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/same-sex-couple-moves-hc-against-gift-tax-rules/articleshow/123325951.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/gurgaon/gurgaon-reports-45-dengue-cases-in-a-month-highest-in-haryana/articleshow/123286205.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-weather-today-uttarkashi-cloudburst-rains-us-india-trade-talks-50-percent-tariffs-pm-modi-monsoon-parliament-session-donald-trump-vladimir-putin-russia-trade-ukraine-russia-peace-talks-august-10/liveblog/123212929.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/pune/punes-street-food-crisis-1500-poisoning-cases-in-six-months-students-worst-hit/</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/mumbai/bombay-high-court-bans-djs-in-ganeshotsav-and-other-processions-in-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A4%A7-%E0%A4%A8-%E0%A4%A4-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%9A-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%9A-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%A4%E0%A4%A1%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%95-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1KKmSa</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/hsrp-deadline-extended-till-november-30-for-installation-of-high-security-registration-number-plates-decision-by-state-govt-1457957.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/12/new-rules-for-admission-to-the-ministry-online-registration-mandatory-effective-from-august-15.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-august-2025-tuesday-latest-marathi-news-update-maharashtra-politics-marathi-news-1376706</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/the-government-will-decide-on-a-special-policy-regarding-backward-class-housing-societies-in-the-state-assembly-deputy-speaker-annasaheb-bansode/</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B2%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A5%80%E0%A4%9A%E0%A4%BE-%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/113758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-cm-bhagwant-mann-writes-to-union-minister-shivraj-singh-chouhan-dont-drop-road-bridge-projects/articleshow/123317920.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mysuru/agri-minister-reaffirms-support-for-farmers/articleshow/123325241.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/3-model-village-heads-from-gujarat-get-invited-to-i-day-celebrations-in-delhi/articleshow/123310840.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-junior-minister-yogesh-kadam-seeks-more-decision-making-powers-and-access-to-cabinet-meetings/articleshow/123284395.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mangaluru/fishermen-must-prioritise-safety-hebbalkar/articleshow/123309750.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/divyansh-bhardwaj-bags-best-sarpanch-in-raj/articleshow/123312215.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>https://theindianawaaz.com/india-celebrates-79th-independence-day-with-patriotic-fervour-and-statewide-announcements-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/money/topstories/prime-focus-to-invest-3-000-crore-for-200-acre-film-city-in-mumbai/ar-AA1E3P8B?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>https://www.rprealtyplus.com/news-views/handover-of-first-redeveloped-flats-under-bdd-chawl-in-mumbai-121347.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mumbai-gets-2-bridges-and-a-promenade-101755198444321.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>https://www.oneindia.com/mumbai/mumbai-metro-3-aqua-line-delayed-opening-011-7827273.html?ref_source=OI-EN&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>https://munsifdaily.com/rapid-redevelopment-essential-for-a-slum-free/</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/redeveloping-dharavi-is-like-building-a-new-city-maharashtra-cm/ar-AA1KyuMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/video/news/meat-sale-ban-on-aug-15-order-in-place-since-1988-says-maharashtra-cm-devendra-fadnavis/vi-AA1KwqG0?ocid=hpmsn</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/news/india/cji-gavai-launches-bombay-hcs-4th-bench-in-kolhapur/articleshow/123351073.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/capitaland-plans-rs-192-billion-investment-in-maharashtra/77631</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/no-need-to-worry-about-us-tariffs-duty-hike-on-shrimp-chance-to-boost-indian-market-nitesh-rane/articleshow/123240165.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india--singapore-advance-green-shipping-corridor-plans/77605</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/7-devotees-died-as-pickup-overturned-in-pune-pm-modi-expressed-grief/</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>https://www.univarta.com/news/gujarat-maharashtra/story/3549222.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/13/tn-launches-door-delivery-of-ration-items-to-elderly-differently-abled.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-labour-dept-simplifies-access-to-welfare-schemes/articleshow/123289483.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chennai/tn-govt-will-not-let-down-sanitary-workers-stalin/articleshow/123311969.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/breaking-party-line-mithun-likens-lakshmir-bhandar-to-alms-tmc-hits-back/articleshow/123289871.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/msedcl-achieves-milestone-of-1gw-domestic-rooftop-solar-capacity/articleshow/123302393.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/visakhapatnam/independence-day-2-police-officers-from-andhra-pradesh-to-receive-presidents-medal-for-distinguished-service/articleshow/123302786.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/goa/1-in-4-live-in-shanties-across-urban-south-goa-govt-data/articleshow/123351269.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-ring-road-plan-pmrda-holds-preliminary-talks-with-villages-for-upcoming-town-planning-schemes/articleshow/123320219.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/hubballi/hubballi-nk-region-celebrate-independence-day-with-fervour/articleshow/123325559.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/13/dcm132-biz-briefs-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/wealth/save/how-much-will-the-central-government-employees-salaries-increase-in-the-8th-pay-commission/will-the-upcoming-8th-pay-commission-deliver-a-big-salary-hike/slideshow/123238308.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/ls-passes-two-tax-bills-amid-din-without-debate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>https://ommcomnews.com/india-news/maha-cabinet-clears-recruitment-of-15000-cops-hikes-margin-for-fair-price-shopkeepers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/en/mumbai-news/maharashtra-cabinet-approves-recruitment-of-15000-police-personnel-19857478</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>https://thelivenagpur.com/2025/08/12/app-based-taxi-drivers-in-nagpur-boycott-ola-uber-rapido-over-alleged-exploitation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/pune-records-19195-consumers-generating-89-mw-rooftop-solar-power-under-pm-suryaghar-muft-bijli-yojana-msedcl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
         <is>
           <t>https://www.mypunepulse.com/solapur-mumbai-flight-service-to-begin-soon/</t>
         </is>
